--- a/dust_collection_tool.xlsx
+++ b/dust_collection_tool.xlsx
@@ -10,11 +10,12 @@
     <sheet name="Dashboard" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Makine Giris" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Borulama Hesaplari" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Boru Capi Tablosu" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Filtre Secimi" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Fan Secimi" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Urun Veritabani" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="Teklif Ozeti" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Fabrika Yerlesim Plani" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Boru Capi Tablosu" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Filtre Secimi" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Fan Secimi" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Urun Veritabani" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Teklif Ozeti" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
     <definedName name="ToplamHavaDebisi">'Borulama Hesaplari'!$E$4</definedName>
@@ -46,7 +47,7 @@
     <numFmt numFmtId="174" formatCode="#,##0 &quot;kWh&quot;"/>
     <numFmt numFmtId="175" formatCode="#,##0.0 &quot;m2&quot;"/>
   </numFmts>
-  <fonts count="17">
+  <fonts count="19">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -123,6 +124,14 @@
       <sz val="13"/>
     </font>
     <font>
+      <b val="1"/>
+      <color rgb="001F3864"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <sz val="10"/>
+    </font>
+    <font>
       <i val="1"/>
       <color rgb="00777777"/>
       <sz val="9"/>
@@ -181,7 +190,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="20">
     <border>
       <left/>
       <right/>
@@ -223,60 +232,266 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="hair">
+        <color rgb="00C9C9C9"/>
+      </left>
+      <right style="hair">
+        <color rgb="00C9C9C9"/>
+      </right>
+      <top style="hair">
+        <color rgb="00C9C9C9"/>
+      </top>
+      <bottom style="hair">
+        <color rgb="00C9C9C9"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="hair">
+        <color rgb="00C9C9C9"/>
+      </left>
+      <right style="hair">
+        <color rgb="00C9C9C9"/>
+      </right>
+      <top style="thick">
+        <color rgb="00000000"/>
+      </top>
+      <bottom style="hair">
+        <color rgb="00C9C9C9"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="hair">
+        <color rgb="00C9C9C9"/>
+      </left>
+      <right style="hair">
+        <color rgb="00C9C9C9"/>
+      </right>
+      <top style="hair">
+        <color rgb="00C9C9C9"/>
+      </top>
+      <bottom style="thick">
+        <color rgb="00000000"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thick">
+        <color rgb="00000000"/>
+      </left>
+      <right style="hair">
+        <color rgb="00C9C9C9"/>
+      </right>
+      <top style="hair">
+        <color rgb="00C9C9C9"/>
+      </top>
+      <bottom style="hair">
+        <color rgb="00C9C9C9"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="hair">
+        <color rgb="00C9C9C9"/>
+      </left>
+      <right style="thick">
+        <color rgb="00000000"/>
+      </right>
+      <top style="hair">
+        <color rgb="00C9C9C9"/>
+      </top>
+      <bottom style="hair">
+        <color rgb="00C9C9C9"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thick">
+        <color rgb="00000000"/>
+      </left>
+      <right style="hair">
+        <color rgb="00C9C9C9"/>
+      </right>
+      <top style="thick">
+        <color rgb="00000000"/>
+      </top>
+      <bottom style="hair">
+        <color rgb="00C9C9C9"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="hair">
+        <color rgb="00C9C9C9"/>
+      </left>
+      <right style="thick">
+        <color rgb="00000000"/>
+      </right>
+      <top style="thick">
+        <color rgb="00000000"/>
+      </top>
+      <bottom style="hair">
+        <color rgb="00C9C9C9"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thick">
+        <color rgb="00000000"/>
+      </left>
+      <right style="hair">
+        <color rgb="00C9C9C9"/>
+      </right>
+      <top style="hair">
+        <color rgb="00C9C9C9"/>
+      </top>
+      <bottom style="thick">
+        <color rgb="00000000"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="hair">
+        <color rgb="00C9C9C9"/>
+      </left>
+      <right style="thick">
+        <color rgb="00000000"/>
+      </right>
+      <top style="hair">
+        <color rgb="00C9C9C9"/>
+      </top>
+      <bottom style="thick">
+        <color rgb="00000000"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="hair">
+        <color rgb="00C9C9C9"/>
+      </left>
+      <right style="hair">
+        <color rgb="00C9C9C9"/>
+      </right>
+      <top style="hair">
+        <color rgb="00C9C9C9"/>
+      </top>
+      <bottom style="thick">
+        <color rgb="001F3864"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="hair">
+        <color rgb="00C9C9C9"/>
+      </left>
+      <right style="medium">
+        <color rgb="002E5395"/>
+      </right>
+      <top style="hair">
+        <color rgb="00C9C9C9"/>
+      </top>
+      <bottom style="thick">
+        <color rgb="001F3864"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="hair">
+        <color rgb="00C9C9C9"/>
+      </left>
+      <right style="medium">
+        <color rgb="002E5395"/>
+      </right>
+      <top style="hair">
+        <color rgb="00C9C9C9"/>
+      </top>
+      <bottom style="hair">
+        <color rgb="00C9C9C9"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="hair">
+        <color rgb="00C9C9C9"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="hair">
+        <color rgb="00C9C9C9"/>
+      </right>
+      <top style="hair">
+        <color rgb="00C9C9C9"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="hair">
+        <color rgb="00C9C9C9"/>
+      </top>
+      <bottom style="hair">
+        <color rgb="00C9C9C9"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="hair">
+        <color rgb="00C9C9C9"/>
+      </right>
+      <top style="hair">
+        <color rgb="00C9C9C9"/>
+      </top>
+      <bottom style="hair">
+        <color rgb="00C9C9C9"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="61">
+  <cellXfs count="79">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="169" fontId="16" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="170" fontId="16" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="171" fontId="16" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="172" fontId="16" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="173" fontId="16" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="174" fontId="16" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="175" fontId="16" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="166" fontId="7" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="3" fontId="7" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -297,6 +512,10 @@
     <xf numFmtId="3" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="11" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
@@ -322,6 +541,7 @@
     <xf numFmtId="2" fontId="8" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="168" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
@@ -336,23 +556,58 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
+    <xf numFmtId="169" fontId="18" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
+    <xf numFmtId="170" fontId="18" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
+    <xf numFmtId="171" fontId="18" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
+    <xf numFmtId="172" fontId="18" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="173" fontId="18" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="174" fontId="18" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="175" fontId="18" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
@@ -363,15 +618,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="167" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -391,9 +637,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -737,6 +980,911 @@
 </wsDr>
 </file>
 
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>5</col>
+      <colOff>0</colOff>
+      <row>10</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="152400" cy="152400"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>13</col>
+      <colOff>0</colOff>
+      <row>10</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="152400" cy="152400"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="2" name="Image 2" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>21</col>
+      <colOff>0</colOff>
+      <row>10</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="152400" cy="152400"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="3" name="Image 3" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>29</col>
+      <colOff>0</colOff>
+      <row>10</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="152400" cy="152400"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="4" name="Image 4" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>37</col>
+      <colOff>0</colOff>
+      <row>10</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="152400" cy="152400"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="5" name="Image 5" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>45</col>
+      <colOff>0</colOff>
+      <row>10</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="152400" cy="152400"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="6" name="Image 6" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>5</col>
+      <colOff>0</colOff>
+      <row>18</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="152400" cy="152400"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="7" name="Image 7" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId7"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>13</col>
+      <colOff>0</colOff>
+      <row>18</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="152400" cy="152400"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="8" name="Image 8" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId8"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>21</col>
+      <colOff>0</colOff>
+      <row>18</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="152400" cy="152400"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="9" name="Image 9" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId9"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>29</col>
+      <colOff>0</colOff>
+      <row>18</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="152400" cy="152400"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="10" name="Image 10" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId10"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>37</col>
+      <colOff>0</colOff>
+      <row>18</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="152400" cy="152400"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="11" name="Image 11" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId11"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>45</col>
+      <colOff>0</colOff>
+      <row>18</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="152400" cy="152400"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="12" name="Image 12" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId12"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>5</col>
+      <colOff>0</colOff>
+      <row>26</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="152400" cy="152400"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="13" name="Image 13" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId13"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>13</col>
+      <colOff>0</colOff>
+      <row>26</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="152400" cy="152400"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="14" name="Image 14" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId14"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>21</col>
+      <colOff>0</colOff>
+      <row>26</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="152400" cy="152400"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="15" name="Image 15" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId15"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>29</col>
+      <colOff>0</colOff>
+      <row>26</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="152400" cy="152400"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="16" name="Image 16" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId16"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>37</col>
+      <colOff>0</colOff>
+      <row>26</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="152400" cy="152400"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="17" name="Image 17" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId17"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>45</col>
+      <colOff>0</colOff>
+      <row>26</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="152400" cy="152400"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="18" name="Image 18" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId18"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>5</col>
+      <colOff>0</colOff>
+      <row>34</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="152400" cy="152400"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="19" name="Image 19" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId19"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>13</col>
+      <colOff>0</colOff>
+      <row>34</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="152400" cy="152400"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="20" name="Image 20" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId20"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>21</col>
+      <colOff>0</colOff>
+      <row>34</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="152400" cy="152400"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="21" name="Image 21" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId21"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>29</col>
+      <colOff>0</colOff>
+      <row>34</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="152400" cy="152400"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="22" name="Image 22" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId22"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>37</col>
+      <colOff>0</colOff>
+      <row>34</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="152400" cy="152400"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="23" name="Image 23" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId23"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>45</col>
+      <colOff>0</colOff>
+      <row>34</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="152400" cy="152400"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="24" name="Image 24" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId24"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>10</col>
+      <colOff>0</colOff>
+      <row>21</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="419100" cy="314325"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="25" name="Image 25" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId25"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>22</col>
+      <colOff>0</colOff>
+      <row>21</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="419100" cy="314325"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="26" name="Image 26" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId26"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>34</col>
+      <colOff>0</colOff>
+      <row>21</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="419100" cy="314325"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="27" name="Image 27" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId27"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>6</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="476250" cy="476250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="28" name="Image 28" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId28"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>46</col>
+      <colOff>0</colOff>
+      <row>6</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="476250" cy="476250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="29" name="Image 29" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId29"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>44</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="342900" cy="228600"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="30" name="Image 30" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId30"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>45</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="342900" cy="228600"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="31" name="Image 31" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId31"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>46</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="342900" cy="228600"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="32" name="Image 32" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId32"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>47</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="342900" cy="228600"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="33" name="Image 33" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId33"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>48</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="342900" cy="228600"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="34" name="Image 34" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId34"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>49</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="342900" cy="228600"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="35" name="Image 35" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId35"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>50</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="342900" cy="228600"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="36" name="Image 36" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId36"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="tblUrunDB" displayName="tblUrunDB" ref="A4:M44" headerRowCount="1">
   <autoFilter ref="A4:M44"/>
@@ -1076,184 +2224,184 @@
       <c r="H1" s="2" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A3" s="59" t="inlineStr">
         <is>
           <t>Toplam Hava Debisi</t>
         </is>
       </c>
-      <c r="B3" s="4" t="n"/>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="B3" s="34" t="n"/>
+      <c r="D3" s="59" t="inlineStr">
         <is>
           <t>Ana Boru Capi</t>
         </is>
       </c>
-      <c r="E3" s="4" t="n"/>
-      <c r="G3" s="3" t="inlineStr">
+      <c r="E3" s="34" t="n"/>
+      <c r="G3" s="59" t="inlineStr">
         <is>
           <t>Gercek Hava Hizi</t>
         </is>
       </c>
-      <c r="H3" s="4" t="n"/>
+      <c r="H3" s="34" t="n"/>
     </row>
     <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="5">
+      <c r="A4" s="60">
         <f>'Borulama Hesaplari'!E4</f>
         <v/>
       </c>
-      <c r="B4" s="4" t="n"/>
-      <c r="D4" s="6">
+      <c r="B4" s="34" t="n"/>
+      <c r="D4" s="61">
         <f>'Borulama Hesaplari'!E8</f>
         <v/>
       </c>
-      <c r="E4" s="4" t="n"/>
-      <c r="G4" s="7">
+      <c r="E4" s="34" t="n"/>
+      <c r="G4" s="62">
         <f>'Borulama Hesaplari'!E10</f>
         <v/>
       </c>
-      <c r="H4" s="4" t="n"/>
+      <c r="H4" s="34" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="inlineStr">
+      <c r="A5" s="59" t="inlineStr">
         <is>
           <t>Toplam Basinc Kaybi</t>
         </is>
       </c>
-      <c r="B5" s="4" t="n"/>
-      <c r="D5" s="3" t="inlineStr">
+      <c r="B5" s="34" t="n"/>
+      <c r="D5" s="59" t="inlineStr">
         <is>
           <t>Secilen Filtre</t>
         </is>
       </c>
-      <c r="E5" s="4" t="n"/>
-      <c r="G5" s="3" t="inlineStr">
+      <c r="E5" s="34" t="n"/>
+      <c r="G5" s="59" t="inlineStr">
         <is>
           <t>Secilen Fan</t>
         </is>
       </c>
-      <c r="H5" s="4" t="n"/>
+      <c r="H5" s="34" t="n"/>
     </row>
     <row r="6" ht="30" customHeight="1">
-      <c r="A6" s="8">
+      <c r="A6" s="63">
         <f>'Fan Secimi'!B7</f>
         <v/>
       </c>
-      <c r="B6" s="4" t="n"/>
-      <c r="D6" s="9">
+      <c r="B6" s="34" t="n"/>
+      <c r="D6" s="64">
         <f>'Filtre Secimi'!B10</f>
         <v/>
       </c>
-      <c r="E6" s="4" t="n"/>
-      <c r="G6" s="9">
+      <c r="E6" s="34" t="n"/>
+      <c r="G6" s="64">
         <f>'Fan Secimi'!B14</f>
         <v/>
       </c>
-      <c r="H6" s="4" t="n"/>
+      <c r="H6" s="34" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="inlineStr">
+      <c r="A7" s="59" t="inlineStr">
         <is>
           <t>Fan Motor Gucu</t>
         </is>
       </c>
-      <c r="B7" s="4" t="n"/>
-      <c r="D7" s="3" t="inlineStr">
+      <c r="B7" s="34" t="n"/>
+      <c r="D7" s="59" t="inlineStr">
         <is>
           <t>Yillik Enerji Tuketimi</t>
         </is>
       </c>
-      <c r="E7" s="4" t="n"/>
-      <c r="G7" s="3" t="inlineStr">
+      <c r="E7" s="34" t="n"/>
+      <c r="G7" s="59" t="inlineStr">
         <is>
           <t>Filtre Alani</t>
         </is>
       </c>
-      <c r="H7" s="4" t="n"/>
+      <c r="H7" s="34" t="n"/>
     </row>
     <row r="8" ht="30" customHeight="1">
-      <c r="A8" s="10">
+      <c r="A8" s="65">
         <f>'Fan Secimi'!B29</f>
         <v/>
       </c>
-      <c r="B8" s="4" t="n"/>
-      <c r="D8" s="11">
+      <c r="B8" s="34" t="n"/>
+      <c r="D8" s="66">
         <f>'Fan Secimi'!B31</f>
         <v/>
       </c>
-      <c r="E8" s="4" t="n"/>
-      <c r="G8" s="12">
+      <c r="E8" s="34" t="n"/>
+      <c r="G8" s="67">
         <f>'Filtre Secimi'!B12</f>
         <v/>
       </c>
-      <c r="H8" s="4" t="n"/>
+      <c r="H8" s="34" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="13" t="inlineStr">
+      <c r="A10" s="23" t="inlineStr">
         <is>
           <t>BASINC KAYBI BILESENLERI</t>
         </is>
       </c>
-      <c r="B10" s="14" t="n"/>
-      <c r="C10" s="14" t="n"/>
-      <c r="D10" s="14" t="n"/>
+      <c r="B10" s="24" t="n"/>
+      <c r="C10" s="24" t="n"/>
+      <c r="D10" s="24" t="n"/>
     </row>
     <row r="11" ht="32" customHeight="1">
-      <c r="A11" s="15" t="inlineStr">
+      <c r="A11" s="4" t="inlineStr">
         <is>
           <t>Bilesen</t>
         </is>
       </c>
-      <c r="B11" s="15" t="inlineStr">
+      <c r="B11" s="4" t="inlineStr">
         <is>
           <t>Deger (Pa)</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="4" t="inlineStr">
+      <c r="A12" s="34" t="inlineStr">
         <is>
           <t>Statik (Surtunme) Kaybi</t>
         </is>
       </c>
-      <c r="B12" s="16">
+      <c r="B12" s="68">
         <f>'Borulama Hesaplari'!E14</f>
         <v/>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="4" t="inlineStr">
+      <c r="A13" s="34" t="inlineStr">
         <is>
           <t>Dinamik (Yerel) Kaybi</t>
         </is>
       </c>
-      <c r="B13" s="16">
+      <c r="B13" s="68">
         <f>'Borulama Hesaplari'!E16</f>
         <v/>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="4" t="inlineStr">
+      <c r="A14" s="34" t="inlineStr">
         <is>
           <t>Filtre Basinc Kaybi</t>
         </is>
       </c>
-      <c r="B14" s="16">
+      <c r="B14" s="68">
         <f>'Filtre Secimi'!B23</f>
         <v/>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="13" t="inlineStr">
+      <c r="A27" s="23" t="inlineStr">
         <is>
           <t>MAKINE BAZLI HAVA DEBISI DAGILIMI</t>
         </is>
       </c>
-      <c r="B27" s="14" t="n"/>
-      <c r="C27" s="14" t="n"/>
-      <c r="D27" s="14" t="n"/>
-      <c r="E27" s="14" t="n"/>
-      <c r="F27" s="14" t="n"/>
-      <c r="G27" s="14" t="n"/>
-      <c r="H27" s="14" t="n"/>
+      <c r="B27" s="24" t="n"/>
+      <c r="C27" s="24" t="n"/>
+      <c r="D27" s="24" t="n"/>
+      <c r="E27" s="24" t="n"/>
+      <c r="F27" s="24" t="n"/>
+      <c r="G27" s="24" t="n"/>
+      <c r="H27" s="24" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="21">
@@ -1291,7 +2439,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:L25"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
@@ -1326,686 +2474,686 @@
       <c r="L1" s="2" t="n"/>
     </row>
     <row r="2">
-      <c r="A2" s="17" t="inlineStr">
+      <c r="A2" s="14" t="inlineStr">
         <is>
           <t>Proje Adi:</t>
         </is>
       </c>
-      <c r="B2" s="18" t="inlineStr"/>
-      <c r="D2" s="17" t="inlineStr">
+      <c r="B2" s="15" t="inlineStr"/>
+      <c r="D2" s="14" t="inlineStr">
         <is>
           <t>Tarih:</t>
         </is>
       </c>
-      <c r="E2" s="19" t="n"/>
-      <c r="G2" s="17" t="inlineStr">
+      <c r="E2" s="16" t="n"/>
+      <c r="G2" s="14" t="inlineStr">
         <is>
           <t>Hazirlayan:</t>
         </is>
       </c>
-      <c r="H2" s="18" t="inlineStr"/>
+      <c r="H2" s="15" t="inlineStr"/>
     </row>
     <row r="4" ht="32" customHeight="1">
-      <c r="A4" s="15" t="inlineStr">
+      <c r="A4" s="4" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="B4" s="15" t="inlineStr">
+      <c r="B4" s="4" t="inlineStr">
         <is>
           <t>Makine Adi</t>
         </is>
       </c>
-      <c r="C4" s="15" t="inlineStr">
+      <c r="C4" s="4" t="inlineStr">
         <is>
           <t>Makine Tipi</t>
         </is>
       </c>
-      <c r="D4" s="15" t="inlineStr">
+      <c r="D4" s="4" t="inlineStr">
         <is>
           <t>Makine
 Adedi</t>
         </is>
       </c>
-      <c r="E4" s="15" t="inlineStr">
+      <c r="E4" s="4" t="inlineStr">
         <is>
           <t>Emis
 Noktasi Sayisi</t>
         </is>
       </c>
-      <c r="F4" s="15" t="inlineStr">
+      <c r="F4" s="4" t="inlineStr">
         <is>
           <t>Emis Noktasi
 Capi (mm)</t>
         </is>
       </c>
-      <c r="G4" s="15" t="inlineStr">
+      <c r="G4" s="4" t="inlineStr">
         <is>
           <t>Makine Hava
 Debisi (m3/h)</t>
         </is>
       </c>
-      <c r="H4" s="15" t="inlineStr">
+      <c r="H4" s="4" t="inlineStr">
         <is>
           <t>Eszamanli
 Calisma K.(%)</t>
         </is>
       </c>
-      <c r="I4" s="15" t="inlineStr">
+      <c r="I4" s="4" t="inlineStr">
         <is>
           <t>Calisma
 Suresi (sa/gun)</t>
         </is>
       </c>
-      <c r="J4" s="15" t="inlineStr">
+      <c r="J4" s="4" t="inlineStr">
         <is>
           <t>Toplam Debi
 (m3/h)</t>
         </is>
       </c>
-      <c r="K4" s="15" t="inlineStr">
+      <c r="K4" s="4" t="inlineStr">
         <is>
           <t>Gunluk Tuketim
 (m3/gun)</t>
         </is>
       </c>
-      <c r="L4" s="15" t="inlineStr">
+      <c r="L4" s="4" t="inlineStr">
         <is>
           <t>Durum</t>
         </is>
       </c>
     </row>
     <row r="5" ht="18" customHeight="1">
-      <c r="A5" s="20" t="n">
+      <c r="A5" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="B5" s="18" t="inlineStr"/>
-      <c r="C5" s="18" t="inlineStr"/>
-      <c r="D5" s="21" t="inlineStr"/>
-      <c r="E5" s="21" t="inlineStr"/>
-      <c r="F5" s="21" t="inlineStr"/>
-      <c r="G5" s="21" t="inlineStr"/>
-      <c r="H5" s="22" t="n">
+      <c r="B5" s="15" t="inlineStr"/>
+      <c r="C5" s="15" t="inlineStr"/>
+      <c r="D5" s="17" t="inlineStr"/>
+      <c r="E5" s="17" t="inlineStr"/>
+      <c r="F5" s="17" t="inlineStr"/>
+      <c r="G5" s="17" t="inlineStr"/>
+      <c r="H5" s="18" t="n">
         <v>100</v>
       </c>
-      <c r="I5" s="22" t="n">
+      <c r="I5" s="18" t="n">
         <v>8</v>
       </c>
-      <c r="J5" s="23">
+      <c r="J5" s="19">
         <f>IF(B5="","",D5*G5*(H5/100))</f>
         <v/>
       </c>
-      <c r="K5" s="23">
+      <c r="K5" s="19">
         <f>IF(B5="","",J5*I5)</f>
         <v/>
       </c>
-      <c r="L5" s="24">
+      <c r="L5" s="20">
         <f>IF(B5="","Bos Satir",IF(OR(D5&lt;=0,G5&lt;=0,H5&lt;=0,H5&gt;100),"HATA: Kontrol Et","OK"))</f>
         <v/>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1">
-      <c r="A6" s="20" t="n">
+      <c r="A6" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="B6" s="18" t="inlineStr"/>
-      <c r="C6" s="18" t="inlineStr"/>
-      <c r="D6" s="21" t="inlineStr"/>
-      <c r="E6" s="21" t="inlineStr"/>
-      <c r="F6" s="21" t="inlineStr"/>
-      <c r="G6" s="21" t="inlineStr"/>
-      <c r="H6" s="22" t="n">
+      <c r="B6" s="15" t="inlineStr"/>
+      <c r="C6" s="15" t="inlineStr"/>
+      <c r="D6" s="17" t="inlineStr"/>
+      <c r="E6" s="17" t="inlineStr"/>
+      <c r="F6" s="17" t="inlineStr"/>
+      <c r="G6" s="17" t="inlineStr"/>
+      <c r="H6" s="18" t="n">
         <v>100</v>
       </c>
-      <c r="I6" s="22" t="n">
+      <c r="I6" s="18" t="n">
         <v>8</v>
       </c>
-      <c r="J6" s="23">
+      <c r="J6" s="19">
         <f>IF(B6="","",D6*G6*(H6/100))</f>
         <v/>
       </c>
-      <c r="K6" s="23">
+      <c r="K6" s="19">
         <f>IF(B6="","",J6*I6)</f>
         <v/>
       </c>
-      <c r="L6" s="24">
+      <c r="L6" s="20">
         <f>IF(B6="","Bos Satir",IF(OR(D6&lt;=0,G6&lt;=0,H6&lt;=0,H6&gt;100),"HATA: Kontrol Et","OK"))</f>
         <v/>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
-      <c r="A7" s="20" t="n">
+      <c r="A7" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="B7" s="18" t="inlineStr"/>
-      <c r="C7" s="18" t="inlineStr"/>
-      <c r="D7" s="21" t="inlineStr"/>
-      <c r="E7" s="21" t="inlineStr"/>
-      <c r="F7" s="21" t="inlineStr"/>
-      <c r="G7" s="21" t="inlineStr"/>
-      <c r="H7" s="22" t="n">
+      <c r="B7" s="15" t="inlineStr"/>
+      <c r="C7" s="15" t="inlineStr"/>
+      <c r="D7" s="17" t="inlineStr"/>
+      <c r="E7" s="17" t="inlineStr"/>
+      <c r="F7" s="17" t="inlineStr"/>
+      <c r="G7" s="17" t="inlineStr"/>
+      <c r="H7" s="18" t="n">
         <v>100</v>
       </c>
-      <c r="I7" s="22" t="n">
+      <c r="I7" s="18" t="n">
         <v>8</v>
       </c>
-      <c r="J7" s="23">
+      <c r="J7" s="19">
         <f>IF(B7="","",D7*G7*(H7/100))</f>
         <v/>
       </c>
-      <c r="K7" s="23">
+      <c r="K7" s="19">
         <f>IF(B7="","",J7*I7)</f>
         <v/>
       </c>
-      <c r="L7" s="24">
+      <c r="L7" s="20">
         <f>IF(B7="","Bos Satir",IF(OR(D7&lt;=0,G7&lt;=0,H7&lt;=0,H7&gt;100),"HATA: Kontrol Et","OK"))</f>
         <v/>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
-      <c r="A8" s="20" t="n">
+      <c r="A8" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="B8" s="18" t="inlineStr"/>
-      <c r="C8" s="18" t="inlineStr"/>
-      <c r="D8" s="21" t="inlineStr"/>
-      <c r="E8" s="21" t="inlineStr"/>
-      <c r="F8" s="21" t="inlineStr"/>
-      <c r="G8" s="21" t="inlineStr"/>
-      <c r="H8" s="22" t="n">
+      <c r="B8" s="15" t="inlineStr"/>
+      <c r="C8" s="15" t="inlineStr"/>
+      <c r="D8" s="17" t="inlineStr"/>
+      <c r="E8" s="17" t="inlineStr"/>
+      <c r="F8" s="17" t="inlineStr"/>
+      <c r="G8" s="17" t="inlineStr"/>
+      <c r="H8" s="18" t="n">
         <v>100</v>
       </c>
-      <c r="I8" s="22" t="n">
+      <c r="I8" s="18" t="n">
         <v>8</v>
       </c>
-      <c r="J8" s="23">
+      <c r="J8" s="19">
         <f>IF(B8="","",D8*G8*(H8/100))</f>
         <v/>
       </c>
-      <c r="K8" s="23">
+      <c r="K8" s="19">
         <f>IF(B8="","",J8*I8)</f>
         <v/>
       </c>
-      <c r="L8" s="24">
+      <c r="L8" s="20">
         <f>IF(B8="","Bos Satir",IF(OR(D8&lt;=0,G8&lt;=0,H8&lt;=0,H8&gt;100),"HATA: Kontrol Et","OK"))</f>
         <v/>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
-      <c r="A9" s="20" t="n">
+      <c r="A9" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="B9" s="18" t="inlineStr"/>
-      <c r="C9" s="18" t="inlineStr"/>
-      <c r="D9" s="21" t="inlineStr"/>
-      <c r="E9" s="21" t="inlineStr"/>
-      <c r="F9" s="21" t="inlineStr"/>
-      <c r="G9" s="21" t="inlineStr"/>
-      <c r="H9" s="22" t="n">
+      <c r="B9" s="15" t="inlineStr"/>
+      <c r="C9" s="15" t="inlineStr"/>
+      <c r="D9" s="17" t="inlineStr"/>
+      <c r="E9" s="17" t="inlineStr"/>
+      <c r="F9" s="17" t="inlineStr"/>
+      <c r="G9" s="17" t="inlineStr"/>
+      <c r="H9" s="18" t="n">
         <v>100</v>
       </c>
-      <c r="I9" s="22" t="n">
+      <c r="I9" s="18" t="n">
         <v>8</v>
       </c>
-      <c r="J9" s="23">
+      <c r="J9" s="19">
         <f>IF(B9="","",D9*G9*(H9/100))</f>
         <v/>
       </c>
-      <c r="K9" s="23">
+      <c r="K9" s="19">
         <f>IF(B9="","",J9*I9)</f>
         <v/>
       </c>
-      <c r="L9" s="24">
+      <c r="L9" s="20">
         <f>IF(B9="","Bos Satir",IF(OR(D9&lt;=0,G9&lt;=0,H9&lt;=0,H9&gt;100),"HATA: Kontrol Et","OK"))</f>
         <v/>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
-      <c r="A10" s="20" t="n">
+      <c r="A10" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="B10" s="18" t="inlineStr"/>
-      <c r="C10" s="18" t="inlineStr"/>
-      <c r="D10" s="21" t="inlineStr"/>
-      <c r="E10" s="21" t="inlineStr"/>
-      <c r="F10" s="21" t="inlineStr"/>
-      <c r="G10" s="21" t="inlineStr"/>
-      <c r="H10" s="22" t="n">
+      <c r="B10" s="15" t="inlineStr"/>
+      <c r="C10" s="15" t="inlineStr"/>
+      <c r="D10" s="17" t="inlineStr"/>
+      <c r="E10" s="17" t="inlineStr"/>
+      <c r="F10" s="17" t="inlineStr"/>
+      <c r="G10" s="17" t="inlineStr"/>
+      <c r="H10" s="18" t="n">
         <v>100</v>
       </c>
-      <c r="I10" s="22" t="n">
+      <c r="I10" s="18" t="n">
         <v>8</v>
       </c>
-      <c r="J10" s="23">
+      <c r="J10" s="19">
         <f>IF(B10="","",D10*G10*(H10/100))</f>
         <v/>
       </c>
-      <c r="K10" s="23">
+      <c r="K10" s="19">
         <f>IF(B10="","",J10*I10)</f>
         <v/>
       </c>
-      <c r="L10" s="24">
+      <c r="L10" s="20">
         <f>IF(B10="","Bos Satir",IF(OR(D10&lt;=0,G10&lt;=0,H10&lt;=0,H10&gt;100),"HATA: Kontrol Et","OK"))</f>
         <v/>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1">
-      <c r="A11" s="20" t="n">
+      <c r="A11" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="B11" s="18" t="inlineStr"/>
-      <c r="C11" s="18" t="inlineStr"/>
-      <c r="D11" s="21" t="inlineStr"/>
-      <c r="E11" s="21" t="inlineStr"/>
-      <c r="F11" s="21" t="inlineStr"/>
-      <c r="G11" s="21" t="inlineStr"/>
-      <c r="H11" s="22" t="n">
+      <c r="B11" s="15" t="inlineStr"/>
+      <c r="C11" s="15" t="inlineStr"/>
+      <c r="D11" s="17" t="inlineStr"/>
+      <c r="E11" s="17" t="inlineStr"/>
+      <c r="F11" s="17" t="inlineStr"/>
+      <c r="G11" s="17" t="inlineStr"/>
+      <c r="H11" s="18" t="n">
         <v>100</v>
       </c>
-      <c r="I11" s="22" t="n">
+      <c r="I11" s="18" t="n">
         <v>8</v>
       </c>
-      <c r="J11" s="23">
+      <c r="J11" s="19">
         <f>IF(B11="","",D11*G11*(H11/100))</f>
         <v/>
       </c>
-      <c r="K11" s="23">
+      <c r="K11" s="19">
         <f>IF(B11="","",J11*I11)</f>
         <v/>
       </c>
-      <c r="L11" s="24">
+      <c r="L11" s="20">
         <f>IF(B11="","Bos Satir",IF(OR(D11&lt;=0,G11&lt;=0,H11&lt;=0,H11&gt;100),"HATA: Kontrol Et","OK"))</f>
         <v/>
       </c>
     </row>
     <row r="12" ht="18" customHeight="1">
-      <c r="A12" s="20" t="n">
+      <c r="A12" s="5" t="n">
         <v>8</v>
       </c>
-      <c r="B12" s="18" t="inlineStr"/>
-      <c r="C12" s="18" t="inlineStr"/>
-      <c r="D12" s="21" t="inlineStr"/>
-      <c r="E12" s="21" t="inlineStr"/>
-      <c r="F12" s="21" t="inlineStr"/>
-      <c r="G12" s="21" t="inlineStr"/>
-      <c r="H12" s="22" t="n">
+      <c r="B12" s="15" t="inlineStr"/>
+      <c r="C12" s="15" t="inlineStr"/>
+      <c r="D12" s="17" t="inlineStr"/>
+      <c r="E12" s="17" t="inlineStr"/>
+      <c r="F12" s="17" t="inlineStr"/>
+      <c r="G12" s="17" t="inlineStr"/>
+      <c r="H12" s="18" t="n">
         <v>100</v>
       </c>
-      <c r="I12" s="22" t="n">
+      <c r="I12" s="18" t="n">
         <v>8</v>
       </c>
-      <c r="J12" s="23">
+      <c r="J12" s="19">
         <f>IF(B12="","",D12*G12*(H12/100))</f>
         <v/>
       </c>
-      <c r="K12" s="23">
+      <c r="K12" s="19">
         <f>IF(B12="","",J12*I12)</f>
         <v/>
       </c>
-      <c r="L12" s="24">
+      <c r="L12" s="20">
         <f>IF(B12="","Bos Satir",IF(OR(D12&lt;=0,G12&lt;=0,H12&lt;=0,H12&gt;100),"HATA: Kontrol Et","OK"))</f>
         <v/>
       </c>
     </row>
     <row r="13" ht="18" customHeight="1">
-      <c r="A13" s="20" t="n">
+      <c r="A13" s="5" t="n">
         <v>9</v>
       </c>
-      <c r="B13" s="18" t="inlineStr"/>
-      <c r="C13" s="18" t="inlineStr"/>
-      <c r="D13" s="21" t="inlineStr"/>
-      <c r="E13" s="21" t="inlineStr"/>
-      <c r="F13" s="21" t="inlineStr"/>
-      <c r="G13" s="21" t="inlineStr"/>
-      <c r="H13" s="22" t="n">
+      <c r="B13" s="15" t="inlineStr"/>
+      <c r="C13" s="15" t="inlineStr"/>
+      <c r="D13" s="17" t="inlineStr"/>
+      <c r="E13" s="17" t="inlineStr"/>
+      <c r="F13" s="17" t="inlineStr"/>
+      <c r="G13" s="17" t="inlineStr"/>
+      <c r="H13" s="18" t="n">
         <v>100</v>
       </c>
-      <c r="I13" s="22" t="n">
+      <c r="I13" s="18" t="n">
         <v>8</v>
       </c>
-      <c r="J13" s="23">
+      <c r="J13" s="19">
         <f>IF(B13="","",D13*G13*(H13/100))</f>
         <v/>
       </c>
-      <c r="K13" s="23">
+      <c r="K13" s="19">
         <f>IF(B13="","",J13*I13)</f>
         <v/>
       </c>
-      <c r="L13" s="24">
+      <c r="L13" s="20">
         <f>IF(B13="","Bos Satir",IF(OR(D13&lt;=0,G13&lt;=0,H13&lt;=0,H13&gt;100),"HATA: Kontrol Et","OK"))</f>
         <v/>
       </c>
     </row>
     <row r="14" ht="18" customHeight="1">
-      <c r="A14" s="20" t="n">
+      <c r="A14" s="5" t="n">
         <v>10</v>
       </c>
-      <c r="B14" s="18" t="inlineStr"/>
-      <c r="C14" s="18" t="inlineStr"/>
-      <c r="D14" s="21" t="inlineStr"/>
-      <c r="E14" s="21" t="inlineStr"/>
-      <c r="F14" s="21" t="inlineStr"/>
-      <c r="G14" s="21" t="inlineStr"/>
-      <c r="H14" s="22" t="n">
+      <c r="B14" s="15" t="inlineStr"/>
+      <c r="C14" s="15" t="inlineStr"/>
+      <c r="D14" s="17" t="inlineStr"/>
+      <c r="E14" s="17" t="inlineStr"/>
+      <c r="F14" s="17" t="inlineStr"/>
+      <c r="G14" s="17" t="inlineStr"/>
+      <c r="H14" s="18" t="n">
         <v>100</v>
       </c>
-      <c r="I14" s="22" t="n">
+      <c r="I14" s="18" t="n">
         <v>8</v>
       </c>
-      <c r="J14" s="23">
+      <c r="J14" s="19">
         <f>IF(B14="","",D14*G14*(H14/100))</f>
         <v/>
       </c>
-      <c r="K14" s="23">
+      <c r="K14" s="19">
         <f>IF(B14="","",J14*I14)</f>
         <v/>
       </c>
-      <c r="L14" s="24">
+      <c r="L14" s="20">
         <f>IF(B14="","Bos Satir",IF(OR(D14&lt;=0,G14&lt;=0,H14&lt;=0,H14&gt;100),"HATA: Kontrol Et","OK"))</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="18" customHeight="1">
-      <c r="A15" s="20" t="n">
+      <c r="A15" s="5" t="n">
         <v>11</v>
       </c>
-      <c r="B15" s="18" t="inlineStr"/>
-      <c r="C15" s="18" t="inlineStr"/>
-      <c r="D15" s="21" t="inlineStr"/>
-      <c r="E15" s="21" t="inlineStr"/>
-      <c r="F15" s="21" t="inlineStr"/>
-      <c r="G15" s="21" t="inlineStr"/>
-      <c r="H15" s="22" t="n">
+      <c r="B15" s="15" t="inlineStr"/>
+      <c r="C15" s="15" t="inlineStr"/>
+      <c r="D15" s="17" t="inlineStr"/>
+      <c r="E15" s="17" t="inlineStr"/>
+      <c r="F15" s="17" t="inlineStr"/>
+      <c r="G15" s="17" t="inlineStr"/>
+      <c r="H15" s="18" t="n">
         <v>100</v>
       </c>
-      <c r="I15" s="22" t="n">
+      <c r="I15" s="18" t="n">
         <v>8</v>
       </c>
-      <c r="J15" s="23">
+      <c r="J15" s="19">
         <f>IF(B15="","",D15*G15*(H15/100))</f>
         <v/>
       </c>
-      <c r="K15" s="23">
+      <c r="K15" s="19">
         <f>IF(B15="","",J15*I15)</f>
         <v/>
       </c>
-      <c r="L15" s="24">
+      <c r="L15" s="20">
         <f>IF(B15="","Bos Satir",IF(OR(D15&lt;=0,G15&lt;=0,H15&lt;=0,H15&gt;100),"HATA: Kontrol Et","OK"))</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="18" customHeight="1">
-      <c r="A16" s="20" t="n">
+      <c r="A16" s="5" t="n">
         <v>12</v>
       </c>
-      <c r="B16" s="18" t="inlineStr"/>
-      <c r="C16" s="18" t="inlineStr"/>
-      <c r="D16" s="21" t="inlineStr"/>
-      <c r="E16" s="21" t="inlineStr"/>
-      <c r="F16" s="21" t="inlineStr"/>
-      <c r="G16" s="21" t="inlineStr"/>
-      <c r="H16" s="22" t="n">
+      <c r="B16" s="15" t="inlineStr"/>
+      <c r="C16" s="15" t="inlineStr"/>
+      <c r="D16" s="17" t="inlineStr"/>
+      <c r="E16" s="17" t="inlineStr"/>
+      <c r="F16" s="17" t="inlineStr"/>
+      <c r="G16" s="17" t="inlineStr"/>
+      <c r="H16" s="18" t="n">
         <v>100</v>
       </c>
-      <c r="I16" s="22" t="n">
+      <c r="I16" s="18" t="n">
         <v>8</v>
       </c>
-      <c r="J16" s="23">
+      <c r="J16" s="19">
         <f>IF(B16="","",D16*G16*(H16/100))</f>
         <v/>
       </c>
-      <c r="K16" s="23">
+      <c r="K16" s="19">
         <f>IF(B16="","",J16*I16)</f>
         <v/>
       </c>
-      <c r="L16" s="24">
+      <c r="L16" s="20">
         <f>IF(B16="","Bos Satir",IF(OR(D16&lt;=0,G16&lt;=0,H16&lt;=0,H16&gt;100),"HATA: Kontrol Et","OK"))</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="18" customHeight="1">
-      <c r="A17" s="20" t="n">
+      <c r="A17" s="5" t="n">
         <v>13</v>
       </c>
-      <c r="B17" s="18" t="inlineStr"/>
-      <c r="C17" s="18" t="inlineStr"/>
-      <c r="D17" s="21" t="inlineStr"/>
-      <c r="E17" s="21" t="inlineStr"/>
-      <c r="F17" s="21" t="inlineStr"/>
-      <c r="G17" s="21" t="inlineStr"/>
-      <c r="H17" s="22" t="n">
+      <c r="B17" s="15" t="inlineStr"/>
+      <c r="C17" s="15" t="inlineStr"/>
+      <c r="D17" s="17" t="inlineStr"/>
+      <c r="E17" s="17" t="inlineStr"/>
+      <c r="F17" s="17" t="inlineStr"/>
+      <c r="G17" s="17" t="inlineStr"/>
+      <c r="H17" s="18" t="n">
         <v>100</v>
       </c>
-      <c r="I17" s="22" t="n">
+      <c r="I17" s="18" t="n">
         <v>8</v>
       </c>
-      <c r="J17" s="23">
+      <c r="J17" s="19">
         <f>IF(B17="","",D17*G17*(H17/100))</f>
         <v/>
       </c>
-      <c r="K17" s="23">
+      <c r="K17" s="19">
         <f>IF(B17="","",J17*I17)</f>
         <v/>
       </c>
-      <c r="L17" s="24">
+      <c r="L17" s="20">
         <f>IF(B17="","Bos Satir",IF(OR(D17&lt;=0,G17&lt;=0,H17&lt;=0,H17&gt;100),"HATA: Kontrol Et","OK"))</f>
         <v/>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1">
-      <c r="A18" s="20" t="n">
+      <c r="A18" s="5" t="n">
         <v>14</v>
       </c>
-      <c r="B18" s="18" t="inlineStr"/>
-      <c r="C18" s="18" t="inlineStr"/>
-      <c r="D18" s="21" t="inlineStr"/>
-      <c r="E18" s="21" t="inlineStr"/>
-      <c r="F18" s="21" t="inlineStr"/>
-      <c r="G18" s="21" t="inlineStr"/>
-      <c r="H18" s="22" t="n">
+      <c r="B18" s="15" t="inlineStr"/>
+      <c r="C18" s="15" t="inlineStr"/>
+      <c r="D18" s="17" t="inlineStr"/>
+      <c r="E18" s="17" t="inlineStr"/>
+      <c r="F18" s="17" t="inlineStr"/>
+      <c r="G18" s="17" t="inlineStr"/>
+      <c r="H18" s="18" t="n">
         <v>100</v>
       </c>
-      <c r="I18" s="22" t="n">
+      <c r="I18" s="18" t="n">
         <v>8</v>
       </c>
-      <c r="J18" s="23">
+      <c r="J18" s="19">
         <f>IF(B18="","",D18*G18*(H18/100))</f>
         <v/>
       </c>
-      <c r="K18" s="23">
+      <c r="K18" s="19">
         <f>IF(B18="","",J18*I18)</f>
         <v/>
       </c>
-      <c r="L18" s="24">
+      <c r="L18" s="20">
         <f>IF(B18="","Bos Satir",IF(OR(D18&lt;=0,G18&lt;=0,H18&lt;=0,H18&gt;100),"HATA: Kontrol Et","OK"))</f>
         <v/>
       </c>
     </row>
     <row r="19" ht="18" customHeight="1">
-      <c r="A19" s="20" t="n">
+      <c r="A19" s="5" t="n">
         <v>15</v>
       </c>
-      <c r="B19" s="18" t="inlineStr"/>
-      <c r="C19" s="18" t="inlineStr"/>
-      <c r="D19" s="21" t="inlineStr"/>
-      <c r="E19" s="21" t="inlineStr"/>
-      <c r="F19" s="21" t="inlineStr"/>
-      <c r="G19" s="21" t="inlineStr"/>
-      <c r="H19" s="22" t="n">
+      <c r="B19" s="15" t="inlineStr"/>
+      <c r="C19" s="15" t="inlineStr"/>
+      <c r="D19" s="17" t="inlineStr"/>
+      <c r="E19" s="17" t="inlineStr"/>
+      <c r="F19" s="17" t="inlineStr"/>
+      <c r="G19" s="17" t="inlineStr"/>
+      <c r="H19" s="18" t="n">
         <v>100</v>
       </c>
-      <c r="I19" s="22" t="n">
+      <c r="I19" s="18" t="n">
         <v>8</v>
       </c>
-      <c r="J19" s="23">
+      <c r="J19" s="19">
         <f>IF(B19="","",D19*G19*(H19/100))</f>
         <v/>
       </c>
-      <c r="K19" s="23">
+      <c r="K19" s="19">
         <f>IF(B19="","",J19*I19)</f>
         <v/>
       </c>
-      <c r="L19" s="24">
+      <c r="L19" s="20">
         <f>IF(B19="","Bos Satir",IF(OR(D19&lt;=0,G19&lt;=0,H19&lt;=0,H19&gt;100),"HATA: Kontrol Et","OK"))</f>
         <v/>
       </c>
     </row>
     <row r="20" ht="18" customHeight="1">
-      <c r="A20" s="20" t="n">
+      <c r="A20" s="5" t="n">
         <v>16</v>
       </c>
-      <c r="B20" s="18" t="inlineStr"/>
-      <c r="C20" s="18" t="inlineStr"/>
-      <c r="D20" s="21" t="inlineStr"/>
-      <c r="E20" s="21" t="inlineStr"/>
-      <c r="F20" s="21" t="inlineStr"/>
-      <c r="G20" s="21" t="inlineStr"/>
-      <c r="H20" s="22" t="n">
+      <c r="B20" s="15" t="inlineStr"/>
+      <c r="C20" s="15" t="inlineStr"/>
+      <c r="D20" s="17" t="inlineStr"/>
+      <c r="E20" s="17" t="inlineStr"/>
+      <c r="F20" s="17" t="inlineStr"/>
+      <c r="G20" s="17" t="inlineStr"/>
+      <c r="H20" s="18" t="n">
         <v>100</v>
       </c>
-      <c r="I20" s="22" t="n">
+      <c r="I20" s="18" t="n">
         <v>8</v>
       </c>
-      <c r="J20" s="23">
+      <c r="J20" s="19">
         <f>IF(B20="","",D20*G20*(H20/100))</f>
         <v/>
       </c>
-      <c r="K20" s="23">
+      <c r="K20" s="19">
         <f>IF(B20="","",J20*I20)</f>
         <v/>
       </c>
-      <c r="L20" s="24">
+      <c r="L20" s="20">
         <f>IF(B20="","Bos Satir",IF(OR(D20&lt;=0,G20&lt;=0,H20&lt;=0,H20&gt;100),"HATA: Kontrol Et","OK"))</f>
         <v/>
       </c>
     </row>
     <row r="21" ht="18" customHeight="1">
-      <c r="A21" s="20" t="n">
+      <c r="A21" s="5" t="n">
         <v>17</v>
       </c>
-      <c r="B21" s="18" t="inlineStr"/>
-      <c r="C21" s="18" t="inlineStr"/>
-      <c r="D21" s="21" t="inlineStr"/>
-      <c r="E21" s="21" t="inlineStr"/>
-      <c r="F21" s="21" t="inlineStr"/>
-      <c r="G21" s="21" t="inlineStr"/>
-      <c r="H21" s="22" t="n">
+      <c r="B21" s="15" t="inlineStr"/>
+      <c r="C21" s="15" t="inlineStr"/>
+      <c r="D21" s="17" t="inlineStr"/>
+      <c r="E21" s="17" t="inlineStr"/>
+      <c r="F21" s="17" t="inlineStr"/>
+      <c r="G21" s="17" t="inlineStr"/>
+      <c r="H21" s="18" t="n">
         <v>100</v>
       </c>
-      <c r="I21" s="22" t="n">
+      <c r="I21" s="18" t="n">
         <v>8</v>
       </c>
-      <c r="J21" s="23">
+      <c r="J21" s="19">
         <f>IF(B21="","",D21*G21*(H21/100))</f>
         <v/>
       </c>
-      <c r="K21" s="23">
+      <c r="K21" s="19">
         <f>IF(B21="","",J21*I21)</f>
         <v/>
       </c>
-      <c r="L21" s="24">
+      <c r="L21" s="20">
         <f>IF(B21="","Bos Satir",IF(OR(D21&lt;=0,G21&lt;=0,H21&lt;=0,H21&gt;100),"HATA: Kontrol Et","OK"))</f>
         <v/>
       </c>
     </row>
     <row r="22" ht="18" customHeight="1">
-      <c r="A22" s="20" t="n">
+      <c r="A22" s="5" t="n">
         <v>18</v>
       </c>
-      <c r="B22" s="18" t="inlineStr"/>
-      <c r="C22" s="18" t="inlineStr"/>
-      <c r="D22" s="21" t="inlineStr"/>
-      <c r="E22" s="21" t="inlineStr"/>
-      <c r="F22" s="21" t="inlineStr"/>
-      <c r="G22" s="21" t="inlineStr"/>
-      <c r="H22" s="22" t="n">
+      <c r="B22" s="15" t="inlineStr"/>
+      <c r="C22" s="15" t="inlineStr"/>
+      <c r="D22" s="17" t="inlineStr"/>
+      <c r="E22" s="17" t="inlineStr"/>
+      <c r="F22" s="17" t="inlineStr"/>
+      <c r="G22" s="17" t="inlineStr"/>
+      <c r="H22" s="18" t="n">
         <v>100</v>
       </c>
-      <c r="I22" s="22" t="n">
+      <c r="I22" s="18" t="n">
         <v>8</v>
       </c>
-      <c r="J22" s="23">
+      <c r="J22" s="19">
         <f>IF(B22="","",D22*G22*(H22/100))</f>
         <v/>
       </c>
-      <c r="K22" s="23">
+      <c r="K22" s="19">
         <f>IF(B22="","",J22*I22)</f>
         <v/>
       </c>
-      <c r="L22" s="24">
+      <c r="L22" s="20">
         <f>IF(B22="","Bos Satir",IF(OR(D22&lt;=0,G22&lt;=0,H22&lt;=0,H22&gt;100),"HATA: Kontrol Et","OK"))</f>
         <v/>
       </c>
     </row>
     <row r="23" ht="18" customHeight="1">
-      <c r="A23" s="20" t="n">
+      <c r="A23" s="5" t="n">
         <v>19</v>
       </c>
-      <c r="B23" s="18" t="inlineStr"/>
-      <c r="C23" s="18" t="inlineStr"/>
-      <c r="D23" s="21" t="inlineStr"/>
-      <c r="E23" s="21" t="inlineStr"/>
-      <c r="F23" s="21" t="inlineStr"/>
-      <c r="G23" s="21" t="inlineStr"/>
-      <c r="H23" s="22" t="n">
+      <c r="B23" s="15" t="inlineStr"/>
+      <c r="C23" s="15" t="inlineStr"/>
+      <c r="D23" s="17" t="inlineStr"/>
+      <c r="E23" s="17" t="inlineStr"/>
+      <c r="F23" s="17" t="inlineStr"/>
+      <c r="G23" s="17" t="inlineStr"/>
+      <c r="H23" s="18" t="n">
         <v>100</v>
       </c>
-      <c r="I23" s="22" t="n">
+      <c r="I23" s="18" t="n">
         <v>8</v>
       </c>
-      <c r="J23" s="23">
+      <c r="J23" s="19">
         <f>IF(B23="","",D23*G23*(H23/100))</f>
         <v/>
       </c>
-      <c r="K23" s="23">
+      <c r="K23" s="19">
         <f>IF(B23="","",J23*I23)</f>
         <v/>
       </c>
-      <c r="L23" s="24">
+      <c r="L23" s="20">
         <f>IF(B23="","Bos Satir",IF(OR(D23&lt;=0,G23&lt;=0,H23&lt;=0,H23&gt;100),"HATA: Kontrol Et","OK"))</f>
         <v/>
       </c>
     </row>
     <row r="24" ht="18" customHeight="1">
-      <c r="A24" s="20" t="n">
+      <c r="A24" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="B24" s="18" t="inlineStr"/>
-      <c r="C24" s="18" t="inlineStr"/>
-      <c r="D24" s="21" t="inlineStr"/>
-      <c r="E24" s="21" t="inlineStr"/>
-      <c r="F24" s="21" t="inlineStr"/>
-      <c r="G24" s="21" t="inlineStr"/>
-      <c r="H24" s="22" t="n">
+      <c r="B24" s="15" t="inlineStr"/>
+      <c r="C24" s="15" t="inlineStr"/>
+      <c r="D24" s="17" t="inlineStr"/>
+      <c r="E24" s="17" t="inlineStr"/>
+      <c r="F24" s="17" t="inlineStr"/>
+      <c r="G24" s="17" t="inlineStr"/>
+      <c r="H24" s="18" t="n">
         <v>100</v>
       </c>
-      <c r="I24" s="22" t="n">
+      <c r="I24" s="18" t="n">
         <v>8</v>
       </c>
-      <c r="J24" s="23">
+      <c r="J24" s="19">
         <f>IF(B24="","",D24*G24*(H24/100))</f>
         <v/>
       </c>
-      <c r="K24" s="23">
+      <c r="K24" s="19">
         <f>IF(B24="","",J24*I24)</f>
         <v/>
       </c>
-      <c r="L24" s="24">
+      <c r="L24" s="20">
         <f>IF(B24="","Bos Satir",IF(OR(D24&lt;=0,G24&lt;=0,H24&lt;=0,H24&gt;100),"HATA: Kontrol Et","OK"))</f>
         <v/>
       </c>
     </row>
     <row r="25" ht="20" customHeight="1">
-      <c r="B25" s="25" t="inlineStr">
+      <c r="B25" s="21" t="inlineStr">
         <is>
           <t>TOPLAM</t>
         </is>
       </c>
-      <c r="J25" s="26">
+      <c r="J25" s="22">
         <f>SUM(J5:J24)</f>
         <v/>
       </c>
-      <c r="K25" s="26">
+      <c r="K25" s="22">
         <f>SUM(K5:K24)</f>
         <v/>
       </c>
@@ -2047,7 +3195,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:E27"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
@@ -2068,373 +3216,373 @@
       <c r="E1" s="2" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="13" t="inlineStr">
+      <c r="A3" s="23" t="inlineStr">
         <is>
           <t>GIRIS VERILERI</t>
         </is>
       </c>
-      <c r="B3" s="14" t="n"/>
+      <c r="B3" s="24" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="27" t="inlineStr"/>
-      <c r="B4" s="28" t="n"/>
-      <c r="D4" s="17" t="inlineStr">
+      <c r="A4" s="25" t="inlineStr"/>
+      <c r="B4" s="26" t="n"/>
+      <c r="D4" s="14" t="inlineStr">
         <is>
           <t>Toplam Hava Debisi (m3/h)</t>
         </is>
       </c>
-      <c r="E4" s="23">
+      <c r="E4" s="19">
         <f>IFERROR('Makine Giris'!J25,0)</f>
         <v/>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="17" t="inlineStr">
+      <c r="A5" s="14" t="inlineStr">
         <is>
           <t>Bransman (Dal Hatti) Uzunlugu (m)</t>
         </is>
       </c>
-      <c r="B5" s="29" t="n">
+      <c r="B5" s="27" t="n">
         <v>25</v>
       </c>
-      <c r="D5" s="17" t="inlineStr">
+      <c r="D5" s="14" t="inlineStr">
         <is>
           <t>Toplam Hava Debisi (m3/s)</t>
         </is>
       </c>
-      <c r="E5" s="30">
+      <c r="E5" s="28">
         <f>E4/3600</f>
         <v/>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="17" t="inlineStr">
+      <c r="A6" s="14" t="inlineStr">
         <is>
           <t>45 derece Dirsek Sayisi (adet)</t>
         </is>
       </c>
-      <c r="B6" s="22" t="n">
+      <c r="B6" s="18" t="n">
         <v>4</v>
       </c>
-      <c r="D6" s="17" t="inlineStr">
+      <c r="D6" s="14" t="inlineStr">
         <is>
           <t>Gerekli Boru Kesit Alani (m2)</t>
         </is>
       </c>
-      <c r="E6" s="31">
+      <c r="E6" s="29">
         <f>E5/B11</f>
         <v/>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="17" t="inlineStr">
+      <c r="A7" s="14" t="inlineStr">
         <is>
           <t>90 derece Dirsek Sayisi (adet)</t>
         </is>
       </c>
-      <c r="B7" s="22" t="n">
+      <c r="B7" s="18" t="n">
         <v>6</v>
       </c>
-      <c r="D7" s="17" t="inlineStr">
+      <c r="D7" s="14" t="inlineStr">
         <is>
           <t>Gerekli Boru Capi (mm)</t>
         </is>
       </c>
-      <c r="E7" s="32">
+      <c r="E7" s="30">
         <f>SQRT(4*E6/PI())*1000</f>
         <v/>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="17" t="inlineStr">
+      <c r="A8" s="14" t="inlineStr">
         <is>
           <t>T Baglanti Sayisi (adet)</t>
         </is>
       </c>
-      <c r="B8" s="22" t="n">
+      <c r="B8" s="18" t="n">
         <v>5</v>
       </c>
-      <c r="D8" s="17" t="inlineStr">
+      <c r="D8" s="14" t="inlineStr">
         <is>
           <t>Onerilen Standart Cap (mm)</t>
         </is>
       </c>
-      <c r="E8" s="26">
+      <c r="E8" s="22">
         <f>_xlfn.XLOOKUP(E7,'Boru Capi Tablosu'!$B$5:$B$27,'Boru Capi Tablosu'!$B$5:$B$27,,1)</f>
         <v/>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="17" t="inlineStr">
+      <c r="A9" s="14" t="inlineStr">
         <is>
           <t>Reduksiyon Sayisi (adet)</t>
         </is>
       </c>
-      <c r="B9" s="22" t="n">
+      <c r="B9" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="D9" s="17" t="inlineStr">
+      <c r="D9" s="14" t="inlineStr">
         <is>
           <t>Secilen Borunun Kesit Alani (m2)</t>
         </is>
       </c>
-      <c r="E9" s="31">
+      <c r="E9" s="29">
         <f>PI()/4*(E8/1000)^2</f>
         <v/>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="17" t="inlineStr">
+      <c r="A10" s="14" t="inlineStr">
         <is>
           <t>Boru Malzemesi</t>
         </is>
       </c>
-      <c r="B10" s="18" t="inlineStr">
+      <c r="B10" s="15" t="inlineStr">
         <is>
           <t>Galvanizli Sac</t>
         </is>
       </c>
-      <c r="D10" s="17" t="inlineStr">
+      <c r="D10" s="14" t="inlineStr">
         <is>
           <t>Gercek Hava Hizi (m/s)</t>
         </is>
       </c>
-      <c r="E10" s="33">
+      <c r="E10" s="31">
         <f>E5/E9</f>
         <v/>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="17" t="inlineStr">
+      <c r="A11" s="14" t="inlineStr">
         <is>
           <t>Hedef Tasima Hizi (m/s)</t>
         </is>
       </c>
-      <c r="B11" s="34" t="n">
+      <c r="B11" s="32" t="n">
         <v>22</v>
       </c>
-      <c r="D11" s="17" t="inlineStr">
+      <c r="D11" s="14" t="inlineStr">
         <is>
           <t>Hava Yogunlugu (kg/m3)</t>
         </is>
       </c>
-      <c r="E11" s="35">
+      <c r="E11" s="33">
         <f>1.2</f>
         <v/>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="17" t="inlineStr">
+      <c r="A12" s="14" t="inlineStr">
         <is>
           <t>Guvenlik Payi (%)</t>
         </is>
       </c>
-      <c r="B12" s="22" t="n">
+      <c r="B12" s="18" t="n">
         <v>15</v>
       </c>
-      <c r="D12" s="17" t="inlineStr">
+      <c r="D12" s="14" t="inlineStr">
         <is>
           <t>Surtunme Katsayisi - lambda</t>
         </is>
       </c>
-      <c r="E12" s="30">
+      <c r="E12" s="28">
         <f>_xlfn.XLOOKUP(B10,$A$16:$A$19,$B$16:$B$19)</f>
         <v/>
       </c>
     </row>
     <row r="13">
-      <c r="D13" s="17" t="inlineStr">
+      <c r="D13" s="14" t="inlineStr">
         <is>
           <t>Toplam Hat Uzunlugu (m)</t>
         </is>
       </c>
-      <c r="E13" s="32">
+      <c r="E13" s="30">
         <f>B4+B5</f>
         <v/>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="13" t="inlineStr">
+      <c r="A14" s="23" t="inlineStr">
         <is>
           <t>MALZEME SURTUNME KATSAYISI (lambda)</t>
         </is>
       </c>
-      <c r="B14" s="14" t="n"/>
-      <c r="D14" s="17" t="inlineStr">
+      <c r="B14" s="24" t="n"/>
+      <c r="D14" s="14" t="inlineStr">
         <is>
           <t>Statik (Surtunme) Basinc Kaybi (Pa)</t>
         </is>
       </c>
-      <c r="E14" s="23">
+      <c r="E14" s="19">
         <f>E12*(E13/(E8/1000))*(E11*E10^2/2)</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="32" customHeight="1">
-      <c r="A15" s="15" t="inlineStr">
+      <c r="A15" s="4" t="inlineStr">
         <is>
           <t>Boru Malzemesi</t>
         </is>
       </c>
-      <c r="B15" s="15" t="inlineStr">
+      <c r="B15" s="4" t="inlineStr">
         <is>
           <t>Lambda</t>
         </is>
       </c>
-      <c r="D15" s="17" t="inlineStr">
+      <c r="D15" s="14" t="inlineStr">
         <is>
           <t>Yerel Direnc Katsayilari Toplami (sigma-zeta)</t>
         </is>
       </c>
-      <c r="E15" s="35">
+      <c r="E15" s="33">
         <f>B6*0.15+B7*0.3+B8*1+B9*0.2</f>
         <v/>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="4" t="inlineStr">
+      <c r="A16" s="34" t="inlineStr">
         <is>
           <t>Galvanizli Sac</t>
         </is>
       </c>
-      <c r="B16" s="36" t="n">
+      <c r="B16" s="35" t="n">
         <v>0.02</v>
       </c>
-      <c r="D16" s="17" t="inlineStr">
+      <c r="D16" s="14" t="inlineStr">
         <is>
           <t>Dinamik (Yerel) Basinc Kaybi (Pa)</t>
         </is>
       </c>
-      <c r="E16" s="23">
+      <c r="E16" s="19">
         <f>E15*(E11*E10^2/2)</f>
         <v/>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="4" t="inlineStr">
+      <c r="A17" s="34" t="inlineStr">
         <is>
           <t>Paslanmaz Celik</t>
         </is>
       </c>
-      <c r="B17" s="36" t="n">
+      <c r="B17" s="35" t="n">
         <v>0.018</v>
       </c>
-      <c r="D17" s="17" t="inlineStr">
+      <c r="D17" s="14" t="inlineStr">
         <is>
           <t>Ara Toplam Basinc Kaybi (Pa)</t>
         </is>
       </c>
-      <c r="E17" s="23">
+      <c r="E17" s="19">
         <f>E14+E16</f>
         <v/>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="4" t="inlineStr">
+      <c r="A18" s="34" t="inlineStr">
         <is>
           <t>Spiral Sac</t>
         </is>
       </c>
-      <c r="B18" s="36" t="n">
+      <c r="B18" s="35" t="n">
         <v>0.022</v>
       </c>
-      <c r="D18" s="17" t="inlineStr">
+      <c r="D18" s="14" t="inlineStr">
         <is>
           <t>Guvenlik Payi Eklenmis Toplam Basinc Kaybi (Pa)</t>
         </is>
       </c>
-      <c r="E18" s="26">
+      <c r="E18" s="22">
         <f>E17*(1+B12/100)</f>
         <v/>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="4" t="inlineStr">
+      <c r="A19" s="34" t="inlineStr">
         <is>
           <t>PVC</t>
         </is>
       </c>
-      <c r="B19" s="36" t="n">
+      <c r="B19" s="35" t="n">
         <v>0.025</v>
       </c>
-      <c r="D19" s="37" t="inlineStr">
+      <c r="D19" s="36" t="inlineStr">
         <is>
           <t>TOPLAM SISTEM BASINC KAYBI (Pa)</t>
         </is>
       </c>
-      <c r="E19" s="38">
+      <c r="E19" s="37">
         <f>E18</f>
         <v/>
       </c>
     </row>
     <row r="20" ht="28" customHeight="1">
-      <c r="D20" s="17" t="inlineStr">
+      <c r="D20" s="14" t="inlineStr">
         <is>
           <t>Hiz Kontrolu / Uyari</t>
         </is>
       </c>
-      <c r="E20" s="39">
+      <c r="E20" s="38">
         <f>IF(E10&lt;18,"UYARI: Hiz dusuk - boru icinde toz cokebilir",IF(E10&gt;30,"UYARI: Hiz yuksek - asinma/enerji kaybi riski","Hiz uygun (18-28 m/s)"))</f>
         <v/>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="13" t="inlineStr">
+      <c r="A22" s="23" t="inlineStr">
         <is>
           <t>YEREL DIRENC (ZETA) KATSAYILARI</t>
         </is>
       </c>
-      <c r="B22" s="14" t="n"/>
+      <c r="B22" s="24" t="n"/>
     </row>
     <row r="23" ht="32" customHeight="1">
-      <c r="A23" s="15" t="inlineStr">
+      <c r="A23" s="4" t="inlineStr">
         <is>
           <t>Eleman</t>
         </is>
       </c>
-      <c r="B23" s="15" t="inlineStr">
+      <c r="B23" s="4" t="inlineStr">
         <is>
           <t>Zeta</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="4" t="inlineStr">
+      <c r="A24" s="34" t="inlineStr">
         <is>
           <t>45 derece Dirsek</t>
         </is>
       </c>
-      <c r="B24" s="40" t="n">
+      <c r="B24" s="39" t="n">
         <v>0.15</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="4" t="inlineStr">
+      <c r="A25" s="34" t="inlineStr">
         <is>
           <t>90 derece Dirsek</t>
         </is>
       </c>
-      <c r="B25" s="40" t="n">
+      <c r="B25" s="39" t="n">
         <v>0.3</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="4" t="inlineStr">
+      <c r="A26" s="34" t="inlineStr">
         <is>
           <t>T Baglanti</t>
         </is>
       </c>
-      <c r="B26" s="40" t="n">
+      <c r="B26" s="39" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="4" t="inlineStr">
+      <c r="A27" s="34" t="inlineStr">
         <is>
           <t>Reduksiyon</t>
         </is>
       </c>
-      <c r="B27" s="40" t="n">
+      <c r="B27" s="39" t="n">
         <v>0.2</v>
       </c>
     </row>
@@ -2489,8 +3637,2096 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:AY53"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <cols>
+    <col width="2.2" customWidth="1" min="2" max="2"/>
+    <col width="2.2" customWidth="1" min="3" max="3"/>
+    <col width="2.2" customWidth="1" min="4" max="4"/>
+    <col width="2.2" customWidth="1" min="5" max="5"/>
+    <col width="2.2" customWidth="1" min="6" max="6"/>
+    <col width="2.2" customWidth="1" min="7" max="7"/>
+    <col width="2.2" customWidth="1" min="8" max="8"/>
+    <col width="2.2" customWidth="1" min="9" max="9"/>
+    <col width="2.2" customWidth="1" min="10" max="10"/>
+    <col width="2.2" customWidth="1" min="11" max="11"/>
+    <col width="2.2" customWidth="1" min="12" max="12"/>
+    <col width="2.2" customWidth="1" min="13" max="13"/>
+    <col width="2.2" customWidth="1" min="14" max="14"/>
+    <col width="2.2" customWidth="1" min="15" max="15"/>
+    <col width="2.2" customWidth="1" min="16" max="16"/>
+    <col width="2.2" customWidth="1" min="17" max="17"/>
+    <col width="2.2" customWidth="1" min="18" max="18"/>
+    <col width="2.2" customWidth="1" min="19" max="19"/>
+    <col width="2.2" customWidth="1" min="20" max="20"/>
+    <col width="2.2" customWidth="1" min="21" max="21"/>
+    <col width="2.2" customWidth="1" min="22" max="22"/>
+    <col width="2.2" customWidth="1" min="23" max="23"/>
+    <col width="2.2" customWidth="1" min="24" max="24"/>
+    <col width="2.2" customWidth="1" min="25" max="25"/>
+    <col width="2.2" customWidth="1" min="26" max="26"/>
+    <col width="2.2" customWidth="1" min="27" max="27"/>
+    <col width="2.2" customWidth="1" min="28" max="28"/>
+    <col width="2.2" customWidth="1" min="29" max="29"/>
+    <col width="2.2" customWidth="1" min="30" max="30"/>
+    <col width="2.2" customWidth="1" min="31" max="31"/>
+    <col width="2.2" customWidth="1" min="32" max="32"/>
+    <col width="2.2" customWidth="1" min="33" max="33"/>
+    <col width="2.2" customWidth="1" min="34" max="34"/>
+    <col width="2.2" customWidth="1" min="35" max="35"/>
+    <col width="2.2" customWidth="1" min="36" max="36"/>
+    <col width="2.2" customWidth="1" min="37" max="37"/>
+    <col width="2.2" customWidth="1" min="38" max="38"/>
+    <col width="2.2" customWidth="1" min="39" max="39"/>
+    <col width="2.2" customWidth="1" min="40" max="40"/>
+    <col width="2.2" customWidth="1" min="41" max="41"/>
+    <col width="2.2" customWidth="1" min="42" max="42"/>
+    <col width="2.2" customWidth="1" min="43" max="43"/>
+    <col width="2.2" customWidth="1" min="44" max="44"/>
+    <col width="2.2" customWidth="1" min="45" max="45"/>
+    <col width="2.2" customWidth="1" min="46" max="46"/>
+    <col width="2.2" customWidth="1" min="47" max="47"/>
+    <col width="2.2" customWidth="1" min="48" max="48"/>
+    <col width="2.2" customWidth="1" min="49" max="49"/>
+    <col width="2.2" customWidth="1" min="50" max="50"/>
+    <col width="2.2" customWidth="1" min="51" max="51"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="26" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>FABRIKA YERLESIM PLANI VE BORU GUZERGAHI (1 kare = 0.5 m)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="2" t="n"/>
+      <c r="D1" s="2" t="n"/>
+      <c r="E1" s="2" t="n"/>
+      <c r="F1" s="2" t="n"/>
+      <c r="G1" s="2" t="n"/>
+      <c r="H1" s="2" t="n"/>
+      <c r="I1" s="2" t="n"/>
+      <c r="J1" s="2" t="n"/>
+      <c r="K1" s="2" t="n"/>
+      <c r="L1" s="2" t="n"/>
+      <c r="M1" s="2" t="n"/>
+      <c r="N1" s="2" t="n"/>
+      <c r="O1" s="2" t="n"/>
+      <c r="P1" s="2" t="n"/>
+      <c r="Q1" s="2" t="n"/>
+      <c r="R1" s="2" t="n"/>
+      <c r="S1" s="2" t="n"/>
+      <c r="T1" s="2" t="n"/>
+    </row>
+    <row r="2" ht="42" customHeight="1">
+      <c r="A2" s="40" t="inlineStr">
+        <is>
+          <t>Bu sayfa olcekli bir cizim/izgara alanidir. Hazir kolon, makine, filtre, fan ikonlari ve ornek bir boru guzergahi yerlestirilmistir. Ilave serbest cizim icin: Ekle &gt; Sekiller &gt; Serbest Form / Cizgi / Baglayici kullanabilirsiniz. Sekli cizerken ALT tusunu basili tutarsaniz sekil otomatik olarak hucre kenarlarina (izgaraya) hizalanir. Kolon ve makine ikonlarini kopyalayip plana istediginiz yere tasiyabilirsiniz.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="14" t="inlineStr">
+        <is>
+          <t>Olcek:</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>1 kare = 0.5 m  |  Plan boyutu (varsayilan): 25 m x 18 m</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="15" customHeight="1">
+      <c r="B7" s="41" t="n"/>
+      <c r="C7" s="42" t="n"/>
+      <c r="D7" s="42" t="n"/>
+      <c r="E7" s="42" t="n"/>
+      <c r="F7" s="42" t="n"/>
+      <c r="G7" s="42" t="n"/>
+      <c r="H7" s="42" t="n"/>
+      <c r="I7" s="42" t="n"/>
+      <c r="J7" s="42" t="n"/>
+      <c r="K7" s="42" t="n"/>
+      <c r="L7" s="42" t="n"/>
+      <c r="M7" s="42" t="n"/>
+      <c r="N7" s="42" t="n"/>
+      <c r="O7" s="42" t="n"/>
+      <c r="P7" s="42" t="n"/>
+      <c r="Q7" s="42" t="n"/>
+      <c r="R7" s="42" t="n"/>
+      <c r="S7" s="42" t="n"/>
+      <c r="T7" s="42" t="n"/>
+      <c r="U7" s="42" t="n"/>
+      <c r="V7" s="42" t="n"/>
+      <c r="W7" s="42" t="n"/>
+      <c r="X7" s="42" t="n"/>
+      <c r="Y7" s="42" t="n"/>
+      <c r="Z7" s="42" t="n"/>
+      <c r="AA7" s="42" t="n"/>
+      <c r="AB7" s="42" t="n"/>
+      <c r="AC7" s="42" t="n"/>
+      <c r="AD7" s="42" t="n"/>
+      <c r="AE7" s="42" t="n"/>
+      <c r="AF7" s="42" t="n"/>
+      <c r="AG7" s="42" t="n"/>
+      <c r="AH7" s="42" t="n"/>
+      <c r="AI7" s="42" t="n"/>
+      <c r="AJ7" s="42" t="n"/>
+      <c r="AK7" s="42" t="n"/>
+      <c r="AL7" s="42" t="n"/>
+      <c r="AM7" s="42" t="n"/>
+      <c r="AN7" s="42" t="n"/>
+      <c r="AO7" s="42" t="n"/>
+      <c r="AP7" s="42" t="n"/>
+      <c r="AQ7" s="42" t="n"/>
+      <c r="AR7" s="42" t="n"/>
+      <c r="AS7" s="42" t="n"/>
+      <c r="AT7" s="42" t="n"/>
+      <c r="AU7" s="42" t="n"/>
+      <c r="AV7" s="42" t="n"/>
+      <c r="AW7" s="42" t="n"/>
+      <c r="AX7" s="42" t="n"/>
+      <c r="AY7" s="43" t="n"/>
+    </row>
+    <row r="8" ht="15" customHeight="1">
+      <c r="B8" s="44" t="n"/>
+      <c r="C8" s="45" t="n"/>
+      <c r="D8" s="45" t="n"/>
+      <c r="E8" s="45" t="n"/>
+      <c r="F8" s="45" t="n"/>
+      <c r="G8" s="45" t="n"/>
+      <c r="H8" s="45" t="n"/>
+      <c r="I8" s="45" t="n"/>
+      <c r="J8" s="45" t="n"/>
+      <c r="K8" s="45" t="n"/>
+      <c r="L8" s="45" t="n"/>
+      <c r="M8" s="45" t="n"/>
+      <c r="N8" s="45" t="n"/>
+      <c r="O8" s="45" t="n"/>
+      <c r="P8" s="45" t="n"/>
+      <c r="Q8" s="45" t="n"/>
+      <c r="R8" s="45" t="n"/>
+      <c r="S8" s="45" t="n"/>
+      <c r="T8" s="45" t="n"/>
+      <c r="U8" s="45" t="n"/>
+      <c r="V8" s="45" t="n"/>
+      <c r="W8" s="45" t="n"/>
+      <c r="X8" s="45" t="n"/>
+      <c r="Y8" s="45" t="n"/>
+      <c r="Z8" s="45" t="n"/>
+      <c r="AA8" s="45" t="n"/>
+      <c r="AB8" s="45" t="n"/>
+      <c r="AC8" s="45" t="n"/>
+      <c r="AD8" s="45" t="n"/>
+      <c r="AE8" s="45" t="n"/>
+      <c r="AF8" s="45" t="n"/>
+      <c r="AG8" s="45" t="n"/>
+      <c r="AH8" s="45" t="n"/>
+      <c r="AI8" s="45" t="n"/>
+      <c r="AJ8" s="45" t="n"/>
+      <c r="AK8" s="45" t="n"/>
+      <c r="AL8" s="45" t="n"/>
+      <c r="AM8" s="45" t="n"/>
+      <c r="AN8" s="45" t="n"/>
+      <c r="AO8" s="45" t="n"/>
+      <c r="AP8" s="45" t="n"/>
+      <c r="AQ8" s="45" t="n"/>
+      <c r="AR8" s="45" t="n"/>
+      <c r="AS8" s="45" t="n"/>
+      <c r="AT8" s="45" t="n"/>
+      <c r="AU8" s="45" t="n"/>
+      <c r="AV8" s="45" t="n"/>
+      <c r="AW8" s="45" t="n"/>
+      <c r="AX8" s="45" t="n"/>
+      <c r="AY8" s="46" t="n"/>
+    </row>
+    <row r="9" ht="15" customHeight="1">
+      <c r="B9" s="44" t="n"/>
+      <c r="C9" s="45" t="n"/>
+      <c r="D9" s="45" t="n"/>
+      <c r="E9" s="45" t="n"/>
+      <c r="F9" s="45" t="n"/>
+      <c r="G9" s="45" t="n"/>
+      <c r="H9" s="45" t="n"/>
+      <c r="I9" s="45" t="n"/>
+      <c r="J9" s="45" t="n"/>
+      <c r="K9" s="45" t="n"/>
+      <c r="L9" s="45" t="n"/>
+      <c r="M9" s="45" t="n"/>
+      <c r="N9" s="45" t="n"/>
+      <c r="O9" s="45" t="n"/>
+      <c r="P9" s="45" t="n"/>
+      <c r="Q9" s="45" t="n"/>
+      <c r="R9" s="45" t="n"/>
+      <c r="S9" s="45" t="n"/>
+      <c r="T9" s="45" t="n"/>
+      <c r="U9" s="45" t="n"/>
+      <c r="V9" s="45" t="n"/>
+      <c r="W9" s="45" t="n"/>
+      <c r="X9" s="45" t="n"/>
+      <c r="Y9" s="45" t="n"/>
+      <c r="Z9" s="45" t="n"/>
+      <c r="AA9" s="45" t="n"/>
+      <c r="AB9" s="45" t="n"/>
+      <c r="AC9" s="45" t="n"/>
+      <c r="AD9" s="45" t="n"/>
+      <c r="AE9" s="45" t="n"/>
+      <c r="AF9" s="45" t="n"/>
+      <c r="AG9" s="45" t="n"/>
+      <c r="AH9" s="45" t="n"/>
+      <c r="AI9" s="45" t="n"/>
+      <c r="AJ9" s="45" t="n"/>
+      <c r="AK9" s="45" t="n"/>
+      <c r="AL9" s="45" t="n"/>
+      <c r="AM9" s="45" t="n"/>
+      <c r="AN9" s="45" t="n"/>
+      <c r="AO9" s="45" t="n"/>
+      <c r="AP9" s="45" t="n"/>
+      <c r="AQ9" s="45" t="n"/>
+      <c r="AR9" s="45" t="n"/>
+      <c r="AS9" s="45" t="n"/>
+      <c r="AT9" s="45" t="n"/>
+      <c r="AU9" s="45" t="n"/>
+      <c r="AV9" s="45" t="n"/>
+      <c r="AW9" s="45" t="n"/>
+      <c r="AX9" s="45" t="n"/>
+      <c r="AY9" s="46" t="n"/>
+    </row>
+    <row r="10" ht="15" customHeight="1">
+      <c r="B10" s="44" t="n"/>
+      <c r="C10" s="45" t="n"/>
+      <c r="D10" s="45" t="n"/>
+      <c r="E10" s="45" t="n"/>
+      <c r="F10" s="45" t="n"/>
+      <c r="G10" s="45" t="n"/>
+      <c r="H10" s="47" t="n"/>
+      <c r="I10" s="47" t="n"/>
+      <c r="J10" s="47" t="n"/>
+      <c r="K10" s="47" t="n"/>
+      <c r="L10" s="48" t="n"/>
+      <c r="M10" s="47" t="n"/>
+      <c r="N10" s="47" t="n"/>
+      <c r="O10" s="47" t="n"/>
+      <c r="P10" s="47" t="n"/>
+      <c r="Q10" s="47" t="n"/>
+      <c r="R10" s="47" t="n"/>
+      <c r="S10" s="47" t="n"/>
+      <c r="T10" s="47" t="n"/>
+      <c r="U10" s="47" t="n"/>
+      <c r="V10" s="47" t="n"/>
+      <c r="W10" s="47" t="n"/>
+      <c r="X10" s="48" t="n"/>
+      <c r="Y10" s="47" t="n"/>
+      <c r="Z10" s="47" t="n"/>
+      <c r="AA10" s="47" t="n"/>
+      <c r="AB10" s="47" t="n"/>
+      <c r="AC10" s="47" t="n"/>
+      <c r="AD10" s="47" t="n"/>
+      <c r="AE10" s="47" t="n"/>
+      <c r="AF10" s="47" t="n"/>
+      <c r="AG10" s="47" t="n"/>
+      <c r="AH10" s="47" t="n"/>
+      <c r="AI10" s="47" t="n"/>
+      <c r="AJ10" s="48" t="n"/>
+      <c r="AK10" s="47" t="n"/>
+      <c r="AL10" s="47" t="n"/>
+      <c r="AM10" s="47" t="n"/>
+      <c r="AN10" s="47" t="n"/>
+      <c r="AO10" s="47" t="n"/>
+      <c r="AP10" s="47" t="n"/>
+      <c r="AQ10" s="47" t="n"/>
+      <c r="AR10" s="47" t="n"/>
+      <c r="AS10" s="47" t="n"/>
+      <c r="AT10" s="45" t="n"/>
+      <c r="AU10" s="45" t="n"/>
+      <c r="AV10" s="45" t="n"/>
+      <c r="AW10" s="45" t="n"/>
+      <c r="AX10" s="45" t="n"/>
+      <c r="AY10" s="46" t="n"/>
+    </row>
+    <row r="11" ht="15" customHeight="1">
+      <c r="B11" s="44" t="n"/>
+      <c r="C11" s="49">
+        <f>'Filtre Secimi'!B10</f>
+        <v/>
+      </c>
+      <c r="D11" s="45" t="n"/>
+      <c r="E11" s="45" t="n"/>
+      <c r="F11" s="45" t="n"/>
+      <c r="G11" s="45" t="n"/>
+      <c r="H11" s="45" t="n"/>
+      <c r="I11" s="45" t="n"/>
+      <c r="J11" s="45" t="n"/>
+      <c r="K11" s="45" t="n"/>
+      <c r="L11" s="50" t="n"/>
+      <c r="M11" s="45" t="n"/>
+      <c r="N11" s="45" t="n"/>
+      <c r="O11" s="45" t="n"/>
+      <c r="P11" s="45" t="n"/>
+      <c r="Q11" s="45" t="n"/>
+      <c r="R11" s="45" t="n"/>
+      <c r="S11" s="45" t="n"/>
+      <c r="T11" s="45" t="n"/>
+      <c r="U11" s="45" t="n"/>
+      <c r="V11" s="45" t="n"/>
+      <c r="W11" s="45" t="n"/>
+      <c r="X11" s="50" t="n"/>
+      <c r="Y11" s="45" t="n"/>
+      <c r="Z11" s="45" t="n"/>
+      <c r="AA11" s="45" t="n"/>
+      <c r="AB11" s="45" t="n"/>
+      <c r="AC11" s="45" t="n"/>
+      <c r="AD11" s="45" t="n"/>
+      <c r="AE11" s="45" t="n"/>
+      <c r="AF11" s="45" t="n"/>
+      <c r="AG11" s="45" t="n"/>
+      <c r="AH11" s="45" t="n"/>
+      <c r="AI11" s="45" t="n"/>
+      <c r="AJ11" s="50" t="n"/>
+      <c r="AK11" s="45" t="n"/>
+      <c r="AL11" s="45" t="n"/>
+      <c r="AM11" s="45" t="n"/>
+      <c r="AN11" s="45" t="n"/>
+      <c r="AO11" s="45" t="n"/>
+      <c r="AP11" s="45" t="n"/>
+      <c r="AQ11" s="45" t="n"/>
+      <c r="AR11" s="45" t="n"/>
+      <c r="AS11" s="45" t="n"/>
+      <c r="AT11" s="45" t="n"/>
+      <c r="AU11" s="49">
+        <f>'Fan Secimi'!B14</f>
+        <v/>
+      </c>
+      <c r="AV11" s="51" t="n"/>
+      <c r="AW11" s="51" t="n"/>
+      <c r="AX11" s="52" t="n"/>
+      <c r="AY11" s="46" t="n"/>
+    </row>
+    <row r="12" ht="15" customHeight="1">
+      <c r="B12" s="44" t="n"/>
+      <c r="C12" s="45" t="n"/>
+      <c r="D12" s="45" t="n"/>
+      <c r="E12" s="45" t="n"/>
+      <c r="F12" s="45" t="n"/>
+      <c r="G12" s="45" t="n"/>
+      <c r="H12" s="45" t="n"/>
+      <c r="I12" s="45" t="n"/>
+      <c r="J12" s="45" t="n"/>
+      <c r="K12" s="45" t="n"/>
+      <c r="L12" s="50" t="n"/>
+      <c r="M12" s="45" t="n"/>
+      <c r="N12" s="45" t="n"/>
+      <c r="O12" s="45" t="n"/>
+      <c r="P12" s="45" t="n"/>
+      <c r="Q12" s="45" t="n"/>
+      <c r="R12" s="45" t="n"/>
+      <c r="S12" s="45" t="n"/>
+      <c r="T12" s="45" t="n"/>
+      <c r="U12" s="45" t="n"/>
+      <c r="V12" s="45" t="n"/>
+      <c r="W12" s="45" t="n"/>
+      <c r="X12" s="50" t="n"/>
+      <c r="Y12" s="45" t="n"/>
+      <c r="Z12" s="45" t="n"/>
+      <c r="AA12" s="45" t="n"/>
+      <c r="AB12" s="45" t="n"/>
+      <c r="AC12" s="45" t="n"/>
+      <c r="AD12" s="45" t="n"/>
+      <c r="AE12" s="45" t="n"/>
+      <c r="AF12" s="45" t="n"/>
+      <c r="AG12" s="45" t="n"/>
+      <c r="AH12" s="45" t="n"/>
+      <c r="AI12" s="45" t="n"/>
+      <c r="AJ12" s="50" t="n"/>
+      <c r="AK12" s="45" t="n"/>
+      <c r="AL12" s="45" t="n"/>
+      <c r="AM12" s="45" t="n"/>
+      <c r="AN12" s="45" t="n"/>
+      <c r="AO12" s="45" t="n"/>
+      <c r="AP12" s="45" t="n"/>
+      <c r="AQ12" s="45" t="n"/>
+      <c r="AR12" s="45" t="n"/>
+      <c r="AS12" s="45" t="n"/>
+      <c r="AT12" s="45" t="n"/>
+      <c r="AU12" s="45" t="n"/>
+      <c r="AV12" s="45" t="n"/>
+      <c r="AW12" s="45" t="n"/>
+      <c r="AX12" s="45" t="n"/>
+      <c r="AY12" s="46" t="n"/>
+    </row>
+    <row r="13" ht="15" customHeight="1">
+      <c r="B13" s="44" t="n"/>
+      <c r="C13" s="45" t="n"/>
+      <c r="D13" s="45" t="n"/>
+      <c r="E13" s="45" t="n"/>
+      <c r="F13" s="45" t="n"/>
+      <c r="G13" s="45" t="n"/>
+      <c r="H13" s="45" t="n"/>
+      <c r="I13" s="45" t="n"/>
+      <c r="J13" s="45" t="n"/>
+      <c r="K13" s="45" t="n"/>
+      <c r="L13" s="50" t="n"/>
+      <c r="M13" s="45" t="n"/>
+      <c r="N13" s="45" t="n"/>
+      <c r="O13" s="45" t="n"/>
+      <c r="P13" s="45" t="n"/>
+      <c r="Q13" s="45" t="n"/>
+      <c r="R13" s="45" t="n"/>
+      <c r="S13" s="45" t="n"/>
+      <c r="T13" s="45" t="n"/>
+      <c r="U13" s="45" t="n"/>
+      <c r="V13" s="45" t="n"/>
+      <c r="W13" s="45" t="n"/>
+      <c r="X13" s="50" t="n"/>
+      <c r="Y13" s="45" t="n"/>
+      <c r="Z13" s="45" t="n"/>
+      <c r="AA13" s="45" t="n"/>
+      <c r="AB13" s="45" t="n"/>
+      <c r="AC13" s="45" t="n"/>
+      <c r="AD13" s="45" t="n"/>
+      <c r="AE13" s="45" t="n"/>
+      <c r="AF13" s="45" t="n"/>
+      <c r="AG13" s="45" t="n"/>
+      <c r="AH13" s="45" t="n"/>
+      <c r="AI13" s="45" t="n"/>
+      <c r="AJ13" s="50" t="n"/>
+      <c r="AK13" s="45" t="n"/>
+      <c r="AL13" s="45" t="n"/>
+      <c r="AM13" s="45" t="n"/>
+      <c r="AN13" s="45" t="n"/>
+      <c r="AO13" s="45" t="n"/>
+      <c r="AP13" s="45" t="n"/>
+      <c r="AQ13" s="45" t="n"/>
+      <c r="AR13" s="45" t="n"/>
+      <c r="AS13" s="45" t="n"/>
+      <c r="AT13" s="45" t="n"/>
+      <c r="AU13" s="45" t="n"/>
+      <c r="AV13" s="45" t="n"/>
+      <c r="AW13" s="45" t="n"/>
+      <c r="AX13" s="45" t="n"/>
+      <c r="AY13" s="46" t="n"/>
+    </row>
+    <row r="14" ht="15" customHeight="1">
+      <c r="B14" s="44" t="n"/>
+      <c r="C14" s="45" t="n"/>
+      <c r="D14" s="45" t="n"/>
+      <c r="E14" s="45" t="n"/>
+      <c r="F14" s="45" t="n"/>
+      <c r="G14" s="45" t="n"/>
+      <c r="H14" s="45" t="n"/>
+      <c r="I14" s="45" t="n"/>
+      <c r="J14" s="45" t="n"/>
+      <c r="K14" s="45" t="n"/>
+      <c r="L14" s="50" t="n"/>
+      <c r="M14" s="45" t="n"/>
+      <c r="N14" s="45" t="n"/>
+      <c r="O14" s="45" t="n"/>
+      <c r="P14" s="45" t="n"/>
+      <c r="Q14" s="45" t="n"/>
+      <c r="R14" s="45" t="n"/>
+      <c r="S14" s="45" t="n"/>
+      <c r="T14" s="45" t="n"/>
+      <c r="U14" s="45" t="n"/>
+      <c r="V14" s="45" t="n"/>
+      <c r="W14" s="45" t="n"/>
+      <c r="X14" s="50" t="n"/>
+      <c r="Y14" s="45" t="n"/>
+      <c r="Z14" s="45" t="n"/>
+      <c r="AA14" s="45" t="n"/>
+      <c r="AB14" s="45" t="n"/>
+      <c r="AC14" s="45" t="n"/>
+      <c r="AD14" s="45" t="n"/>
+      <c r="AE14" s="45" t="n"/>
+      <c r="AF14" s="45" t="n"/>
+      <c r="AG14" s="45" t="n"/>
+      <c r="AH14" s="45" t="n"/>
+      <c r="AI14" s="45" t="n"/>
+      <c r="AJ14" s="50" t="n"/>
+      <c r="AK14" s="45" t="n"/>
+      <c r="AL14" s="45" t="n"/>
+      <c r="AM14" s="45" t="n"/>
+      <c r="AN14" s="45" t="n"/>
+      <c r="AO14" s="45" t="n"/>
+      <c r="AP14" s="45" t="n"/>
+      <c r="AQ14" s="45" t="n"/>
+      <c r="AR14" s="45" t="n"/>
+      <c r="AS14" s="45" t="n"/>
+      <c r="AT14" s="45" t="n"/>
+      <c r="AU14" s="45" t="n"/>
+      <c r="AV14" s="45" t="n"/>
+      <c r="AW14" s="45" t="n"/>
+      <c r="AX14" s="45" t="n"/>
+      <c r="AY14" s="46" t="n"/>
+    </row>
+    <row r="15" ht="15" customHeight="1">
+      <c r="B15" s="44" t="n"/>
+      <c r="C15" s="45" t="n"/>
+      <c r="D15" s="45" t="n"/>
+      <c r="E15" s="45" t="n"/>
+      <c r="F15" s="45" t="n"/>
+      <c r="G15" s="45" t="n"/>
+      <c r="H15" s="45" t="n"/>
+      <c r="I15" s="45" t="n"/>
+      <c r="J15" s="45" t="n"/>
+      <c r="K15" s="45" t="n"/>
+      <c r="L15" s="50" t="n"/>
+      <c r="M15" s="45" t="n"/>
+      <c r="N15" s="45" t="n"/>
+      <c r="O15" s="45" t="n"/>
+      <c r="P15" s="45" t="n"/>
+      <c r="Q15" s="45" t="n"/>
+      <c r="R15" s="45" t="n"/>
+      <c r="S15" s="45" t="n"/>
+      <c r="T15" s="45" t="n"/>
+      <c r="U15" s="45" t="n"/>
+      <c r="V15" s="45" t="n"/>
+      <c r="W15" s="45" t="n"/>
+      <c r="X15" s="50" t="n"/>
+      <c r="Y15" s="45" t="n"/>
+      <c r="Z15" s="45" t="n"/>
+      <c r="AA15" s="45" t="n"/>
+      <c r="AB15" s="45" t="n"/>
+      <c r="AC15" s="45" t="n"/>
+      <c r="AD15" s="45" t="n"/>
+      <c r="AE15" s="45" t="n"/>
+      <c r="AF15" s="45" t="n"/>
+      <c r="AG15" s="45" t="n"/>
+      <c r="AH15" s="45" t="n"/>
+      <c r="AI15" s="45" t="n"/>
+      <c r="AJ15" s="50" t="n"/>
+      <c r="AK15" s="45" t="n"/>
+      <c r="AL15" s="45" t="n"/>
+      <c r="AM15" s="45" t="n"/>
+      <c r="AN15" s="45" t="n"/>
+      <c r="AO15" s="45" t="n"/>
+      <c r="AP15" s="45" t="n"/>
+      <c r="AQ15" s="45" t="n"/>
+      <c r="AR15" s="45" t="n"/>
+      <c r="AS15" s="45" t="n"/>
+      <c r="AT15" s="45" t="n"/>
+      <c r="AU15" s="45" t="n"/>
+      <c r="AV15" s="45" t="n"/>
+      <c r="AW15" s="45" t="n"/>
+      <c r="AX15" s="45" t="n"/>
+      <c r="AY15" s="46" t="n"/>
+    </row>
+    <row r="16" ht="15" customHeight="1">
+      <c r="B16" s="44" t="n"/>
+      <c r="C16" s="45" t="n"/>
+      <c r="D16" s="45" t="n"/>
+      <c r="E16" s="45" t="n"/>
+      <c r="F16" s="45" t="n"/>
+      <c r="G16" s="45" t="n"/>
+      <c r="H16" s="45" t="n"/>
+      <c r="I16" s="45" t="n"/>
+      <c r="J16" s="45" t="n"/>
+      <c r="K16" s="45" t="n"/>
+      <c r="L16" s="50" t="n"/>
+      <c r="M16" s="45" t="n"/>
+      <c r="N16" s="45" t="n"/>
+      <c r="O16" s="45" t="n"/>
+      <c r="P16" s="45" t="n"/>
+      <c r="Q16" s="45" t="n"/>
+      <c r="R16" s="45" t="n"/>
+      <c r="S16" s="45" t="n"/>
+      <c r="T16" s="45" t="n"/>
+      <c r="U16" s="45" t="n"/>
+      <c r="V16" s="45" t="n"/>
+      <c r="W16" s="45" t="n"/>
+      <c r="X16" s="50" t="n"/>
+      <c r="Y16" s="45" t="n"/>
+      <c r="Z16" s="45" t="n"/>
+      <c r="AA16" s="45" t="n"/>
+      <c r="AB16" s="45" t="n"/>
+      <c r="AC16" s="45" t="n"/>
+      <c r="AD16" s="45" t="n"/>
+      <c r="AE16" s="45" t="n"/>
+      <c r="AF16" s="45" t="n"/>
+      <c r="AG16" s="45" t="n"/>
+      <c r="AH16" s="45" t="n"/>
+      <c r="AI16" s="45" t="n"/>
+      <c r="AJ16" s="50" t="n"/>
+      <c r="AK16" s="45" t="n"/>
+      <c r="AL16" s="45" t="n"/>
+      <c r="AM16" s="45" t="n"/>
+      <c r="AN16" s="45" t="n"/>
+      <c r="AO16" s="45" t="n"/>
+      <c r="AP16" s="45" t="n"/>
+      <c r="AQ16" s="45" t="n"/>
+      <c r="AR16" s="45" t="n"/>
+      <c r="AS16" s="45" t="n"/>
+      <c r="AT16" s="45" t="n"/>
+      <c r="AU16" s="45" t="n"/>
+      <c r="AV16" s="45" t="n"/>
+      <c r="AW16" s="45" t="n"/>
+      <c r="AX16" s="45" t="n"/>
+      <c r="AY16" s="46" t="n"/>
+    </row>
+    <row r="17" ht="15" customHeight="1">
+      <c r="B17" s="44" t="n"/>
+      <c r="C17" s="45" t="n"/>
+      <c r="D17" s="45" t="n"/>
+      <c r="E17" s="45" t="n"/>
+      <c r="F17" s="45" t="n"/>
+      <c r="G17" s="45" t="n"/>
+      <c r="H17" s="45" t="n"/>
+      <c r="I17" s="45" t="n"/>
+      <c r="J17" s="45" t="n"/>
+      <c r="K17" s="45" t="n"/>
+      <c r="L17" s="50" t="n"/>
+      <c r="M17" s="45" t="n"/>
+      <c r="N17" s="45" t="n"/>
+      <c r="O17" s="45" t="n"/>
+      <c r="P17" s="45" t="n"/>
+      <c r="Q17" s="45" t="n"/>
+      <c r="R17" s="45" t="n"/>
+      <c r="S17" s="45" t="n"/>
+      <c r="T17" s="45" t="n"/>
+      <c r="U17" s="45" t="n"/>
+      <c r="V17" s="45" t="n"/>
+      <c r="W17" s="45" t="n"/>
+      <c r="X17" s="50" t="n"/>
+      <c r="Y17" s="45" t="n"/>
+      <c r="Z17" s="45" t="n"/>
+      <c r="AA17" s="45" t="n"/>
+      <c r="AB17" s="45" t="n"/>
+      <c r="AC17" s="45" t="n"/>
+      <c r="AD17" s="45" t="n"/>
+      <c r="AE17" s="45" t="n"/>
+      <c r="AF17" s="45" t="n"/>
+      <c r="AG17" s="45" t="n"/>
+      <c r="AH17" s="45" t="n"/>
+      <c r="AI17" s="45" t="n"/>
+      <c r="AJ17" s="50" t="n"/>
+      <c r="AK17" s="45" t="n"/>
+      <c r="AL17" s="45" t="n"/>
+      <c r="AM17" s="45" t="n"/>
+      <c r="AN17" s="45" t="n"/>
+      <c r="AO17" s="45" t="n"/>
+      <c r="AP17" s="45" t="n"/>
+      <c r="AQ17" s="45" t="n"/>
+      <c r="AR17" s="45" t="n"/>
+      <c r="AS17" s="45" t="n"/>
+      <c r="AT17" s="45" t="n"/>
+      <c r="AU17" s="45" t="n"/>
+      <c r="AV17" s="45" t="n"/>
+      <c r="AW17" s="45" t="n"/>
+      <c r="AX17" s="45" t="n"/>
+      <c r="AY17" s="46" t="n"/>
+    </row>
+    <row r="18" ht="15" customHeight="1">
+      <c r="B18" s="44" t="n"/>
+      <c r="C18" s="45" t="n"/>
+      <c r="D18" s="45" t="n"/>
+      <c r="E18" s="45" t="n"/>
+      <c r="F18" s="45" t="n"/>
+      <c r="G18" s="45" t="n"/>
+      <c r="H18" s="45" t="n"/>
+      <c r="I18" s="45" t="n"/>
+      <c r="J18" s="45" t="n"/>
+      <c r="K18" s="45" t="n"/>
+      <c r="L18" s="50" t="n"/>
+      <c r="M18" s="45" t="n"/>
+      <c r="N18" s="45" t="n"/>
+      <c r="O18" s="45" t="n"/>
+      <c r="P18" s="45" t="n"/>
+      <c r="Q18" s="45" t="n"/>
+      <c r="R18" s="45" t="n"/>
+      <c r="S18" s="45" t="n"/>
+      <c r="T18" s="45" t="n"/>
+      <c r="U18" s="45" t="n"/>
+      <c r="V18" s="45" t="n"/>
+      <c r="W18" s="45" t="n"/>
+      <c r="X18" s="50" t="n"/>
+      <c r="Y18" s="45" t="n"/>
+      <c r="Z18" s="45" t="n"/>
+      <c r="AA18" s="45" t="n"/>
+      <c r="AB18" s="45" t="n"/>
+      <c r="AC18" s="45" t="n"/>
+      <c r="AD18" s="45" t="n"/>
+      <c r="AE18" s="45" t="n"/>
+      <c r="AF18" s="45" t="n"/>
+      <c r="AG18" s="45" t="n"/>
+      <c r="AH18" s="45" t="n"/>
+      <c r="AI18" s="45" t="n"/>
+      <c r="AJ18" s="50" t="n"/>
+      <c r="AK18" s="45" t="n"/>
+      <c r="AL18" s="45" t="n"/>
+      <c r="AM18" s="45" t="n"/>
+      <c r="AN18" s="45" t="n"/>
+      <c r="AO18" s="45" t="n"/>
+      <c r="AP18" s="45" t="n"/>
+      <c r="AQ18" s="45" t="n"/>
+      <c r="AR18" s="45" t="n"/>
+      <c r="AS18" s="45" t="n"/>
+      <c r="AT18" s="45" t="n"/>
+      <c r="AU18" s="45" t="n"/>
+      <c r="AV18" s="45" t="n"/>
+      <c r="AW18" s="45" t="n"/>
+      <c r="AX18" s="45" t="n"/>
+      <c r="AY18" s="46" t="n"/>
+    </row>
+    <row r="19" ht="15" customHeight="1">
+      <c r="B19" s="44" t="n"/>
+      <c r="C19" s="45" t="n"/>
+      <c r="D19" s="45" t="n"/>
+      <c r="E19" s="45" t="n"/>
+      <c r="F19" s="45" t="n"/>
+      <c r="G19" s="45" t="n"/>
+      <c r="H19" s="45" t="n"/>
+      <c r="I19" s="45" t="n"/>
+      <c r="J19" s="45" t="n"/>
+      <c r="K19" s="45" t="n"/>
+      <c r="L19" s="50" t="n"/>
+      <c r="M19" s="45" t="n"/>
+      <c r="N19" s="45" t="n"/>
+      <c r="O19" s="45" t="n"/>
+      <c r="P19" s="45" t="n"/>
+      <c r="Q19" s="45" t="n"/>
+      <c r="R19" s="45" t="n"/>
+      <c r="S19" s="45" t="n"/>
+      <c r="T19" s="45" t="n"/>
+      <c r="U19" s="45" t="n"/>
+      <c r="V19" s="45" t="n"/>
+      <c r="W19" s="45" t="n"/>
+      <c r="X19" s="50" t="n"/>
+      <c r="Y19" s="45" t="n"/>
+      <c r="Z19" s="45" t="n"/>
+      <c r="AA19" s="45" t="n"/>
+      <c r="AB19" s="45" t="n"/>
+      <c r="AC19" s="45" t="n"/>
+      <c r="AD19" s="45" t="n"/>
+      <c r="AE19" s="45" t="n"/>
+      <c r="AF19" s="45" t="n"/>
+      <c r="AG19" s="45" t="n"/>
+      <c r="AH19" s="45" t="n"/>
+      <c r="AI19" s="45" t="n"/>
+      <c r="AJ19" s="50" t="n"/>
+      <c r="AK19" s="45" t="n"/>
+      <c r="AL19" s="45" t="n"/>
+      <c r="AM19" s="45" t="n"/>
+      <c r="AN19" s="45" t="n"/>
+      <c r="AO19" s="45" t="n"/>
+      <c r="AP19" s="45" t="n"/>
+      <c r="AQ19" s="45" t="n"/>
+      <c r="AR19" s="45" t="n"/>
+      <c r="AS19" s="45" t="n"/>
+      <c r="AT19" s="45" t="n"/>
+      <c r="AU19" s="45" t="n"/>
+      <c r="AV19" s="45" t="n"/>
+      <c r="AW19" s="45" t="n"/>
+      <c r="AX19" s="45" t="n"/>
+      <c r="AY19" s="46" t="n"/>
+    </row>
+    <row r="20" ht="15" customHeight="1">
+      <c r="B20" s="44" t="n"/>
+      <c r="C20" s="45" t="n"/>
+      <c r="D20" s="45" t="n"/>
+      <c r="E20" s="45" t="n"/>
+      <c r="F20" s="45" t="n"/>
+      <c r="G20" s="45" t="n"/>
+      <c r="H20" s="45" t="n"/>
+      <c r="I20" s="45" t="n"/>
+      <c r="J20" s="45" t="n"/>
+      <c r="K20" s="45" t="n"/>
+      <c r="L20" s="50" t="n"/>
+      <c r="M20" s="45" t="n"/>
+      <c r="N20" s="45" t="n"/>
+      <c r="O20" s="45" t="n"/>
+      <c r="P20" s="45" t="n"/>
+      <c r="Q20" s="45" t="n"/>
+      <c r="R20" s="45" t="n"/>
+      <c r="S20" s="45" t="n"/>
+      <c r="T20" s="45" t="n"/>
+      <c r="U20" s="45" t="n"/>
+      <c r="V20" s="45" t="n"/>
+      <c r="W20" s="45" t="n"/>
+      <c r="X20" s="50" t="n"/>
+      <c r="Y20" s="45" t="n"/>
+      <c r="Z20" s="45" t="n"/>
+      <c r="AA20" s="45" t="n"/>
+      <c r="AB20" s="45" t="n"/>
+      <c r="AC20" s="45" t="n"/>
+      <c r="AD20" s="45" t="n"/>
+      <c r="AE20" s="45" t="n"/>
+      <c r="AF20" s="45" t="n"/>
+      <c r="AG20" s="45" t="n"/>
+      <c r="AH20" s="45" t="n"/>
+      <c r="AI20" s="45" t="n"/>
+      <c r="AJ20" s="50" t="n"/>
+      <c r="AK20" s="45" t="n"/>
+      <c r="AL20" s="45" t="n"/>
+      <c r="AM20" s="45" t="n"/>
+      <c r="AN20" s="45" t="n"/>
+      <c r="AO20" s="45" t="n"/>
+      <c r="AP20" s="45" t="n"/>
+      <c r="AQ20" s="45" t="n"/>
+      <c r="AR20" s="45" t="n"/>
+      <c r="AS20" s="45" t="n"/>
+      <c r="AT20" s="45" t="n"/>
+      <c r="AU20" s="45" t="n"/>
+      <c r="AV20" s="45" t="n"/>
+      <c r="AW20" s="45" t="n"/>
+      <c r="AX20" s="45" t="n"/>
+      <c r="AY20" s="46" t="n"/>
+    </row>
+    <row r="21" ht="15" customHeight="1">
+      <c r="B21" s="44" t="n"/>
+      <c r="C21" s="45" t="n"/>
+      <c r="D21" s="45" t="n"/>
+      <c r="E21" s="45" t="n"/>
+      <c r="F21" s="45" t="n"/>
+      <c r="G21" s="45" t="n"/>
+      <c r="H21" s="45" t="n"/>
+      <c r="I21" s="45" t="n"/>
+      <c r="J21" s="45" t="n"/>
+      <c r="K21" s="45" t="n"/>
+      <c r="L21" s="50" t="n"/>
+      <c r="M21" s="45" t="n"/>
+      <c r="N21" s="45" t="n"/>
+      <c r="O21" s="45" t="n"/>
+      <c r="P21" s="45" t="n"/>
+      <c r="Q21" s="45" t="n"/>
+      <c r="R21" s="45" t="n"/>
+      <c r="S21" s="45" t="n"/>
+      <c r="T21" s="45" t="n"/>
+      <c r="U21" s="45" t="n"/>
+      <c r="V21" s="45" t="n"/>
+      <c r="W21" s="45" t="n"/>
+      <c r="X21" s="50" t="n"/>
+      <c r="Y21" s="45" t="n"/>
+      <c r="Z21" s="45" t="n"/>
+      <c r="AA21" s="45" t="n"/>
+      <c r="AB21" s="45" t="n"/>
+      <c r="AC21" s="45" t="n"/>
+      <c r="AD21" s="45" t="n"/>
+      <c r="AE21" s="45" t="n"/>
+      <c r="AF21" s="45" t="n"/>
+      <c r="AG21" s="45" t="n"/>
+      <c r="AH21" s="45" t="n"/>
+      <c r="AI21" s="45" t="n"/>
+      <c r="AJ21" s="50" t="n"/>
+      <c r="AK21" s="45" t="n"/>
+      <c r="AL21" s="45" t="n"/>
+      <c r="AM21" s="45" t="n"/>
+      <c r="AN21" s="45" t="n"/>
+      <c r="AO21" s="45" t="n"/>
+      <c r="AP21" s="45" t="n"/>
+      <c r="AQ21" s="45" t="n"/>
+      <c r="AR21" s="45" t="n"/>
+      <c r="AS21" s="45" t="n"/>
+      <c r="AT21" s="45" t="n"/>
+      <c r="AU21" s="45" t="n"/>
+      <c r="AV21" s="45" t="n"/>
+      <c r="AW21" s="45" t="n"/>
+      <c r="AX21" s="45" t="n"/>
+      <c r="AY21" s="46" t="n"/>
+    </row>
+    <row r="22" ht="15" customHeight="1">
+      <c r="B22" s="44" t="n"/>
+      <c r="C22" s="45" t="n"/>
+      <c r="D22" s="45" t="n"/>
+      <c r="E22" s="45" t="n"/>
+      <c r="F22" s="45" t="n"/>
+      <c r="G22" s="45" t="n"/>
+      <c r="H22" s="45" t="n"/>
+      <c r="I22" s="45" t="n"/>
+      <c r="J22" s="45" t="n"/>
+      <c r="K22" s="45" t="n"/>
+      <c r="L22" s="45" t="n"/>
+      <c r="M22" s="45" t="n"/>
+      <c r="N22" s="45" t="n"/>
+      <c r="O22" s="45" t="n"/>
+      <c r="P22" s="45" t="n"/>
+      <c r="Q22" s="45" t="n"/>
+      <c r="R22" s="45" t="n"/>
+      <c r="S22" s="45" t="n"/>
+      <c r="T22" s="45" t="n"/>
+      <c r="U22" s="45" t="n"/>
+      <c r="V22" s="45" t="n"/>
+      <c r="W22" s="45" t="n"/>
+      <c r="X22" s="45" t="n"/>
+      <c r="Y22" s="45" t="n"/>
+      <c r="Z22" s="45" t="n"/>
+      <c r="AA22" s="45" t="n"/>
+      <c r="AB22" s="45" t="n"/>
+      <c r="AC22" s="45" t="n"/>
+      <c r="AD22" s="45" t="n"/>
+      <c r="AE22" s="45" t="n"/>
+      <c r="AF22" s="45" t="n"/>
+      <c r="AG22" s="45" t="n"/>
+      <c r="AH22" s="45" t="n"/>
+      <c r="AI22" s="45" t="n"/>
+      <c r="AJ22" s="45" t="n"/>
+      <c r="AK22" s="45" t="n"/>
+      <c r="AL22" s="45" t="n"/>
+      <c r="AM22" s="45" t="n"/>
+      <c r="AN22" s="45" t="n"/>
+      <c r="AO22" s="45" t="n"/>
+      <c r="AP22" s="45" t="n"/>
+      <c r="AQ22" s="45" t="n"/>
+      <c r="AR22" s="45" t="n"/>
+      <c r="AS22" s="45" t="n"/>
+      <c r="AT22" s="45" t="n"/>
+      <c r="AU22" s="45" t="n"/>
+      <c r="AV22" s="45" t="n"/>
+      <c r="AW22" s="45" t="n"/>
+      <c r="AX22" s="45" t="n"/>
+      <c r="AY22" s="46" t="n"/>
+    </row>
+    <row r="23" ht="15" customHeight="1">
+      <c r="B23" s="44" t="n"/>
+      <c r="C23" s="45" t="n"/>
+      <c r="D23" s="45" t="n"/>
+      <c r="E23" s="45" t="n"/>
+      <c r="F23" s="45" t="n"/>
+      <c r="G23" s="45" t="n"/>
+      <c r="H23" s="45" t="n"/>
+      <c r="I23" s="45" t="n"/>
+      <c r="J23" s="45" t="n"/>
+      <c r="K23" s="45" t="n"/>
+      <c r="L23" s="45" t="n"/>
+      <c r="M23" s="45" t="n"/>
+      <c r="N23" s="45" t="n"/>
+      <c r="O23" s="45" t="n"/>
+      <c r="P23" s="45" t="n"/>
+      <c r="Q23" s="45" t="n"/>
+      <c r="R23" s="45" t="n"/>
+      <c r="S23" s="45" t="n"/>
+      <c r="T23" s="45" t="n"/>
+      <c r="U23" s="45" t="n"/>
+      <c r="V23" s="45" t="n"/>
+      <c r="W23" s="45" t="n"/>
+      <c r="X23" s="45" t="n"/>
+      <c r="Y23" s="45" t="n"/>
+      <c r="Z23" s="45" t="n"/>
+      <c r="AA23" s="45" t="n"/>
+      <c r="AB23" s="45" t="n"/>
+      <c r="AC23" s="45" t="n"/>
+      <c r="AD23" s="45" t="n"/>
+      <c r="AE23" s="45" t="n"/>
+      <c r="AF23" s="45" t="n"/>
+      <c r="AG23" s="45" t="n"/>
+      <c r="AH23" s="45" t="n"/>
+      <c r="AI23" s="45" t="n"/>
+      <c r="AJ23" s="45" t="n"/>
+      <c r="AK23" s="45" t="n"/>
+      <c r="AL23" s="45" t="n"/>
+      <c r="AM23" s="45" t="n"/>
+      <c r="AN23" s="45" t="n"/>
+      <c r="AO23" s="45" t="n"/>
+      <c r="AP23" s="45" t="n"/>
+      <c r="AQ23" s="45" t="n"/>
+      <c r="AR23" s="45" t="n"/>
+      <c r="AS23" s="45" t="n"/>
+      <c r="AT23" s="45" t="n"/>
+      <c r="AU23" s="45" t="n"/>
+      <c r="AV23" s="45" t="n"/>
+      <c r="AW23" s="45" t="n"/>
+      <c r="AX23" s="45" t="n"/>
+      <c r="AY23" s="46" t="n"/>
+    </row>
+    <row r="24" ht="15" customHeight="1">
+      <c r="B24" s="44" t="n"/>
+      <c r="C24" s="45" t="n"/>
+      <c r="D24" s="45" t="n"/>
+      <c r="E24" s="45" t="n"/>
+      <c r="F24" s="45" t="n"/>
+      <c r="G24" s="45" t="n"/>
+      <c r="H24" s="45" t="n"/>
+      <c r="I24" s="45" t="n"/>
+      <c r="J24" s="45" t="n"/>
+      <c r="K24" s="45" t="n"/>
+      <c r="L24" s="45" t="n"/>
+      <c r="M24" s="45" t="n"/>
+      <c r="N24" s="45" t="n"/>
+      <c r="O24" s="45" t="n"/>
+      <c r="P24" s="45" t="n"/>
+      <c r="Q24" s="45" t="n"/>
+      <c r="R24" s="45" t="n"/>
+      <c r="S24" s="45" t="n"/>
+      <c r="T24" s="45" t="n"/>
+      <c r="U24" s="45" t="n"/>
+      <c r="V24" s="45" t="n"/>
+      <c r="W24" s="45" t="n"/>
+      <c r="X24" s="45" t="n"/>
+      <c r="Y24" s="45" t="n"/>
+      <c r="Z24" s="45" t="n"/>
+      <c r="AA24" s="45" t="n"/>
+      <c r="AB24" s="45" t="n"/>
+      <c r="AC24" s="45" t="n"/>
+      <c r="AD24" s="45" t="n"/>
+      <c r="AE24" s="45" t="n"/>
+      <c r="AF24" s="45" t="n"/>
+      <c r="AG24" s="45" t="n"/>
+      <c r="AH24" s="45" t="n"/>
+      <c r="AI24" s="45" t="n"/>
+      <c r="AJ24" s="45" t="n"/>
+      <c r="AK24" s="45" t="n"/>
+      <c r="AL24" s="45" t="n"/>
+      <c r="AM24" s="45" t="n"/>
+      <c r="AN24" s="45" t="n"/>
+      <c r="AO24" s="45" t="n"/>
+      <c r="AP24" s="45" t="n"/>
+      <c r="AQ24" s="45" t="n"/>
+      <c r="AR24" s="45" t="n"/>
+      <c r="AS24" s="45" t="n"/>
+      <c r="AT24" s="45" t="n"/>
+      <c r="AU24" s="45" t="n"/>
+      <c r="AV24" s="45" t="n"/>
+      <c r="AW24" s="45" t="n"/>
+      <c r="AX24" s="45" t="n"/>
+      <c r="AY24" s="46" t="n"/>
+    </row>
+    <row r="25" ht="15" customHeight="1">
+      <c r="B25" s="44" t="n"/>
+      <c r="C25" s="45" t="n"/>
+      <c r="D25" s="45" t="n"/>
+      <c r="E25" s="45" t="n"/>
+      <c r="F25" s="45" t="n"/>
+      <c r="G25" s="45" t="n"/>
+      <c r="H25" s="45" t="n"/>
+      <c r="I25" s="45" t="n"/>
+      <c r="J25" s="53">
+        <f>IFERROR('Makine Giris'!B5,"Makine 1")</f>
+        <v/>
+      </c>
+      <c r="K25" s="51" t="n"/>
+      <c r="L25" s="51" t="n"/>
+      <c r="M25" s="51" t="n"/>
+      <c r="N25" s="52" t="n"/>
+      <c r="O25" s="45" t="n"/>
+      <c r="P25" s="45" t="n"/>
+      <c r="Q25" s="45" t="n"/>
+      <c r="R25" s="45" t="n"/>
+      <c r="S25" s="45" t="n"/>
+      <c r="T25" s="45" t="n"/>
+      <c r="U25" s="45" t="n"/>
+      <c r="V25" s="53">
+        <f>IFERROR('Makine Giris'!B6,"Makine 2")</f>
+        <v/>
+      </c>
+      <c r="W25" s="51" t="n"/>
+      <c r="X25" s="51" t="n"/>
+      <c r="Y25" s="51" t="n"/>
+      <c r="Z25" s="52" t="n"/>
+      <c r="AA25" s="45" t="n"/>
+      <c r="AB25" s="45" t="n"/>
+      <c r="AC25" s="45" t="n"/>
+      <c r="AD25" s="45" t="n"/>
+      <c r="AE25" s="45" t="n"/>
+      <c r="AF25" s="45" t="n"/>
+      <c r="AG25" s="45" t="n"/>
+      <c r="AH25" s="53">
+        <f>IFERROR('Makine Giris'!B7,"Makine 3")</f>
+        <v/>
+      </c>
+      <c r="AI25" s="51" t="n"/>
+      <c r="AJ25" s="51" t="n"/>
+      <c r="AK25" s="51" t="n"/>
+      <c r="AL25" s="52" t="n"/>
+      <c r="AM25" s="45" t="n"/>
+      <c r="AN25" s="45" t="n"/>
+      <c r="AO25" s="45" t="n"/>
+      <c r="AP25" s="45" t="n"/>
+      <c r="AQ25" s="45" t="n"/>
+      <c r="AR25" s="45" t="n"/>
+      <c r="AS25" s="45" t="n"/>
+      <c r="AT25" s="45" t="n"/>
+      <c r="AU25" s="45" t="n"/>
+      <c r="AV25" s="45" t="n"/>
+      <c r="AW25" s="45" t="n"/>
+      <c r="AX25" s="45" t="n"/>
+      <c r="AY25" s="46" t="n"/>
+    </row>
+    <row r="26" ht="15" customHeight="1">
+      <c r="B26" s="44" t="n"/>
+      <c r="C26" s="45" t="n"/>
+      <c r="D26" s="45" t="n"/>
+      <c r="E26" s="45" t="n"/>
+      <c r="F26" s="45" t="n"/>
+      <c r="G26" s="45" t="n"/>
+      <c r="H26" s="45" t="n"/>
+      <c r="I26" s="45" t="n"/>
+      <c r="J26" s="45" t="n"/>
+      <c r="K26" s="45" t="n"/>
+      <c r="L26" s="45" t="n"/>
+      <c r="M26" s="45" t="n"/>
+      <c r="N26" s="45" t="n"/>
+      <c r="O26" s="45" t="n"/>
+      <c r="P26" s="45" t="n"/>
+      <c r="Q26" s="45" t="n"/>
+      <c r="R26" s="45" t="n"/>
+      <c r="S26" s="45" t="n"/>
+      <c r="T26" s="45" t="n"/>
+      <c r="U26" s="45" t="n"/>
+      <c r="V26" s="45" t="n"/>
+      <c r="W26" s="45" t="n"/>
+      <c r="X26" s="45" t="n"/>
+      <c r="Y26" s="45" t="n"/>
+      <c r="Z26" s="45" t="n"/>
+      <c r="AA26" s="45" t="n"/>
+      <c r="AB26" s="45" t="n"/>
+      <c r="AC26" s="45" t="n"/>
+      <c r="AD26" s="45" t="n"/>
+      <c r="AE26" s="45" t="n"/>
+      <c r="AF26" s="45" t="n"/>
+      <c r="AG26" s="45" t="n"/>
+      <c r="AH26" s="45" t="n"/>
+      <c r="AI26" s="45" t="n"/>
+      <c r="AJ26" s="45" t="n"/>
+      <c r="AK26" s="45" t="n"/>
+      <c r="AL26" s="45" t="n"/>
+      <c r="AM26" s="45" t="n"/>
+      <c r="AN26" s="45" t="n"/>
+      <c r="AO26" s="45" t="n"/>
+      <c r="AP26" s="45" t="n"/>
+      <c r="AQ26" s="45" t="n"/>
+      <c r="AR26" s="45" t="n"/>
+      <c r="AS26" s="45" t="n"/>
+      <c r="AT26" s="45" t="n"/>
+      <c r="AU26" s="45" t="n"/>
+      <c r="AV26" s="45" t="n"/>
+      <c r="AW26" s="45" t="n"/>
+      <c r="AX26" s="45" t="n"/>
+      <c r="AY26" s="46" t="n"/>
+    </row>
+    <row r="27" ht="15" customHeight="1">
+      <c r="B27" s="44" t="n"/>
+      <c r="C27" s="45" t="n"/>
+      <c r="D27" s="45" t="n"/>
+      <c r="E27" s="45" t="n"/>
+      <c r="F27" s="45" t="n"/>
+      <c r="G27" s="45" t="n"/>
+      <c r="H27" s="45" t="n"/>
+      <c r="I27" s="45" t="n"/>
+      <c r="J27" s="45" t="n"/>
+      <c r="K27" s="45" t="n"/>
+      <c r="L27" s="45" t="n"/>
+      <c r="M27" s="45" t="n"/>
+      <c r="N27" s="45" t="n"/>
+      <c r="O27" s="45" t="n"/>
+      <c r="P27" s="45" t="n"/>
+      <c r="Q27" s="45" t="n"/>
+      <c r="R27" s="45" t="n"/>
+      <c r="S27" s="45" t="n"/>
+      <c r="T27" s="45" t="n"/>
+      <c r="U27" s="45" t="n"/>
+      <c r="V27" s="45" t="n"/>
+      <c r="W27" s="45" t="n"/>
+      <c r="X27" s="45" t="n"/>
+      <c r="Y27" s="45" t="n"/>
+      <c r="Z27" s="45" t="n"/>
+      <c r="AA27" s="45" t="n"/>
+      <c r="AB27" s="45" t="n"/>
+      <c r="AC27" s="45" t="n"/>
+      <c r="AD27" s="45" t="n"/>
+      <c r="AE27" s="45" t="n"/>
+      <c r="AF27" s="45" t="n"/>
+      <c r="AG27" s="45" t="n"/>
+      <c r="AH27" s="45" t="n"/>
+      <c r="AI27" s="45" t="n"/>
+      <c r="AJ27" s="45" t="n"/>
+      <c r="AK27" s="45" t="n"/>
+      <c r="AL27" s="45" t="n"/>
+      <c r="AM27" s="45" t="n"/>
+      <c r="AN27" s="45" t="n"/>
+      <c r="AO27" s="45" t="n"/>
+      <c r="AP27" s="45" t="n"/>
+      <c r="AQ27" s="45" t="n"/>
+      <c r="AR27" s="45" t="n"/>
+      <c r="AS27" s="45" t="n"/>
+      <c r="AT27" s="45" t="n"/>
+      <c r="AU27" s="45" t="n"/>
+      <c r="AV27" s="45" t="n"/>
+      <c r="AW27" s="45" t="n"/>
+      <c r="AX27" s="45" t="n"/>
+      <c r="AY27" s="46" t="n"/>
+    </row>
+    <row r="28" ht="15" customHeight="1">
+      <c r="B28" s="44" t="n"/>
+      <c r="C28" s="45" t="n"/>
+      <c r="D28" s="45" t="n"/>
+      <c r="E28" s="45" t="n"/>
+      <c r="F28" s="45" t="n"/>
+      <c r="G28" s="45" t="n"/>
+      <c r="H28" s="45" t="n"/>
+      <c r="I28" s="45" t="n"/>
+      <c r="J28" s="45" t="n"/>
+      <c r="K28" s="45" t="n"/>
+      <c r="L28" s="45" t="n"/>
+      <c r="M28" s="45" t="n"/>
+      <c r="N28" s="45" t="n"/>
+      <c r="O28" s="45" t="n"/>
+      <c r="P28" s="45" t="n"/>
+      <c r="Q28" s="45" t="n"/>
+      <c r="R28" s="45" t="n"/>
+      <c r="S28" s="45" t="n"/>
+      <c r="T28" s="45" t="n"/>
+      <c r="U28" s="45" t="n"/>
+      <c r="V28" s="45" t="n"/>
+      <c r="W28" s="45" t="n"/>
+      <c r="X28" s="45" t="n"/>
+      <c r="Y28" s="45" t="n"/>
+      <c r="Z28" s="45" t="n"/>
+      <c r="AA28" s="45" t="n"/>
+      <c r="AB28" s="45" t="n"/>
+      <c r="AC28" s="45" t="n"/>
+      <c r="AD28" s="45" t="n"/>
+      <c r="AE28" s="45" t="n"/>
+      <c r="AF28" s="45" t="n"/>
+      <c r="AG28" s="45" t="n"/>
+      <c r="AH28" s="45" t="n"/>
+      <c r="AI28" s="45" t="n"/>
+      <c r="AJ28" s="45" t="n"/>
+      <c r="AK28" s="45" t="n"/>
+      <c r="AL28" s="45" t="n"/>
+      <c r="AM28" s="45" t="n"/>
+      <c r="AN28" s="45" t="n"/>
+      <c r="AO28" s="45" t="n"/>
+      <c r="AP28" s="45" t="n"/>
+      <c r="AQ28" s="45" t="n"/>
+      <c r="AR28" s="45" t="n"/>
+      <c r="AS28" s="45" t="n"/>
+      <c r="AT28" s="45" t="n"/>
+      <c r="AU28" s="45" t="n"/>
+      <c r="AV28" s="45" t="n"/>
+      <c r="AW28" s="45" t="n"/>
+      <c r="AX28" s="45" t="n"/>
+      <c r="AY28" s="46" t="n"/>
+    </row>
+    <row r="29" ht="15" customHeight="1">
+      <c r="B29" s="44" t="n"/>
+      <c r="C29" s="45" t="n"/>
+      <c r="D29" s="45" t="n"/>
+      <c r="E29" s="45" t="n"/>
+      <c r="F29" s="45" t="n"/>
+      <c r="G29" s="45" t="n"/>
+      <c r="H29" s="45" t="n"/>
+      <c r="I29" s="45" t="n"/>
+      <c r="J29" s="45" t="n"/>
+      <c r="K29" s="45" t="n"/>
+      <c r="L29" s="45" t="n"/>
+      <c r="M29" s="45" t="n"/>
+      <c r="N29" s="45" t="n"/>
+      <c r="O29" s="45" t="n"/>
+      <c r="P29" s="45" t="n"/>
+      <c r="Q29" s="45" t="n"/>
+      <c r="R29" s="45" t="n"/>
+      <c r="S29" s="45" t="n"/>
+      <c r="T29" s="45" t="n"/>
+      <c r="U29" s="45" t="n"/>
+      <c r="V29" s="45" t="n"/>
+      <c r="W29" s="45" t="n"/>
+      <c r="X29" s="45" t="n"/>
+      <c r="Y29" s="45" t="n"/>
+      <c r="Z29" s="45" t="n"/>
+      <c r="AA29" s="45" t="n"/>
+      <c r="AB29" s="45" t="n"/>
+      <c r="AC29" s="45" t="n"/>
+      <c r="AD29" s="45" t="n"/>
+      <c r="AE29" s="45" t="n"/>
+      <c r="AF29" s="45" t="n"/>
+      <c r="AG29" s="45" t="n"/>
+      <c r="AH29" s="45" t="n"/>
+      <c r="AI29" s="45" t="n"/>
+      <c r="AJ29" s="45" t="n"/>
+      <c r="AK29" s="45" t="n"/>
+      <c r="AL29" s="45" t="n"/>
+      <c r="AM29" s="45" t="n"/>
+      <c r="AN29" s="45" t="n"/>
+      <c r="AO29" s="45" t="n"/>
+      <c r="AP29" s="45" t="n"/>
+      <c r="AQ29" s="45" t="n"/>
+      <c r="AR29" s="45" t="n"/>
+      <c r="AS29" s="45" t="n"/>
+      <c r="AT29" s="45" t="n"/>
+      <c r="AU29" s="45" t="n"/>
+      <c r="AV29" s="45" t="n"/>
+      <c r="AW29" s="45" t="n"/>
+      <c r="AX29" s="45" t="n"/>
+      <c r="AY29" s="46" t="n"/>
+    </row>
+    <row r="30" ht="15" customHeight="1">
+      <c r="B30" s="44" t="n"/>
+      <c r="C30" s="45" t="n"/>
+      <c r="D30" s="45" t="n"/>
+      <c r="E30" s="45" t="n"/>
+      <c r="F30" s="45" t="n"/>
+      <c r="G30" s="45" t="n"/>
+      <c r="H30" s="45" t="n"/>
+      <c r="I30" s="45" t="n"/>
+      <c r="J30" s="45" t="n"/>
+      <c r="K30" s="45" t="n"/>
+      <c r="L30" s="45" t="n"/>
+      <c r="M30" s="45" t="n"/>
+      <c r="N30" s="45" t="n"/>
+      <c r="O30" s="45" t="n"/>
+      <c r="P30" s="45" t="n"/>
+      <c r="Q30" s="45" t="n"/>
+      <c r="R30" s="45" t="n"/>
+      <c r="S30" s="45" t="n"/>
+      <c r="T30" s="45" t="n"/>
+      <c r="U30" s="45" t="n"/>
+      <c r="V30" s="45" t="n"/>
+      <c r="W30" s="45" t="n"/>
+      <c r="X30" s="45" t="n"/>
+      <c r="Y30" s="45" t="n"/>
+      <c r="Z30" s="45" t="n"/>
+      <c r="AA30" s="45" t="n"/>
+      <c r="AB30" s="45" t="n"/>
+      <c r="AC30" s="45" t="n"/>
+      <c r="AD30" s="45" t="n"/>
+      <c r="AE30" s="45" t="n"/>
+      <c r="AF30" s="45" t="n"/>
+      <c r="AG30" s="45" t="n"/>
+      <c r="AH30" s="45" t="n"/>
+      <c r="AI30" s="45" t="n"/>
+      <c r="AJ30" s="45" t="n"/>
+      <c r="AK30" s="45" t="n"/>
+      <c r="AL30" s="45" t="n"/>
+      <c r="AM30" s="45" t="n"/>
+      <c r="AN30" s="45" t="n"/>
+      <c r="AO30" s="45" t="n"/>
+      <c r="AP30" s="45" t="n"/>
+      <c r="AQ30" s="45" t="n"/>
+      <c r="AR30" s="45" t="n"/>
+      <c r="AS30" s="45" t="n"/>
+      <c r="AT30" s="45" t="n"/>
+      <c r="AU30" s="45" t="n"/>
+      <c r="AV30" s="45" t="n"/>
+      <c r="AW30" s="45" t="n"/>
+      <c r="AX30" s="45" t="n"/>
+      <c r="AY30" s="46" t="n"/>
+    </row>
+    <row r="31" ht="15" customHeight="1">
+      <c r="B31" s="44" t="n"/>
+      <c r="C31" s="45" t="n"/>
+      <c r="D31" s="45" t="n"/>
+      <c r="E31" s="45" t="n"/>
+      <c r="F31" s="45" t="n"/>
+      <c r="G31" s="45" t="n"/>
+      <c r="H31" s="45" t="n"/>
+      <c r="I31" s="45" t="n"/>
+      <c r="J31" s="45" t="n"/>
+      <c r="K31" s="45" t="n"/>
+      <c r="L31" s="45" t="n"/>
+      <c r="M31" s="45" t="n"/>
+      <c r="N31" s="45" t="n"/>
+      <c r="O31" s="45" t="n"/>
+      <c r="P31" s="45" t="n"/>
+      <c r="Q31" s="45" t="n"/>
+      <c r="R31" s="45" t="n"/>
+      <c r="S31" s="45" t="n"/>
+      <c r="T31" s="45" t="n"/>
+      <c r="U31" s="45" t="n"/>
+      <c r="V31" s="45" t="n"/>
+      <c r="W31" s="45" t="n"/>
+      <c r="X31" s="45" t="n"/>
+      <c r="Y31" s="45" t="n"/>
+      <c r="Z31" s="45" t="n"/>
+      <c r="AA31" s="45" t="n"/>
+      <c r="AB31" s="45" t="n"/>
+      <c r="AC31" s="45" t="n"/>
+      <c r="AD31" s="45" t="n"/>
+      <c r="AE31" s="45" t="n"/>
+      <c r="AF31" s="45" t="n"/>
+      <c r="AG31" s="45" t="n"/>
+      <c r="AH31" s="45" t="n"/>
+      <c r="AI31" s="45" t="n"/>
+      <c r="AJ31" s="45" t="n"/>
+      <c r="AK31" s="45" t="n"/>
+      <c r="AL31" s="45" t="n"/>
+      <c r="AM31" s="45" t="n"/>
+      <c r="AN31" s="45" t="n"/>
+      <c r="AO31" s="45" t="n"/>
+      <c r="AP31" s="45" t="n"/>
+      <c r="AQ31" s="45" t="n"/>
+      <c r="AR31" s="45" t="n"/>
+      <c r="AS31" s="45" t="n"/>
+      <c r="AT31" s="45" t="n"/>
+      <c r="AU31" s="45" t="n"/>
+      <c r="AV31" s="45" t="n"/>
+      <c r="AW31" s="45" t="n"/>
+      <c r="AX31" s="45" t="n"/>
+      <c r="AY31" s="46" t="n"/>
+    </row>
+    <row r="32" ht="15" customHeight="1">
+      <c r="B32" s="44" t="n"/>
+      <c r="C32" s="45" t="n"/>
+      <c r="D32" s="45" t="n"/>
+      <c r="E32" s="45" t="n"/>
+      <c r="F32" s="45" t="n"/>
+      <c r="G32" s="45" t="n"/>
+      <c r="H32" s="45" t="n"/>
+      <c r="I32" s="45" t="n"/>
+      <c r="J32" s="45" t="n"/>
+      <c r="K32" s="45" t="n"/>
+      <c r="L32" s="45" t="n"/>
+      <c r="M32" s="45" t="n"/>
+      <c r="N32" s="45" t="n"/>
+      <c r="O32" s="45" t="n"/>
+      <c r="P32" s="45" t="n"/>
+      <c r="Q32" s="45" t="n"/>
+      <c r="R32" s="45" t="n"/>
+      <c r="S32" s="45" t="n"/>
+      <c r="T32" s="45" t="n"/>
+      <c r="U32" s="45" t="n"/>
+      <c r="V32" s="45" t="n"/>
+      <c r="W32" s="45" t="n"/>
+      <c r="X32" s="45" t="n"/>
+      <c r="Y32" s="45" t="n"/>
+      <c r="Z32" s="45" t="n"/>
+      <c r="AA32" s="45" t="n"/>
+      <c r="AB32" s="45" t="n"/>
+      <c r="AC32" s="45" t="n"/>
+      <c r="AD32" s="45" t="n"/>
+      <c r="AE32" s="45" t="n"/>
+      <c r="AF32" s="45" t="n"/>
+      <c r="AG32" s="45" t="n"/>
+      <c r="AH32" s="45" t="n"/>
+      <c r="AI32" s="45" t="n"/>
+      <c r="AJ32" s="45" t="n"/>
+      <c r="AK32" s="45" t="n"/>
+      <c r="AL32" s="45" t="n"/>
+      <c r="AM32" s="45" t="n"/>
+      <c r="AN32" s="45" t="n"/>
+      <c r="AO32" s="45" t="n"/>
+      <c r="AP32" s="45" t="n"/>
+      <c r="AQ32" s="45" t="n"/>
+      <c r="AR32" s="45" t="n"/>
+      <c r="AS32" s="45" t="n"/>
+      <c r="AT32" s="45" t="n"/>
+      <c r="AU32" s="45" t="n"/>
+      <c r="AV32" s="45" t="n"/>
+      <c r="AW32" s="45" t="n"/>
+      <c r="AX32" s="45" t="n"/>
+      <c r="AY32" s="46" t="n"/>
+    </row>
+    <row r="33" ht="15" customHeight="1">
+      <c r="B33" s="44" t="n"/>
+      <c r="C33" s="45" t="n"/>
+      <c r="D33" s="45" t="n"/>
+      <c r="E33" s="45" t="n"/>
+      <c r="F33" s="45" t="n"/>
+      <c r="G33" s="45" t="n"/>
+      <c r="H33" s="45" t="n"/>
+      <c r="I33" s="45" t="n"/>
+      <c r="J33" s="45" t="n"/>
+      <c r="K33" s="45" t="n"/>
+      <c r="L33" s="45" t="n"/>
+      <c r="M33" s="45" t="n"/>
+      <c r="N33" s="45" t="n"/>
+      <c r="O33" s="45" t="n"/>
+      <c r="P33" s="45" t="n"/>
+      <c r="Q33" s="45" t="n"/>
+      <c r="R33" s="45" t="n"/>
+      <c r="S33" s="45" t="n"/>
+      <c r="T33" s="45" t="n"/>
+      <c r="U33" s="45" t="n"/>
+      <c r="V33" s="45" t="n"/>
+      <c r="W33" s="45" t="n"/>
+      <c r="X33" s="45" t="n"/>
+      <c r="Y33" s="45" t="n"/>
+      <c r="Z33" s="45" t="n"/>
+      <c r="AA33" s="45" t="n"/>
+      <c r="AB33" s="45" t="n"/>
+      <c r="AC33" s="45" t="n"/>
+      <c r="AD33" s="45" t="n"/>
+      <c r="AE33" s="45" t="n"/>
+      <c r="AF33" s="45" t="n"/>
+      <c r="AG33" s="45" t="n"/>
+      <c r="AH33" s="45" t="n"/>
+      <c r="AI33" s="45" t="n"/>
+      <c r="AJ33" s="45" t="n"/>
+      <c r="AK33" s="45" t="n"/>
+      <c r="AL33" s="45" t="n"/>
+      <c r="AM33" s="45" t="n"/>
+      <c r="AN33" s="45" t="n"/>
+      <c r="AO33" s="45" t="n"/>
+      <c r="AP33" s="45" t="n"/>
+      <c r="AQ33" s="45" t="n"/>
+      <c r="AR33" s="45" t="n"/>
+      <c r="AS33" s="45" t="n"/>
+      <c r="AT33" s="45" t="n"/>
+      <c r="AU33" s="45" t="n"/>
+      <c r="AV33" s="45" t="n"/>
+      <c r="AW33" s="45" t="n"/>
+      <c r="AX33" s="45" t="n"/>
+      <c r="AY33" s="46" t="n"/>
+    </row>
+    <row r="34" ht="15" customHeight="1">
+      <c r="B34" s="44" t="n"/>
+      <c r="C34" s="45" t="n"/>
+      <c r="D34" s="45" t="n"/>
+      <c r="E34" s="45" t="n"/>
+      <c r="F34" s="45" t="n"/>
+      <c r="G34" s="45" t="n"/>
+      <c r="H34" s="45" t="n"/>
+      <c r="I34" s="45" t="n"/>
+      <c r="J34" s="45" t="n"/>
+      <c r="K34" s="45" t="n"/>
+      <c r="L34" s="45" t="n"/>
+      <c r="M34" s="45" t="n"/>
+      <c r="N34" s="45" t="n"/>
+      <c r="O34" s="45" t="n"/>
+      <c r="P34" s="45" t="n"/>
+      <c r="Q34" s="45" t="n"/>
+      <c r="R34" s="45" t="n"/>
+      <c r="S34" s="45" t="n"/>
+      <c r="T34" s="45" t="n"/>
+      <c r="U34" s="45" t="n"/>
+      <c r="V34" s="45" t="n"/>
+      <c r="W34" s="45" t="n"/>
+      <c r="X34" s="45" t="n"/>
+      <c r="Y34" s="45" t="n"/>
+      <c r="Z34" s="45" t="n"/>
+      <c r="AA34" s="45" t="n"/>
+      <c r="AB34" s="45" t="n"/>
+      <c r="AC34" s="45" t="n"/>
+      <c r="AD34" s="45" t="n"/>
+      <c r="AE34" s="45" t="n"/>
+      <c r="AF34" s="45" t="n"/>
+      <c r="AG34" s="45" t="n"/>
+      <c r="AH34" s="45" t="n"/>
+      <c r="AI34" s="45" t="n"/>
+      <c r="AJ34" s="45" t="n"/>
+      <c r="AK34" s="45" t="n"/>
+      <c r="AL34" s="45" t="n"/>
+      <c r="AM34" s="45" t="n"/>
+      <c r="AN34" s="45" t="n"/>
+      <c r="AO34" s="45" t="n"/>
+      <c r="AP34" s="45" t="n"/>
+      <c r="AQ34" s="45" t="n"/>
+      <c r="AR34" s="45" t="n"/>
+      <c r="AS34" s="45" t="n"/>
+      <c r="AT34" s="45" t="n"/>
+      <c r="AU34" s="45" t="n"/>
+      <c r="AV34" s="45" t="n"/>
+      <c r="AW34" s="45" t="n"/>
+      <c r="AX34" s="45" t="n"/>
+      <c r="AY34" s="46" t="n"/>
+    </row>
+    <row r="35" ht="15" customHeight="1">
+      <c r="B35" s="44" t="n"/>
+      <c r="C35" s="45" t="n"/>
+      <c r="D35" s="45" t="n"/>
+      <c r="E35" s="45" t="n"/>
+      <c r="F35" s="45" t="n"/>
+      <c r="G35" s="45" t="n"/>
+      <c r="H35" s="45" t="n"/>
+      <c r="I35" s="45" t="n"/>
+      <c r="J35" s="45" t="n"/>
+      <c r="K35" s="45" t="n"/>
+      <c r="L35" s="45" t="n"/>
+      <c r="M35" s="45" t="n"/>
+      <c r="N35" s="45" t="n"/>
+      <c r="O35" s="45" t="n"/>
+      <c r="P35" s="45" t="n"/>
+      <c r="Q35" s="45" t="n"/>
+      <c r="R35" s="45" t="n"/>
+      <c r="S35" s="45" t="n"/>
+      <c r="T35" s="45" t="n"/>
+      <c r="U35" s="45" t="n"/>
+      <c r="V35" s="45" t="n"/>
+      <c r="W35" s="45" t="n"/>
+      <c r="X35" s="45" t="n"/>
+      <c r="Y35" s="45" t="n"/>
+      <c r="Z35" s="45" t="n"/>
+      <c r="AA35" s="45" t="n"/>
+      <c r="AB35" s="45" t="n"/>
+      <c r="AC35" s="45" t="n"/>
+      <c r="AD35" s="45" t="n"/>
+      <c r="AE35" s="45" t="n"/>
+      <c r="AF35" s="45" t="n"/>
+      <c r="AG35" s="45" t="n"/>
+      <c r="AH35" s="45" t="n"/>
+      <c r="AI35" s="45" t="n"/>
+      <c r="AJ35" s="45" t="n"/>
+      <c r="AK35" s="45" t="n"/>
+      <c r="AL35" s="45" t="n"/>
+      <c r="AM35" s="45" t="n"/>
+      <c r="AN35" s="45" t="n"/>
+      <c r="AO35" s="45" t="n"/>
+      <c r="AP35" s="45" t="n"/>
+      <c r="AQ35" s="45" t="n"/>
+      <c r="AR35" s="45" t="n"/>
+      <c r="AS35" s="45" t="n"/>
+      <c r="AT35" s="45" t="n"/>
+      <c r="AU35" s="45" t="n"/>
+      <c r="AV35" s="45" t="n"/>
+      <c r="AW35" s="45" t="n"/>
+      <c r="AX35" s="45" t="n"/>
+      <c r="AY35" s="46" t="n"/>
+    </row>
+    <row r="36" ht="15" customHeight="1">
+      <c r="B36" s="44" t="n"/>
+      <c r="C36" s="45" t="n"/>
+      <c r="D36" s="45" t="n"/>
+      <c r="E36" s="45" t="n"/>
+      <c r="F36" s="45" t="n"/>
+      <c r="G36" s="45" t="n"/>
+      <c r="H36" s="45" t="n"/>
+      <c r="I36" s="45" t="n"/>
+      <c r="J36" s="45" t="n"/>
+      <c r="K36" s="45" t="n"/>
+      <c r="L36" s="45" t="n"/>
+      <c r="M36" s="45" t="n"/>
+      <c r="N36" s="45" t="n"/>
+      <c r="O36" s="45" t="n"/>
+      <c r="P36" s="45" t="n"/>
+      <c r="Q36" s="45" t="n"/>
+      <c r="R36" s="45" t="n"/>
+      <c r="S36" s="45" t="n"/>
+      <c r="T36" s="45" t="n"/>
+      <c r="U36" s="45" t="n"/>
+      <c r="V36" s="45" t="n"/>
+      <c r="W36" s="45" t="n"/>
+      <c r="X36" s="45" t="n"/>
+      <c r="Y36" s="45" t="n"/>
+      <c r="Z36" s="45" t="n"/>
+      <c r="AA36" s="45" t="n"/>
+      <c r="AB36" s="45" t="n"/>
+      <c r="AC36" s="45" t="n"/>
+      <c r="AD36" s="45" t="n"/>
+      <c r="AE36" s="45" t="n"/>
+      <c r="AF36" s="45" t="n"/>
+      <c r="AG36" s="45" t="n"/>
+      <c r="AH36" s="45" t="n"/>
+      <c r="AI36" s="45" t="n"/>
+      <c r="AJ36" s="45" t="n"/>
+      <c r="AK36" s="45" t="n"/>
+      <c r="AL36" s="45" t="n"/>
+      <c r="AM36" s="45" t="n"/>
+      <c r="AN36" s="45" t="n"/>
+      <c r="AO36" s="45" t="n"/>
+      <c r="AP36" s="45" t="n"/>
+      <c r="AQ36" s="45" t="n"/>
+      <c r="AR36" s="45" t="n"/>
+      <c r="AS36" s="45" t="n"/>
+      <c r="AT36" s="45" t="n"/>
+      <c r="AU36" s="45" t="n"/>
+      <c r="AV36" s="45" t="n"/>
+      <c r="AW36" s="45" t="n"/>
+      <c r="AX36" s="45" t="n"/>
+      <c r="AY36" s="46" t="n"/>
+    </row>
+    <row r="37" ht="15" customHeight="1">
+      <c r="B37" s="44" t="n"/>
+      <c r="C37" s="45" t="n"/>
+      <c r="D37" s="45" t="n"/>
+      <c r="E37" s="45" t="n"/>
+      <c r="F37" s="45" t="n"/>
+      <c r="G37" s="45" t="n"/>
+      <c r="H37" s="45" t="n"/>
+      <c r="I37" s="45" t="n"/>
+      <c r="J37" s="45" t="n"/>
+      <c r="K37" s="45" t="n"/>
+      <c r="L37" s="45" t="n"/>
+      <c r="M37" s="45" t="n"/>
+      <c r="N37" s="45" t="n"/>
+      <c r="O37" s="45" t="n"/>
+      <c r="P37" s="45" t="n"/>
+      <c r="Q37" s="45" t="n"/>
+      <c r="R37" s="45" t="n"/>
+      <c r="S37" s="45" t="n"/>
+      <c r="T37" s="45" t="n"/>
+      <c r="U37" s="45" t="n"/>
+      <c r="V37" s="45" t="n"/>
+      <c r="W37" s="45" t="n"/>
+      <c r="X37" s="45" t="n"/>
+      <c r="Y37" s="45" t="n"/>
+      <c r="Z37" s="45" t="n"/>
+      <c r="AA37" s="45" t="n"/>
+      <c r="AB37" s="45" t="n"/>
+      <c r="AC37" s="45" t="n"/>
+      <c r="AD37" s="45" t="n"/>
+      <c r="AE37" s="45" t="n"/>
+      <c r="AF37" s="45" t="n"/>
+      <c r="AG37" s="45" t="n"/>
+      <c r="AH37" s="45" t="n"/>
+      <c r="AI37" s="45" t="n"/>
+      <c r="AJ37" s="45" t="n"/>
+      <c r="AK37" s="45" t="n"/>
+      <c r="AL37" s="45" t="n"/>
+      <c r="AM37" s="45" t="n"/>
+      <c r="AN37" s="45" t="n"/>
+      <c r="AO37" s="45" t="n"/>
+      <c r="AP37" s="45" t="n"/>
+      <c r="AQ37" s="45" t="n"/>
+      <c r="AR37" s="45" t="n"/>
+      <c r="AS37" s="45" t="n"/>
+      <c r="AT37" s="45" t="n"/>
+      <c r="AU37" s="45" t="n"/>
+      <c r="AV37" s="45" t="n"/>
+      <c r="AW37" s="45" t="n"/>
+      <c r="AX37" s="45" t="n"/>
+      <c r="AY37" s="46" t="n"/>
+    </row>
+    <row r="38" ht="15" customHeight="1">
+      <c r="B38" s="44" t="n"/>
+      <c r="C38" s="45" t="n"/>
+      <c r="D38" s="45" t="n"/>
+      <c r="E38" s="45" t="n"/>
+      <c r="F38" s="45" t="n"/>
+      <c r="G38" s="45" t="n"/>
+      <c r="H38" s="45" t="n"/>
+      <c r="I38" s="45" t="n"/>
+      <c r="J38" s="45" t="n"/>
+      <c r="K38" s="45" t="n"/>
+      <c r="L38" s="45" t="n"/>
+      <c r="M38" s="45" t="n"/>
+      <c r="N38" s="45" t="n"/>
+      <c r="O38" s="45" t="n"/>
+      <c r="P38" s="45" t="n"/>
+      <c r="Q38" s="45" t="n"/>
+      <c r="R38" s="45" t="n"/>
+      <c r="S38" s="45" t="n"/>
+      <c r="T38" s="45" t="n"/>
+      <c r="U38" s="45" t="n"/>
+      <c r="V38" s="45" t="n"/>
+      <c r="W38" s="45" t="n"/>
+      <c r="X38" s="45" t="n"/>
+      <c r="Y38" s="45" t="n"/>
+      <c r="Z38" s="45" t="n"/>
+      <c r="AA38" s="45" t="n"/>
+      <c r="AB38" s="45" t="n"/>
+      <c r="AC38" s="45" t="n"/>
+      <c r="AD38" s="45" t="n"/>
+      <c r="AE38" s="45" t="n"/>
+      <c r="AF38" s="45" t="n"/>
+      <c r="AG38" s="45" t="n"/>
+      <c r="AH38" s="45" t="n"/>
+      <c r="AI38" s="45" t="n"/>
+      <c r="AJ38" s="45" t="n"/>
+      <c r="AK38" s="45" t="n"/>
+      <c r="AL38" s="45" t="n"/>
+      <c r="AM38" s="45" t="n"/>
+      <c r="AN38" s="45" t="n"/>
+      <c r="AO38" s="45" t="n"/>
+      <c r="AP38" s="45" t="n"/>
+      <c r="AQ38" s="45" t="n"/>
+      <c r="AR38" s="45" t="n"/>
+      <c r="AS38" s="45" t="n"/>
+      <c r="AT38" s="45" t="n"/>
+      <c r="AU38" s="45" t="n"/>
+      <c r="AV38" s="45" t="n"/>
+      <c r="AW38" s="45" t="n"/>
+      <c r="AX38" s="45" t="n"/>
+      <c r="AY38" s="46" t="n"/>
+    </row>
+    <row r="39" ht="15" customHeight="1">
+      <c r="B39" s="44" t="n"/>
+      <c r="C39" s="45" t="n"/>
+      <c r="D39" s="45" t="n"/>
+      <c r="E39" s="45" t="n"/>
+      <c r="F39" s="45" t="n"/>
+      <c r="G39" s="45" t="n"/>
+      <c r="H39" s="45" t="n"/>
+      <c r="I39" s="45" t="n"/>
+      <c r="J39" s="45" t="n"/>
+      <c r="K39" s="45" t="n"/>
+      <c r="L39" s="45" t="n"/>
+      <c r="M39" s="45" t="n"/>
+      <c r="N39" s="45" t="n"/>
+      <c r="O39" s="45" t="n"/>
+      <c r="P39" s="45" t="n"/>
+      <c r="Q39" s="45" t="n"/>
+      <c r="R39" s="45" t="n"/>
+      <c r="S39" s="45" t="n"/>
+      <c r="T39" s="45" t="n"/>
+      <c r="U39" s="45" t="n"/>
+      <c r="V39" s="45" t="n"/>
+      <c r="W39" s="45" t="n"/>
+      <c r="X39" s="45" t="n"/>
+      <c r="Y39" s="45" t="n"/>
+      <c r="Z39" s="45" t="n"/>
+      <c r="AA39" s="45" t="n"/>
+      <c r="AB39" s="45" t="n"/>
+      <c r="AC39" s="45" t="n"/>
+      <c r="AD39" s="45" t="n"/>
+      <c r="AE39" s="45" t="n"/>
+      <c r="AF39" s="45" t="n"/>
+      <c r="AG39" s="45" t="n"/>
+      <c r="AH39" s="45" t="n"/>
+      <c r="AI39" s="45" t="n"/>
+      <c r="AJ39" s="45" t="n"/>
+      <c r="AK39" s="45" t="n"/>
+      <c r="AL39" s="45" t="n"/>
+      <c r="AM39" s="45" t="n"/>
+      <c r="AN39" s="45" t="n"/>
+      <c r="AO39" s="45" t="n"/>
+      <c r="AP39" s="45" t="n"/>
+      <c r="AQ39" s="45" t="n"/>
+      <c r="AR39" s="45" t="n"/>
+      <c r="AS39" s="45" t="n"/>
+      <c r="AT39" s="45" t="n"/>
+      <c r="AU39" s="45" t="n"/>
+      <c r="AV39" s="45" t="n"/>
+      <c r="AW39" s="45" t="n"/>
+      <c r="AX39" s="45" t="n"/>
+      <c r="AY39" s="46" t="n"/>
+    </row>
+    <row r="40" ht="15" customHeight="1">
+      <c r="B40" s="44" t="n"/>
+      <c r="C40" s="45" t="n"/>
+      <c r="D40" s="45" t="n"/>
+      <c r="E40" s="45" t="n"/>
+      <c r="F40" s="45" t="n"/>
+      <c r="G40" s="45" t="n"/>
+      <c r="H40" s="45" t="n"/>
+      <c r="I40" s="45" t="n"/>
+      <c r="J40" s="45" t="n"/>
+      <c r="K40" s="45" t="n"/>
+      <c r="L40" s="45" t="n"/>
+      <c r="M40" s="45" t="n"/>
+      <c r="N40" s="45" t="n"/>
+      <c r="O40" s="45" t="n"/>
+      <c r="P40" s="45" t="n"/>
+      <c r="Q40" s="45" t="n"/>
+      <c r="R40" s="45" t="n"/>
+      <c r="S40" s="45" t="n"/>
+      <c r="T40" s="45" t="n"/>
+      <c r="U40" s="45" t="n"/>
+      <c r="V40" s="45" t="n"/>
+      <c r="W40" s="45" t="n"/>
+      <c r="X40" s="45" t="n"/>
+      <c r="Y40" s="45" t="n"/>
+      <c r="Z40" s="45" t="n"/>
+      <c r="AA40" s="45" t="n"/>
+      <c r="AB40" s="45" t="n"/>
+      <c r="AC40" s="45" t="n"/>
+      <c r="AD40" s="45" t="n"/>
+      <c r="AE40" s="45" t="n"/>
+      <c r="AF40" s="45" t="n"/>
+      <c r="AG40" s="45" t="n"/>
+      <c r="AH40" s="45" t="n"/>
+      <c r="AI40" s="45" t="n"/>
+      <c r="AJ40" s="45" t="n"/>
+      <c r="AK40" s="45" t="n"/>
+      <c r="AL40" s="45" t="n"/>
+      <c r="AM40" s="45" t="n"/>
+      <c r="AN40" s="45" t="n"/>
+      <c r="AO40" s="45" t="n"/>
+      <c r="AP40" s="45" t="n"/>
+      <c r="AQ40" s="45" t="n"/>
+      <c r="AR40" s="45" t="n"/>
+      <c r="AS40" s="45" t="n"/>
+      <c r="AT40" s="45" t="n"/>
+      <c r="AU40" s="45" t="n"/>
+      <c r="AV40" s="45" t="n"/>
+      <c r="AW40" s="45" t="n"/>
+      <c r="AX40" s="45" t="n"/>
+      <c r="AY40" s="46" t="n"/>
+    </row>
+    <row r="41" ht="15" customHeight="1">
+      <c r="B41" s="44" t="n"/>
+      <c r="C41" s="45" t="n"/>
+      <c r="D41" s="45" t="n"/>
+      <c r="E41" s="45" t="n"/>
+      <c r="F41" s="45" t="n"/>
+      <c r="G41" s="45" t="n"/>
+      <c r="H41" s="45" t="n"/>
+      <c r="I41" s="45" t="n"/>
+      <c r="J41" s="45" t="n"/>
+      <c r="K41" s="45" t="n"/>
+      <c r="L41" s="45" t="n"/>
+      <c r="M41" s="45" t="n"/>
+      <c r="N41" s="45" t="n"/>
+      <c r="O41" s="45" t="n"/>
+      <c r="P41" s="45" t="n"/>
+      <c r="Q41" s="45" t="n"/>
+      <c r="R41" s="45" t="n"/>
+      <c r="S41" s="45" t="n"/>
+      <c r="T41" s="45" t="n"/>
+      <c r="U41" s="45" t="n"/>
+      <c r="V41" s="45" t="n"/>
+      <c r="W41" s="45" t="n"/>
+      <c r="X41" s="45" t="n"/>
+      <c r="Y41" s="45" t="n"/>
+      <c r="Z41" s="45" t="n"/>
+      <c r="AA41" s="45" t="n"/>
+      <c r="AB41" s="45" t="n"/>
+      <c r="AC41" s="45" t="n"/>
+      <c r="AD41" s="45" t="n"/>
+      <c r="AE41" s="45" t="n"/>
+      <c r="AF41" s="45" t="n"/>
+      <c r="AG41" s="45" t="n"/>
+      <c r="AH41" s="45" t="n"/>
+      <c r="AI41" s="45" t="n"/>
+      <c r="AJ41" s="45" t="n"/>
+      <c r="AK41" s="45" t="n"/>
+      <c r="AL41" s="45" t="n"/>
+      <c r="AM41" s="45" t="n"/>
+      <c r="AN41" s="45" t="n"/>
+      <c r="AO41" s="45" t="n"/>
+      <c r="AP41" s="45" t="n"/>
+      <c r="AQ41" s="45" t="n"/>
+      <c r="AR41" s="45" t="n"/>
+      <c r="AS41" s="45" t="n"/>
+      <c r="AT41" s="45" t="n"/>
+      <c r="AU41" s="45" t="n"/>
+      <c r="AV41" s="45" t="n"/>
+      <c r="AW41" s="45" t="n"/>
+      <c r="AX41" s="45" t="n"/>
+      <c r="AY41" s="46" t="n"/>
+    </row>
+    <row r="42" ht="15" customHeight="1">
+      <c r="B42" s="54" t="n"/>
+      <c r="C42" s="55" t="n"/>
+      <c r="D42" s="55" t="n"/>
+      <c r="E42" s="55" t="n"/>
+      <c r="F42" s="55" t="n"/>
+      <c r="G42" s="55" t="n"/>
+      <c r="H42" s="55" t="n"/>
+      <c r="I42" s="55" t="n"/>
+      <c r="J42" s="55" t="n"/>
+      <c r="K42" s="55" t="n"/>
+      <c r="L42" s="55" t="n"/>
+      <c r="M42" s="55" t="n"/>
+      <c r="N42" s="55" t="n"/>
+      <c r="O42" s="55" t="n"/>
+      <c r="P42" s="55" t="n"/>
+      <c r="Q42" s="55" t="n"/>
+      <c r="R42" s="55" t="n"/>
+      <c r="S42" s="55" t="n"/>
+      <c r="T42" s="55" t="n"/>
+      <c r="U42" s="55" t="n"/>
+      <c r="V42" s="55" t="n"/>
+      <c r="W42" s="55" t="n"/>
+      <c r="X42" s="55" t="n"/>
+      <c r="Y42" s="55" t="n"/>
+      <c r="Z42" s="55" t="n"/>
+      <c r="AA42" s="55" t="n"/>
+      <c r="AB42" s="55" t="n"/>
+      <c r="AC42" s="55" t="n"/>
+      <c r="AD42" s="55" t="n"/>
+      <c r="AE42" s="55" t="n"/>
+      <c r="AF42" s="55" t="n"/>
+      <c r="AG42" s="55" t="n"/>
+      <c r="AH42" s="55" t="n"/>
+      <c r="AI42" s="55" t="n"/>
+      <c r="AJ42" s="55" t="n"/>
+      <c r="AK42" s="55" t="n"/>
+      <c r="AL42" s="55" t="n"/>
+      <c r="AM42" s="55" t="n"/>
+      <c r="AN42" s="55" t="n"/>
+      <c r="AO42" s="55" t="n"/>
+      <c r="AP42" s="55" t="n"/>
+      <c r="AQ42" s="55" t="n"/>
+      <c r="AR42" s="55" t="n"/>
+      <c r="AS42" s="55" t="n"/>
+      <c r="AT42" s="55" t="n"/>
+      <c r="AU42" s="55" t="n"/>
+      <c r="AV42" s="55" t="n"/>
+      <c r="AW42" s="55" t="n"/>
+      <c r="AX42" s="55" t="n"/>
+      <c r="AY42" s="56" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="23" t="inlineStr">
+        <is>
+          <t>SEMBOL LEJANDI</t>
+        </is>
+      </c>
+      <c r="B44" s="24" t="n"/>
+      <c r="C44" s="24" t="n"/>
+      <c r="D44" s="24" t="n"/>
+      <c r="E44" s="24" t="n"/>
+      <c r="F44" s="24" t="n"/>
+      <c r="G44" s="24" t="n"/>
+      <c r="H44" s="24" t="n"/>
+      <c r="I44" s="24" t="n"/>
+      <c r="J44" s="24" t="n"/>
+    </row>
+    <row r="45" ht="20" customHeight="1">
+      <c r="C45" s="57" t="inlineStr">
+        <is>
+          <t>Yapi Kolonu (tipik 4m x 4m aralik)</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="20" customHeight="1">
+      <c r="C46" s="57" t="inlineStr">
+        <is>
+          <t>Ana Hat Borusu</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="20" customHeight="1">
+      <c r="C47" s="57" t="inlineStr">
+        <is>
+          <t>Bransman (Dal) Borusu</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="20" customHeight="1">
+      <c r="C48" s="57" t="inlineStr">
+        <is>
+          <t>90 derece Dirsek</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="20" customHeight="1">
+      <c r="C49" s="57" t="inlineStr">
+        <is>
+          <t>Filtre Unitesi</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="20" customHeight="1">
+      <c r="C50" s="57" t="inlineStr">
+        <is>
+          <t>Fan (Aspirator)</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="20" customHeight="1">
+      <c r="C51" s="57" t="inlineStr">
+        <is>
+          <t>Makine / Emis Noktasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="58" t="inlineStr">
+        <is>
+          <t>Not: Plan olcek/duvar konumlari temsilidir. Gercek fabrika olcum/proje verisine gore izgara satir-sutun sayisi (GRID_COL0..GRID_COLN, GRID_ROW0..GRID_ROWN) ve kolon araligi guncellenmelidir.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="15">
+    <mergeCell ref="A1:T1"/>
+    <mergeCell ref="A44:J44"/>
+    <mergeCell ref="C48:J48"/>
+    <mergeCell ref="V25:Z25"/>
+    <mergeCell ref="J25:N25"/>
+    <mergeCell ref="C46:J46"/>
+    <mergeCell ref="C47:J47"/>
+    <mergeCell ref="C51:J51"/>
+    <mergeCell ref="AH25:AL25"/>
+    <mergeCell ref="A53:T53"/>
+    <mergeCell ref="C50:J50"/>
+    <mergeCell ref="A2:T2"/>
+    <mergeCell ref="C45:J45"/>
+    <mergeCell ref="AU11:AX11"/>
+    <mergeCell ref="C49:J49"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:D27"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>
@@ -2509,420 +5745,420 @@
       <c r="D1" s="2" t="n"/>
     </row>
     <row r="2" ht="28" customHeight="1">
-      <c r="A2" s="41" t="inlineStr">
+      <c r="A2" s="9" t="inlineStr">
         <is>
           <t>Sistemde kullanilan standart spiral/duz dikiş boru capi serisi. Hesap sayfalari bu listeden bir ust standart capi otomatik secer (XLOOKUP, esit-veya-buyuk esleme).</t>
         </is>
       </c>
     </row>
     <row r="4" ht="32" customHeight="1">
-      <c r="A4" s="15" t="inlineStr">
+      <c r="A4" s="4" t="inlineStr">
         <is>
           <t>Sira</t>
         </is>
       </c>
-      <c r="B4" s="15" t="inlineStr">
+      <c r="B4" s="4" t="inlineStr">
         <is>
           <t>Standart Cap (mm)</t>
         </is>
       </c>
-      <c r="C4" s="15" t="inlineStr">
+      <c r="C4" s="4" t="inlineStr">
         <is>
           <t>Kesit Alani (m2)</t>
         </is>
       </c>
-      <c r="D4" s="15" t="inlineStr">
+      <c r="D4" s="4" t="inlineStr">
         <is>
           <t>Tavsiye Edilen Hiz Araligi (m/s)</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="20" t="n">
+      <c r="A5" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="B5" s="42" t="n">
+      <c r="B5" s="10" t="n">
         <v>80</v>
       </c>
-      <c r="C5" s="43">
+      <c r="C5" s="11">
         <f>PI()/4*(B5/1000)^2</f>
         <v/>
       </c>
-      <c r="D5" s="20" t="inlineStr">
+      <c r="D5" s="5" t="inlineStr">
         <is>
           <t>18 - 28 m/s (ahsap tozu tasima)</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="44" t="n">
+      <c r="A6" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="B6" s="45" t="n">
+      <c r="B6" s="12" t="n">
         <v>100</v>
       </c>
-      <c r="C6" s="46">
+      <c r="C6" s="13">
         <f>PI()/4*(B6/1000)^2</f>
         <v/>
       </c>
-      <c r="D6" s="44" t="inlineStr">
+      <c r="D6" s="7" t="inlineStr">
         <is>
           <t>18 - 28 m/s (ahsap tozu tasima)</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="20" t="n">
+      <c r="A7" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="B7" s="42" t="n">
+      <c r="B7" s="10" t="n">
         <v>120</v>
       </c>
-      <c r="C7" s="43">
+      <c r="C7" s="11">
         <f>PI()/4*(B7/1000)^2</f>
         <v/>
       </c>
-      <c r="D7" s="20" t="inlineStr">
+      <c r="D7" s="5" t="inlineStr">
         <is>
           <t>18 - 28 m/s (ahsap tozu tasima)</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="44" t="n">
+      <c r="A8" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="B8" s="45" t="n">
+      <c r="B8" s="12" t="n">
         <v>125</v>
       </c>
-      <c r="C8" s="46">
+      <c r="C8" s="13">
         <f>PI()/4*(B8/1000)^2</f>
         <v/>
       </c>
-      <c r="D8" s="44" t="inlineStr">
+      <c r="D8" s="7" t="inlineStr">
         <is>
           <t>18 - 28 m/s (ahsap tozu tasima)</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="20" t="n">
+      <c r="A9" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="B9" s="42" t="n">
+      <c r="B9" s="10" t="n">
         <v>140</v>
       </c>
-      <c r="C9" s="43">
+      <c r="C9" s="11">
         <f>PI()/4*(B9/1000)^2</f>
         <v/>
       </c>
-      <c r="D9" s="20" t="inlineStr">
+      <c r="D9" s="5" t="inlineStr">
         <is>
           <t>18 - 28 m/s (ahsap tozu tasima)</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="44" t="n">
+      <c r="A10" s="7" t="n">
         <v>6</v>
       </c>
-      <c r="B10" s="45" t="n">
+      <c r="B10" s="12" t="n">
         <v>150</v>
       </c>
-      <c r="C10" s="46">
+      <c r="C10" s="13">
         <f>PI()/4*(B10/1000)^2</f>
         <v/>
       </c>
-      <c r="D10" s="44" t="inlineStr">
+      <c r="D10" s="7" t="inlineStr">
         <is>
           <t>18 - 28 m/s (ahsap tozu tasima)</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="20" t="n">
+      <c r="A11" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="B11" s="42" t="n">
+      <c r="B11" s="10" t="n">
         <v>160</v>
       </c>
-      <c r="C11" s="43">
+      <c r="C11" s="11">
         <f>PI()/4*(B11/1000)^2</f>
         <v/>
       </c>
-      <c r="D11" s="20" t="inlineStr">
+      <c r="D11" s="5" t="inlineStr">
         <is>
           <t>18 - 28 m/s (ahsap tozu tasima)</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="44" t="n">
+      <c r="A12" s="7" t="n">
         <v>8</v>
       </c>
-      <c r="B12" s="45" t="n">
+      <c r="B12" s="12" t="n">
         <v>180</v>
       </c>
-      <c r="C12" s="46">
+      <c r="C12" s="13">
         <f>PI()/4*(B12/1000)^2</f>
         <v/>
       </c>
-      <c r="D12" s="44" t="inlineStr">
+      <c r="D12" s="7" t="inlineStr">
         <is>
           <t>18 - 28 m/s (ahsap tozu tasima)</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="20" t="n">
+      <c r="A13" s="5" t="n">
         <v>9</v>
       </c>
-      <c r="B13" s="42" t="n">
+      <c r="B13" s="10" t="n">
         <v>200</v>
       </c>
-      <c r="C13" s="43">
+      <c r="C13" s="11">
         <f>PI()/4*(B13/1000)^2</f>
         <v/>
       </c>
-      <c r="D13" s="20" t="inlineStr">
+      <c r="D13" s="5" t="inlineStr">
         <is>
           <t>18 - 28 m/s (ahsap tozu tasima)</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="44" t="n">
+      <c r="A14" s="7" t="n">
         <v>10</v>
       </c>
-      <c r="B14" s="45" t="n">
+      <c r="B14" s="12" t="n">
         <v>220</v>
       </c>
-      <c r="C14" s="46">
+      <c r="C14" s="13">
         <f>PI()/4*(B14/1000)^2</f>
         <v/>
       </c>
-      <c r="D14" s="44" t="inlineStr">
+      <c r="D14" s="7" t="inlineStr">
         <is>
           <t>18 - 28 m/s (ahsap tozu tasima)</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="20" t="n">
+      <c r="A15" s="5" t="n">
         <v>11</v>
       </c>
-      <c r="B15" s="42" t="n">
+      <c r="B15" s="10" t="n">
         <v>250</v>
       </c>
-      <c r="C15" s="43">
+      <c r="C15" s="11">
         <f>PI()/4*(B15/1000)^2</f>
         <v/>
       </c>
-      <c r="D15" s="20" t="inlineStr">
+      <c r="D15" s="5" t="inlineStr">
         <is>
           <t>18 - 28 m/s (ahsap tozu tasima)</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="44" t="n">
+      <c r="A16" s="7" t="n">
         <v>12</v>
       </c>
-      <c r="B16" s="45" t="n">
+      <c r="B16" s="12" t="n">
         <v>280</v>
       </c>
-      <c r="C16" s="46">
+      <c r="C16" s="13">
         <f>PI()/4*(B16/1000)^2</f>
         <v/>
       </c>
-      <c r="D16" s="44" t="inlineStr">
+      <c r="D16" s="7" t="inlineStr">
         <is>
           <t>18 - 28 m/s (ahsap tozu tasima)</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="20" t="n">
+      <c r="A17" s="5" t="n">
         <v>13</v>
       </c>
-      <c r="B17" s="42" t="n">
+      <c r="B17" s="10" t="n">
         <v>300</v>
       </c>
-      <c r="C17" s="43">
+      <c r="C17" s="11">
         <f>PI()/4*(B17/1000)^2</f>
         <v/>
       </c>
-      <c r="D17" s="20" t="inlineStr">
+      <c r="D17" s="5" t="inlineStr">
         <is>
           <t>18 - 28 m/s (ahsap tozu tasima)</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="44" t="n">
+      <c r="A18" s="7" t="n">
         <v>14</v>
       </c>
-      <c r="B18" s="45" t="n">
+      <c r="B18" s="12" t="n">
         <v>315</v>
       </c>
-      <c r="C18" s="46">
+      <c r="C18" s="13">
         <f>PI()/4*(B18/1000)^2</f>
         <v/>
       </c>
-      <c r="D18" s="44" t="inlineStr">
+      <c r="D18" s="7" t="inlineStr">
         <is>
           <t>18 - 28 m/s (ahsap tozu tasima)</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="20" t="n">
+      <c r="A19" s="5" t="n">
         <v>15</v>
       </c>
-      <c r="B19" s="42" t="n">
+      <c r="B19" s="10" t="n">
         <v>350</v>
       </c>
-      <c r="C19" s="43">
+      <c r="C19" s="11">
         <f>PI()/4*(B19/1000)^2</f>
         <v/>
       </c>
-      <c r="D19" s="20" t="inlineStr">
+      <c r="D19" s="5" t="inlineStr">
         <is>
           <t>18 - 28 m/s (ahsap tozu tasima)</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="44" t="n">
+      <c r="A20" s="7" t="n">
         <v>16</v>
       </c>
-      <c r="B20" s="45" t="n">
+      <c r="B20" s="12" t="n">
         <v>400</v>
       </c>
-      <c r="C20" s="46">
+      <c r="C20" s="13">
         <f>PI()/4*(B20/1000)^2</f>
         <v/>
       </c>
-      <c r="D20" s="44" t="inlineStr">
+      <c r="D20" s="7" t="inlineStr">
         <is>
           <t>18 - 28 m/s (ahsap tozu tasima)</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="20" t="n">
+      <c r="A21" s="5" t="n">
         <v>17</v>
       </c>
-      <c r="B21" s="42" t="n">
+      <c r="B21" s="10" t="n">
         <v>450</v>
       </c>
-      <c r="C21" s="43">
+      <c r="C21" s="11">
         <f>PI()/4*(B21/1000)^2</f>
         <v/>
       </c>
-      <c r="D21" s="20" t="inlineStr">
+      <c r="D21" s="5" t="inlineStr">
         <is>
           <t>18 - 28 m/s (ahsap tozu tasima)</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="44" t="n">
+      <c r="A22" s="7" t="n">
         <v>18</v>
       </c>
-      <c r="B22" s="45" t="n">
+      <c r="B22" s="12" t="n">
         <v>500</v>
       </c>
-      <c r="C22" s="46">
+      <c r="C22" s="13">
         <f>PI()/4*(B22/1000)^2</f>
         <v/>
       </c>
-      <c r="D22" s="44" t="inlineStr">
+      <c r="D22" s="7" t="inlineStr">
         <is>
           <t>18 - 28 m/s (ahsap tozu tasima)</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="20" t="n">
+      <c r="A23" s="5" t="n">
         <v>19</v>
       </c>
-      <c r="B23" s="42" t="n">
+      <c r="B23" s="10" t="n">
         <v>560</v>
       </c>
-      <c r="C23" s="43">
+      <c r="C23" s="11">
         <f>PI()/4*(B23/1000)^2</f>
         <v/>
       </c>
-      <c r="D23" s="20" t="inlineStr">
+      <c r="D23" s="5" t="inlineStr">
         <is>
           <t>18 - 28 m/s (ahsap tozu tasima)</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="44" t="n">
+      <c r="A24" s="7" t="n">
         <v>20</v>
       </c>
-      <c r="B24" s="45" t="n">
+      <c r="B24" s="12" t="n">
         <v>600</v>
       </c>
-      <c r="C24" s="46">
+      <c r="C24" s="13">
         <f>PI()/4*(B24/1000)^2</f>
         <v/>
       </c>
-      <c r="D24" s="44" t="inlineStr">
+      <c r="D24" s="7" t="inlineStr">
         <is>
           <t>18 - 28 m/s (ahsap tozu tasima)</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="20" t="n">
+      <c r="A25" s="5" t="n">
         <v>21</v>
       </c>
-      <c r="B25" s="42" t="n">
+      <c r="B25" s="10" t="n">
         <v>630</v>
       </c>
-      <c r="C25" s="43">
+      <c r="C25" s="11">
         <f>PI()/4*(B25/1000)^2</f>
         <v/>
       </c>
-      <c r="D25" s="20" t="inlineStr">
+      <c r="D25" s="5" t="inlineStr">
         <is>
           <t>18 - 28 m/s (ahsap tozu tasima)</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="44" t="n">
+      <c r="A26" s="7" t="n">
         <v>22</v>
       </c>
-      <c r="B26" s="45" t="n">
+      <c r="B26" s="12" t="n">
         <v>710</v>
       </c>
-      <c r="C26" s="46">
+      <c r="C26" s="13">
         <f>PI()/4*(B26/1000)^2</f>
         <v/>
       </c>
-      <c r="D26" s="44" t="inlineStr">
+      <c r="D26" s="7" t="inlineStr">
         <is>
           <t>18 - 28 m/s (ahsap tozu tasima)</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="20" t="n">
+      <c r="A27" s="5" t="n">
         <v>23</v>
       </c>
-      <c r="B27" s="42" t="n">
+      <c r="B27" s="10" t="n">
         <v>800</v>
       </c>
-      <c r="C27" s="43">
+      <c r="C27" s="11">
         <f>PI()/4*(B27/1000)^2</f>
         <v/>
       </c>
-      <c r="D27" s="20" t="inlineStr">
+      <c r="D27" s="5" t="inlineStr">
         <is>
           <t>18 - 28 m/s (ahsap tozu tasima)</t>
         </is>
@@ -2937,7 +6173,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2965,179 +6201,179 @@
       <c r="E1" s="2" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="13" t="inlineStr">
+      <c r="A3" s="23" t="inlineStr">
         <is>
           <t>SISTEM GEREKSINIMI</t>
         </is>
       </c>
-      <c r="B3" s="14" t="n"/>
+      <c r="B3" s="24" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="17" t="inlineStr">
+      <c r="A4" s="14" t="inlineStr">
         <is>
           <t>Toplam Hava Debisi (m3/h)</t>
         </is>
       </c>
-      <c r="B4" s="23">
+      <c r="B4" s="19">
         <f>'Borulama Hesaplari'!E4</f>
         <v/>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="17" t="inlineStr">
+      <c r="A5" s="14" t="inlineStr">
         <is>
           <t>Uygun Minimum Filtre Debisi (m3/h)</t>
         </is>
       </c>
-      <c r="B5" s="23">
+      <c r="B5" s="19">
         <f>MIN(_xlfn._xlws.FILTER('Urun Veritabani'!$E$5:$E$44,('Urun Veritabani'!$C$5:$C$44="Filtre")*('Urun Veritabani'!$E$5:$E$44&gt;=B4),999999999))</f>
         <v/>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="17" t="inlineStr">
+      <c r="A6" s="14" t="inlineStr">
         <is>
           <t>Uygun Filtre Bulundu mu?</t>
         </is>
       </c>
-      <c r="B6" s="47">
+      <c r="B6" s="69">
         <f>IF(B5&gt;=999999999,"HAYIR - Veritabanini genisletin","EVET")</f>
         <v/>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="13" t="inlineStr">
+      <c r="A8" s="23" t="inlineStr">
         <is>
           <t>SECILEN FILTRE OZELLIKLERI</t>
         </is>
       </c>
-      <c r="B8" s="14" t="n"/>
+      <c r="B8" s="24" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="17" t="inlineStr">
+      <c r="A9" s="14" t="inlineStr">
         <is>
           <t>Marka</t>
         </is>
       </c>
-      <c r="B9" s="47">
+      <c r="B9" s="69">
         <f>_xlfn.XLOOKUP(1,('Urun Veritabani'!$C$5:$C$44="Filtre")*('Urun Veritabani'!$E$5:$E$44=B5),'Urun Veritabani'!$A$5:$A$44)</f>
         <v/>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="17" t="inlineStr">
+      <c r="A10" s="14" t="inlineStr">
         <is>
           <t>Filtre Modeli (Urun Kodu)</t>
         </is>
       </c>
-      <c r="B10" s="47">
+      <c r="B10" s="69">
         <f>_xlfn.XLOOKUP(1,('Urun Veritabani'!$C$5:$C$44="Filtre")*('Urun Veritabani'!$E$5:$E$44=B5),'Urun Veritabani'!$B$5:$B$44)</f>
         <v/>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="17" t="inlineStr">
+      <c r="A11" s="14" t="inlineStr">
         <is>
           <t>Nominal Debi (m3/h)</t>
         </is>
       </c>
-      <c r="B11" s="23">
+      <c r="B11" s="19">
         <f>B5</f>
         <v/>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="17" t="inlineStr">
+      <c r="A12" s="14" t="inlineStr">
         <is>
           <t>Filtre Alani (m2)</t>
         </is>
       </c>
-      <c r="B12" s="32">
+      <c r="B12" s="30">
         <f>_xlfn.XLOOKUP(1,('Urun Veritabani'!$C$5:$C$44="Filtre")*('Urun Veritabani'!$E$5:$E$44=B5),'Urun Veritabani'!$H$5:$H$44)</f>
         <v/>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="17" t="inlineStr">
+      <c r="A13" s="14" t="inlineStr">
         <is>
           <t>Fan Gucu (kW)</t>
         </is>
       </c>
-      <c r="B13" s="32">
+      <c r="B13" s="30">
         <f>_xlfn.XLOOKUP(1,('Urun Veritabani'!$C$5:$C$44="Filtre")*('Urun Veritabani'!$E$5:$E$44=B5),'Urun Veritabani'!$G$5:$G$44)</f>
         <v/>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="17" t="inlineStr">
+      <c r="A14" s="14" t="inlineStr">
         <is>
           <t>Hava Tanki Hacmi (m3)</t>
         </is>
       </c>
-      <c r="B14" s="32">
+      <c r="B14" s="30">
         <f>_xlfn.XLOOKUP(1,('Urun Veritabani'!$C$5:$C$44="Filtre")*('Urun Veritabani'!$E$5:$E$44=B5),'Urun Veritabani'!$K$5:$K$44)</f>
         <v/>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="17" t="inlineStr">
+      <c r="A15" s="14" t="inlineStr">
         <is>
           <t>Temizlik Sistemi</t>
         </is>
       </c>
-      <c r="B15" s="24">
+      <c r="B15" s="20">
         <f>_xlfn.XLOOKUP(1,('Urun Veritabani'!$C$5:$C$44="Filtre")*('Urun Veritabani'!$E$5:$E$44=B5),'Urun Veritabani'!$L$5:$L$44)</f>
         <v/>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="17" t="inlineStr">
+      <c r="A16" s="14" t="inlineStr">
         <is>
           <t>Aciklama</t>
         </is>
       </c>
-      <c r="B16" s="24">
+      <c r="B16" s="20">
         <f>_xlfn.XLOOKUP(1,('Urun Veritabani'!$C$5:$C$44="Filtre")*('Urun Veritabani'!$E$5:$E$44=B5),'Urun Veritabani'!$M$5:$M$44)</f>
         <v/>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="13" t="inlineStr">
+      <c r="A18" s="23" t="inlineStr">
         <is>
           <t>MUHENDISLIK KONTROLU - FILTRE YUZEY HIZI (Air-to-Cloth Ratio)</t>
         </is>
       </c>
-      <c r="B18" s="14" t="n"/>
+      <c r="B18" s="24" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="17" t="inlineStr">
+      <c r="A19" s="14" t="inlineStr">
         <is>
           <t>Filtre Yuzey Hizi (m/s) = (Debi/3600)/Alan</t>
         </is>
       </c>
-      <c r="B19" s="30">
+      <c r="B19" s="28">
         <f>(B5/3600)/B12</f>
         <v/>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="17" t="inlineStr">
+      <c r="A20" s="14" t="inlineStr">
         <is>
           <t>Kontrol (Tavsiye: 0.020 - 0.045 m/s)</t>
         </is>
       </c>
-      <c r="B20" s="48">
+      <c r="B20" s="70">
         <f>IF(B19&lt;0.02,"Filtre alani fazla buyuk (verimsiz)",IF(B19&gt;0.045,"UYARI: Filtre alani yetersiz olabilir","Uygun"))</f>
         <v/>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="17" t="inlineStr">
+      <c r="A23" s="14" t="inlineStr">
         <is>
           <t>Filtre Basinc Kaybi (Pa) [Fan secimine eklenir]</t>
         </is>
       </c>
-      <c r="B23" s="23">
+      <c r="B23" s="19">
         <f>_xlfn.XLOOKUP(1,('Urun Veritabani'!$C$5:$C$44="Filtre")*('Urun Veritabani'!$E$5:$E$44=B5),'Urun Veritabani'!$F$5:$F$44)</f>
         <v/>
       </c>
@@ -3169,7 +6405,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3197,262 +6433,262 @@
       <c r="E1" s="2" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="13" t="inlineStr">
+      <c r="A3" s="23" t="inlineStr">
         <is>
           <t>SISTEM GEREKSINIMI</t>
         </is>
       </c>
-      <c r="B3" s="14" t="n"/>
+      <c r="B3" s="24" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="17" t="inlineStr">
+      <c r="A4" s="14" t="inlineStr">
         <is>
           <t>Toplam Hava Debisi (m3/h)</t>
         </is>
       </c>
-      <c r="B4" s="23">
+      <c r="B4" s="19">
         <f>'Borulama Hesaplari'!E4</f>
         <v/>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="17" t="inlineStr">
+      <c r="A5" s="14" t="inlineStr">
         <is>
           <t>Borulama Basinc Kaybi (Pa)</t>
         </is>
       </c>
-      <c r="B5" s="23">
+      <c r="B5" s="19">
         <f>'Borulama Hesaplari'!E19</f>
         <v/>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="17" t="inlineStr">
+      <c r="A6" s="14" t="inlineStr">
         <is>
           <t>Filtre Basinc Kaybi (Pa)</t>
         </is>
       </c>
-      <c r="B6" s="23">
+      <c r="B6" s="19">
         <f>'Filtre Secimi'!B23</f>
         <v/>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="17" t="inlineStr">
+      <c r="A7" s="14" t="inlineStr">
         <is>
           <t>TOPLAM SISTEM BASINCI (Fan Secimi Icin) (Pa)</t>
         </is>
       </c>
-      <c r="B7" s="49">
+      <c r="B7" s="71">
         <f>B5+B6</f>
         <v/>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="17" t="inlineStr">
+      <c r="A9" s="14" t="inlineStr">
         <is>
           <t>Uygun Minimum Fan Debisi (m3/h)</t>
         </is>
       </c>
-      <c r="B9" s="23">
+      <c r="B9" s="19">
         <f>MIN(_xlfn._xlws.FILTER('Urun Veritabani'!$E$5:$E$44,('Urun Veritabani'!$C$5:$C$44="Fan")*('Urun Veritabani'!$E$5:$E$44&gt;=B4)*('Urun Veritabani'!$F$5:$F$44&gt;=B7),999999999))</f>
         <v/>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="17" t="inlineStr">
+      <c r="A10" s="14" t="inlineStr">
         <is>
           <t>Uygun Fan Bulundu mu?</t>
         </is>
       </c>
-      <c r="B10" s="47">
+      <c r="B10" s="69">
         <f>IF(B9&gt;=999999999,"HAYIR - Veritabanini genisletin","EVET")</f>
         <v/>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="13" t="inlineStr">
+      <c r="A12" s="23" t="inlineStr">
         <is>
           <t>SECILEN FAN OZELLIKLERI</t>
         </is>
       </c>
-      <c r="B12" s="14" t="n"/>
+      <c r="B12" s="24" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="17" t="inlineStr">
+      <c r="A13" s="14" t="inlineStr">
         <is>
           <t>Marka</t>
         </is>
       </c>
-      <c r="B13" s="47">
+      <c r="B13" s="69">
         <f>_xlfn.XLOOKUP(1,('Urun Veritabani'!$C$5:$C$44="Fan")*('Urun Veritabani'!$E$5:$E$44=B9)*('Urun Veritabani'!$F$5:$F$44&gt;=B7),'Urun Veritabani'!$A$5:$A$44)</f>
         <v/>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="17" t="inlineStr">
+      <c r="A14" s="14" t="inlineStr">
         <is>
           <t>Fan Modeli (Urun Kodu)</t>
         </is>
       </c>
-      <c r="B14" s="47">
+      <c r="B14" s="69">
         <f>_xlfn.XLOOKUP(1,('Urun Veritabani'!$C$5:$C$44="Fan")*('Urun Veritabani'!$E$5:$E$44=B9)*('Urun Veritabani'!$F$5:$F$44&gt;=B7),'Urun Veritabani'!$B$5:$B$44)</f>
         <v/>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="17" t="inlineStr">
+      <c r="A15" s="14" t="inlineStr">
         <is>
           <t>Cap (mm)</t>
         </is>
       </c>
-      <c r="B15" s="23">
+      <c r="B15" s="19">
         <f>_xlfn.XLOOKUP(1,('Urun Veritabani'!$C$5:$C$44="Fan")*('Urun Veritabani'!$E$5:$E$44=B9)*('Urun Veritabani'!$F$5:$F$44&gt;=B7),'Urun Veritabani'!$D$5:$D$44)</f>
         <v/>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="17" t="inlineStr">
+      <c r="A16" s="14" t="inlineStr">
         <is>
           <t>Nominal Debi (m3/h)</t>
         </is>
       </c>
-      <c r="B16" s="23">
+      <c r="B16" s="19">
         <f>B9</f>
         <v/>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="17" t="inlineStr">
+      <c r="A17" s="14" t="inlineStr">
         <is>
           <t>Basinc Kapasitesi (Pa)</t>
         </is>
       </c>
-      <c r="B17" s="23">
+      <c r="B17" s="19">
         <f>_xlfn.XLOOKUP(1,('Urun Veritabani'!$C$5:$C$44="Fan")*('Urun Veritabani'!$E$5:$E$44=B9)*('Urun Veritabani'!$F$5:$F$44&gt;=B7),'Urun Veritabani'!$F$5:$F$44)</f>
         <v/>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="17" t="inlineStr">
+      <c r="A18" s="14" t="inlineStr">
         <is>
           <t>Veritabani Motor Gucu (kW)</t>
         </is>
       </c>
-      <c r="B18" s="32">
+      <c r="B18" s="30">
         <f>_xlfn.XLOOKUP(1,('Urun Veritabani'!$C$5:$C$44="Fan")*('Urun Veritabani'!$E$5:$E$44=B9)*('Urun Veritabani'!$F$5:$F$44&gt;=B7),'Urun Veritabani'!$G$5:$G$44)</f>
         <v/>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="17" t="inlineStr">
+      <c r="A19" s="14" t="inlineStr">
         <is>
           <t>Fan Devri (rpm)</t>
         </is>
       </c>
-      <c r="B19" s="23">
+      <c r="B19" s="19">
         <f>_xlfn.XLOOKUP(1,('Urun Veritabani'!$C$5:$C$44="Fan")*('Urun Veritabani'!$E$5:$E$44=B9)*('Urun Veritabani'!$F$5:$F$44&gt;=B7),'Urun Veritabani'!$I$5:$I$44)</f>
         <v/>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="17" t="inlineStr">
+      <c r="A20" s="14" t="inlineStr">
         <is>
           <t>Fan Verimi (%)</t>
         </is>
       </c>
-      <c r="B20" s="23">
+      <c r="B20" s="19">
         <f>_xlfn.XLOOKUP(1,('Urun Veritabani'!$C$5:$C$44="Fan")*('Urun Veritabani'!$E$5:$E$44=B9)*('Urun Veritabani'!$F$5:$F$44&gt;=B7),'Urun Veritabani'!$J$5:$J$44)</f>
         <v/>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="13" t="inlineStr">
+      <c r="A22" s="23" t="inlineStr">
         <is>
           <t>TEORIK MOTOR GUCU HESABI VE KONTROL</t>
         </is>
       </c>
-      <c r="B22" s="14" t="n"/>
+      <c r="B22" s="24" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="17" t="inlineStr">
+      <c r="A23" s="14" t="inlineStr">
         <is>
           <t>Teorik Motor Gucu (kW) = Q[m3/s] x dP[Pa] / (1000 x Verim)</t>
         </is>
       </c>
-      <c r="B23" s="35">
+      <c r="B23" s="33">
         <f>(B4/3600)*B7/(1000*(B20/100))</f>
         <v/>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="17" t="inlineStr">
+      <c r="A24" s="14" t="inlineStr">
         <is>
           <t>Kontrol (Teorik &lt;= Veritabani Motoru x 1.1)</t>
         </is>
       </c>
-      <c r="B24" s="50">
+      <c r="B24" s="72">
         <f>IF(B23&gt;B18*1.1,"UYARI: Motor gucu yetersiz olabilir","Uygun")</f>
         <v/>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="13" t="inlineStr">
+      <c r="A26" s="23" t="inlineStr">
         <is>
           <t>ENERJI TUKETIMI</t>
         </is>
       </c>
-      <c r="B26" s="14" t="n"/>
+      <c r="B26" s="24" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" s="17" t="inlineStr">
+      <c r="A27" s="14" t="inlineStr">
         <is>
           <t>Sistem Calisma Suresi (saat/gun)</t>
         </is>
       </c>
-      <c r="B27" s="22" t="n">
+      <c r="B27" s="18" t="n">
         <v>8</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="17" t="inlineStr">
+      <c r="A28" s="14" t="inlineStr">
         <is>
           <t>Yillik Calisma Gunu (gun/yil)</t>
         </is>
       </c>
-      <c r="B28" s="22" t="n">
+      <c r="B28" s="18" t="n">
         <v>250</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="17" t="inlineStr">
+      <c r="A29" s="14" t="inlineStr">
         <is>
           <t>Motor Gucu (kW) [Kullanilan]</t>
         </is>
       </c>
-      <c r="B29" s="33">
+      <c r="B29" s="31">
         <f>MAX(B23,B18)</f>
         <v/>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="17" t="inlineStr">
+      <c r="A30" s="14" t="inlineStr">
         <is>
           <t>Enerji Tuketimi (kWh/gun)</t>
         </is>
       </c>
-      <c r="B30" s="32">
+      <c r="B30" s="30">
         <f>B29*B27</f>
         <v/>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="17" t="inlineStr">
+      <c r="A31" s="14" t="inlineStr">
         <is>
           <t>Enerji Tuketimi (kWh/yil)</t>
         </is>
       </c>
-      <c r="B31" s="23">
+      <c r="B31" s="19">
         <f>B30*B28</f>
         <v/>
       </c>
@@ -3485,14 +6721,14 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:M44"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
@@ -3529,1908 +6765,1908 @@
       <c r="M1" s="2" t="n"/>
     </row>
     <row r="2" ht="30" customHeight="1">
-      <c r="A2" s="51" t="inlineStr">
+      <c r="A2" s="3" t="inlineStr">
         <is>
           <t>NOT: Asagidaki teknik degerler (debi, basinc, guc, alan) ilgili marka model serileri esas alinarak muhendislik tahmini olarak olusturulmustur. Kataloglarin genel urun sayfalarinda detayli teknik deger (m3/h, Pa, kW) yayinlanmadigindan, kesin teklif oncesi SMT Europe / Siloma / Saf Teknik yetkili satis/teknik servisinden guncel datasheet degerleri ile bu tablo dogrulanmalidir.</t>
         </is>
       </c>
     </row>
     <row r="4" ht="32" customHeight="1">
-      <c r="A4" s="15" t="inlineStr">
+      <c r="A4" s="4" t="inlineStr">
         <is>
           <t>Marka</t>
         </is>
       </c>
-      <c r="B4" s="15" t="inlineStr">
+      <c r="B4" s="4" t="inlineStr">
         <is>
           <t>Urun Kodu</t>
         </is>
       </c>
-      <c r="C4" s="15" t="inlineStr">
+      <c r="C4" s="4" t="inlineStr">
         <is>
           <t>Urun Tipi</t>
         </is>
       </c>
-      <c r="D4" s="15" t="inlineStr">
+      <c r="D4" s="4" t="inlineStr">
         <is>
           <t>Cap (mm)</t>
         </is>
       </c>
-      <c r="E4" s="15" t="inlineStr">
+      <c r="E4" s="4" t="inlineStr">
         <is>
           <t>Debi (m3/h)</t>
         </is>
       </c>
-      <c r="F4" s="15" t="inlineStr">
+      <c r="F4" s="4" t="inlineStr">
         <is>
           <t>Basinc (Pa)</t>
         </is>
       </c>
-      <c r="G4" s="15" t="inlineStr">
+      <c r="G4" s="4" t="inlineStr">
         <is>
           <t>Motor Gucu (kW)</t>
         </is>
       </c>
-      <c r="H4" s="15" t="inlineStr">
+      <c r="H4" s="4" t="inlineStr">
         <is>
           <t>Filtre Alani (m2)</t>
         </is>
       </c>
-      <c r="I4" s="15" t="inlineStr">
+      <c r="I4" s="4" t="inlineStr">
         <is>
           <t>Fan Devri (rpm)</t>
         </is>
       </c>
-      <c r="J4" s="15" t="inlineStr">
+      <c r="J4" s="4" t="inlineStr">
         <is>
           <t>Fan Verimi (%)</t>
         </is>
       </c>
-      <c r="K4" s="15" t="inlineStr">
+      <c r="K4" s="4" t="inlineStr">
         <is>
           <t>Hava Tanki Hacmi (m3)</t>
         </is>
       </c>
-      <c r="L4" s="15" t="inlineStr">
+      <c r="L4" s="4" t="inlineStr">
         <is>
           <t>Temizlik Sistemi</t>
         </is>
       </c>
-      <c r="M4" s="15" t="inlineStr">
+      <c r="M4" s="4" t="inlineStr">
         <is>
           <t>Aciklama</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="20" t="inlineStr">
+      <c r="A5" s="5" t="inlineStr">
         <is>
           <t>Saf Teknik</t>
         </is>
       </c>
-      <c r="B5" s="20" t="inlineStr">
+      <c r="B5" s="5" t="inlineStr">
         <is>
           <t>SF-312</t>
         </is>
       </c>
-      <c r="C5" s="20" t="inlineStr">
+      <c r="C5" s="5" t="inlineStr">
         <is>
           <t>Filtre</t>
         </is>
       </c>
-      <c r="D5" s="20" t="n"/>
-      <c r="E5" s="52" t="n">
+      <c r="D5" s="5" t="n"/>
+      <c r="E5" s="6" t="n">
         <v>3000</v>
       </c>
-      <c r="F5" s="52" t="n">
+      <c r="F5" s="6" t="n">
         <v>1444</v>
       </c>
-      <c r="G5" s="52" t="n">
+      <c r="G5" s="6" t="n">
         <v>2.2</v>
       </c>
-      <c r="H5" s="52" t="n">
+      <c r="H5" s="6" t="n">
         <v>33.3</v>
       </c>
-      <c r="I5" s="52" t="n"/>
-      <c r="J5" s="52" t="n"/>
-      <c r="K5" s="52" t="n">
+      <c r="I5" s="6" t="n"/>
+      <c r="J5" s="6" t="n"/>
+      <c r="K5" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="L5" s="20" t="inlineStr">
+      <c r="L5" s="5" t="inlineStr">
         <is>
           <t>Mekanik Sarsma</t>
         </is>
       </c>
-      <c r="M5" s="20" t="inlineStr">
+      <c r="M5" s="5" t="inlineStr">
         <is>
           <t>SF-312 torba/kartus filtre unitesi - mekanik sarsma temizlikli</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="44" t="inlineStr">
+      <c r="A6" s="7" t="inlineStr">
         <is>
           <t>Saf Teknik</t>
         </is>
       </c>
-      <c r="B6" s="44" t="inlineStr">
+      <c r="B6" s="7" t="inlineStr">
         <is>
           <t>SF-315</t>
         </is>
       </c>
-      <c r="C6" s="44" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
         <is>
           <t>Filtre</t>
         </is>
       </c>
-      <c r="D6" s="44" t="n"/>
-      <c r="E6" s="53" t="n">
+      <c r="D6" s="7" t="n"/>
+      <c r="E6" s="8" t="n">
         <v>4500</v>
       </c>
-      <c r="F6" s="53" t="n">
+      <c r="F6" s="8" t="n">
         <v>1465</v>
       </c>
-      <c r="G6" s="53" t="n">
+      <c r="G6" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="H6" s="53" t="n">
+      <c r="H6" s="8" t="n">
         <v>50</v>
       </c>
-      <c r="I6" s="53" t="n"/>
-      <c r="J6" s="53" t="n"/>
-      <c r="K6" s="53" t="n">
+      <c r="I6" s="8" t="n"/>
+      <c r="J6" s="8" t="n"/>
+      <c r="K6" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="L6" s="44" t="inlineStr">
+      <c r="L6" s="7" t="inlineStr">
         <is>
           <t>Mekanik Sarsma</t>
         </is>
       </c>
-      <c r="M6" s="44" t="inlineStr">
+      <c r="M6" s="7" t="inlineStr">
         <is>
           <t>SF-315 torba/kartus filtre unitesi - mekanik sarsma temizlikli</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="20" t="inlineStr">
+      <c r="A7" s="5" t="inlineStr">
         <is>
           <t>Saf Teknik</t>
         </is>
       </c>
-      <c r="B7" s="20" t="inlineStr">
+      <c r="B7" s="5" t="inlineStr">
         <is>
           <t>SF-318</t>
         </is>
       </c>
-      <c r="C7" s="20" t="inlineStr">
+      <c r="C7" s="5" t="inlineStr">
         <is>
           <t>Filtre</t>
         </is>
       </c>
-      <c r="D7" s="20" t="n"/>
-      <c r="E7" s="52" t="n">
+      <c r="D7" s="5" t="n"/>
+      <c r="E7" s="6" t="n">
         <v>6000</v>
       </c>
-      <c r="F7" s="52" t="n">
+      <c r="F7" s="6" t="n">
         <v>1487</v>
       </c>
-      <c r="G7" s="52" t="n">
+      <c r="G7" s="6" t="n">
         <v>5.5</v>
       </c>
-      <c r="H7" s="52" t="n">
+      <c r="H7" s="6" t="n">
         <v>66.7</v>
       </c>
-      <c r="I7" s="52" t="n"/>
-      <c r="J7" s="52" t="n"/>
-      <c r="K7" s="52" t="n">
+      <c r="I7" s="6" t="n"/>
+      <c r="J7" s="6" t="n"/>
+      <c r="K7" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="L7" s="20" t="inlineStr">
+      <c r="L7" s="5" t="inlineStr">
         <is>
           <t>Mekanik Sarsma</t>
         </is>
       </c>
-      <c r="M7" s="20" t="inlineStr">
+      <c r="M7" s="5" t="inlineStr">
         <is>
           <t>SF-318 torba/kartus filtre unitesi - mekanik sarsma temizlikli</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="44" t="inlineStr">
+      <c r="A8" s="7" t="inlineStr">
         <is>
           <t>Saf Teknik</t>
         </is>
       </c>
-      <c r="B8" s="44" t="inlineStr">
+      <c r="B8" s="7" t="inlineStr">
         <is>
           <t>SF-321</t>
         </is>
       </c>
-      <c r="C8" s="44" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
         <is>
           <t>Filtre</t>
         </is>
       </c>
-      <c r="D8" s="44" t="n"/>
-      <c r="E8" s="53" t="n">
+      <c r="D8" s="7" t="n"/>
+      <c r="E8" s="8" t="n">
         <v>8000</v>
       </c>
-      <c r="F8" s="53" t="n">
+      <c r="F8" s="8" t="n">
         <v>1516</v>
       </c>
-      <c r="G8" s="53" t="n">
+      <c r="G8" s="8" t="n">
         <v>7.5</v>
       </c>
-      <c r="H8" s="53" t="n">
+      <c r="H8" s="8" t="n">
         <v>88.90000000000001</v>
       </c>
-      <c r="I8" s="53" t="n"/>
-      <c r="J8" s="53" t="n"/>
-      <c r="K8" s="53" t="n">
+      <c r="I8" s="8" t="n"/>
+      <c r="J8" s="8" t="n"/>
+      <c r="K8" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="L8" s="44" t="inlineStr">
+      <c r="L8" s="7" t="inlineStr">
         <is>
           <t>Mekanik Sarsma</t>
         </is>
       </c>
-      <c r="M8" s="44" t="inlineStr">
+      <c r="M8" s="7" t="inlineStr">
         <is>
           <t>SF-321 torba/kartus filtre unitesi - mekanik sarsma temizlikli</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="20" t="inlineStr">
+      <c r="A9" s="5" t="inlineStr">
         <is>
           <t>Saf Teknik</t>
         </is>
       </c>
-      <c r="B9" s="20" t="inlineStr">
+      <c r="B9" s="5" t="inlineStr">
         <is>
           <t>SF-324</t>
         </is>
       </c>
-      <c r="C9" s="20" t="inlineStr">
+      <c r="C9" s="5" t="inlineStr">
         <is>
           <t>Filtre</t>
         </is>
       </c>
-      <c r="D9" s="20" t="n"/>
-      <c r="E9" s="52" t="n">
+      <c r="D9" s="5" t="n"/>
+      <c r="E9" s="6" t="n">
         <v>10000</v>
       </c>
-      <c r="F9" s="52" t="n">
+      <c r="F9" s="6" t="n">
         <v>1545</v>
       </c>
-      <c r="G9" s="52" t="n">
+      <c r="G9" s="6" t="n">
         <v>7.5</v>
       </c>
-      <c r="H9" s="52" t="n">
+      <c r="H9" s="6" t="n">
         <v>111.1</v>
       </c>
-      <c r="I9" s="52" t="n"/>
-      <c r="J9" s="52" t="n"/>
-      <c r="K9" s="52" t="n">
+      <c r="I9" s="6" t="n"/>
+      <c r="J9" s="6" t="n"/>
+      <c r="K9" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="L9" s="20" t="inlineStr">
+      <c r="L9" s="5" t="inlineStr">
         <is>
           <t>Mekanik Sarsma</t>
         </is>
       </c>
-      <c r="M9" s="20" t="inlineStr">
+      <c r="M9" s="5" t="inlineStr">
         <is>
           <t>SF-324 torba/kartus filtre unitesi - mekanik sarsma temizlikli</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="44" t="inlineStr">
+      <c r="A10" s="7" t="inlineStr">
         <is>
           <t>Saf Teknik</t>
         </is>
       </c>
-      <c r="B10" s="44" t="inlineStr">
+      <c r="B10" s="7" t="inlineStr">
         <is>
           <t>KP-12</t>
         </is>
       </c>
-      <c r="C10" s="44" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
         <is>
           <t>Filtre</t>
         </is>
       </c>
-      <c r="D10" s="44" t="n"/>
-      <c r="E10" s="53" t="n">
+      <c r="D10" s="7" t="n"/>
+      <c r="E10" s="8" t="n">
         <v>1200</v>
       </c>
-      <c r="F10" s="53" t="n">
+      <c r="F10" s="8" t="n">
         <v>1417</v>
       </c>
-      <c r="G10" s="53" t="n">
+      <c r="G10" s="8" t="n">
         <v>1.1</v>
       </c>
-      <c r="H10" s="53" t="n">
+      <c r="H10" s="8" t="n">
         <v>13.3</v>
       </c>
-      <c r="I10" s="53" t="n"/>
-      <c r="J10" s="53" t="n"/>
-      <c r="K10" s="53" t="n">
+      <c r="I10" s="8" t="n"/>
+      <c r="J10" s="8" t="n"/>
+      <c r="K10" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="L10" s="44" t="inlineStr">
+      <c r="L10" s="7" t="inlineStr">
         <is>
           <t>Mekanik Sarsma</t>
         </is>
       </c>
-      <c r="M10" s="44" t="inlineStr">
+      <c r="M10" s="7" t="inlineStr">
         <is>
           <t>KP-12 torba/kartus filtre unitesi - mekanik sarsma temizlikli</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="20" t="inlineStr">
+      <c r="A11" s="5" t="inlineStr">
         <is>
           <t>Saf Teknik</t>
         </is>
       </c>
-      <c r="B11" s="20" t="inlineStr">
+      <c r="B11" s="5" t="inlineStr">
         <is>
           <t>KP-20</t>
         </is>
       </c>
-      <c r="C11" s="20" t="inlineStr">
+      <c r="C11" s="5" t="inlineStr">
         <is>
           <t>Filtre</t>
         </is>
       </c>
-      <c r="D11" s="20" t="n"/>
-      <c r="E11" s="52" t="n">
+      <c r="D11" s="5" t="n"/>
+      <c r="E11" s="6" t="n">
         <v>2000</v>
       </c>
-      <c r="F11" s="52" t="n">
+      <c r="F11" s="6" t="n">
         <v>1429</v>
       </c>
-      <c r="G11" s="52" t="n">
+      <c r="G11" s="6" t="n">
         <v>1.5</v>
       </c>
-      <c r="H11" s="52" t="n">
+      <c r="H11" s="6" t="n">
         <v>22.2</v>
       </c>
-      <c r="I11" s="52" t="n"/>
-      <c r="J11" s="52" t="n"/>
-      <c r="K11" s="52" t="n">
+      <c r="I11" s="6" t="n"/>
+      <c r="J11" s="6" t="n"/>
+      <c r="K11" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="L11" s="20" t="inlineStr">
+      <c r="L11" s="5" t="inlineStr">
         <is>
           <t>Mekanik Sarsma</t>
         </is>
       </c>
-      <c r="M11" s="20" t="inlineStr">
+      <c r="M11" s="5" t="inlineStr">
         <is>
           <t>KP-20 torba/kartus filtre unitesi - mekanik sarsma temizlikli</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="44" t="inlineStr">
+      <c r="A12" s="7" t="inlineStr">
         <is>
           <t>Saf Teknik</t>
         </is>
       </c>
-      <c r="B12" s="44" t="inlineStr">
+      <c r="B12" s="7" t="inlineStr">
         <is>
           <t>KP-30</t>
         </is>
       </c>
-      <c r="C12" s="44" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
         <is>
           <t>Filtre</t>
         </is>
       </c>
-      <c r="D12" s="44" t="n"/>
-      <c r="E12" s="53" t="n">
+      <c r="D12" s="7" t="n"/>
+      <c r="E12" s="8" t="n">
         <v>3000</v>
       </c>
-      <c r="F12" s="53" t="n">
+      <c r="F12" s="8" t="n">
         <v>1444</v>
       </c>
-      <c r="G12" s="53" t="n">
+      <c r="G12" s="8" t="n">
         <v>2.2</v>
       </c>
-      <c r="H12" s="53" t="n">
+      <c r="H12" s="8" t="n">
         <v>33.3</v>
       </c>
-      <c r="I12" s="53" t="n"/>
-      <c r="J12" s="53" t="n"/>
-      <c r="K12" s="53" t="n">
+      <c r="I12" s="8" t="n"/>
+      <c r="J12" s="8" t="n"/>
+      <c r="K12" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="L12" s="44" t="inlineStr">
+      <c r="L12" s="7" t="inlineStr">
         <is>
           <t>Mekanik Sarsma</t>
         </is>
       </c>
-      <c r="M12" s="44" t="inlineStr">
+      <c r="M12" s="7" t="inlineStr">
         <is>
           <t>KP-30 torba/kartus filtre unitesi - mekanik sarsma temizlikli</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="20" t="inlineStr">
+      <c r="A13" s="5" t="inlineStr">
         <is>
           <t>Saf Teknik</t>
         </is>
       </c>
-      <c r="B13" s="20" t="inlineStr">
+      <c r="B13" s="5" t="inlineStr">
         <is>
           <t>KP-40</t>
         </is>
       </c>
-      <c r="C13" s="20" t="inlineStr">
+      <c r="C13" s="5" t="inlineStr">
         <is>
           <t>Filtre</t>
         </is>
       </c>
-      <c r="D13" s="20" t="n"/>
-      <c r="E13" s="52" t="n">
+      <c r="D13" s="5" t="n"/>
+      <c r="E13" s="6" t="n">
         <v>4000</v>
       </c>
-      <c r="F13" s="52" t="n">
+      <c r="F13" s="6" t="n">
         <v>1458</v>
       </c>
-      <c r="G13" s="52" t="n">
+      <c r="G13" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="H13" s="52" t="n">
+      <c r="H13" s="6" t="n">
         <v>44.4</v>
       </c>
-      <c r="I13" s="52" t="n"/>
-      <c r="J13" s="52" t="n"/>
-      <c r="K13" s="52" t="n">
+      <c r="I13" s="6" t="n"/>
+      <c r="J13" s="6" t="n"/>
+      <c r="K13" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="L13" s="20" t="inlineStr">
+      <c r="L13" s="5" t="inlineStr">
         <is>
           <t>Mekanik Sarsma</t>
         </is>
       </c>
-      <c r="M13" s="20" t="inlineStr">
+      <c r="M13" s="5" t="inlineStr">
         <is>
           <t>KP-40 torba/kartus filtre unitesi - mekanik sarsma temizlikli</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="44" t="inlineStr">
+      <c r="A14" s="7" t="inlineStr">
         <is>
           <t>Saf Teknik</t>
         </is>
       </c>
-      <c r="B14" s="44" t="inlineStr">
+      <c r="B14" s="7" t="inlineStr">
         <is>
           <t>KP-50</t>
         </is>
       </c>
-      <c r="C14" s="44" t="inlineStr">
+      <c r="C14" s="7" t="inlineStr">
         <is>
           <t>Filtre</t>
         </is>
       </c>
-      <c r="D14" s="44" t="n"/>
-      <c r="E14" s="53" t="n">
+      <c r="D14" s="7" t="n"/>
+      <c r="E14" s="8" t="n">
         <v>5000</v>
       </c>
-      <c r="F14" s="53" t="n">
+      <c r="F14" s="8" t="n">
         <v>1473</v>
       </c>
-      <c r="G14" s="53" t="n">
+      <c r="G14" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="H14" s="53" t="n">
+      <c r="H14" s="8" t="n">
         <v>55.6</v>
       </c>
-      <c r="I14" s="53" t="n"/>
-      <c r="J14" s="53" t="n"/>
-      <c r="K14" s="53" t="n">
+      <c r="I14" s="8" t="n"/>
+      <c r="J14" s="8" t="n"/>
+      <c r="K14" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="L14" s="44" t="inlineStr">
+      <c r="L14" s="7" t="inlineStr">
         <is>
           <t>Mekanik Sarsma</t>
         </is>
       </c>
-      <c r="M14" s="44" t="inlineStr">
+      <c r="M14" s="7" t="inlineStr">
         <is>
           <t>KP-50 torba/kartus filtre unitesi - mekanik sarsma temizlikli</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="20" t="inlineStr">
+      <c r="A15" s="5" t="inlineStr">
         <is>
           <t>Saf Teknik</t>
         </is>
       </c>
-      <c r="B15" s="20" t="inlineStr">
+      <c r="B15" s="5" t="inlineStr">
         <is>
           <t>KP-60</t>
         </is>
       </c>
-      <c r="C15" s="20" t="inlineStr">
+      <c r="C15" s="5" t="inlineStr">
         <is>
           <t>Filtre</t>
         </is>
       </c>
-      <c r="D15" s="20" t="n"/>
-      <c r="E15" s="52" t="n">
+      <c r="D15" s="5" t="n"/>
+      <c r="E15" s="6" t="n">
         <v>6000</v>
       </c>
-      <c r="F15" s="52" t="n">
+      <c r="F15" s="6" t="n">
         <v>1487</v>
       </c>
-      <c r="G15" s="52" t="n">
+      <c r="G15" s="6" t="n">
         <v>5.5</v>
       </c>
-      <c r="H15" s="52" t="n">
+      <c r="H15" s="6" t="n">
         <v>66.7</v>
       </c>
-      <c r="I15" s="52" t="n"/>
-      <c r="J15" s="52" t="n"/>
-      <c r="K15" s="52" t="n">
+      <c r="I15" s="6" t="n"/>
+      <c r="J15" s="6" t="n"/>
+      <c r="K15" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="L15" s="20" t="inlineStr">
+      <c r="L15" s="5" t="inlineStr">
         <is>
           <t>Mekanik Sarsma</t>
         </is>
       </c>
-      <c r="M15" s="20" t="inlineStr">
+      <c r="M15" s="5" t="inlineStr">
         <is>
           <t>KP-60 torba/kartus filtre unitesi - mekanik sarsma temizlikli</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="44" t="inlineStr">
+      <c r="A16" s="7" t="inlineStr">
         <is>
           <t>Saf Teknik</t>
         </is>
       </c>
-      <c r="B16" s="44" t="inlineStr">
+      <c r="B16" s="7" t="inlineStr">
         <is>
           <t>BB-1521</t>
         </is>
       </c>
-      <c r="C16" s="44" t="inlineStr">
+      <c r="C16" s="7" t="inlineStr">
         <is>
           <t>Filtre</t>
         </is>
       </c>
-      <c r="D16" s="44" t="n"/>
-      <c r="E16" s="53" t="n">
+      <c r="D16" s="7" t="n"/>
+      <c r="E16" s="8" t="n">
         <v>15000</v>
       </c>
-      <c r="F16" s="53" t="n">
+      <c r="F16" s="8" t="n">
         <v>1618</v>
       </c>
-      <c r="G16" s="53" t="n">
+      <c r="G16" s="8" t="n">
         <v>15</v>
       </c>
-      <c r="H16" s="53" t="n">
+      <c r="H16" s="8" t="n">
         <v>109.6</v>
       </c>
-      <c r="I16" s="53" t="n"/>
-      <c r="J16" s="53" t="n"/>
-      <c r="K16" s="53" t="n">
+      <c r="I16" s="8" t="n"/>
+      <c r="J16" s="8" t="n"/>
+      <c r="K16" s="8" t="n">
         <v>0.7</v>
       </c>
-      <c r="L16" s="44" t="inlineStr">
+      <c r="L16" s="7" t="inlineStr">
         <is>
           <t>Jet Pulse (Basincli Hava)</t>
         </is>
       </c>
-      <c r="M16" s="44" t="inlineStr">
+      <c r="M16" s="7" t="inlineStr">
         <is>
           <t>BB-1521 torba/kartus filtre unitesi - jet pulse (basincli hava) temizlikli</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="20" t="inlineStr">
+      <c r="A17" s="5" t="inlineStr">
         <is>
           <t>Saf Teknik</t>
         </is>
       </c>
-      <c r="B17" s="20" t="inlineStr">
+      <c r="B17" s="5" t="inlineStr">
         <is>
           <t>BB-1524</t>
         </is>
       </c>
-      <c r="C17" s="20" t="inlineStr">
+      <c r="C17" s="5" t="inlineStr">
         <is>
           <t>Filtre</t>
         </is>
       </c>
-      <c r="D17" s="20" t="n"/>
-      <c r="E17" s="52" t="n">
+      <c r="D17" s="5" t="n"/>
+      <c r="E17" s="6" t="n">
         <v>20000</v>
       </c>
-      <c r="F17" s="52" t="n">
+      <c r="F17" s="6" t="n">
         <v>1691</v>
       </c>
-      <c r="G17" s="52" t="n">
+      <c r="G17" s="6" t="n">
         <v>18.5</v>
       </c>
-      <c r="H17" s="52" t="n">
+      <c r="H17" s="6" t="n">
         <v>146.2</v>
       </c>
-      <c r="I17" s="52" t="n"/>
-      <c r="J17" s="52" t="n"/>
-      <c r="K17" s="52" t="n">
+      <c r="I17" s="6" t="n"/>
+      <c r="J17" s="6" t="n"/>
+      <c r="K17" s="6" t="n">
         <v>0.8</v>
       </c>
-      <c r="L17" s="20" t="inlineStr">
+      <c r="L17" s="5" t="inlineStr">
         <is>
           <t>Jet Pulse (Basincli Hava)</t>
         </is>
       </c>
-      <c r="M17" s="20" t="inlineStr">
+      <c r="M17" s="5" t="inlineStr">
         <is>
           <t>BB-1524 torba/kartus filtre unitesi - jet pulse (basincli hava) temizlikli</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="44" t="inlineStr">
+      <c r="A18" s="7" t="inlineStr">
         <is>
           <t>Saf Teknik</t>
         </is>
       </c>
-      <c r="B18" s="44" t="inlineStr">
+      <c r="B18" s="7" t="inlineStr">
         <is>
           <t>BB-1526</t>
         </is>
       </c>
-      <c r="C18" s="44" t="inlineStr">
+      <c r="C18" s="7" t="inlineStr">
         <is>
           <t>Filtre</t>
         </is>
       </c>
-      <c r="D18" s="44" t="n"/>
-      <c r="E18" s="53" t="n">
+      <c r="D18" s="7" t="n"/>
+      <c r="E18" s="8" t="n">
         <v>26000</v>
       </c>
-      <c r="F18" s="53" t="n">
+      <c r="F18" s="8" t="n">
         <v>1778</v>
       </c>
-      <c r="G18" s="53" t="n">
+      <c r="G18" s="8" t="n">
         <v>22</v>
       </c>
-      <c r="H18" s="53" t="n">
+      <c r="H18" s="8" t="n">
         <v>190.1</v>
       </c>
-      <c r="I18" s="53" t="n"/>
-      <c r="J18" s="53" t="n"/>
-      <c r="K18" s="53" t="n">
+      <c r="I18" s="8" t="n"/>
+      <c r="J18" s="8" t="n"/>
+      <c r="K18" s="8" t="n">
         <v>0.9</v>
       </c>
-      <c r="L18" s="44" t="inlineStr">
+      <c r="L18" s="7" t="inlineStr">
         <is>
           <t>Jet Pulse (Basincli Hava)</t>
         </is>
       </c>
-      <c r="M18" s="44" t="inlineStr">
+      <c r="M18" s="7" t="inlineStr">
         <is>
           <t>BB-1526 torba/kartus filtre unitesi - jet pulse (basincli hava) temizlikli</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="20" t="inlineStr">
+      <c r="A19" s="5" t="inlineStr">
         <is>
           <t>Siloma</t>
         </is>
       </c>
-      <c r="B19" s="20" t="inlineStr">
+      <c r="B19" s="5" t="inlineStr">
         <is>
           <t>SPE-30000</t>
         </is>
       </c>
-      <c r="C19" s="20" t="inlineStr">
+      <c r="C19" s="5" t="inlineStr">
         <is>
           <t>Filtre</t>
         </is>
       </c>
-      <c r="D19" s="20" t="n"/>
-      <c r="E19" s="52" t="n">
+      <c r="D19" s="5" t="n"/>
+      <c r="E19" s="6" t="n">
         <v>30000</v>
       </c>
-      <c r="F19" s="52" t="n">
+      <c r="F19" s="6" t="n">
         <v>1836</v>
       </c>
-      <c r="G19" s="52" t="n">
+      <c r="G19" s="6" t="n">
         <v>30</v>
       </c>
-      <c r="H19" s="52" t="n">
+      <c r="H19" s="6" t="n">
         <v>219.3</v>
       </c>
-      <c r="I19" s="52" t="n"/>
-      <c r="J19" s="52" t="n"/>
-      <c r="K19" s="52" t="n">
+      <c r="I19" s="6" t="n"/>
+      <c r="J19" s="6" t="n"/>
+      <c r="K19" s="6" t="n">
         <v>1.1</v>
       </c>
-      <c r="L19" s="20" t="inlineStr">
+      <c r="L19" s="5" t="inlineStr">
         <is>
           <t>Jet Pulse (Basincli Hava)</t>
         </is>
       </c>
-      <c r="M19" s="20" t="inlineStr">
+      <c r="M19" s="5" t="inlineStr">
         <is>
           <t>SPE-30000 torba/kartus filtre unitesi - jet pulse (basincli hava) temizlikli</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="44" t="inlineStr">
+      <c r="A20" s="7" t="inlineStr">
         <is>
           <t>Siloma</t>
         </is>
       </c>
-      <c r="B20" s="44" t="inlineStr">
+      <c r="B20" s="7" t="inlineStr">
         <is>
           <t>SPE-40000</t>
         </is>
       </c>
-      <c r="C20" s="44" t="inlineStr">
+      <c r="C20" s="7" t="inlineStr">
         <is>
           <t>Filtre</t>
         </is>
       </c>
-      <c r="D20" s="44" t="n"/>
-      <c r="E20" s="53" t="n">
+      <c r="D20" s="7" t="n"/>
+      <c r="E20" s="8" t="n">
         <v>40000</v>
       </c>
-      <c r="F20" s="53" t="n">
+      <c r="F20" s="8" t="n">
         <v>1982</v>
       </c>
-      <c r="G20" s="53" t="n">
+      <c r="G20" s="8" t="n">
         <v>37</v>
       </c>
-      <c r="H20" s="53" t="n">
+      <c r="H20" s="8" t="n">
         <v>292.4</v>
       </c>
-      <c r="I20" s="53" t="n"/>
-      <c r="J20" s="53" t="n"/>
-      <c r="K20" s="53" t="n">
+      <c r="I20" s="8" t="n"/>
+      <c r="J20" s="8" t="n"/>
+      <c r="K20" s="8" t="n">
         <v>1.3</v>
       </c>
-      <c r="L20" s="44" t="inlineStr">
+      <c r="L20" s="7" t="inlineStr">
         <is>
           <t>Jet Pulse (Basincli Hava)</t>
         </is>
       </c>
-      <c r="M20" s="44" t="inlineStr">
+      <c r="M20" s="7" t="inlineStr">
         <is>
           <t>SPE-40000 torba/kartus filtre unitesi - jet pulse (basincli hava) temizlikli</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="20" t="inlineStr">
+      <c r="A21" s="5" t="inlineStr">
         <is>
           <t>Siloma</t>
         </is>
       </c>
-      <c r="B21" s="20" t="inlineStr">
+      <c r="B21" s="5" t="inlineStr">
         <is>
           <t>SPE-55000</t>
         </is>
       </c>
-      <c r="C21" s="20" t="inlineStr">
+      <c r="C21" s="5" t="inlineStr">
         <is>
           <t>Filtre</t>
         </is>
       </c>
-      <c r="D21" s="20" t="n"/>
-      <c r="E21" s="52" t="n">
+      <c r="D21" s="5" t="n"/>
+      <c r="E21" s="6" t="n">
         <v>55000</v>
       </c>
-      <c r="F21" s="52" t="n">
+      <c r="F21" s="6" t="n">
         <v>2200</v>
       </c>
-      <c r="G21" s="52" t="n">
+      <c r="G21" s="6" t="n">
         <v>75</v>
       </c>
-      <c r="H21" s="52" t="n">
+      <c r="H21" s="6" t="n">
         <v>402</v>
       </c>
-      <c r="I21" s="52" t="n"/>
-      <c r="J21" s="52" t="n"/>
-      <c r="K21" s="52" t="n">
+      <c r="I21" s="6" t="n"/>
+      <c r="J21" s="6" t="n"/>
+      <c r="K21" s="6" t="n">
         <v>1.7</v>
       </c>
-      <c r="L21" s="20" t="inlineStr">
+      <c r="L21" s="5" t="inlineStr">
         <is>
           <t>Jet Pulse (Basincli Hava)</t>
         </is>
       </c>
-      <c r="M21" s="20" t="inlineStr">
+      <c r="M21" s="5" t="inlineStr">
         <is>
           <t>SPE-55000 torba/kartus filtre unitesi - jet pulse (basincli hava) temizlikli</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="44" t="inlineStr">
+      <c r="A22" s="7" t="inlineStr">
         <is>
           <t>SMT Europe</t>
         </is>
       </c>
-      <c r="B22" s="44" t="inlineStr">
+      <c r="B22" s="7" t="inlineStr">
         <is>
           <t>SNF-10</t>
         </is>
       </c>
-      <c r="C22" s="44" t="inlineStr">
+      <c r="C22" s="7" t="inlineStr">
         <is>
           <t>Filtre</t>
         </is>
       </c>
-      <c r="D22" s="44" t="n"/>
-      <c r="E22" s="53" t="n">
+      <c r="D22" s="7" t="n"/>
+      <c r="E22" s="8" t="n">
         <v>4000</v>
       </c>
-      <c r="F22" s="53" t="n">
+      <c r="F22" s="8" t="n">
         <v>1458</v>
       </c>
-      <c r="G22" s="53" t="n">
+      <c r="G22" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="H22" s="53" t="n">
+      <c r="H22" s="8" t="n">
         <v>37</v>
       </c>
-      <c r="I22" s="53" t="n"/>
-      <c r="J22" s="53" t="n"/>
-      <c r="K22" s="53" t="n">
+      <c r="I22" s="8" t="n"/>
+      <c r="J22" s="8" t="n"/>
+      <c r="K22" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="L22" s="44" t="inlineStr">
+      <c r="L22" s="7" t="inlineStr">
         <is>
           <t>Titresimli (Vibrasyon)</t>
         </is>
       </c>
-      <c r="M22" s="44" t="inlineStr">
+      <c r="M22" s="7" t="inlineStr">
         <is>
           <t>SNF-10 torba/kartus filtre unitesi - titresimli (vibrasyon) temizlikli</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="20" t="inlineStr">
+      <c r="A23" s="5" t="inlineStr">
         <is>
           <t>SMT Europe</t>
         </is>
       </c>
-      <c r="B23" s="20" t="inlineStr">
+      <c r="B23" s="5" t="inlineStr">
         <is>
           <t>MS-15</t>
         </is>
       </c>
-      <c r="C23" s="20" t="inlineStr">
+      <c r="C23" s="5" t="inlineStr">
         <is>
           <t>Filtre</t>
         </is>
       </c>
-      <c r="D23" s="20" t="n"/>
-      <c r="E23" s="52" t="n">
+      <c r="D23" s="5" t="n"/>
+      <c r="E23" s="6" t="n">
         <v>5000</v>
       </c>
-      <c r="F23" s="52" t="n">
+      <c r="F23" s="6" t="n">
         <v>1473</v>
       </c>
-      <c r="G23" s="52" t="n">
+      <c r="G23" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="H23" s="52" t="n">
+      <c r="H23" s="6" t="n">
         <v>46.3</v>
       </c>
-      <c r="I23" s="52" t="n"/>
-      <c r="J23" s="52" t="n"/>
-      <c r="K23" s="52" t="n">
+      <c r="I23" s="6" t="n"/>
+      <c r="J23" s="6" t="n"/>
+      <c r="K23" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="L23" s="20" t="inlineStr">
+      <c r="L23" s="5" t="inlineStr">
         <is>
           <t>Titresimli (Vibrasyon)</t>
         </is>
       </c>
-      <c r="M23" s="20" t="inlineStr">
+      <c r="M23" s="5" t="inlineStr">
         <is>
           <t>MS-15 torba/kartus filtre unitesi - titresimli (vibrasyon) temizlikli</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="44" t="inlineStr">
+      <c r="A24" s="7" t="inlineStr">
         <is>
           <t>SMT Europe</t>
         </is>
       </c>
-      <c r="B24" s="44" t="inlineStr">
+      <c r="B24" s="7" t="inlineStr">
         <is>
           <t>MS-25</t>
         </is>
       </c>
-      <c r="C24" s="44" t="inlineStr">
+      <c r="C24" s="7" t="inlineStr">
         <is>
           <t>Filtre</t>
         </is>
       </c>
-      <c r="D24" s="44" t="n"/>
-      <c r="E24" s="53" t="n">
+      <c r="D24" s="7" t="n"/>
+      <c r="E24" s="8" t="n">
         <v>8000</v>
       </c>
-      <c r="F24" s="53" t="n">
+      <c r="F24" s="8" t="n">
         <v>1516</v>
       </c>
-      <c r="G24" s="53" t="n">
+      <c r="G24" s="8" t="n">
         <v>7.5</v>
       </c>
-      <c r="H24" s="53" t="n">
+      <c r="H24" s="8" t="n">
         <v>74.09999999999999</v>
       </c>
-      <c r="I24" s="53" t="n"/>
-      <c r="J24" s="53" t="n"/>
-      <c r="K24" s="53" t="n">
+      <c r="I24" s="8" t="n"/>
+      <c r="J24" s="8" t="n"/>
+      <c r="K24" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="L24" s="44" t="inlineStr">
+      <c r="L24" s="7" t="inlineStr">
         <is>
           <t>Titresimli (Vibrasyon)</t>
         </is>
       </c>
-      <c r="M24" s="44" t="inlineStr">
+      <c r="M24" s="7" t="inlineStr">
         <is>
           <t>MS-25 torba/kartus filtre unitesi - titresimli (vibrasyon) temizlikli</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="20" t="inlineStr">
+      <c r="A25" s="5" t="inlineStr">
         <is>
           <t>SMT Europe</t>
         </is>
       </c>
-      <c r="B25" s="20" t="inlineStr">
+      <c r="B25" s="5" t="inlineStr">
         <is>
           <t>MSP-20</t>
         </is>
       </c>
-      <c r="C25" s="20" t="inlineStr">
+      <c r="C25" s="5" t="inlineStr">
         <is>
           <t>Filtre</t>
         </is>
       </c>
-      <c r="D25" s="20" t="n"/>
-      <c r="E25" s="52" t="n">
+      <c r="D25" s="5" t="n"/>
+      <c r="E25" s="6" t="n">
         <v>7000</v>
       </c>
-      <c r="F25" s="52" t="n">
+      <c r="F25" s="6" t="n">
         <v>1502</v>
       </c>
-      <c r="G25" s="52" t="n">
+      <c r="G25" s="6" t="n">
         <v>5.5</v>
       </c>
-      <c r="H25" s="52" t="n">
+      <c r="H25" s="6" t="n">
         <v>51.2</v>
       </c>
-      <c r="I25" s="52" t="n"/>
-      <c r="J25" s="52" t="n"/>
-      <c r="K25" s="52" t="n">
+      <c r="I25" s="6" t="n"/>
+      <c r="J25" s="6" t="n"/>
+      <c r="K25" s="6" t="n">
         <v>0.5</v>
       </c>
-      <c r="L25" s="20" t="inlineStr">
+      <c r="L25" s="5" t="inlineStr">
         <is>
           <t>Jet Pulse (Basincli Hava)</t>
         </is>
       </c>
-      <c r="M25" s="20" t="inlineStr">
+      <c r="M25" s="5" t="inlineStr">
         <is>
           <t>MSP-20 torba/kartus filtre unitesi - jet pulse (basincli hava) temizlikli</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="44" t="inlineStr">
+      <c r="A26" s="7" t="inlineStr">
         <is>
           <t>SMT Europe</t>
         </is>
       </c>
-      <c r="B26" s="44" t="inlineStr">
+      <c r="B26" s="7" t="inlineStr">
         <is>
           <t>MSP-35</t>
         </is>
       </c>
-      <c r="C26" s="44" t="inlineStr">
+      <c r="C26" s="7" t="inlineStr">
         <is>
           <t>Filtre</t>
         </is>
       </c>
-      <c r="D26" s="44" t="n"/>
-      <c r="E26" s="53" t="n">
+      <c r="D26" s="7" t="n"/>
+      <c r="E26" s="8" t="n">
         <v>12000</v>
       </c>
-      <c r="F26" s="53" t="n">
+      <c r="F26" s="8" t="n">
         <v>1575</v>
       </c>
-      <c r="G26" s="53" t="n">
+      <c r="G26" s="8" t="n">
         <v>11</v>
       </c>
-      <c r="H26" s="53" t="n">
+      <c r="H26" s="8" t="n">
         <v>87.7</v>
       </c>
-      <c r="I26" s="53" t="n"/>
-      <c r="J26" s="53" t="n"/>
-      <c r="K26" s="53" t="n">
+      <c r="I26" s="8" t="n"/>
+      <c r="J26" s="8" t="n"/>
+      <c r="K26" s="8" t="n">
         <v>0.6</v>
       </c>
-      <c r="L26" s="44" t="inlineStr">
+      <c r="L26" s="7" t="inlineStr">
         <is>
           <t>Jet Pulse (Basincli Hava)</t>
         </is>
       </c>
-      <c r="M26" s="44" t="inlineStr">
+      <c r="M26" s="7" t="inlineStr">
         <is>
           <t>MSP-35 torba/kartus filtre unitesi - jet pulse (basincli hava) temizlikli</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="20" t="inlineStr">
+      <c r="A27" s="5" t="inlineStr">
         <is>
           <t>SMT Europe</t>
         </is>
       </c>
-      <c r="B27" s="20" t="inlineStr">
+      <c r="B27" s="5" t="inlineStr">
         <is>
           <t>SWF-30</t>
         </is>
       </c>
-      <c r="C27" s="20" t="inlineStr">
+      <c r="C27" s="5" t="inlineStr">
         <is>
           <t>Filtre</t>
         </is>
       </c>
-      <c r="D27" s="20" t="n"/>
-      <c r="E27" s="52" t="n">
+      <c r="D27" s="5" t="n"/>
+      <c r="E27" s="6" t="n">
         <v>10000</v>
       </c>
-      <c r="F27" s="52" t="n">
+      <c r="F27" s="6" t="n">
         <v>1545</v>
       </c>
-      <c r="G27" s="52" t="n">
+      <c r="G27" s="6" t="n">
         <v>7.5</v>
       </c>
-      <c r="H27" s="52" t="n">
+      <c r="H27" s="6" t="n">
         <v>73.09999999999999</v>
       </c>
-      <c r="I27" s="52" t="n"/>
-      <c r="J27" s="52" t="n"/>
-      <c r="K27" s="52" t="n">
+      <c r="I27" s="6" t="n"/>
+      <c r="J27" s="6" t="n"/>
+      <c r="K27" s="6" t="n">
         <v>0.6</v>
       </c>
-      <c r="L27" s="20" t="inlineStr">
+      <c r="L27" s="5" t="inlineStr">
         <is>
           <t>Jet Pulse (Basincli Hava)</t>
         </is>
       </c>
-      <c r="M27" s="20" t="inlineStr">
+      <c r="M27" s="5" t="inlineStr">
         <is>
           <t>SWF-30 torba/kartus filtre unitesi - jet pulse (basincli hava) temizlikli</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="44" t="inlineStr">
+      <c r="A28" s="7" t="inlineStr">
         <is>
           <t>Saf Teknik</t>
         </is>
       </c>
-      <c r="B28" s="44" t="inlineStr">
+      <c r="B28" s="7" t="inlineStr">
         <is>
           <t>SF-213</t>
         </is>
       </c>
-      <c r="C28" s="44" t="inlineStr">
+      <c r="C28" s="7" t="inlineStr">
         <is>
           <t>Fan</t>
         </is>
       </c>
-      <c r="D28" s="44" t="n">
+      <c r="D28" s="7" t="n">
         <v>190</v>
       </c>
-      <c r="E28" s="53" t="n">
+      <c r="E28" s="8" t="n">
         <v>2000</v>
       </c>
-      <c r="F28" s="53" t="n">
+      <c r="F28" s="8" t="n">
         <v>1551</v>
       </c>
-      <c r="G28" s="53" t="n">
+      <c r="G28" s="8" t="n">
         <v>1.5</v>
       </c>
-      <c r="H28" s="53" t="n"/>
-      <c r="I28" s="53" t="n">
+      <c r="H28" s="8" t="n"/>
+      <c r="I28" s="8" t="n">
         <v>2900</v>
       </c>
-      <c r="J28" s="53" t="n">
+      <c r="J28" s="8" t="n">
         <v>66</v>
       </c>
-      <c r="K28" s="53" t="n"/>
-      <c r="L28" s="44" t="inlineStr">
+      <c r="K28" s="8" t="n"/>
+      <c r="L28" s="7" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="M28" s="44" t="inlineStr">
+      <c r="M28" s="7" t="inlineStr">
         <is>
           <t>SF-213 radyal (santrifuj) transfer fani</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="20" t="inlineStr">
+      <c r="A29" s="5" t="inlineStr">
         <is>
           <t>Saf Teknik</t>
         </is>
       </c>
-      <c r="B29" s="20" t="inlineStr">
+      <c r="B29" s="5" t="inlineStr">
         <is>
           <t>SF-214</t>
         </is>
       </c>
-      <c r="C29" s="20" t="inlineStr">
+      <c r="C29" s="5" t="inlineStr">
         <is>
           <t>Fan</t>
         </is>
       </c>
-      <c r="D29" s="20" t="n">
+      <c r="D29" s="5" t="n">
         <v>230</v>
       </c>
-      <c r="E29" s="52" t="n">
+      <c r="E29" s="6" t="n">
         <v>3000</v>
       </c>
-      <c r="F29" s="52" t="n">
+      <c r="F29" s="6" t="n">
         <v>1577</v>
       </c>
-      <c r="G29" s="52" t="n">
+      <c r="G29" s="6" t="n">
         <v>2.2</v>
       </c>
-      <c r="H29" s="52" t="n"/>
-      <c r="I29" s="52" t="n">
+      <c r="H29" s="6" t="n"/>
+      <c r="I29" s="6" t="n">
         <v>2900</v>
       </c>
-      <c r="J29" s="52" t="n">
+      <c r="J29" s="6" t="n">
         <v>66</v>
       </c>
-      <c r="K29" s="52" t="n"/>
-      <c r="L29" s="20" t="inlineStr">
+      <c r="K29" s="6" t="n"/>
+      <c r="L29" s="5" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="M29" s="20" t="inlineStr">
+      <c r="M29" s="5" t="inlineStr">
         <is>
           <t>SF-214 radyal (santrifuj) transfer fani</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="44" t="inlineStr">
+      <c r="A30" s="7" t="inlineStr">
         <is>
           <t>Saf Teknik</t>
         </is>
       </c>
-      <c r="B30" s="44" t="inlineStr">
+      <c r="B30" s="7" t="inlineStr">
         <is>
           <t>SF-215</t>
         </is>
       </c>
-      <c r="C30" s="44" t="inlineStr">
+      <c r="C30" s="7" t="inlineStr">
         <is>
           <t>Fan</t>
         </is>
       </c>
-      <c r="D30" s="44" t="n">
+      <c r="D30" s="7" t="n">
         <v>270</v>
       </c>
-      <c r="E30" s="53" t="n">
+      <c r="E30" s="8" t="n">
         <v>4000</v>
       </c>
-      <c r="F30" s="53" t="n">
+      <c r="F30" s="8" t="n">
         <v>1603</v>
       </c>
-      <c r="G30" s="53" t="n">
+      <c r="G30" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="H30" s="53" t="n"/>
-      <c r="I30" s="53" t="n">
+      <c r="H30" s="8" t="n"/>
+      <c r="I30" s="8" t="n">
         <v>2900</v>
       </c>
-      <c r="J30" s="53" t="n">
+      <c r="J30" s="8" t="n">
         <v>66</v>
       </c>
-      <c r="K30" s="53" t="n"/>
-      <c r="L30" s="44" t="inlineStr">
+      <c r="K30" s="8" t="n"/>
+      <c r="L30" s="7" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="M30" s="44" t="inlineStr">
+      <c r="M30" s="7" t="inlineStr">
         <is>
           <t>SF-215 radyal (santrifuj) transfer fani</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="20" t="inlineStr">
+      <c r="A31" s="5" t="inlineStr">
         <is>
           <t>Saf Teknik</t>
         </is>
       </c>
-      <c r="B31" s="20" t="inlineStr">
+      <c r="B31" s="5" t="inlineStr">
         <is>
           <t>SF-216</t>
         </is>
       </c>
-      <c r="C31" s="20" t="inlineStr">
+      <c r="C31" s="5" t="inlineStr">
         <is>
           <t>Fan</t>
         </is>
       </c>
-      <c r="D31" s="20" t="n">
+      <c r="D31" s="5" t="n">
         <v>310</v>
       </c>
-      <c r="E31" s="52" t="n">
+      <c r="E31" s="6" t="n">
         <v>5500</v>
       </c>
-      <c r="F31" s="52" t="n">
+      <c r="F31" s="6" t="n">
         <v>1641</v>
       </c>
-      <c r="G31" s="52" t="n">
+      <c r="G31" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="H31" s="52" t="n"/>
-      <c r="I31" s="52" t="n">
+      <c r="H31" s="6" t="n"/>
+      <c r="I31" s="6" t="n">
         <v>2900</v>
       </c>
-      <c r="J31" s="52" t="n">
+      <c r="J31" s="6" t="n">
         <v>66</v>
       </c>
-      <c r="K31" s="52" t="n"/>
-      <c r="L31" s="20" t="inlineStr">
+      <c r="K31" s="6" t="n"/>
+      <c r="L31" s="5" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="M31" s="20" t="inlineStr">
+      <c r="M31" s="5" t="inlineStr">
         <is>
           <t>SF-216 radyal (santrifuj) transfer fani</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="44" t="inlineStr">
+      <c r="A32" s="7" t="inlineStr">
         <is>
           <t>Saf Teknik</t>
         </is>
       </c>
-      <c r="B32" s="44" t="inlineStr">
+      <c r="B32" s="7" t="inlineStr">
         <is>
           <t>SF-217</t>
         </is>
       </c>
-      <c r="C32" s="44" t="inlineStr">
+      <c r="C32" s="7" t="inlineStr">
         <is>
           <t>Fan</t>
         </is>
       </c>
-      <c r="D32" s="44" t="n">
+      <c r="D32" s="7" t="n">
         <v>350</v>
       </c>
-      <c r="E32" s="53" t="n">
+      <c r="E32" s="8" t="n">
         <v>7000</v>
       </c>
-      <c r="F32" s="53" t="n">
+      <c r="F32" s="8" t="n">
         <v>1680</v>
       </c>
-      <c r="G32" s="53" t="n">
+      <c r="G32" s="8" t="n">
         <v>5.5</v>
       </c>
-      <c r="H32" s="53" t="n"/>
-      <c r="I32" s="53" t="n">
+      <c r="H32" s="8" t="n"/>
+      <c r="I32" s="8" t="n">
         <v>2900</v>
       </c>
-      <c r="J32" s="53" t="n">
+      <c r="J32" s="8" t="n">
         <v>67</v>
       </c>
-      <c r="K32" s="53" t="n"/>
-      <c r="L32" s="44" t="inlineStr">
+      <c r="K32" s="8" t="n"/>
+      <c r="L32" s="7" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="M32" s="44" t="inlineStr">
+      <c r="M32" s="7" t="inlineStr">
         <is>
           <t>SF-217 radyal (santrifuj) transfer fani</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="20" t="inlineStr">
+      <c r="A33" s="5" t="inlineStr">
         <is>
           <t>Saf Teknik</t>
         </is>
       </c>
-      <c r="B33" s="20" t="inlineStr">
+      <c r="B33" s="5" t="inlineStr">
         <is>
           <t>SF-218</t>
         </is>
       </c>
-      <c r="C33" s="20" t="inlineStr">
+      <c r="C33" s="5" t="inlineStr">
         <is>
           <t>Fan</t>
         </is>
       </c>
-      <c r="D33" s="20" t="n">
+      <c r="D33" s="5" t="n">
         <v>400</v>
       </c>
-      <c r="E33" s="52" t="n">
+      <c r="E33" s="6" t="n">
         <v>9000</v>
       </c>
-      <c r="F33" s="52" t="n">
+      <c r="F33" s="6" t="n">
         <v>1731</v>
       </c>
-      <c r="G33" s="52" t="n">
+      <c r="G33" s="6" t="n">
         <v>7.5</v>
       </c>
-      <c r="H33" s="52" t="n"/>
-      <c r="I33" s="52" t="n">
+      <c r="H33" s="6" t="n"/>
+      <c r="I33" s="6" t="n">
         <v>1450</v>
       </c>
-      <c r="J33" s="52" t="n">
+      <c r="J33" s="6" t="n">
         <v>67</v>
       </c>
-      <c r="K33" s="52" t="n"/>
-      <c r="L33" s="20" t="inlineStr">
+      <c r="K33" s="6" t="n"/>
+      <c r="L33" s="5" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="M33" s="20" t="inlineStr">
+      <c r="M33" s="5" t="inlineStr">
         <is>
           <t>SF-218 radyal (santrifuj) transfer fani</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="44" t="inlineStr">
+      <c r="A34" s="7" t="inlineStr">
         <is>
           <t>Saf Teknik</t>
         </is>
       </c>
-      <c r="B34" s="44" t="inlineStr">
+      <c r="B34" s="7" t="inlineStr">
         <is>
           <t>SF-219</t>
         </is>
       </c>
-      <c r="C34" s="44" t="inlineStr">
+      <c r="C34" s="7" t="inlineStr">
         <is>
           <t>Fan</t>
         </is>
       </c>
-      <c r="D34" s="44" t="n">
+      <c r="D34" s="7" t="n">
         <v>460</v>
       </c>
-      <c r="E34" s="53" t="n">
+      <c r="E34" s="8" t="n">
         <v>12000</v>
       </c>
-      <c r="F34" s="53" t="n">
+      <c r="F34" s="8" t="n">
         <v>1809</v>
       </c>
-      <c r="G34" s="53" t="n">
+      <c r="G34" s="8" t="n">
         <v>11</v>
       </c>
-      <c r="H34" s="53" t="n"/>
-      <c r="I34" s="53" t="n">
+      <c r="H34" s="8" t="n"/>
+      <c r="I34" s="8" t="n">
         <v>1450</v>
       </c>
-      <c r="J34" s="53" t="n">
+      <c r="J34" s="8" t="n">
         <v>68</v>
       </c>
-      <c r="K34" s="53" t="n"/>
-      <c r="L34" s="44" t="inlineStr">
+      <c r="K34" s="8" t="n"/>
+      <c r="L34" s="7" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="M34" s="44" t="inlineStr">
+      <c r="M34" s="7" t="inlineStr">
         <is>
           <t>SF-219 radyal (santrifuj) transfer fani</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="20" t="inlineStr">
+      <c r="A35" s="5" t="inlineStr">
         <is>
           <t>Saf Teknik</t>
         </is>
       </c>
-      <c r="B35" s="20" t="inlineStr">
+      <c r="B35" s="5" t="inlineStr">
         <is>
           <t>SF-2110</t>
         </is>
       </c>
-      <c r="C35" s="20" t="inlineStr">
+      <c r="C35" s="5" t="inlineStr">
         <is>
           <t>Fan</t>
         </is>
       </c>
-      <c r="D35" s="20" t="n">
+      <c r="D35" s="5" t="n">
         <v>530</v>
       </c>
-      <c r="E35" s="52" t="n">
+      <c r="E35" s="6" t="n">
         <v>16000</v>
       </c>
-      <c r="F35" s="52" t="n">
+      <c r="F35" s="6" t="n">
         <v>1911</v>
       </c>
-      <c r="G35" s="52" t="n">
+      <c r="G35" s="6" t="n">
         <v>15</v>
       </c>
-      <c r="H35" s="52" t="n"/>
-      <c r="I35" s="52" t="n">
+      <c r="H35" s="6" t="n"/>
+      <c r="I35" s="6" t="n">
         <v>1450</v>
       </c>
-      <c r="J35" s="52" t="n">
+      <c r="J35" s="6" t="n">
         <v>69</v>
       </c>
-      <c r="K35" s="52" t="n"/>
-      <c r="L35" s="20" t="inlineStr">
+      <c r="K35" s="6" t="n"/>
+      <c r="L35" s="5" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="M35" s="20" t="inlineStr">
+      <c r="M35" s="5" t="inlineStr">
         <is>
           <t>SF-2110 radyal (santrifuj) transfer fani</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="44" t="inlineStr">
+      <c r="A36" s="7" t="inlineStr">
         <is>
           <t>Saf Teknik</t>
         </is>
       </c>
-      <c r="B36" s="44" t="inlineStr">
+      <c r="B36" s="7" t="inlineStr">
         <is>
           <t>SF-2111</t>
         </is>
       </c>
-      <c r="C36" s="44" t="inlineStr">
+      <c r="C36" s="7" t="inlineStr">
         <is>
           <t>Fan</t>
         </is>
       </c>
-      <c r="D36" s="44" t="n">
+      <c r="D36" s="7" t="n">
         <v>590</v>
       </c>
-      <c r="E36" s="53" t="n">
+      <c r="E36" s="8" t="n">
         <v>20000</v>
       </c>
-      <c r="F36" s="53" t="n">
+      <c r="F36" s="8" t="n">
         <v>2014</v>
       </c>
-      <c r="G36" s="53" t="n">
+      <c r="G36" s="8" t="n">
         <v>18.5</v>
       </c>
-      <c r="H36" s="53" t="n"/>
-      <c r="I36" s="53" t="n">
+      <c r="H36" s="8" t="n"/>
+      <c r="I36" s="8" t="n">
         <v>1450</v>
       </c>
-      <c r="J36" s="53" t="n">
+      <c r="J36" s="8" t="n">
         <v>70</v>
       </c>
-      <c r="K36" s="53" t="n"/>
-      <c r="L36" s="44" t="inlineStr">
+      <c r="K36" s="8" t="n"/>
+      <c r="L36" s="7" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="M36" s="44" t="inlineStr">
+      <c r="M36" s="7" t="inlineStr">
         <is>
           <t>SF-2111 radyal (santrifuj) transfer fani</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="20" t="inlineStr">
+      <c r="A37" s="5" t="inlineStr">
         <is>
           <t>Saf Teknik</t>
         </is>
       </c>
-      <c r="B37" s="20" t="inlineStr">
+      <c r="B37" s="5" t="inlineStr">
         <is>
           <t>SF-2112</t>
         </is>
       </c>
-      <c r="C37" s="20" t="inlineStr">
+      <c r="C37" s="5" t="inlineStr">
         <is>
           <t>Fan</t>
         </is>
       </c>
-      <c r="D37" s="20" t="n">
+      <c r="D37" s="5" t="n">
         <v>680</v>
       </c>
-      <c r="E37" s="52" t="n">
+      <c r="E37" s="6" t="n">
         <v>26000</v>
       </c>
-      <c r="F37" s="52" t="n">
+      <c r="F37" s="6" t="n">
         <v>2169</v>
       </c>
-      <c r="G37" s="52" t="n">
+      <c r="G37" s="6" t="n">
         <v>22</v>
       </c>
-      <c r="H37" s="52" t="n"/>
-      <c r="I37" s="52" t="n">
+      <c r="H37" s="6" t="n"/>
+      <c r="I37" s="6" t="n">
         <v>1450</v>
       </c>
-      <c r="J37" s="52" t="n">
+      <c r="J37" s="6" t="n">
         <v>72</v>
       </c>
-      <c r="K37" s="52" t="n"/>
-      <c r="L37" s="20" t="inlineStr">
+      <c r="K37" s="6" t="n"/>
+      <c r="L37" s="5" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="M37" s="20" t="inlineStr">
+      <c r="M37" s="5" t="inlineStr">
         <is>
           <t>SF-2112 radyal (santrifuj) transfer fani</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="44" t="inlineStr">
+      <c r="A38" s="7" t="inlineStr">
         <is>
           <t>Siloma</t>
         </is>
       </c>
-      <c r="B38" s="44" t="inlineStr">
+      <c r="B38" s="7" t="inlineStr">
         <is>
           <t>STF-218</t>
         </is>
       </c>
-      <c r="C38" s="44" t="inlineStr">
+      <c r="C38" s="7" t="inlineStr">
         <is>
           <t>Fan</t>
         </is>
       </c>
-      <c r="D38" s="44" t="n">
+      <c r="D38" s="7" t="n">
         <v>400</v>
       </c>
-      <c r="E38" s="53" t="n">
+      <c r="E38" s="8" t="n">
         <v>9000</v>
       </c>
-      <c r="F38" s="53" t="n">
+      <c r="F38" s="8" t="n">
         <v>1731</v>
       </c>
-      <c r="G38" s="53" t="n">
+      <c r="G38" s="8" t="n">
         <v>7.5</v>
       </c>
-      <c r="H38" s="53" t="n"/>
-      <c r="I38" s="53" t="n">
+      <c r="H38" s="8" t="n"/>
+      <c r="I38" s="8" t="n">
         <v>1450</v>
       </c>
-      <c r="J38" s="53" t="n">
+      <c r="J38" s="8" t="n">
         <v>67</v>
       </c>
-      <c r="K38" s="53" t="n"/>
-      <c r="L38" s="44" t="inlineStr">
+      <c r="K38" s="8" t="n"/>
+      <c r="L38" s="7" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="M38" s="44" t="inlineStr">
+      <c r="M38" s="7" t="inlineStr">
         <is>
           <t>STF-218 radyal (santrifuj) transfer fani</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="20" t="inlineStr">
+      <c r="A39" s="5" t="inlineStr">
         <is>
           <t>Siloma</t>
         </is>
       </c>
-      <c r="B39" s="20" t="inlineStr">
+      <c r="B39" s="5" t="inlineStr">
         <is>
           <t>STF-2110</t>
         </is>
       </c>
-      <c r="C39" s="20" t="inlineStr">
+      <c r="C39" s="5" t="inlineStr">
         <is>
           <t>Fan</t>
         </is>
       </c>
-      <c r="D39" s="20" t="n">
+      <c r="D39" s="5" t="n">
         <v>530</v>
       </c>
-      <c r="E39" s="52" t="n">
+      <c r="E39" s="6" t="n">
         <v>16000</v>
       </c>
-      <c r="F39" s="52" t="n">
+      <c r="F39" s="6" t="n">
         <v>1911</v>
       </c>
-      <c r="G39" s="52" t="n">
+      <c r="G39" s="6" t="n">
         <v>15</v>
       </c>
-      <c r="H39" s="52" t="n"/>
-      <c r="I39" s="52" t="n">
+      <c r="H39" s="6" t="n"/>
+      <c r="I39" s="6" t="n">
         <v>1450</v>
       </c>
-      <c r="J39" s="52" t="n">
+      <c r="J39" s="6" t="n">
         <v>69</v>
       </c>
-      <c r="K39" s="52" t="n"/>
-      <c r="L39" s="20" t="inlineStr">
+      <c r="K39" s="6" t="n"/>
+      <c r="L39" s="5" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="M39" s="20" t="inlineStr">
+      <c r="M39" s="5" t="inlineStr">
         <is>
           <t>STF-2110 radyal (santrifuj) transfer fani</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="44" t="inlineStr">
+      <c r="A40" s="7" t="inlineStr">
         <is>
           <t>Siloma</t>
         </is>
       </c>
-      <c r="B40" s="44" t="inlineStr">
+      <c r="B40" s="7" t="inlineStr">
         <is>
           <t>STF-2112</t>
         </is>
       </c>
-      <c r="C40" s="44" t="inlineStr">
+      <c r="C40" s="7" t="inlineStr">
         <is>
           <t>Fan</t>
         </is>
       </c>
-      <c r="D40" s="44" t="n">
+      <c r="D40" s="7" t="n">
         <v>680</v>
       </c>
-      <c r="E40" s="53" t="n">
+      <c r="E40" s="8" t="n">
         <v>26000</v>
       </c>
-      <c r="F40" s="53" t="n">
+      <c r="F40" s="8" t="n">
         <v>2169</v>
       </c>
-      <c r="G40" s="53" t="n">
+      <c r="G40" s="8" t="n">
         <v>22</v>
       </c>
-      <c r="H40" s="53" t="n"/>
-      <c r="I40" s="53" t="n">
+      <c r="H40" s="8" t="n"/>
+      <c r="I40" s="8" t="n">
         <v>1450</v>
       </c>
-      <c r="J40" s="53" t="n">
+      <c r="J40" s="8" t="n">
         <v>72</v>
       </c>
-      <c r="K40" s="53" t="n"/>
-      <c r="L40" s="44" t="inlineStr">
+      <c r="K40" s="8" t="n"/>
+      <c r="L40" s="7" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="M40" s="44" t="inlineStr">
+      <c r="M40" s="7" t="inlineStr">
         <is>
           <t>STF-2112 radyal (santrifuj) transfer fani</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="20" t="inlineStr">
+      <c r="A41" s="5" t="inlineStr">
         <is>
           <t>Siloma</t>
         </is>
       </c>
-      <c r="B41" s="20" t="inlineStr">
+      <c r="B41" s="5" t="inlineStr">
         <is>
           <t>STF-2115</t>
         </is>
       </c>
-      <c r="C41" s="20" t="inlineStr">
+      <c r="C41" s="5" t="inlineStr">
         <is>
           <t>Fan</t>
         </is>
       </c>
-      <c r="D41" s="20" t="n">
+      <c r="D41" s="5" t="n">
         <v>790</v>
       </c>
-      <c r="E41" s="52" t="n">
+      <c r="E41" s="6" t="n">
         <v>35000</v>
       </c>
-      <c r="F41" s="52" t="n">
+      <c r="F41" s="6" t="n">
         <v>2400</v>
       </c>
-      <c r="G41" s="52" t="n">
+      <c r="G41" s="6" t="n">
         <v>37</v>
       </c>
-      <c r="H41" s="52" t="n"/>
-      <c r="I41" s="52" t="n">
+      <c r="H41" s="6" t="n"/>
+      <c r="I41" s="6" t="n">
         <v>1450</v>
       </c>
-      <c r="J41" s="52" t="n">
+      <c r="J41" s="6" t="n">
         <v>74</v>
       </c>
-      <c r="K41" s="52" t="n"/>
-      <c r="L41" s="20" t="inlineStr">
+      <c r="K41" s="6" t="n"/>
+      <c r="L41" s="5" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="M41" s="20" t="inlineStr">
+      <c r="M41" s="5" t="inlineStr">
         <is>
           <t>STF-2115 radyal (santrifuj) transfer fani</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="44" t="inlineStr">
+      <c r="A42" s="7" t="inlineStr">
         <is>
           <t>SMT Europe</t>
         </is>
       </c>
-      <c r="B42" s="44" t="inlineStr">
+      <c r="B42" s="7" t="inlineStr">
         <is>
           <t>SMT-TF-10</t>
         </is>
       </c>
-      <c r="C42" s="44" t="inlineStr">
+      <c r="C42" s="7" t="inlineStr">
         <is>
           <t>Fan</t>
         </is>
       </c>
-      <c r="D42" s="44" t="n">
+      <c r="D42" s="7" t="n">
         <v>300</v>
       </c>
-      <c r="E42" s="53" t="n">
+      <c r="E42" s="8" t="n">
         <v>5000</v>
       </c>
-      <c r="F42" s="53" t="n">
+      <c r="F42" s="8" t="n">
         <v>1629</v>
       </c>
-      <c r="G42" s="53" t="n">
+      <c r="G42" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="H42" s="53" t="n"/>
-      <c r="I42" s="53" t="n">
+      <c r="H42" s="8" t="n"/>
+      <c r="I42" s="8" t="n">
         <v>2900</v>
       </c>
-      <c r="J42" s="53" t="n">
+      <c r="J42" s="8" t="n">
         <v>66</v>
       </c>
-      <c r="K42" s="53" t="n"/>
-      <c r="L42" s="44" t="inlineStr">
+      <c r="K42" s="8" t="n"/>
+      <c r="L42" s="7" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="M42" s="44" t="inlineStr">
+      <c r="M42" s="7" t="inlineStr">
         <is>
           <t>SMT-TF-10 radyal (santrifuj) transfer fani</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="20" t="inlineStr">
+      <c r="A43" s="5" t="inlineStr">
         <is>
           <t>SMT Europe</t>
         </is>
       </c>
-      <c r="B43" s="20" t="inlineStr">
+      <c r="B43" s="5" t="inlineStr">
         <is>
           <t>SMT-TF-20</t>
         </is>
       </c>
-      <c r="C43" s="20" t="inlineStr">
+      <c r="C43" s="5" t="inlineStr">
         <is>
           <t>Fan</t>
         </is>
       </c>
-      <c r="D43" s="20" t="n">
+      <c r="D43" s="5" t="n">
         <v>420</v>
       </c>
-      <c r="E43" s="52" t="n">
+      <c r="E43" s="6" t="n">
         <v>10000</v>
       </c>
-      <c r="F43" s="52" t="n">
+      <c r="F43" s="6" t="n">
         <v>1757</v>
       </c>
-      <c r="G43" s="52" t="n">
+      <c r="G43" s="6" t="n">
         <v>7.5</v>
       </c>
-      <c r="H43" s="52" t="n"/>
-      <c r="I43" s="52" t="n">
+      <c r="H43" s="6" t="n"/>
+      <c r="I43" s="6" t="n">
         <v>1450</v>
       </c>
-      <c r="J43" s="52" t="n">
+      <c r="J43" s="6" t="n">
         <v>68</v>
       </c>
-      <c r="K43" s="52" t="n"/>
-      <c r="L43" s="20" t="inlineStr">
+      <c r="K43" s="6" t="n"/>
+      <c r="L43" s="5" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="M43" s="20" t="inlineStr">
+      <c r="M43" s="5" t="inlineStr">
         <is>
           <t>SMT-TF-20 radyal (santrifuj) transfer fani</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="44" t="inlineStr">
+      <c r="A44" s="7" t="inlineStr">
         <is>
           <t>SMT Europe</t>
         </is>
       </c>
-      <c r="B44" s="44" t="inlineStr">
+      <c r="B44" s="7" t="inlineStr">
         <is>
           <t>SMT-TF-30</t>
         </is>
       </c>
-      <c r="C44" s="44" t="inlineStr">
+      <c r="C44" s="7" t="inlineStr">
         <is>
           <t>Fan</t>
         </is>
       </c>
-      <c r="D44" s="44" t="n">
+      <c r="D44" s="7" t="n">
         <v>560</v>
       </c>
-      <c r="E44" s="53" t="n">
+      <c r="E44" s="8" t="n">
         <v>18000</v>
       </c>
-      <c r="F44" s="53" t="n">
+      <c r="F44" s="8" t="n">
         <v>1963</v>
       </c>
-      <c r="G44" s="53" t="n">
+      <c r="G44" s="8" t="n">
         <v>15</v>
       </c>
-      <c r="H44" s="53" t="n"/>
-      <c r="I44" s="53" t="n">
+      <c r="H44" s="8" t="n"/>
+      <c r="I44" s="8" t="n">
         <v>1450</v>
       </c>
-      <c r="J44" s="53" t="n">
+      <c r="J44" s="8" t="n">
         <v>70</v>
       </c>
-      <c r="K44" s="53" t="n"/>
-      <c r="L44" s="44" t="inlineStr">
+      <c r="K44" s="8" t="n"/>
+      <c r="L44" s="7" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="M44" s="44" t="inlineStr">
+      <c r="M44" s="7" t="inlineStr">
         <is>
           <t>SMT-TF-30 radyal (santrifuj) transfer fani</t>
         </is>
@@ -5448,7 +8684,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5476,408 +8712,408 @@
       <c r="E1" s="2" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="13" t="inlineStr">
+      <c r="A3" s="23" t="inlineStr">
         <is>
           <t>MUSTERI / PROJE BILGILERI</t>
         </is>
       </c>
-      <c r="B3" s="14" t="n"/>
-      <c r="C3" s="14" t="n"/>
-      <c r="D3" s="14" t="n"/>
-      <c r="E3" s="14" t="n"/>
+      <c r="B3" s="24" t="n"/>
+      <c r="C3" s="24" t="n"/>
+      <c r="D3" s="24" t="n"/>
+      <c r="E3" s="24" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="17" t="inlineStr">
+      <c r="A4" s="14" t="inlineStr">
         <is>
           <t>Musteri / Firma Adi:</t>
         </is>
       </c>
-      <c r="B4" s="18" t="inlineStr"/>
-      <c r="D4" s="17" t="inlineStr">
+      <c r="B4" s="15" t="inlineStr"/>
+      <c r="D4" s="14" t="inlineStr">
         <is>
           <t>Teklif No:</t>
         </is>
       </c>
-      <c r="E4" s="18" t="inlineStr"/>
+      <c r="E4" s="15" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="17" t="inlineStr">
+      <c r="A5" s="14" t="inlineStr">
         <is>
           <t>Proje:</t>
         </is>
       </c>
-      <c r="B5" s="18">
+      <c r="B5" s="15">
         <f>'Makine Giris'!B2</f>
         <v/>
       </c>
-      <c r="D5" s="17" t="inlineStr">
+      <c r="D5" s="14" t="inlineStr">
         <is>
           <t>Tarih:</t>
         </is>
       </c>
-      <c r="E5" s="19">
+      <c r="E5" s="16">
         <f>'Makine Giris'!E2</f>
         <v/>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="17" t="inlineStr">
+      <c r="A6" s="14" t="inlineStr">
         <is>
           <t>Hazirlayan:</t>
         </is>
       </c>
-      <c r="B6" s="18">
+      <c r="B6" s="15">
         <f>'Makine Giris'!H2</f>
         <v/>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="13" t="inlineStr">
+      <c r="A8" s="23" t="inlineStr">
         <is>
           <t>SISTEM OZETI</t>
         </is>
       </c>
-      <c r="B8" s="14" t="n"/>
-      <c r="C8" s="14" t="n"/>
-      <c r="D8" s="14" t="n"/>
-      <c r="E8" s="14" t="n"/>
+      <c r="B8" s="24" t="n"/>
+      <c r="C8" s="24" t="n"/>
+      <c r="D8" s="24" t="n"/>
+      <c r="E8" s="24" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="17" t="inlineStr">
+      <c r="A9" s="14" t="inlineStr">
         <is>
           <t>Toplam Hava Debisi (m3/h)</t>
         </is>
       </c>
-      <c r="B9" s="26">
+      <c r="B9" s="22">
         <f>'Borulama Hesaplari'!E4</f>
         <v/>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="17" t="inlineStr">
+      <c r="A10" s="14" t="inlineStr">
         <is>
           <t>Ana Boru Capi (mm)</t>
         </is>
       </c>
-      <c r="B10" s="26">
+      <c r="B10" s="22">
         <f>'Borulama Hesaplari'!E8</f>
         <v/>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="17" t="inlineStr">
+      <c r="A11" s="14" t="inlineStr">
         <is>
           <t>Gercek Hava Hizi (m/s)</t>
         </is>
       </c>
-      <c r="B11" s="54">
+      <c r="B11" s="73">
         <f>'Borulama Hesaplari'!E10</f>
         <v/>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="17" t="inlineStr">
+      <c r="A12" s="14" t="inlineStr">
         <is>
           <t>Toplam Sistem Basinc Kaybi (Pa)</t>
         </is>
       </c>
-      <c r="B12" s="26">
+      <c r="B12" s="22">
         <f>'Fan Secimi'!B7</f>
         <v/>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="17" t="inlineStr">
+      <c r="A13" s="14" t="inlineStr">
         <is>
           <t>Secilen Filtre Modeli</t>
         </is>
       </c>
-      <c r="B13" s="47">
+      <c r="B13" s="69">
         <f>'Filtre Secimi'!B9&amp;" - "&amp;'Filtre Secimi'!B10</f>
         <v/>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="17" t="inlineStr">
+      <c r="A14" s="14" t="inlineStr">
         <is>
           <t>Filtre Alani (m2)</t>
         </is>
       </c>
-      <c r="B14" s="55">
+      <c r="B14" s="74">
         <f>'Filtre Secimi'!B12</f>
         <v/>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="17" t="inlineStr">
+      <c r="A15" s="14" t="inlineStr">
         <is>
           <t>Secilen Fan Modeli</t>
         </is>
       </c>
-      <c r="B15" s="47">
+      <c r="B15" s="69">
         <f>'Fan Secimi'!B13&amp;" - "&amp;'Fan Secimi'!B14</f>
         <v/>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="17" t="inlineStr">
+      <c r="A16" s="14" t="inlineStr">
         <is>
           <t>Fan Motor Gucu (kW)</t>
         </is>
       </c>
-      <c r="B16" s="54">
+      <c r="B16" s="73">
         <f>'Fan Secimi'!B29</f>
         <v/>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="17" t="inlineStr">
+      <c r="A17" s="14" t="inlineStr">
         <is>
           <t>Tahmini Enerji Tuketimi (kWh/gun)</t>
         </is>
       </c>
-      <c r="B17" s="55">
+      <c r="B17" s="74">
         <f>'Fan Secimi'!B30</f>
         <v/>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="17" t="inlineStr">
+      <c r="A18" s="14" t="inlineStr">
         <is>
           <t>Tahmini Enerji Tuketimi (kWh/yil)</t>
         </is>
       </c>
-      <c r="B18" s="26">
+      <c r="B18" s="22">
         <f>'Fan Secimi'!B31</f>
         <v/>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="13" t="inlineStr">
+      <c r="A20" s="23" t="inlineStr">
         <is>
           <t>KULLANILAN EKIPMAN LISTESI (BOM)</t>
         </is>
       </c>
-      <c r="B20" s="14" t="n"/>
-      <c r="C20" s="14" t="n"/>
-      <c r="D20" s="14" t="n"/>
-      <c r="E20" s="14" t="n"/>
+      <c r="B20" s="24" t="n"/>
+      <c r="C20" s="24" t="n"/>
+      <c r="D20" s="24" t="n"/>
+      <c r="E20" s="24" t="n"/>
     </row>
     <row r="21" ht="32" customHeight="1">
-      <c r="A21" s="15" t="inlineStr">
+      <c r="A21" s="4" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="B21" s="15" t="inlineStr">
+      <c r="B21" s="4" t="inlineStr">
         <is>
           <t>Ekipman / Kalem</t>
         </is>
       </c>
-      <c r="C21" s="15" t="inlineStr">
+      <c r="C21" s="4" t="inlineStr">
         <is>
           <t>Ozellik</t>
         </is>
       </c>
-      <c r="D21" s="15" t="inlineStr">
+      <c r="D21" s="4" t="inlineStr">
         <is>
           <t>Miktar</t>
         </is>
       </c>
-      <c r="E21" s="15" t="inlineStr">
+      <c r="E21" s="4" t="inlineStr">
         <is>
           <t>Birim</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="56" t="n">
+      <c r="A22" s="75" t="n">
         <v>1</v>
       </c>
-      <c r="B22" s="57" t="inlineStr">
+      <c r="B22" s="76" t="inlineStr">
         <is>
           <t>Ana Boru Hatti</t>
         </is>
       </c>
-      <c r="C22" s="56">
+      <c r="C22" s="75">
         <f>'Borulama Hesaplari'!E8&amp;" mm Cap"</f>
         <v/>
       </c>
-      <c r="D22" s="56">
+      <c r="D22" s="75">
         <f>'Borulama Hesaplari'!B4</f>
         <v/>
       </c>
-      <c r="E22" s="56" t="inlineStr">
+      <c r="E22" s="75" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="58" t="n">
+      <c r="A23" s="77" t="n">
         <v>2</v>
       </c>
-      <c r="B23" s="59" t="inlineStr">
+      <c r="B23" s="78" t="inlineStr">
         <is>
           <t>Bransman Hatlari</t>
         </is>
       </c>
-      <c r="C23" s="58">
+      <c r="C23" s="77">
         <f>'Borulama Hesaplari'!E8&amp;" mm Cap"</f>
         <v/>
       </c>
-      <c r="D23" s="58">
+      <c r="D23" s="77">
         <f>'Borulama Hesaplari'!B5</f>
         <v/>
       </c>
-      <c r="E23" s="58" t="inlineStr">
+      <c r="E23" s="77" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="56" t="n">
+      <c r="A24" s="75" t="n">
         <v>3</v>
       </c>
-      <c r="B24" s="57" t="inlineStr">
+      <c r="B24" s="76" t="inlineStr">
         <is>
           <t>45 derece Dirsek</t>
         </is>
       </c>
-      <c r="C24" s="56">
+      <c r="C24" s="75">
         <f>'Borulama Hesaplari'!B10</f>
         <v/>
       </c>
-      <c r="D24" s="56">
+      <c r="D24" s="75">
         <f>'Borulama Hesaplari'!B6</f>
         <v/>
       </c>
-      <c r="E24" s="56" t="inlineStr">
+      <c r="E24" s="75" t="inlineStr">
         <is>
           <t>adet</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="58" t="n">
+      <c r="A25" s="77" t="n">
         <v>4</v>
       </c>
-      <c r="B25" s="59" t="inlineStr">
+      <c r="B25" s="78" t="inlineStr">
         <is>
           <t>90 derece Dirsek</t>
         </is>
       </c>
-      <c r="C25" s="58">
+      <c r="C25" s="77">
         <f>'Borulama Hesaplari'!B10</f>
         <v/>
       </c>
-      <c r="D25" s="58">
+      <c r="D25" s="77">
         <f>'Borulama Hesaplari'!B7</f>
         <v/>
       </c>
-      <c r="E25" s="58" t="inlineStr">
+      <c r="E25" s="77" t="inlineStr">
         <is>
           <t>adet</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="56" t="n">
+      <c r="A26" s="75" t="n">
         <v>5</v>
       </c>
-      <c r="B26" s="57" t="inlineStr">
+      <c r="B26" s="76" t="inlineStr">
         <is>
           <t>T Baglanti</t>
         </is>
       </c>
-      <c r="C26" s="56">
+      <c r="C26" s="75">
         <f>'Borulama Hesaplari'!B10</f>
         <v/>
       </c>
-      <c r="D26" s="56">
+      <c r="D26" s="75">
         <f>'Borulama Hesaplari'!B8</f>
         <v/>
       </c>
-      <c r="E26" s="56" t="inlineStr">
+      <c r="E26" s="75" t="inlineStr">
         <is>
           <t>adet</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="58" t="n">
+      <c r="A27" s="77" t="n">
         <v>6</v>
       </c>
-      <c r="B27" s="59" t="inlineStr">
+      <c r="B27" s="78" t="inlineStr">
         <is>
           <t>Reduksiyon</t>
         </is>
       </c>
-      <c r="C27" s="58">
+      <c r="C27" s="77">
         <f>'Borulama Hesaplari'!B10</f>
         <v/>
       </c>
-      <c r="D27" s="58">
+      <c r="D27" s="77">
         <f>'Borulama Hesaplari'!B9</f>
         <v/>
       </c>
-      <c r="E27" s="58" t="inlineStr">
+      <c r="E27" s="77" t="inlineStr">
         <is>
           <t>adet</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="56" t="n">
+      <c r="A28" s="75" t="n">
         <v>7</v>
       </c>
-      <c r="B28" s="57" t="inlineStr">
+      <c r="B28" s="76" t="inlineStr">
         <is>
           <t>Filtre Unitesi</t>
         </is>
       </c>
-      <c r="C28" s="56">
+      <c r="C28" s="75">
         <f>'Filtre Secimi'!B9&amp;" "&amp;'Filtre Secimi'!B10</f>
         <v/>
       </c>
-      <c r="D28" s="56" t="inlineStr">
+      <c r="D28" s="75" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E28" s="56" t="inlineStr">
+      <c r="E28" s="75" t="inlineStr">
         <is>
           <t>adet</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="58" t="n">
+      <c r="A29" s="77" t="n">
         <v>8</v>
       </c>
-      <c r="B29" s="59" t="inlineStr">
+      <c r="B29" s="78" t="inlineStr">
         <is>
           <t>Fan (Aspirator)</t>
         </is>
       </c>
-      <c r="C29" s="58">
+      <c r="C29" s="77">
         <f>'Fan Secimi'!B13&amp;" "&amp;'Fan Secimi'!B14</f>
         <v/>
       </c>
-      <c r="D29" s="58" t="inlineStr">
+      <c r="D29" s="77" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E29" s="58" t="inlineStr">
+      <c r="E29" s="77" t="inlineStr">
         <is>
           <t>adet</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="60" t="inlineStr">
+      <c r="A31" s="58" t="inlineStr">
         <is>
           <t>Bu teklif ozeti otomatik hesaplama araci ile olusturulmustur. Kesin fiyatlandirma ve teknik onay icin yetkili satis muhendisi ile gorusulmesi tavsiye edilir.</t>
         </is>

--- a/dust_collection_tool.xlsx
+++ b/dust_collection_tool.xlsx
@@ -47,7 +47,7 @@
     <numFmt numFmtId="174" formatCode="#,##0 &quot;kWh&quot;"/>
     <numFmt numFmtId="175" formatCode="#,##0.0 &quot;m2&quot;"/>
   </numFmts>
-  <fonts count="19">
+  <fonts count="20">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -122,6 +122,11 @@
       <b val="1"/>
       <color rgb="001F3864"/>
       <sz val="13"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="001F3864"/>
+      <sz val="7"/>
     </font>
     <font>
       <b val="1"/>
@@ -566,45 +571,45 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="15" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="18" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="19" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
+      <alignment horizontal="center" textRotation="90"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="18" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="169" fontId="18" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="169" fontId="19" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="170" fontId="18" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="170" fontId="19" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="171" fontId="18" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="171" fontId="19" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="172" fontId="18" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="172" fontId="19" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="19" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="173" fontId="18" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="173" fontId="19" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="174" fontId="18" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="174" fontId="19" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="175" fontId="18" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="175" fontId="19" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -1134,9 +1139,9 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>5</col>
+      <col>53</col>
       <colOff>0</colOff>
-      <row>18</row>
+      <row>10</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="152400" cy="152400"/>
@@ -1159,9 +1164,9 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>13</col>
+      <col>61</col>
       <colOff>0</colOff>
-      <row>18</row>
+      <row>10</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="152400" cy="152400"/>
@@ -1184,9 +1189,9 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>21</col>
+      <col>69</col>
       <colOff>0</colOff>
-      <row>18</row>
+      <row>10</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="152400" cy="152400"/>
@@ -1209,9 +1214,9 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>29</col>
+      <col>77</col>
       <colOff>0</colOff>
-      <row>18</row>
+      <row>10</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="152400" cy="152400"/>
@@ -1234,7 +1239,7 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>37</col>
+      <col>5</col>
       <colOff>0</colOff>
       <row>18</row>
       <rowOff>0</rowOff>
@@ -1259,7 +1264,7 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>45</col>
+      <col>13</col>
       <colOff>0</colOff>
       <row>18</row>
       <rowOff>0</rowOff>
@@ -1284,9 +1289,9 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>5</col>
+      <col>21</col>
       <colOff>0</colOff>
-      <row>26</row>
+      <row>18</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="152400" cy="152400"/>
@@ -1309,9 +1314,9 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>13</col>
+      <col>29</col>
       <colOff>0</colOff>
-      <row>26</row>
+      <row>18</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="152400" cy="152400"/>
@@ -1334,9 +1339,9 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>21</col>
+      <col>37</col>
       <colOff>0</colOff>
-      <row>26</row>
+      <row>18</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="152400" cy="152400"/>
@@ -1359,9 +1364,9 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>29</col>
+      <col>45</col>
       <colOff>0</colOff>
-      <row>26</row>
+      <row>18</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="152400" cy="152400"/>
@@ -1384,9 +1389,9 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>37</col>
+      <col>53</col>
       <colOff>0</colOff>
-      <row>26</row>
+      <row>18</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="152400" cy="152400"/>
@@ -1409,9 +1414,9 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>45</col>
+      <col>61</col>
       <colOff>0</colOff>
-      <row>26</row>
+      <row>18</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="152400" cy="152400"/>
@@ -1434,9 +1439,9 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>5</col>
+      <col>69</col>
       <colOff>0</colOff>
-      <row>34</row>
+      <row>18</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="152400" cy="152400"/>
@@ -1459,9 +1464,9 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>13</col>
+      <col>77</col>
       <colOff>0</colOff>
-      <row>34</row>
+      <row>18</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="152400" cy="152400"/>
@@ -1484,9 +1489,9 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>21</col>
+      <col>5</col>
       <colOff>0</colOff>
-      <row>34</row>
+      <row>26</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="152400" cy="152400"/>
@@ -1509,9 +1514,9 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>29</col>
+      <col>13</col>
       <colOff>0</colOff>
-      <row>34</row>
+      <row>26</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="152400" cy="152400"/>
@@ -1534,9 +1539,9 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>37</col>
+      <col>21</col>
       <colOff>0</colOff>
-      <row>34</row>
+      <row>26</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="152400" cy="152400"/>
@@ -1559,9 +1564,9 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>45</col>
+      <col>29</col>
       <colOff>0</colOff>
-      <row>34</row>
+      <row>26</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="152400" cy="152400"/>
@@ -1584,12 +1589,12 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>10</col>
+      <col>37</col>
       <colOff>0</colOff>
-      <row>21</row>
+      <row>26</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="419100" cy="314325"/>
+    <ext cx="152400" cy="152400"/>
     <pic>
       <nvPicPr>
         <cNvPr id="25" name="Image 25" descr="Picture"/>
@@ -1609,12 +1614,12 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>22</col>
+      <col>45</col>
       <colOff>0</colOff>
-      <row>21</row>
+      <row>26</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="419100" cy="314325"/>
+    <ext cx="152400" cy="152400"/>
     <pic>
       <nvPicPr>
         <cNvPr id="26" name="Image 26" descr="Picture"/>
@@ -1634,12 +1639,12 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>34</col>
+      <col>53</col>
       <colOff>0</colOff>
-      <row>21</row>
+      <row>26</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="419100" cy="314325"/>
+    <ext cx="152400" cy="152400"/>
     <pic>
       <nvPicPr>
         <cNvPr id="27" name="Image 27" descr="Picture"/>
@@ -1647,6 +1652,831 @@
       </nvPicPr>
       <blipFill>
         <a:blip cstate="print" r:embed="rId27"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>61</col>
+      <colOff>0</colOff>
+      <row>26</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="152400" cy="152400"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="28" name="Image 28" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId28"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>69</col>
+      <colOff>0</colOff>
+      <row>26</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="152400" cy="152400"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="29" name="Image 29" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId29"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>77</col>
+      <colOff>0</colOff>
+      <row>26</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="152400" cy="152400"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="30" name="Image 30" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId30"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>5</col>
+      <colOff>0</colOff>
+      <row>34</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="152400" cy="152400"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="31" name="Image 31" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId31"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>13</col>
+      <colOff>0</colOff>
+      <row>34</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="152400" cy="152400"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="32" name="Image 32" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId32"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>21</col>
+      <colOff>0</colOff>
+      <row>34</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="152400" cy="152400"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="33" name="Image 33" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId33"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>29</col>
+      <colOff>0</colOff>
+      <row>34</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="152400" cy="152400"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="34" name="Image 34" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId34"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>37</col>
+      <colOff>0</colOff>
+      <row>34</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="152400" cy="152400"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="35" name="Image 35" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId35"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>45</col>
+      <colOff>0</colOff>
+      <row>34</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="152400" cy="152400"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="36" name="Image 36" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId36"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>53</col>
+      <colOff>0</colOff>
+      <row>34</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="152400" cy="152400"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="37" name="Image 37" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId37"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>61</col>
+      <colOff>0</colOff>
+      <row>34</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="152400" cy="152400"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="38" name="Image 38" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId38"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>69</col>
+      <colOff>0</colOff>
+      <row>34</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="152400" cy="152400"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="39" name="Image 39" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId39"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>77</col>
+      <colOff>0</colOff>
+      <row>34</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="152400" cy="152400"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="40" name="Image 40" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId40"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>9</col>
+      <colOff>0</colOff>
+      <row>21</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="209550" cy="152400"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="41" name="Image 41" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId41"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>12</col>
+      <colOff>0</colOff>
+      <row>21</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="209550" cy="152400"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="42" name="Image 42" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId42"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>15</col>
+      <colOff>0</colOff>
+      <row>21</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="209550" cy="152400"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="43" name="Image 43" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId43"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>18</col>
+      <colOff>0</colOff>
+      <row>21</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="209550" cy="152400"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="44" name="Image 44" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId44"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>21</col>
+      <colOff>0</colOff>
+      <row>21</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="209550" cy="152400"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="45" name="Image 45" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId45"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>24</col>
+      <colOff>0</colOff>
+      <row>21</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="209550" cy="152400"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="46" name="Image 46" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId46"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>27</col>
+      <colOff>0</colOff>
+      <row>21</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="209550" cy="152400"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="47" name="Image 47" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId47"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>30</col>
+      <colOff>0</colOff>
+      <row>21</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="209550" cy="152400"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="48" name="Image 48" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId48"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>33</col>
+      <colOff>0</colOff>
+      <row>21</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="209550" cy="152400"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="49" name="Image 49" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId49"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>36</col>
+      <colOff>0</colOff>
+      <row>21</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="209550" cy="152400"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="50" name="Image 50" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId50"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>39</col>
+      <colOff>0</colOff>
+      <row>21</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="209550" cy="152400"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="51" name="Image 51" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId51"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>42</col>
+      <colOff>0</colOff>
+      <row>21</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="209550" cy="152400"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="52" name="Image 52" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId52"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>45</col>
+      <colOff>0</colOff>
+      <row>21</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="209550" cy="152400"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="53" name="Image 53" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId53"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>48</col>
+      <colOff>0</colOff>
+      <row>21</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="209550" cy="152400"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="54" name="Image 54" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId54"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>51</col>
+      <colOff>0</colOff>
+      <row>21</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="209550" cy="152400"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="55" name="Image 55" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId55"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>54</col>
+      <colOff>0</colOff>
+      <row>21</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="209550" cy="152400"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="56" name="Image 56" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId56"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>57</col>
+      <colOff>0</colOff>
+      <row>21</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="209550" cy="152400"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="57" name="Image 57" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId57"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>60</col>
+      <colOff>0</colOff>
+      <row>21</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="209550" cy="152400"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="58" name="Image 58" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId58"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>63</col>
+      <colOff>0</colOff>
+      <row>21</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="209550" cy="152400"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="59" name="Image 59" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId59"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>66</col>
+      <colOff>0</colOff>
+      <row>21</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="209550" cy="152400"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="60" name="Image 60" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId60"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1667,11 +2497,11 @@
     <ext cx="476250" cy="476250"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="28" name="Image 28" descr="Picture"/>
+        <cNvPr id="61" name="Image 61" descr="Picture"/>
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId28"/>
+        <a:blip cstate="print" r:embed="rId61"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1684,7 +2514,7 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>46</col>
+      <col>77</col>
       <colOff>0</colOff>
       <row>6</row>
       <rowOff>0</rowOff>
@@ -1692,11 +2522,11 @@
     <ext cx="476250" cy="476250"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="29" name="Image 29" descr="Picture"/>
+        <cNvPr id="62" name="Image 62" descr="Picture"/>
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId29"/>
+        <a:blip cstate="print" r:embed="rId62"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1717,11 +2547,11 @@
     <ext cx="342900" cy="228600"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="30" name="Image 30" descr="Picture"/>
+        <cNvPr id="63" name="Image 63" descr="Picture"/>
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId30"/>
+        <a:blip cstate="print" r:embed="rId63"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1742,11 +2572,11 @@
     <ext cx="342900" cy="228600"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="31" name="Image 31" descr="Picture"/>
+        <cNvPr id="64" name="Image 64" descr="Picture"/>
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId31"/>
+        <a:blip cstate="print" r:embed="rId64"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1767,11 +2597,11 @@
     <ext cx="342900" cy="228600"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="32" name="Image 32" descr="Picture"/>
+        <cNvPr id="65" name="Image 65" descr="Picture"/>
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId32"/>
+        <a:blip cstate="print" r:embed="rId65"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1792,11 +2622,11 @@
     <ext cx="342900" cy="228600"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="33" name="Image 33" descr="Picture"/>
+        <cNvPr id="66" name="Image 66" descr="Picture"/>
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId33"/>
+        <a:blip cstate="print" r:embed="rId66"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1817,11 +2647,11 @@
     <ext cx="342900" cy="228600"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="34" name="Image 34" descr="Picture"/>
+        <cNvPr id="67" name="Image 67" descr="Picture"/>
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId34"/>
+        <a:blip cstate="print" r:embed="rId67"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1842,11 +2672,11 @@
     <ext cx="342900" cy="228600"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="35" name="Image 35" descr="Picture"/>
+        <cNvPr id="68" name="Image 68" descr="Picture"/>
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId35"/>
+        <a:blip cstate="print" r:embed="rId68"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1867,11 +2697,11 @@
     <ext cx="342900" cy="228600"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="36" name="Image 36" descr="Picture"/>
+        <cNvPr id="69" name="Image 69" descr="Picture"/>
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId36"/>
+        <a:blip cstate="print" r:embed="rId69"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -3637,59 +4467,90 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY53"/>
+  <dimension ref="A1:CD53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
-    <col width="2.2" customWidth="1" min="2" max="2"/>
-    <col width="2.2" customWidth="1" min="3" max="3"/>
-    <col width="2.2" customWidth="1" min="4" max="4"/>
-    <col width="2.2" customWidth="1" min="5" max="5"/>
-    <col width="2.2" customWidth="1" min="6" max="6"/>
-    <col width="2.2" customWidth="1" min="7" max="7"/>
-    <col width="2.2" customWidth="1" min="8" max="8"/>
-    <col width="2.2" customWidth="1" min="9" max="9"/>
-    <col width="2.2" customWidth="1" min="10" max="10"/>
-    <col width="2.2" customWidth="1" min="11" max="11"/>
-    <col width="2.2" customWidth="1" min="12" max="12"/>
-    <col width="2.2" customWidth="1" min="13" max="13"/>
-    <col width="2.2" customWidth="1" min="14" max="14"/>
-    <col width="2.2" customWidth="1" min="15" max="15"/>
-    <col width="2.2" customWidth="1" min="16" max="16"/>
-    <col width="2.2" customWidth="1" min="17" max="17"/>
-    <col width="2.2" customWidth="1" min="18" max="18"/>
-    <col width="2.2" customWidth="1" min="19" max="19"/>
-    <col width="2.2" customWidth="1" min="20" max="20"/>
-    <col width="2.2" customWidth="1" min="21" max="21"/>
-    <col width="2.2" customWidth="1" min="22" max="22"/>
-    <col width="2.2" customWidth="1" min="23" max="23"/>
-    <col width="2.2" customWidth="1" min="24" max="24"/>
-    <col width="2.2" customWidth="1" min="25" max="25"/>
-    <col width="2.2" customWidth="1" min="26" max="26"/>
-    <col width="2.2" customWidth="1" min="27" max="27"/>
-    <col width="2.2" customWidth="1" min="28" max="28"/>
-    <col width="2.2" customWidth="1" min="29" max="29"/>
-    <col width="2.2" customWidth="1" min="30" max="30"/>
-    <col width="2.2" customWidth="1" min="31" max="31"/>
-    <col width="2.2" customWidth="1" min="32" max="32"/>
-    <col width="2.2" customWidth="1" min="33" max="33"/>
-    <col width="2.2" customWidth="1" min="34" max="34"/>
-    <col width="2.2" customWidth="1" min="35" max="35"/>
-    <col width="2.2" customWidth="1" min="36" max="36"/>
-    <col width="2.2" customWidth="1" min="37" max="37"/>
-    <col width="2.2" customWidth="1" min="38" max="38"/>
-    <col width="2.2" customWidth="1" min="39" max="39"/>
-    <col width="2.2" customWidth="1" min="40" max="40"/>
-    <col width="2.2" customWidth="1" min="41" max="41"/>
-    <col width="2.2" customWidth="1" min="42" max="42"/>
-    <col width="2.2" customWidth="1" min="43" max="43"/>
-    <col width="2.2" customWidth="1" min="44" max="44"/>
-    <col width="2.2" customWidth="1" min="45" max="45"/>
-    <col width="2.2" customWidth="1" min="46" max="46"/>
-    <col width="2.2" customWidth="1" min="47" max="47"/>
-    <col width="2.2" customWidth="1" min="48" max="48"/>
-    <col width="2.2" customWidth="1" min="49" max="49"/>
-    <col width="2.2" customWidth="1" min="50" max="50"/>
-    <col width="2.2" customWidth="1" min="51" max="51"/>
+    <col width="1.4" customWidth="1" min="2" max="2"/>
+    <col width="1.4" customWidth="1" min="3" max="3"/>
+    <col width="1.4" customWidth="1" min="4" max="4"/>
+    <col width="1.4" customWidth="1" min="5" max="5"/>
+    <col width="1.4" customWidth="1" min="6" max="6"/>
+    <col width="1.4" customWidth="1" min="7" max="7"/>
+    <col width="1.4" customWidth="1" min="8" max="8"/>
+    <col width="1.4" customWidth="1" min="9" max="9"/>
+    <col width="1.4" customWidth="1" min="10" max="10"/>
+    <col width="1.4" customWidth="1" min="11" max="11"/>
+    <col width="1.4" customWidth="1" min="12" max="12"/>
+    <col width="1.4" customWidth="1" min="13" max="13"/>
+    <col width="1.4" customWidth="1" min="14" max="14"/>
+    <col width="1.4" customWidth="1" min="15" max="15"/>
+    <col width="1.4" customWidth="1" min="16" max="16"/>
+    <col width="1.4" customWidth="1" min="17" max="17"/>
+    <col width="1.4" customWidth="1" min="18" max="18"/>
+    <col width="1.4" customWidth="1" min="19" max="19"/>
+    <col width="1.4" customWidth="1" min="20" max="20"/>
+    <col width="1.4" customWidth="1" min="21" max="21"/>
+    <col width="1.4" customWidth="1" min="22" max="22"/>
+    <col width="1.4" customWidth="1" min="23" max="23"/>
+    <col width="1.4" customWidth="1" min="24" max="24"/>
+    <col width="1.4" customWidth="1" min="25" max="25"/>
+    <col width="1.4" customWidth="1" min="26" max="26"/>
+    <col width="1.4" customWidth="1" min="27" max="27"/>
+    <col width="1.4" customWidth="1" min="28" max="28"/>
+    <col width="1.4" customWidth="1" min="29" max="29"/>
+    <col width="1.4" customWidth="1" min="30" max="30"/>
+    <col width="1.4" customWidth="1" min="31" max="31"/>
+    <col width="1.4" customWidth="1" min="32" max="32"/>
+    <col width="1.4" customWidth="1" min="33" max="33"/>
+    <col width="1.4" customWidth="1" min="34" max="34"/>
+    <col width="1.4" customWidth="1" min="35" max="35"/>
+    <col width="1.4" customWidth="1" min="36" max="36"/>
+    <col width="1.4" customWidth="1" min="37" max="37"/>
+    <col width="1.4" customWidth="1" min="38" max="38"/>
+    <col width="1.4" customWidth="1" min="39" max="39"/>
+    <col width="1.4" customWidth="1" min="40" max="40"/>
+    <col width="1.4" customWidth="1" min="41" max="41"/>
+    <col width="1.4" customWidth="1" min="42" max="42"/>
+    <col width="1.4" customWidth="1" min="43" max="43"/>
+    <col width="1.4" customWidth="1" min="44" max="44"/>
+    <col width="1.4" customWidth="1" min="45" max="45"/>
+    <col width="1.4" customWidth="1" min="46" max="46"/>
+    <col width="1.4" customWidth="1" min="47" max="47"/>
+    <col width="1.4" customWidth="1" min="48" max="48"/>
+    <col width="1.4" customWidth="1" min="49" max="49"/>
+    <col width="1.4" customWidth="1" min="50" max="50"/>
+    <col width="1.4" customWidth="1" min="51" max="51"/>
+    <col width="1.4" customWidth="1" min="52" max="52"/>
+    <col width="1.4" customWidth="1" min="53" max="53"/>
+    <col width="1.4" customWidth="1" min="54" max="54"/>
+    <col width="1.4" customWidth="1" min="55" max="55"/>
+    <col width="1.4" customWidth="1" min="56" max="56"/>
+    <col width="1.4" customWidth="1" min="57" max="57"/>
+    <col width="1.4" customWidth="1" min="58" max="58"/>
+    <col width="1.4" customWidth="1" min="59" max="59"/>
+    <col width="1.4" customWidth="1" min="60" max="60"/>
+    <col width="1.4" customWidth="1" min="61" max="61"/>
+    <col width="1.4" customWidth="1" min="62" max="62"/>
+    <col width="1.4" customWidth="1" min="63" max="63"/>
+    <col width="1.4" customWidth="1" min="64" max="64"/>
+    <col width="1.4" customWidth="1" min="65" max="65"/>
+    <col width="1.4" customWidth="1" min="66" max="66"/>
+    <col width="1.4" customWidth="1" min="67" max="67"/>
+    <col width="1.4" customWidth="1" min="68" max="68"/>
+    <col width="1.4" customWidth="1" min="69" max="69"/>
+    <col width="1.4" customWidth="1" min="70" max="70"/>
+    <col width="1.4" customWidth="1" min="71" max="71"/>
+    <col width="1.4" customWidth="1" min="72" max="72"/>
+    <col width="1.4" customWidth="1" min="73" max="73"/>
+    <col width="1.4" customWidth="1" min="74" max="74"/>
+    <col width="1.4" customWidth="1" min="75" max="75"/>
+    <col width="1.4" customWidth="1" min="76" max="76"/>
+    <col width="1.4" customWidth="1" min="77" max="77"/>
+    <col width="1.4" customWidth="1" min="78" max="78"/>
+    <col width="1.4" customWidth="1" min="79" max="79"/>
+    <col width="1.4" customWidth="1" min="80" max="80"/>
+    <col width="1.4" customWidth="1" min="81" max="81"/>
+    <col width="1.4" customWidth="1" min="82" max="82"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
@@ -3733,7 +4594,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>1 kare = 0.5 m  |  Plan boyutu (varsayilan): 25 m x 18 m</t>
+          <t>1 kare = 0.5 m  |  Plan boyutu (varsayilan): 40 m x 18 m</t>
         </is>
       </c>
     </row>
@@ -3787,7 +4648,38 @@
       <c r="AV7" s="42" t="n"/>
       <c r="AW7" s="42" t="n"/>
       <c r="AX7" s="42" t="n"/>
-      <c r="AY7" s="43" t="n"/>
+      <c r="AY7" s="42" t="n"/>
+      <c r="AZ7" s="42" t="n"/>
+      <c r="BA7" s="42" t="n"/>
+      <c r="BB7" s="42" t="n"/>
+      <c r="BC7" s="42" t="n"/>
+      <c r="BD7" s="42" t="n"/>
+      <c r="BE7" s="42" t="n"/>
+      <c r="BF7" s="42" t="n"/>
+      <c r="BG7" s="42" t="n"/>
+      <c r="BH7" s="42" t="n"/>
+      <c r="BI7" s="42" t="n"/>
+      <c r="BJ7" s="42" t="n"/>
+      <c r="BK7" s="42" t="n"/>
+      <c r="BL7" s="42" t="n"/>
+      <c r="BM7" s="42" t="n"/>
+      <c r="BN7" s="42" t="n"/>
+      <c r="BO7" s="42" t="n"/>
+      <c r="BP7" s="42" t="n"/>
+      <c r="BQ7" s="42" t="n"/>
+      <c r="BR7" s="42" t="n"/>
+      <c r="BS7" s="42" t="n"/>
+      <c r="BT7" s="42" t="n"/>
+      <c r="BU7" s="42" t="n"/>
+      <c r="BV7" s="42" t="n"/>
+      <c r="BW7" s="42" t="n"/>
+      <c r="BX7" s="42" t="n"/>
+      <c r="BY7" s="42" t="n"/>
+      <c r="BZ7" s="42" t="n"/>
+      <c r="CA7" s="42" t="n"/>
+      <c r="CB7" s="42" t="n"/>
+      <c r="CC7" s="42" t="n"/>
+      <c r="CD7" s="43" t="n"/>
     </row>
     <row r="8" ht="15" customHeight="1">
       <c r="B8" s="44" t="n"/>
@@ -3839,7 +4731,38 @@
       <c r="AV8" s="45" t="n"/>
       <c r="AW8" s="45" t="n"/>
       <c r="AX8" s="45" t="n"/>
-      <c r="AY8" s="46" t="n"/>
+      <c r="AY8" s="45" t="n"/>
+      <c r="AZ8" s="45" t="n"/>
+      <c r="BA8" s="45" t="n"/>
+      <c r="BB8" s="45" t="n"/>
+      <c r="BC8" s="45" t="n"/>
+      <c r="BD8" s="45" t="n"/>
+      <c r="BE8" s="45" t="n"/>
+      <c r="BF8" s="45" t="n"/>
+      <c r="BG8" s="45" t="n"/>
+      <c r="BH8" s="45" t="n"/>
+      <c r="BI8" s="45" t="n"/>
+      <c r="BJ8" s="45" t="n"/>
+      <c r="BK8" s="45" t="n"/>
+      <c r="BL8" s="45" t="n"/>
+      <c r="BM8" s="45" t="n"/>
+      <c r="BN8" s="45" t="n"/>
+      <c r="BO8" s="45" t="n"/>
+      <c r="BP8" s="45" t="n"/>
+      <c r="BQ8" s="45" t="n"/>
+      <c r="BR8" s="45" t="n"/>
+      <c r="BS8" s="45" t="n"/>
+      <c r="BT8" s="45" t="n"/>
+      <c r="BU8" s="45" t="n"/>
+      <c r="BV8" s="45" t="n"/>
+      <c r="BW8" s="45" t="n"/>
+      <c r="BX8" s="45" t="n"/>
+      <c r="BY8" s="45" t="n"/>
+      <c r="BZ8" s="45" t="n"/>
+      <c r="CA8" s="45" t="n"/>
+      <c r="CB8" s="45" t="n"/>
+      <c r="CC8" s="45" t="n"/>
+      <c r="CD8" s="46" t="n"/>
     </row>
     <row r="9" ht="15" customHeight="1">
       <c r="B9" s="44" t="n"/>
@@ -3891,7 +4814,38 @@
       <c r="AV9" s="45" t="n"/>
       <c r="AW9" s="45" t="n"/>
       <c r="AX9" s="45" t="n"/>
-      <c r="AY9" s="46" t="n"/>
+      <c r="AY9" s="45" t="n"/>
+      <c r="AZ9" s="45" t="n"/>
+      <c r="BA9" s="45" t="n"/>
+      <c r="BB9" s="45" t="n"/>
+      <c r="BC9" s="45" t="n"/>
+      <c r="BD9" s="45" t="n"/>
+      <c r="BE9" s="45" t="n"/>
+      <c r="BF9" s="45" t="n"/>
+      <c r="BG9" s="45" t="n"/>
+      <c r="BH9" s="45" t="n"/>
+      <c r="BI9" s="45" t="n"/>
+      <c r="BJ9" s="45" t="n"/>
+      <c r="BK9" s="45" t="n"/>
+      <c r="BL9" s="45" t="n"/>
+      <c r="BM9" s="45" t="n"/>
+      <c r="BN9" s="45" t="n"/>
+      <c r="BO9" s="45" t="n"/>
+      <c r="BP9" s="45" t="n"/>
+      <c r="BQ9" s="45" t="n"/>
+      <c r="BR9" s="45" t="n"/>
+      <c r="BS9" s="45" t="n"/>
+      <c r="BT9" s="45" t="n"/>
+      <c r="BU9" s="45" t="n"/>
+      <c r="BV9" s="45" t="n"/>
+      <c r="BW9" s="45" t="n"/>
+      <c r="BX9" s="45" t="n"/>
+      <c r="BY9" s="45" t="n"/>
+      <c r="BZ9" s="45" t="n"/>
+      <c r="CA9" s="45" t="n"/>
+      <c r="CB9" s="45" t="n"/>
+      <c r="CC9" s="45" t="n"/>
+      <c r="CD9" s="46" t="n"/>
     </row>
     <row r="10" ht="15" customHeight="1">
       <c r="B10" s="44" t="n"/>
@@ -3903,47 +4857,78 @@
       <c r="H10" s="47" t="n"/>
       <c r="I10" s="47" t="n"/>
       <c r="J10" s="47" t="n"/>
-      <c r="K10" s="47" t="n"/>
-      <c r="L10" s="48" t="n"/>
+      <c r="K10" s="48" t="n"/>
+      <c r="L10" s="47" t="n"/>
       <c r="M10" s="47" t="n"/>
-      <c r="N10" s="47" t="n"/>
+      <c r="N10" s="48" t="n"/>
       <c r="O10" s="47" t="n"/>
       <c r="P10" s="47" t="n"/>
-      <c r="Q10" s="47" t="n"/>
+      <c r="Q10" s="48" t="n"/>
       <c r="R10" s="47" t="n"/>
       <c r="S10" s="47" t="n"/>
-      <c r="T10" s="47" t="n"/>
+      <c r="T10" s="48" t="n"/>
       <c r="U10" s="47" t="n"/>
       <c r="V10" s="47" t="n"/>
-      <c r="W10" s="47" t="n"/>
-      <c r="X10" s="48" t="n"/>
+      <c r="W10" s="48" t="n"/>
+      <c r="X10" s="47" t="n"/>
       <c r="Y10" s="47" t="n"/>
-      <c r="Z10" s="47" t="n"/>
+      <c r="Z10" s="48" t="n"/>
       <c r="AA10" s="47" t="n"/>
       <c r="AB10" s="47" t="n"/>
-      <c r="AC10" s="47" t="n"/>
+      <c r="AC10" s="48" t="n"/>
       <c r="AD10" s="47" t="n"/>
       <c r="AE10" s="47" t="n"/>
-      <c r="AF10" s="47" t="n"/>
+      <c r="AF10" s="48" t="n"/>
       <c r="AG10" s="47" t="n"/>
       <c r="AH10" s="47" t="n"/>
-      <c r="AI10" s="47" t="n"/>
-      <c r="AJ10" s="48" t="n"/>
+      <c r="AI10" s="48" t="n"/>
+      <c r="AJ10" s="47" t="n"/>
       <c r="AK10" s="47" t="n"/>
-      <c r="AL10" s="47" t="n"/>
+      <c r="AL10" s="48" t="n"/>
       <c r="AM10" s="47" t="n"/>
       <c r="AN10" s="47" t="n"/>
-      <c r="AO10" s="47" t="n"/>
+      <c r="AO10" s="48" t="n"/>
       <c r="AP10" s="47" t="n"/>
       <c r="AQ10" s="47" t="n"/>
-      <c r="AR10" s="47" t="n"/>
+      <c r="AR10" s="48" t="n"/>
       <c r="AS10" s="47" t="n"/>
-      <c r="AT10" s="45" t="n"/>
-      <c r="AU10" s="45" t="n"/>
-      <c r="AV10" s="45" t="n"/>
-      <c r="AW10" s="45" t="n"/>
-      <c r="AX10" s="45" t="n"/>
-      <c r="AY10" s="46" t="n"/>
+      <c r="AT10" s="47" t="n"/>
+      <c r="AU10" s="48" t="n"/>
+      <c r="AV10" s="47" t="n"/>
+      <c r="AW10" s="47" t="n"/>
+      <c r="AX10" s="48" t="n"/>
+      <c r="AY10" s="47" t="n"/>
+      <c r="AZ10" s="47" t="n"/>
+      <c r="BA10" s="48" t="n"/>
+      <c r="BB10" s="47" t="n"/>
+      <c r="BC10" s="47" t="n"/>
+      <c r="BD10" s="48" t="n"/>
+      <c r="BE10" s="47" t="n"/>
+      <c r="BF10" s="47" t="n"/>
+      <c r="BG10" s="48" t="n"/>
+      <c r="BH10" s="47" t="n"/>
+      <c r="BI10" s="47" t="n"/>
+      <c r="BJ10" s="48" t="n"/>
+      <c r="BK10" s="47" t="n"/>
+      <c r="BL10" s="47" t="n"/>
+      <c r="BM10" s="48" t="n"/>
+      <c r="BN10" s="47" t="n"/>
+      <c r="BO10" s="47" t="n"/>
+      <c r="BP10" s="48" t="n"/>
+      <c r="BQ10" s="47" t="n"/>
+      <c r="BR10" s="47" t="n"/>
+      <c r="BS10" s="47" t="n"/>
+      <c r="BT10" s="47" t="n"/>
+      <c r="BU10" s="47" t="n"/>
+      <c r="BV10" s="47" t="n"/>
+      <c r="BW10" s="47" t="n"/>
+      <c r="BX10" s="47" t="n"/>
+      <c r="BY10" s="45" t="n"/>
+      <c r="BZ10" s="45" t="n"/>
+      <c r="CA10" s="45" t="n"/>
+      <c r="CB10" s="45" t="n"/>
+      <c r="CC10" s="45" t="n"/>
+      <c r="CD10" s="46" t="n"/>
     </row>
     <row r="11" ht="15" customHeight="1">
       <c r="B11" s="44" t="n"/>
@@ -3958,50 +4943,81 @@
       <c r="H11" s="45" t="n"/>
       <c r="I11" s="45" t="n"/>
       <c r="J11" s="45" t="n"/>
-      <c r="K11" s="45" t="n"/>
-      <c r="L11" s="50" t="n"/>
+      <c r="K11" s="50" t="n"/>
+      <c r="L11" s="45" t="n"/>
       <c r="M11" s="45" t="n"/>
-      <c r="N11" s="45" t="n"/>
+      <c r="N11" s="50" t="n"/>
       <c r="O11" s="45" t="n"/>
       <c r="P11" s="45" t="n"/>
-      <c r="Q11" s="45" t="n"/>
+      <c r="Q11" s="50" t="n"/>
       <c r="R11" s="45" t="n"/>
       <c r="S11" s="45" t="n"/>
-      <c r="T11" s="45" t="n"/>
+      <c r="T11" s="50" t="n"/>
       <c r="U11" s="45" t="n"/>
       <c r="V11" s="45" t="n"/>
-      <c r="W11" s="45" t="n"/>
-      <c r="X11" s="50" t="n"/>
+      <c r="W11" s="50" t="n"/>
+      <c r="X11" s="45" t="n"/>
       <c r="Y11" s="45" t="n"/>
-      <c r="Z11" s="45" t="n"/>
+      <c r="Z11" s="50" t="n"/>
       <c r="AA11" s="45" t="n"/>
       <c r="AB11" s="45" t="n"/>
-      <c r="AC11" s="45" t="n"/>
+      <c r="AC11" s="50" t="n"/>
       <c r="AD11" s="45" t="n"/>
       <c r="AE11" s="45" t="n"/>
-      <c r="AF11" s="45" t="n"/>
+      <c r="AF11" s="50" t="n"/>
       <c r="AG11" s="45" t="n"/>
       <c r="AH11" s="45" t="n"/>
-      <c r="AI11" s="45" t="n"/>
-      <c r="AJ11" s="50" t="n"/>
+      <c r="AI11" s="50" t="n"/>
+      <c r="AJ11" s="45" t="n"/>
       <c r="AK11" s="45" t="n"/>
-      <c r="AL11" s="45" t="n"/>
+      <c r="AL11" s="50" t="n"/>
       <c r="AM11" s="45" t="n"/>
       <c r="AN11" s="45" t="n"/>
-      <c r="AO11" s="45" t="n"/>
+      <c r="AO11" s="50" t="n"/>
       <c r="AP11" s="45" t="n"/>
       <c r="AQ11" s="45" t="n"/>
-      <c r="AR11" s="45" t="n"/>
+      <c r="AR11" s="50" t="n"/>
       <c r="AS11" s="45" t="n"/>
       <c r="AT11" s="45" t="n"/>
-      <c r="AU11" s="49">
+      <c r="AU11" s="50" t="n"/>
+      <c r="AV11" s="45" t="n"/>
+      <c r="AW11" s="45" t="n"/>
+      <c r="AX11" s="50" t="n"/>
+      <c r="AY11" s="45" t="n"/>
+      <c r="AZ11" s="45" t="n"/>
+      <c r="BA11" s="50" t="n"/>
+      <c r="BB11" s="45" t="n"/>
+      <c r="BC11" s="45" t="n"/>
+      <c r="BD11" s="50" t="n"/>
+      <c r="BE11" s="45" t="n"/>
+      <c r="BF11" s="45" t="n"/>
+      <c r="BG11" s="50" t="n"/>
+      <c r="BH11" s="45" t="n"/>
+      <c r="BI11" s="45" t="n"/>
+      <c r="BJ11" s="50" t="n"/>
+      <c r="BK11" s="45" t="n"/>
+      <c r="BL11" s="45" t="n"/>
+      <c r="BM11" s="50" t="n"/>
+      <c r="BN11" s="45" t="n"/>
+      <c r="BO11" s="45" t="n"/>
+      <c r="BP11" s="50" t="n"/>
+      <c r="BQ11" s="45" t="n"/>
+      <c r="BR11" s="45" t="n"/>
+      <c r="BS11" s="45" t="n"/>
+      <c r="BT11" s="45" t="n"/>
+      <c r="BU11" s="45" t="n"/>
+      <c r="BV11" s="45" t="n"/>
+      <c r="BW11" s="45" t="n"/>
+      <c r="BX11" s="45" t="n"/>
+      <c r="BY11" s="45" t="n"/>
+      <c r="BZ11" s="49">
         <f>'Fan Secimi'!B14</f>
         <v/>
       </c>
-      <c r="AV11" s="51" t="n"/>
-      <c r="AW11" s="51" t="n"/>
-      <c r="AX11" s="52" t="n"/>
-      <c r="AY11" s="46" t="n"/>
+      <c r="CA11" s="51" t="n"/>
+      <c r="CB11" s="51" t="n"/>
+      <c r="CC11" s="52" t="n"/>
+      <c r="CD11" s="46" t="n"/>
     </row>
     <row r="12" ht="15" customHeight="1">
       <c r="B12" s="44" t="n"/>
@@ -4013,47 +5029,78 @@
       <c r="H12" s="45" t="n"/>
       <c r="I12" s="45" t="n"/>
       <c r="J12" s="45" t="n"/>
-      <c r="K12" s="45" t="n"/>
-      <c r="L12" s="50" t="n"/>
+      <c r="K12" s="50" t="n"/>
+      <c r="L12" s="45" t="n"/>
       <c r="M12" s="45" t="n"/>
-      <c r="N12" s="45" t="n"/>
+      <c r="N12" s="50" t="n"/>
       <c r="O12" s="45" t="n"/>
       <c r="P12" s="45" t="n"/>
-      <c r="Q12" s="45" t="n"/>
+      <c r="Q12" s="50" t="n"/>
       <c r="R12" s="45" t="n"/>
       <c r="S12" s="45" t="n"/>
-      <c r="T12" s="45" t="n"/>
+      <c r="T12" s="50" t="n"/>
       <c r="U12" s="45" t="n"/>
       <c r="V12" s="45" t="n"/>
-      <c r="W12" s="45" t="n"/>
-      <c r="X12" s="50" t="n"/>
+      <c r="W12" s="50" t="n"/>
+      <c r="X12" s="45" t="n"/>
       <c r="Y12" s="45" t="n"/>
-      <c r="Z12" s="45" t="n"/>
+      <c r="Z12" s="50" t="n"/>
       <c r="AA12" s="45" t="n"/>
       <c r="AB12" s="45" t="n"/>
-      <c r="AC12" s="45" t="n"/>
+      <c r="AC12" s="50" t="n"/>
       <c r="AD12" s="45" t="n"/>
       <c r="AE12" s="45" t="n"/>
-      <c r="AF12" s="45" t="n"/>
+      <c r="AF12" s="50" t="n"/>
       <c r="AG12" s="45" t="n"/>
       <c r="AH12" s="45" t="n"/>
-      <c r="AI12" s="45" t="n"/>
-      <c r="AJ12" s="50" t="n"/>
+      <c r="AI12" s="50" t="n"/>
+      <c r="AJ12" s="45" t="n"/>
       <c r="AK12" s="45" t="n"/>
-      <c r="AL12" s="45" t="n"/>
+      <c r="AL12" s="50" t="n"/>
       <c r="AM12" s="45" t="n"/>
       <c r="AN12" s="45" t="n"/>
-      <c r="AO12" s="45" t="n"/>
+      <c r="AO12" s="50" t="n"/>
       <c r="AP12" s="45" t="n"/>
       <c r="AQ12" s="45" t="n"/>
-      <c r="AR12" s="45" t="n"/>
+      <c r="AR12" s="50" t="n"/>
       <c r="AS12" s="45" t="n"/>
       <c r="AT12" s="45" t="n"/>
-      <c r="AU12" s="45" t="n"/>
+      <c r="AU12" s="50" t="n"/>
       <c r="AV12" s="45" t="n"/>
       <c r="AW12" s="45" t="n"/>
-      <c r="AX12" s="45" t="n"/>
-      <c r="AY12" s="46" t="n"/>
+      <c r="AX12" s="50" t="n"/>
+      <c r="AY12" s="45" t="n"/>
+      <c r="AZ12" s="45" t="n"/>
+      <c r="BA12" s="50" t="n"/>
+      <c r="BB12" s="45" t="n"/>
+      <c r="BC12" s="45" t="n"/>
+      <c r="BD12" s="50" t="n"/>
+      <c r="BE12" s="45" t="n"/>
+      <c r="BF12" s="45" t="n"/>
+      <c r="BG12" s="50" t="n"/>
+      <c r="BH12" s="45" t="n"/>
+      <c r="BI12" s="45" t="n"/>
+      <c r="BJ12" s="50" t="n"/>
+      <c r="BK12" s="45" t="n"/>
+      <c r="BL12" s="45" t="n"/>
+      <c r="BM12" s="50" t="n"/>
+      <c r="BN12" s="45" t="n"/>
+      <c r="BO12" s="45" t="n"/>
+      <c r="BP12" s="50" t="n"/>
+      <c r="BQ12" s="45" t="n"/>
+      <c r="BR12" s="45" t="n"/>
+      <c r="BS12" s="45" t="n"/>
+      <c r="BT12" s="45" t="n"/>
+      <c r="BU12" s="45" t="n"/>
+      <c r="BV12" s="45" t="n"/>
+      <c r="BW12" s="45" t="n"/>
+      <c r="BX12" s="45" t="n"/>
+      <c r="BY12" s="45" t="n"/>
+      <c r="BZ12" s="45" t="n"/>
+      <c r="CA12" s="45" t="n"/>
+      <c r="CB12" s="45" t="n"/>
+      <c r="CC12" s="45" t="n"/>
+      <c r="CD12" s="46" t="n"/>
     </row>
     <row r="13" ht="15" customHeight="1">
       <c r="B13" s="44" t="n"/>
@@ -4065,47 +5112,78 @@
       <c r="H13" s="45" t="n"/>
       <c r="I13" s="45" t="n"/>
       <c r="J13" s="45" t="n"/>
-      <c r="K13" s="45" t="n"/>
-      <c r="L13" s="50" t="n"/>
+      <c r="K13" s="50" t="n"/>
+      <c r="L13" s="45" t="n"/>
       <c r="M13" s="45" t="n"/>
-      <c r="N13" s="45" t="n"/>
+      <c r="N13" s="50" t="n"/>
       <c r="O13" s="45" t="n"/>
       <c r="P13" s="45" t="n"/>
-      <c r="Q13" s="45" t="n"/>
+      <c r="Q13" s="50" t="n"/>
       <c r="R13" s="45" t="n"/>
       <c r="S13" s="45" t="n"/>
-      <c r="T13" s="45" t="n"/>
+      <c r="T13" s="50" t="n"/>
       <c r="U13" s="45" t="n"/>
       <c r="V13" s="45" t="n"/>
-      <c r="W13" s="45" t="n"/>
-      <c r="X13" s="50" t="n"/>
+      <c r="W13" s="50" t="n"/>
+      <c r="X13" s="45" t="n"/>
       <c r="Y13" s="45" t="n"/>
-      <c r="Z13" s="45" t="n"/>
+      <c r="Z13" s="50" t="n"/>
       <c r="AA13" s="45" t="n"/>
       <c r="AB13" s="45" t="n"/>
-      <c r="AC13" s="45" t="n"/>
+      <c r="AC13" s="50" t="n"/>
       <c r="AD13" s="45" t="n"/>
       <c r="AE13" s="45" t="n"/>
-      <c r="AF13" s="45" t="n"/>
+      <c r="AF13" s="50" t="n"/>
       <c r="AG13" s="45" t="n"/>
       <c r="AH13" s="45" t="n"/>
-      <c r="AI13" s="45" t="n"/>
-      <c r="AJ13" s="50" t="n"/>
+      <c r="AI13" s="50" t="n"/>
+      <c r="AJ13" s="45" t="n"/>
       <c r="AK13" s="45" t="n"/>
-      <c r="AL13" s="45" t="n"/>
+      <c r="AL13" s="50" t="n"/>
       <c r="AM13" s="45" t="n"/>
       <c r="AN13" s="45" t="n"/>
-      <c r="AO13" s="45" t="n"/>
+      <c r="AO13" s="50" t="n"/>
       <c r="AP13" s="45" t="n"/>
       <c r="AQ13" s="45" t="n"/>
-      <c r="AR13" s="45" t="n"/>
+      <c r="AR13" s="50" t="n"/>
       <c r="AS13" s="45" t="n"/>
       <c r="AT13" s="45" t="n"/>
-      <c r="AU13" s="45" t="n"/>
+      <c r="AU13" s="50" t="n"/>
       <c r="AV13" s="45" t="n"/>
       <c r="AW13" s="45" t="n"/>
-      <c r="AX13" s="45" t="n"/>
-      <c r="AY13" s="46" t="n"/>
+      <c r="AX13" s="50" t="n"/>
+      <c r="AY13" s="45" t="n"/>
+      <c r="AZ13" s="45" t="n"/>
+      <c r="BA13" s="50" t="n"/>
+      <c r="BB13" s="45" t="n"/>
+      <c r="BC13" s="45" t="n"/>
+      <c r="BD13" s="50" t="n"/>
+      <c r="BE13" s="45" t="n"/>
+      <c r="BF13" s="45" t="n"/>
+      <c r="BG13" s="50" t="n"/>
+      <c r="BH13" s="45" t="n"/>
+      <c r="BI13" s="45" t="n"/>
+      <c r="BJ13" s="50" t="n"/>
+      <c r="BK13" s="45" t="n"/>
+      <c r="BL13" s="45" t="n"/>
+      <c r="BM13" s="50" t="n"/>
+      <c r="BN13" s="45" t="n"/>
+      <c r="BO13" s="45" t="n"/>
+      <c r="BP13" s="50" t="n"/>
+      <c r="BQ13" s="45" t="n"/>
+      <c r="BR13" s="45" t="n"/>
+      <c r="BS13" s="45" t="n"/>
+      <c r="BT13" s="45" t="n"/>
+      <c r="BU13" s="45" t="n"/>
+      <c r="BV13" s="45" t="n"/>
+      <c r="BW13" s="45" t="n"/>
+      <c r="BX13" s="45" t="n"/>
+      <c r="BY13" s="45" t="n"/>
+      <c r="BZ13" s="45" t="n"/>
+      <c r="CA13" s="45" t="n"/>
+      <c r="CB13" s="45" t="n"/>
+      <c r="CC13" s="45" t="n"/>
+      <c r="CD13" s="46" t="n"/>
     </row>
     <row r="14" ht="15" customHeight="1">
       <c r="B14" s="44" t="n"/>
@@ -4117,47 +5195,78 @@
       <c r="H14" s="45" t="n"/>
       <c r="I14" s="45" t="n"/>
       <c r="J14" s="45" t="n"/>
-      <c r="K14" s="45" t="n"/>
-      <c r="L14" s="50" t="n"/>
+      <c r="K14" s="50" t="n"/>
+      <c r="L14" s="45" t="n"/>
       <c r="M14" s="45" t="n"/>
-      <c r="N14" s="45" t="n"/>
+      <c r="N14" s="50" t="n"/>
       <c r="O14" s="45" t="n"/>
       <c r="P14" s="45" t="n"/>
-      <c r="Q14" s="45" t="n"/>
+      <c r="Q14" s="50" t="n"/>
       <c r="R14" s="45" t="n"/>
       <c r="S14" s="45" t="n"/>
-      <c r="T14" s="45" t="n"/>
+      <c r="T14" s="50" t="n"/>
       <c r="U14" s="45" t="n"/>
       <c r="V14" s="45" t="n"/>
-      <c r="W14" s="45" t="n"/>
-      <c r="X14" s="50" t="n"/>
+      <c r="W14" s="50" t="n"/>
+      <c r="X14" s="45" t="n"/>
       <c r="Y14" s="45" t="n"/>
-      <c r="Z14" s="45" t="n"/>
+      <c r="Z14" s="50" t="n"/>
       <c r="AA14" s="45" t="n"/>
       <c r="AB14" s="45" t="n"/>
-      <c r="AC14" s="45" t="n"/>
+      <c r="AC14" s="50" t="n"/>
       <c r="AD14" s="45" t="n"/>
       <c r="AE14" s="45" t="n"/>
-      <c r="AF14" s="45" t="n"/>
+      <c r="AF14" s="50" t="n"/>
       <c r="AG14" s="45" t="n"/>
       <c r="AH14" s="45" t="n"/>
-      <c r="AI14" s="45" t="n"/>
-      <c r="AJ14" s="50" t="n"/>
+      <c r="AI14" s="50" t="n"/>
+      <c r="AJ14" s="45" t="n"/>
       <c r="AK14" s="45" t="n"/>
-      <c r="AL14" s="45" t="n"/>
+      <c r="AL14" s="50" t="n"/>
       <c r="AM14" s="45" t="n"/>
       <c r="AN14" s="45" t="n"/>
-      <c r="AO14" s="45" t="n"/>
+      <c r="AO14" s="50" t="n"/>
       <c r="AP14" s="45" t="n"/>
       <c r="AQ14" s="45" t="n"/>
-      <c r="AR14" s="45" t="n"/>
+      <c r="AR14" s="50" t="n"/>
       <c r="AS14" s="45" t="n"/>
       <c r="AT14" s="45" t="n"/>
-      <c r="AU14" s="45" t="n"/>
+      <c r="AU14" s="50" t="n"/>
       <c r="AV14" s="45" t="n"/>
       <c r="AW14" s="45" t="n"/>
-      <c r="AX14" s="45" t="n"/>
-      <c r="AY14" s="46" t="n"/>
+      <c r="AX14" s="50" t="n"/>
+      <c r="AY14" s="45" t="n"/>
+      <c r="AZ14" s="45" t="n"/>
+      <c r="BA14" s="50" t="n"/>
+      <c r="BB14" s="45" t="n"/>
+      <c r="BC14" s="45" t="n"/>
+      <c r="BD14" s="50" t="n"/>
+      <c r="BE14" s="45" t="n"/>
+      <c r="BF14" s="45" t="n"/>
+      <c r="BG14" s="50" t="n"/>
+      <c r="BH14" s="45" t="n"/>
+      <c r="BI14" s="45" t="n"/>
+      <c r="BJ14" s="50" t="n"/>
+      <c r="BK14" s="45" t="n"/>
+      <c r="BL14" s="45" t="n"/>
+      <c r="BM14" s="50" t="n"/>
+      <c r="BN14" s="45" t="n"/>
+      <c r="BO14" s="45" t="n"/>
+      <c r="BP14" s="50" t="n"/>
+      <c r="BQ14" s="45" t="n"/>
+      <c r="BR14" s="45" t="n"/>
+      <c r="BS14" s="45" t="n"/>
+      <c r="BT14" s="45" t="n"/>
+      <c r="BU14" s="45" t="n"/>
+      <c r="BV14" s="45" t="n"/>
+      <c r="BW14" s="45" t="n"/>
+      <c r="BX14" s="45" t="n"/>
+      <c r="BY14" s="45" t="n"/>
+      <c r="BZ14" s="45" t="n"/>
+      <c r="CA14" s="45" t="n"/>
+      <c r="CB14" s="45" t="n"/>
+      <c r="CC14" s="45" t="n"/>
+      <c r="CD14" s="46" t="n"/>
     </row>
     <row r="15" ht="15" customHeight="1">
       <c r="B15" s="44" t="n"/>
@@ -4169,47 +5278,78 @@
       <c r="H15" s="45" t="n"/>
       <c r="I15" s="45" t="n"/>
       <c r="J15" s="45" t="n"/>
-      <c r="K15" s="45" t="n"/>
-      <c r="L15" s="50" t="n"/>
+      <c r="K15" s="50" t="n"/>
+      <c r="L15" s="45" t="n"/>
       <c r="M15" s="45" t="n"/>
-      <c r="N15" s="45" t="n"/>
+      <c r="N15" s="50" t="n"/>
       <c r="O15" s="45" t="n"/>
       <c r="P15" s="45" t="n"/>
-      <c r="Q15" s="45" t="n"/>
+      <c r="Q15" s="50" t="n"/>
       <c r="R15" s="45" t="n"/>
       <c r="S15" s="45" t="n"/>
-      <c r="T15" s="45" t="n"/>
+      <c r="T15" s="50" t="n"/>
       <c r="U15" s="45" t="n"/>
       <c r="V15" s="45" t="n"/>
-      <c r="W15" s="45" t="n"/>
-      <c r="X15" s="50" t="n"/>
+      <c r="W15" s="50" t="n"/>
+      <c r="X15" s="45" t="n"/>
       <c r="Y15" s="45" t="n"/>
-      <c r="Z15" s="45" t="n"/>
+      <c r="Z15" s="50" t="n"/>
       <c r="AA15" s="45" t="n"/>
       <c r="AB15" s="45" t="n"/>
-      <c r="AC15" s="45" t="n"/>
+      <c r="AC15" s="50" t="n"/>
       <c r="AD15" s="45" t="n"/>
       <c r="AE15" s="45" t="n"/>
-      <c r="AF15" s="45" t="n"/>
+      <c r="AF15" s="50" t="n"/>
       <c r="AG15" s="45" t="n"/>
       <c r="AH15" s="45" t="n"/>
-      <c r="AI15" s="45" t="n"/>
-      <c r="AJ15" s="50" t="n"/>
+      <c r="AI15" s="50" t="n"/>
+      <c r="AJ15" s="45" t="n"/>
       <c r="AK15" s="45" t="n"/>
-      <c r="AL15" s="45" t="n"/>
+      <c r="AL15" s="50" t="n"/>
       <c r="AM15" s="45" t="n"/>
       <c r="AN15" s="45" t="n"/>
-      <c r="AO15" s="45" t="n"/>
+      <c r="AO15" s="50" t="n"/>
       <c r="AP15" s="45" t="n"/>
       <c r="AQ15" s="45" t="n"/>
-      <c r="AR15" s="45" t="n"/>
+      <c r="AR15" s="50" t="n"/>
       <c r="AS15" s="45" t="n"/>
       <c r="AT15" s="45" t="n"/>
-      <c r="AU15" s="45" t="n"/>
+      <c r="AU15" s="50" t="n"/>
       <c r="AV15" s="45" t="n"/>
       <c r="AW15" s="45" t="n"/>
-      <c r="AX15" s="45" t="n"/>
-      <c r="AY15" s="46" t="n"/>
+      <c r="AX15" s="50" t="n"/>
+      <c r="AY15" s="45" t="n"/>
+      <c r="AZ15" s="45" t="n"/>
+      <c r="BA15" s="50" t="n"/>
+      <c r="BB15" s="45" t="n"/>
+      <c r="BC15" s="45" t="n"/>
+      <c r="BD15" s="50" t="n"/>
+      <c r="BE15" s="45" t="n"/>
+      <c r="BF15" s="45" t="n"/>
+      <c r="BG15" s="50" t="n"/>
+      <c r="BH15" s="45" t="n"/>
+      <c r="BI15" s="45" t="n"/>
+      <c r="BJ15" s="50" t="n"/>
+      <c r="BK15" s="45" t="n"/>
+      <c r="BL15" s="45" t="n"/>
+      <c r="BM15" s="50" t="n"/>
+      <c r="BN15" s="45" t="n"/>
+      <c r="BO15" s="45" t="n"/>
+      <c r="BP15" s="50" t="n"/>
+      <c r="BQ15" s="45" t="n"/>
+      <c r="BR15" s="45" t="n"/>
+      <c r="BS15" s="45" t="n"/>
+      <c r="BT15" s="45" t="n"/>
+      <c r="BU15" s="45" t="n"/>
+      <c r="BV15" s="45" t="n"/>
+      <c r="BW15" s="45" t="n"/>
+      <c r="BX15" s="45" t="n"/>
+      <c r="BY15" s="45" t="n"/>
+      <c r="BZ15" s="45" t="n"/>
+      <c r="CA15" s="45" t="n"/>
+      <c r="CB15" s="45" t="n"/>
+      <c r="CC15" s="45" t="n"/>
+      <c r="CD15" s="46" t="n"/>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="B16" s="44" t="n"/>
@@ -4221,47 +5361,78 @@
       <c r="H16" s="45" t="n"/>
       <c r="I16" s="45" t="n"/>
       <c r="J16" s="45" t="n"/>
-      <c r="K16" s="45" t="n"/>
-      <c r="L16" s="50" t="n"/>
+      <c r="K16" s="50" t="n"/>
+      <c r="L16" s="45" t="n"/>
       <c r="M16" s="45" t="n"/>
-      <c r="N16" s="45" t="n"/>
+      <c r="N16" s="50" t="n"/>
       <c r="O16" s="45" t="n"/>
       <c r="P16" s="45" t="n"/>
-      <c r="Q16" s="45" t="n"/>
+      <c r="Q16" s="50" t="n"/>
       <c r="R16" s="45" t="n"/>
       <c r="S16" s="45" t="n"/>
-      <c r="T16" s="45" t="n"/>
+      <c r="T16" s="50" t="n"/>
       <c r="U16" s="45" t="n"/>
       <c r="V16" s="45" t="n"/>
-      <c r="W16" s="45" t="n"/>
-      <c r="X16" s="50" t="n"/>
+      <c r="W16" s="50" t="n"/>
+      <c r="X16" s="45" t="n"/>
       <c r="Y16" s="45" t="n"/>
-      <c r="Z16" s="45" t="n"/>
+      <c r="Z16" s="50" t="n"/>
       <c r="AA16" s="45" t="n"/>
       <c r="AB16" s="45" t="n"/>
-      <c r="AC16" s="45" t="n"/>
+      <c r="AC16" s="50" t="n"/>
       <c r="AD16" s="45" t="n"/>
       <c r="AE16" s="45" t="n"/>
-      <c r="AF16" s="45" t="n"/>
+      <c r="AF16" s="50" t="n"/>
       <c r="AG16" s="45" t="n"/>
       <c r="AH16" s="45" t="n"/>
-      <c r="AI16" s="45" t="n"/>
-      <c r="AJ16" s="50" t="n"/>
+      <c r="AI16" s="50" t="n"/>
+      <c r="AJ16" s="45" t="n"/>
       <c r="AK16" s="45" t="n"/>
-      <c r="AL16" s="45" t="n"/>
+      <c r="AL16" s="50" t="n"/>
       <c r="AM16" s="45" t="n"/>
       <c r="AN16" s="45" t="n"/>
-      <c r="AO16" s="45" t="n"/>
+      <c r="AO16" s="50" t="n"/>
       <c r="AP16" s="45" t="n"/>
       <c r="AQ16" s="45" t="n"/>
-      <c r="AR16" s="45" t="n"/>
+      <c r="AR16" s="50" t="n"/>
       <c r="AS16" s="45" t="n"/>
       <c r="AT16" s="45" t="n"/>
-      <c r="AU16" s="45" t="n"/>
+      <c r="AU16" s="50" t="n"/>
       <c r="AV16" s="45" t="n"/>
       <c r="AW16" s="45" t="n"/>
-      <c r="AX16" s="45" t="n"/>
-      <c r="AY16" s="46" t="n"/>
+      <c r="AX16" s="50" t="n"/>
+      <c r="AY16" s="45" t="n"/>
+      <c r="AZ16" s="45" t="n"/>
+      <c r="BA16" s="50" t="n"/>
+      <c r="BB16" s="45" t="n"/>
+      <c r="BC16" s="45" t="n"/>
+      <c r="BD16" s="50" t="n"/>
+      <c r="BE16" s="45" t="n"/>
+      <c r="BF16" s="45" t="n"/>
+      <c r="BG16" s="50" t="n"/>
+      <c r="BH16" s="45" t="n"/>
+      <c r="BI16" s="45" t="n"/>
+      <c r="BJ16" s="50" t="n"/>
+      <c r="BK16" s="45" t="n"/>
+      <c r="BL16" s="45" t="n"/>
+      <c r="BM16" s="50" t="n"/>
+      <c r="BN16" s="45" t="n"/>
+      <c r="BO16" s="45" t="n"/>
+      <c r="BP16" s="50" t="n"/>
+      <c r="BQ16" s="45" t="n"/>
+      <c r="BR16" s="45" t="n"/>
+      <c r="BS16" s="45" t="n"/>
+      <c r="BT16" s="45" t="n"/>
+      <c r="BU16" s="45" t="n"/>
+      <c r="BV16" s="45" t="n"/>
+      <c r="BW16" s="45" t="n"/>
+      <c r="BX16" s="45" t="n"/>
+      <c r="BY16" s="45" t="n"/>
+      <c r="BZ16" s="45" t="n"/>
+      <c r="CA16" s="45" t="n"/>
+      <c r="CB16" s="45" t="n"/>
+      <c r="CC16" s="45" t="n"/>
+      <c r="CD16" s="46" t="n"/>
     </row>
     <row r="17" ht="15" customHeight="1">
       <c r="B17" s="44" t="n"/>
@@ -4273,47 +5444,78 @@
       <c r="H17" s="45" t="n"/>
       <c r="I17" s="45" t="n"/>
       <c r="J17" s="45" t="n"/>
-      <c r="K17" s="45" t="n"/>
-      <c r="L17" s="50" t="n"/>
+      <c r="K17" s="50" t="n"/>
+      <c r="L17" s="45" t="n"/>
       <c r="M17" s="45" t="n"/>
-      <c r="N17" s="45" t="n"/>
+      <c r="N17" s="50" t="n"/>
       <c r="O17" s="45" t="n"/>
       <c r="P17" s="45" t="n"/>
-      <c r="Q17" s="45" t="n"/>
+      <c r="Q17" s="50" t="n"/>
       <c r="R17" s="45" t="n"/>
       <c r="S17" s="45" t="n"/>
-      <c r="T17" s="45" t="n"/>
+      <c r="T17" s="50" t="n"/>
       <c r="U17" s="45" t="n"/>
       <c r="V17" s="45" t="n"/>
-      <c r="W17" s="45" t="n"/>
-      <c r="X17" s="50" t="n"/>
+      <c r="W17" s="50" t="n"/>
+      <c r="X17" s="45" t="n"/>
       <c r="Y17" s="45" t="n"/>
-      <c r="Z17" s="45" t="n"/>
+      <c r="Z17" s="50" t="n"/>
       <c r="AA17" s="45" t="n"/>
       <c r="AB17" s="45" t="n"/>
-      <c r="AC17" s="45" t="n"/>
+      <c r="AC17" s="50" t="n"/>
       <c r="AD17" s="45" t="n"/>
       <c r="AE17" s="45" t="n"/>
-      <c r="AF17" s="45" t="n"/>
+      <c r="AF17" s="50" t="n"/>
       <c r="AG17" s="45" t="n"/>
       <c r="AH17" s="45" t="n"/>
-      <c r="AI17" s="45" t="n"/>
-      <c r="AJ17" s="50" t="n"/>
+      <c r="AI17" s="50" t="n"/>
+      <c r="AJ17" s="45" t="n"/>
       <c r="AK17" s="45" t="n"/>
-      <c r="AL17" s="45" t="n"/>
+      <c r="AL17" s="50" t="n"/>
       <c r="AM17" s="45" t="n"/>
       <c r="AN17" s="45" t="n"/>
-      <c r="AO17" s="45" t="n"/>
+      <c r="AO17" s="50" t="n"/>
       <c r="AP17" s="45" t="n"/>
       <c r="AQ17" s="45" t="n"/>
-      <c r="AR17" s="45" t="n"/>
+      <c r="AR17" s="50" t="n"/>
       <c r="AS17" s="45" t="n"/>
       <c r="AT17" s="45" t="n"/>
-      <c r="AU17" s="45" t="n"/>
+      <c r="AU17" s="50" t="n"/>
       <c r="AV17" s="45" t="n"/>
       <c r="AW17" s="45" t="n"/>
-      <c r="AX17" s="45" t="n"/>
-      <c r="AY17" s="46" t="n"/>
+      <c r="AX17" s="50" t="n"/>
+      <c r="AY17" s="45" t="n"/>
+      <c r="AZ17" s="45" t="n"/>
+      <c r="BA17" s="50" t="n"/>
+      <c r="BB17" s="45" t="n"/>
+      <c r="BC17" s="45" t="n"/>
+      <c r="BD17" s="50" t="n"/>
+      <c r="BE17" s="45" t="n"/>
+      <c r="BF17" s="45" t="n"/>
+      <c r="BG17" s="50" t="n"/>
+      <c r="BH17" s="45" t="n"/>
+      <c r="BI17" s="45" t="n"/>
+      <c r="BJ17" s="50" t="n"/>
+      <c r="BK17" s="45" t="n"/>
+      <c r="BL17" s="45" t="n"/>
+      <c r="BM17" s="50" t="n"/>
+      <c r="BN17" s="45" t="n"/>
+      <c r="BO17" s="45" t="n"/>
+      <c r="BP17" s="50" t="n"/>
+      <c r="BQ17" s="45" t="n"/>
+      <c r="BR17" s="45" t="n"/>
+      <c r="BS17" s="45" t="n"/>
+      <c r="BT17" s="45" t="n"/>
+      <c r="BU17" s="45" t="n"/>
+      <c r="BV17" s="45" t="n"/>
+      <c r="BW17" s="45" t="n"/>
+      <c r="BX17" s="45" t="n"/>
+      <c r="BY17" s="45" t="n"/>
+      <c r="BZ17" s="45" t="n"/>
+      <c r="CA17" s="45" t="n"/>
+      <c r="CB17" s="45" t="n"/>
+      <c r="CC17" s="45" t="n"/>
+      <c r="CD17" s="46" t="n"/>
     </row>
     <row r="18" ht="15" customHeight="1">
       <c r="B18" s="44" t="n"/>
@@ -4325,47 +5527,78 @@
       <c r="H18" s="45" t="n"/>
       <c r="I18" s="45" t="n"/>
       <c r="J18" s="45" t="n"/>
-      <c r="K18" s="45" t="n"/>
-      <c r="L18" s="50" t="n"/>
+      <c r="K18" s="50" t="n"/>
+      <c r="L18" s="45" t="n"/>
       <c r="M18" s="45" t="n"/>
-      <c r="N18" s="45" t="n"/>
+      <c r="N18" s="50" t="n"/>
       <c r="O18" s="45" t="n"/>
       <c r="P18" s="45" t="n"/>
-      <c r="Q18" s="45" t="n"/>
+      <c r="Q18" s="50" t="n"/>
       <c r="R18" s="45" t="n"/>
       <c r="S18" s="45" t="n"/>
-      <c r="T18" s="45" t="n"/>
+      <c r="T18" s="50" t="n"/>
       <c r="U18" s="45" t="n"/>
       <c r="V18" s="45" t="n"/>
-      <c r="W18" s="45" t="n"/>
-      <c r="X18" s="50" t="n"/>
+      <c r="W18" s="50" t="n"/>
+      <c r="X18" s="45" t="n"/>
       <c r="Y18" s="45" t="n"/>
-      <c r="Z18" s="45" t="n"/>
+      <c r="Z18" s="50" t="n"/>
       <c r="AA18" s="45" t="n"/>
       <c r="AB18" s="45" t="n"/>
-      <c r="AC18" s="45" t="n"/>
+      <c r="AC18" s="50" t="n"/>
       <c r="AD18" s="45" t="n"/>
       <c r="AE18" s="45" t="n"/>
-      <c r="AF18" s="45" t="n"/>
+      <c r="AF18" s="50" t="n"/>
       <c r="AG18" s="45" t="n"/>
       <c r="AH18" s="45" t="n"/>
-      <c r="AI18" s="45" t="n"/>
-      <c r="AJ18" s="50" t="n"/>
+      <c r="AI18" s="50" t="n"/>
+      <c r="AJ18" s="45" t="n"/>
       <c r="AK18" s="45" t="n"/>
-      <c r="AL18" s="45" t="n"/>
+      <c r="AL18" s="50" t="n"/>
       <c r="AM18" s="45" t="n"/>
       <c r="AN18" s="45" t="n"/>
-      <c r="AO18" s="45" t="n"/>
+      <c r="AO18" s="50" t="n"/>
       <c r="AP18" s="45" t="n"/>
       <c r="AQ18" s="45" t="n"/>
-      <c r="AR18" s="45" t="n"/>
+      <c r="AR18" s="50" t="n"/>
       <c r="AS18" s="45" t="n"/>
       <c r="AT18" s="45" t="n"/>
-      <c r="AU18" s="45" t="n"/>
+      <c r="AU18" s="50" t="n"/>
       <c r="AV18" s="45" t="n"/>
       <c r="AW18" s="45" t="n"/>
-      <c r="AX18" s="45" t="n"/>
-      <c r="AY18" s="46" t="n"/>
+      <c r="AX18" s="50" t="n"/>
+      <c r="AY18" s="45" t="n"/>
+      <c r="AZ18" s="45" t="n"/>
+      <c r="BA18" s="50" t="n"/>
+      <c r="BB18" s="45" t="n"/>
+      <c r="BC18" s="45" t="n"/>
+      <c r="BD18" s="50" t="n"/>
+      <c r="BE18" s="45" t="n"/>
+      <c r="BF18" s="45" t="n"/>
+      <c r="BG18" s="50" t="n"/>
+      <c r="BH18" s="45" t="n"/>
+      <c r="BI18" s="45" t="n"/>
+      <c r="BJ18" s="50" t="n"/>
+      <c r="BK18" s="45" t="n"/>
+      <c r="BL18" s="45" t="n"/>
+      <c r="BM18" s="50" t="n"/>
+      <c r="BN18" s="45" t="n"/>
+      <c r="BO18" s="45" t="n"/>
+      <c r="BP18" s="50" t="n"/>
+      <c r="BQ18" s="45" t="n"/>
+      <c r="BR18" s="45" t="n"/>
+      <c r="BS18" s="45" t="n"/>
+      <c r="BT18" s="45" t="n"/>
+      <c r="BU18" s="45" t="n"/>
+      <c r="BV18" s="45" t="n"/>
+      <c r="BW18" s="45" t="n"/>
+      <c r="BX18" s="45" t="n"/>
+      <c r="BY18" s="45" t="n"/>
+      <c r="BZ18" s="45" t="n"/>
+      <c r="CA18" s="45" t="n"/>
+      <c r="CB18" s="45" t="n"/>
+      <c r="CC18" s="45" t="n"/>
+      <c r="CD18" s="46" t="n"/>
     </row>
     <row r="19" ht="15" customHeight="1">
       <c r="B19" s="44" t="n"/>
@@ -4377,47 +5610,78 @@
       <c r="H19" s="45" t="n"/>
       <c r="I19" s="45" t="n"/>
       <c r="J19" s="45" t="n"/>
-      <c r="K19" s="45" t="n"/>
-      <c r="L19" s="50" t="n"/>
+      <c r="K19" s="50" t="n"/>
+      <c r="L19" s="45" t="n"/>
       <c r="M19" s="45" t="n"/>
-      <c r="N19" s="45" t="n"/>
+      <c r="N19" s="50" t="n"/>
       <c r="O19" s="45" t="n"/>
       <c r="P19" s="45" t="n"/>
-      <c r="Q19" s="45" t="n"/>
+      <c r="Q19" s="50" t="n"/>
       <c r="R19" s="45" t="n"/>
       <c r="S19" s="45" t="n"/>
-      <c r="T19" s="45" t="n"/>
+      <c r="T19" s="50" t="n"/>
       <c r="U19" s="45" t="n"/>
       <c r="V19" s="45" t="n"/>
-      <c r="W19" s="45" t="n"/>
-      <c r="X19" s="50" t="n"/>
+      <c r="W19" s="50" t="n"/>
+      <c r="X19" s="45" t="n"/>
       <c r="Y19" s="45" t="n"/>
-      <c r="Z19" s="45" t="n"/>
+      <c r="Z19" s="50" t="n"/>
       <c r="AA19" s="45" t="n"/>
       <c r="AB19" s="45" t="n"/>
-      <c r="AC19" s="45" t="n"/>
+      <c r="AC19" s="50" t="n"/>
       <c r="AD19" s="45" t="n"/>
       <c r="AE19" s="45" t="n"/>
-      <c r="AF19" s="45" t="n"/>
+      <c r="AF19" s="50" t="n"/>
       <c r="AG19" s="45" t="n"/>
       <c r="AH19" s="45" t="n"/>
-      <c r="AI19" s="45" t="n"/>
-      <c r="AJ19" s="50" t="n"/>
+      <c r="AI19" s="50" t="n"/>
+      <c r="AJ19" s="45" t="n"/>
       <c r="AK19" s="45" t="n"/>
-      <c r="AL19" s="45" t="n"/>
+      <c r="AL19" s="50" t="n"/>
       <c r="AM19" s="45" t="n"/>
       <c r="AN19" s="45" t="n"/>
-      <c r="AO19" s="45" t="n"/>
+      <c r="AO19" s="50" t="n"/>
       <c r="AP19" s="45" t="n"/>
       <c r="AQ19" s="45" t="n"/>
-      <c r="AR19" s="45" t="n"/>
+      <c r="AR19" s="50" t="n"/>
       <c r="AS19" s="45" t="n"/>
       <c r="AT19" s="45" t="n"/>
-      <c r="AU19" s="45" t="n"/>
+      <c r="AU19" s="50" t="n"/>
       <c r="AV19" s="45" t="n"/>
       <c r="AW19" s="45" t="n"/>
-      <c r="AX19" s="45" t="n"/>
-      <c r="AY19" s="46" t="n"/>
+      <c r="AX19" s="50" t="n"/>
+      <c r="AY19" s="45" t="n"/>
+      <c r="AZ19" s="45" t="n"/>
+      <c r="BA19" s="50" t="n"/>
+      <c r="BB19" s="45" t="n"/>
+      <c r="BC19" s="45" t="n"/>
+      <c r="BD19" s="50" t="n"/>
+      <c r="BE19" s="45" t="n"/>
+      <c r="BF19" s="45" t="n"/>
+      <c r="BG19" s="50" t="n"/>
+      <c r="BH19" s="45" t="n"/>
+      <c r="BI19" s="45" t="n"/>
+      <c r="BJ19" s="50" t="n"/>
+      <c r="BK19" s="45" t="n"/>
+      <c r="BL19" s="45" t="n"/>
+      <c r="BM19" s="50" t="n"/>
+      <c r="BN19" s="45" t="n"/>
+      <c r="BO19" s="45" t="n"/>
+      <c r="BP19" s="50" t="n"/>
+      <c r="BQ19" s="45" t="n"/>
+      <c r="BR19" s="45" t="n"/>
+      <c r="BS19" s="45" t="n"/>
+      <c r="BT19" s="45" t="n"/>
+      <c r="BU19" s="45" t="n"/>
+      <c r="BV19" s="45" t="n"/>
+      <c r="BW19" s="45" t="n"/>
+      <c r="BX19" s="45" t="n"/>
+      <c r="BY19" s="45" t="n"/>
+      <c r="BZ19" s="45" t="n"/>
+      <c r="CA19" s="45" t="n"/>
+      <c r="CB19" s="45" t="n"/>
+      <c r="CC19" s="45" t="n"/>
+      <c r="CD19" s="46" t="n"/>
     </row>
     <row r="20" ht="15" customHeight="1">
       <c r="B20" s="44" t="n"/>
@@ -4429,47 +5693,78 @@
       <c r="H20" s="45" t="n"/>
       <c r="I20" s="45" t="n"/>
       <c r="J20" s="45" t="n"/>
-      <c r="K20" s="45" t="n"/>
-      <c r="L20" s="50" t="n"/>
+      <c r="K20" s="50" t="n"/>
+      <c r="L20" s="45" t="n"/>
       <c r="M20" s="45" t="n"/>
-      <c r="N20" s="45" t="n"/>
+      <c r="N20" s="50" t="n"/>
       <c r="O20" s="45" t="n"/>
       <c r="P20" s="45" t="n"/>
-      <c r="Q20" s="45" t="n"/>
+      <c r="Q20" s="50" t="n"/>
       <c r="R20" s="45" t="n"/>
       <c r="S20" s="45" t="n"/>
-      <c r="T20" s="45" t="n"/>
+      <c r="T20" s="50" t="n"/>
       <c r="U20" s="45" t="n"/>
       <c r="V20" s="45" t="n"/>
-      <c r="W20" s="45" t="n"/>
-      <c r="X20" s="50" t="n"/>
+      <c r="W20" s="50" t="n"/>
+      <c r="X20" s="45" t="n"/>
       <c r="Y20" s="45" t="n"/>
-      <c r="Z20" s="45" t="n"/>
+      <c r="Z20" s="50" t="n"/>
       <c r="AA20" s="45" t="n"/>
       <c r="AB20" s="45" t="n"/>
-      <c r="AC20" s="45" t="n"/>
+      <c r="AC20" s="50" t="n"/>
       <c r="AD20" s="45" t="n"/>
       <c r="AE20" s="45" t="n"/>
-      <c r="AF20" s="45" t="n"/>
+      <c r="AF20" s="50" t="n"/>
       <c r="AG20" s="45" t="n"/>
       <c r="AH20" s="45" t="n"/>
-      <c r="AI20" s="45" t="n"/>
-      <c r="AJ20" s="50" t="n"/>
+      <c r="AI20" s="50" t="n"/>
+      <c r="AJ20" s="45" t="n"/>
       <c r="AK20" s="45" t="n"/>
-      <c r="AL20" s="45" t="n"/>
+      <c r="AL20" s="50" t="n"/>
       <c r="AM20" s="45" t="n"/>
       <c r="AN20" s="45" t="n"/>
-      <c r="AO20" s="45" t="n"/>
+      <c r="AO20" s="50" t="n"/>
       <c r="AP20" s="45" t="n"/>
       <c r="AQ20" s="45" t="n"/>
-      <c r="AR20" s="45" t="n"/>
+      <c r="AR20" s="50" t="n"/>
       <c r="AS20" s="45" t="n"/>
       <c r="AT20" s="45" t="n"/>
-      <c r="AU20" s="45" t="n"/>
+      <c r="AU20" s="50" t="n"/>
       <c r="AV20" s="45" t="n"/>
       <c r="AW20" s="45" t="n"/>
-      <c r="AX20" s="45" t="n"/>
-      <c r="AY20" s="46" t="n"/>
+      <c r="AX20" s="50" t="n"/>
+      <c r="AY20" s="45" t="n"/>
+      <c r="AZ20" s="45" t="n"/>
+      <c r="BA20" s="50" t="n"/>
+      <c r="BB20" s="45" t="n"/>
+      <c r="BC20" s="45" t="n"/>
+      <c r="BD20" s="50" t="n"/>
+      <c r="BE20" s="45" t="n"/>
+      <c r="BF20" s="45" t="n"/>
+      <c r="BG20" s="50" t="n"/>
+      <c r="BH20" s="45" t="n"/>
+      <c r="BI20" s="45" t="n"/>
+      <c r="BJ20" s="50" t="n"/>
+      <c r="BK20" s="45" t="n"/>
+      <c r="BL20" s="45" t="n"/>
+      <c r="BM20" s="50" t="n"/>
+      <c r="BN20" s="45" t="n"/>
+      <c r="BO20" s="45" t="n"/>
+      <c r="BP20" s="50" t="n"/>
+      <c r="BQ20" s="45" t="n"/>
+      <c r="BR20" s="45" t="n"/>
+      <c r="BS20" s="45" t="n"/>
+      <c r="BT20" s="45" t="n"/>
+      <c r="BU20" s="45" t="n"/>
+      <c r="BV20" s="45" t="n"/>
+      <c r="BW20" s="45" t="n"/>
+      <c r="BX20" s="45" t="n"/>
+      <c r="BY20" s="45" t="n"/>
+      <c r="BZ20" s="45" t="n"/>
+      <c r="CA20" s="45" t="n"/>
+      <c r="CB20" s="45" t="n"/>
+      <c r="CC20" s="45" t="n"/>
+      <c r="CD20" s="46" t="n"/>
     </row>
     <row r="21" ht="15" customHeight="1">
       <c r="B21" s="44" t="n"/>
@@ -4481,47 +5776,78 @@
       <c r="H21" s="45" t="n"/>
       <c r="I21" s="45" t="n"/>
       <c r="J21" s="45" t="n"/>
-      <c r="K21" s="45" t="n"/>
-      <c r="L21" s="50" t="n"/>
+      <c r="K21" s="50" t="n"/>
+      <c r="L21" s="45" t="n"/>
       <c r="M21" s="45" t="n"/>
-      <c r="N21" s="45" t="n"/>
+      <c r="N21" s="50" t="n"/>
       <c r="O21" s="45" t="n"/>
       <c r="P21" s="45" t="n"/>
-      <c r="Q21" s="45" t="n"/>
+      <c r="Q21" s="50" t="n"/>
       <c r="R21" s="45" t="n"/>
       <c r="S21" s="45" t="n"/>
-      <c r="T21" s="45" t="n"/>
+      <c r="T21" s="50" t="n"/>
       <c r="U21" s="45" t="n"/>
       <c r="V21" s="45" t="n"/>
-      <c r="W21" s="45" t="n"/>
-      <c r="X21" s="50" t="n"/>
+      <c r="W21" s="50" t="n"/>
+      <c r="X21" s="45" t="n"/>
       <c r="Y21" s="45" t="n"/>
-      <c r="Z21" s="45" t="n"/>
+      <c r="Z21" s="50" t="n"/>
       <c r="AA21" s="45" t="n"/>
       <c r="AB21" s="45" t="n"/>
-      <c r="AC21" s="45" t="n"/>
+      <c r="AC21" s="50" t="n"/>
       <c r="AD21" s="45" t="n"/>
       <c r="AE21" s="45" t="n"/>
-      <c r="AF21" s="45" t="n"/>
+      <c r="AF21" s="50" t="n"/>
       <c r="AG21" s="45" t="n"/>
       <c r="AH21" s="45" t="n"/>
-      <c r="AI21" s="45" t="n"/>
-      <c r="AJ21" s="50" t="n"/>
+      <c r="AI21" s="50" t="n"/>
+      <c r="AJ21" s="45" t="n"/>
       <c r="AK21" s="45" t="n"/>
-      <c r="AL21" s="45" t="n"/>
+      <c r="AL21" s="50" t="n"/>
       <c r="AM21" s="45" t="n"/>
       <c r="AN21" s="45" t="n"/>
-      <c r="AO21" s="45" t="n"/>
+      <c r="AO21" s="50" t="n"/>
       <c r="AP21" s="45" t="n"/>
       <c r="AQ21" s="45" t="n"/>
-      <c r="AR21" s="45" t="n"/>
+      <c r="AR21" s="50" t="n"/>
       <c r="AS21" s="45" t="n"/>
       <c r="AT21" s="45" t="n"/>
-      <c r="AU21" s="45" t="n"/>
+      <c r="AU21" s="50" t="n"/>
       <c r="AV21" s="45" t="n"/>
       <c r="AW21" s="45" t="n"/>
-      <c r="AX21" s="45" t="n"/>
-      <c r="AY21" s="46" t="n"/>
+      <c r="AX21" s="50" t="n"/>
+      <c r="AY21" s="45" t="n"/>
+      <c r="AZ21" s="45" t="n"/>
+      <c r="BA21" s="50" t="n"/>
+      <c r="BB21" s="45" t="n"/>
+      <c r="BC21" s="45" t="n"/>
+      <c r="BD21" s="50" t="n"/>
+      <c r="BE21" s="45" t="n"/>
+      <c r="BF21" s="45" t="n"/>
+      <c r="BG21" s="50" t="n"/>
+      <c r="BH21" s="45" t="n"/>
+      <c r="BI21" s="45" t="n"/>
+      <c r="BJ21" s="50" t="n"/>
+      <c r="BK21" s="45" t="n"/>
+      <c r="BL21" s="45" t="n"/>
+      <c r="BM21" s="50" t="n"/>
+      <c r="BN21" s="45" t="n"/>
+      <c r="BO21" s="45" t="n"/>
+      <c r="BP21" s="50" t="n"/>
+      <c r="BQ21" s="45" t="n"/>
+      <c r="BR21" s="45" t="n"/>
+      <c r="BS21" s="45" t="n"/>
+      <c r="BT21" s="45" t="n"/>
+      <c r="BU21" s="45" t="n"/>
+      <c r="BV21" s="45" t="n"/>
+      <c r="BW21" s="45" t="n"/>
+      <c r="BX21" s="45" t="n"/>
+      <c r="BY21" s="45" t="n"/>
+      <c r="BZ21" s="45" t="n"/>
+      <c r="CA21" s="45" t="n"/>
+      <c r="CB21" s="45" t="n"/>
+      <c r="CC21" s="45" t="n"/>
+      <c r="CD21" s="46" t="n"/>
     </row>
     <row r="22" ht="15" customHeight="1">
       <c r="B22" s="44" t="n"/>
@@ -4573,7 +5899,38 @@
       <c r="AV22" s="45" t="n"/>
       <c r="AW22" s="45" t="n"/>
       <c r="AX22" s="45" t="n"/>
-      <c r="AY22" s="46" t="n"/>
+      <c r="AY22" s="45" t="n"/>
+      <c r="AZ22" s="45" t="n"/>
+      <c r="BA22" s="45" t="n"/>
+      <c r="BB22" s="45" t="n"/>
+      <c r="BC22" s="45" t="n"/>
+      <c r="BD22" s="45" t="n"/>
+      <c r="BE22" s="45" t="n"/>
+      <c r="BF22" s="45" t="n"/>
+      <c r="BG22" s="45" t="n"/>
+      <c r="BH22" s="45" t="n"/>
+      <c r="BI22" s="45" t="n"/>
+      <c r="BJ22" s="45" t="n"/>
+      <c r="BK22" s="45" t="n"/>
+      <c r="BL22" s="45" t="n"/>
+      <c r="BM22" s="45" t="n"/>
+      <c r="BN22" s="45" t="n"/>
+      <c r="BO22" s="45" t="n"/>
+      <c r="BP22" s="45" t="n"/>
+      <c r="BQ22" s="45" t="n"/>
+      <c r="BR22" s="45" t="n"/>
+      <c r="BS22" s="45" t="n"/>
+      <c r="BT22" s="45" t="n"/>
+      <c r="BU22" s="45" t="n"/>
+      <c r="BV22" s="45" t="n"/>
+      <c r="BW22" s="45" t="n"/>
+      <c r="BX22" s="45" t="n"/>
+      <c r="BY22" s="45" t="n"/>
+      <c r="BZ22" s="45" t="n"/>
+      <c r="CA22" s="45" t="n"/>
+      <c r="CB22" s="45" t="n"/>
+      <c r="CC22" s="45" t="n"/>
+      <c r="CD22" s="46" t="n"/>
     </row>
     <row r="23" ht="15" customHeight="1">
       <c r="B23" s="44" t="n"/>
@@ -4625,9 +5982,40 @@
       <c r="AV23" s="45" t="n"/>
       <c r="AW23" s="45" t="n"/>
       <c r="AX23" s="45" t="n"/>
-      <c r="AY23" s="46" t="n"/>
-    </row>
-    <row r="24" ht="15" customHeight="1">
+      <c r="AY23" s="45" t="n"/>
+      <c r="AZ23" s="45" t="n"/>
+      <c r="BA23" s="45" t="n"/>
+      <c r="BB23" s="45" t="n"/>
+      <c r="BC23" s="45" t="n"/>
+      <c r="BD23" s="45" t="n"/>
+      <c r="BE23" s="45" t="n"/>
+      <c r="BF23" s="45" t="n"/>
+      <c r="BG23" s="45" t="n"/>
+      <c r="BH23" s="45" t="n"/>
+      <c r="BI23" s="45" t="n"/>
+      <c r="BJ23" s="45" t="n"/>
+      <c r="BK23" s="45" t="n"/>
+      <c r="BL23" s="45" t="n"/>
+      <c r="BM23" s="45" t="n"/>
+      <c r="BN23" s="45" t="n"/>
+      <c r="BO23" s="45" t="n"/>
+      <c r="BP23" s="45" t="n"/>
+      <c r="BQ23" s="45" t="n"/>
+      <c r="BR23" s="45" t="n"/>
+      <c r="BS23" s="45" t="n"/>
+      <c r="BT23" s="45" t="n"/>
+      <c r="BU23" s="45" t="n"/>
+      <c r="BV23" s="45" t="n"/>
+      <c r="BW23" s="45" t="n"/>
+      <c r="BX23" s="45" t="n"/>
+      <c r="BY23" s="45" t="n"/>
+      <c r="BZ23" s="45" t="n"/>
+      <c r="CA23" s="45" t="n"/>
+      <c r="CB23" s="45" t="n"/>
+      <c r="CC23" s="45" t="n"/>
+      <c r="CD23" s="46" t="n"/>
+    </row>
+    <row r="24" ht="60" customHeight="1">
       <c r="B24" s="44" t="n"/>
       <c r="C24" s="45" t="n"/>
       <c r="D24" s="45" t="n"/>
@@ -4636,48 +6024,139 @@
       <c r="G24" s="45" t="n"/>
       <c r="H24" s="45" t="n"/>
       <c r="I24" s="45" t="n"/>
-      <c r="J24" s="45" t="n"/>
+      <c r="J24" s="53">
+        <f>IFERROR('Makine Giris'!B5,"M1")</f>
+        <v/>
+      </c>
       <c r="K24" s="45" t="n"/>
       <c r="L24" s="45" t="n"/>
-      <c r="M24" s="45" t="n"/>
+      <c r="M24" s="53">
+        <f>IFERROR('Makine Giris'!B6,"M2")</f>
+        <v/>
+      </c>
       <c r="N24" s="45" t="n"/>
       <c r="O24" s="45" t="n"/>
-      <c r="P24" s="45" t="n"/>
+      <c r="P24" s="53">
+        <f>IFERROR('Makine Giris'!B7,"M3")</f>
+        <v/>
+      </c>
       <c r="Q24" s="45" t="n"/>
       <c r="R24" s="45" t="n"/>
-      <c r="S24" s="45" t="n"/>
+      <c r="S24" s="53">
+        <f>IFERROR('Makine Giris'!B8,"M4")</f>
+        <v/>
+      </c>
       <c r="T24" s="45" t="n"/>
       <c r="U24" s="45" t="n"/>
-      <c r="V24" s="45" t="n"/>
+      <c r="V24" s="53">
+        <f>IFERROR('Makine Giris'!B9,"M5")</f>
+        <v/>
+      </c>
       <c r="W24" s="45" t="n"/>
       <c r="X24" s="45" t="n"/>
-      <c r="Y24" s="45" t="n"/>
+      <c r="Y24" s="53">
+        <f>IFERROR('Makine Giris'!B10,"M6")</f>
+        <v/>
+      </c>
       <c r="Z24" s="45" t="n"/>
       <c r="AA24" s="45" t="n"/>
-      <c r="AB24" s="45" t="n"/>
+      <c r="AB24" s="53">
+        <f>IFERROR('Makine Giris'!B11,"M7")</f>
+        <v/>
+      </c>
       <c r="AC24" s="45" t="n"/>
       <c r="AD24" s="45" t="n"/>
-      <c r="AE24" s="45" t="n"/>
+      <c r="AE24" s="53">
+        <f>IFERROR('Makine Giris'!B12,"M8")</f>
+        <v/>
+      </c>
       <c r="AF24" s="45" t="n"/>
       <c r="AG24" s="45" t="n"/>
-      <c r="AH24" s="45" t="n"/>
+      <c r="AH24" s="53">
+        <f>IFERROR('Makine Giris'!B13,"M9")</f>
+        <v/>
+      </c>
       <c r="AI24" s="45" t="n"/>
       <c r="AJ24" s="45" t="n"/>
-      <c r="AK24" s="45" t="n"/>
+      <c r="AK24" s="53">
+        <f>IFERROR('Makine Giris'!B14,"M10")</f>
+        <v/>
+      </c>
       <c r="AL24" s="45" t="n"/>
       <c r="AM24" s="45" t="n"/>
-      <c r="AN24" s="45" t="n"/>
+      <c r="AN24" s="53">
+        <f>IFERROR('Makine Giris'!B15,"M11")</f>
+        <v/>
+      </c>
       <c r="AO24" s="45" t="n"/>
       <c r="AP24" s="45" t="n"/>
-      <c r="AQ24" s="45" t="n"/>
+      <c r="AQ24" s="53">
+        <f>IFERROR('Makine Giris'!B16,"M12")</f>
+        <v/>
+      </c>
       <c r="AR24" s="45" t="n"/>
       <c r="AS24" s="45" t="n"/>
-      <c r="AT24" s="45" t="n"/>
+      <c r="AT24" s="53">
+        <f>IFERROR('Makine Giris'!B17,"M13")</f>
+        <v/>
+      </c>
       <c r="AU24" s="45" t="n"/>
       <c r="AV24" s="45" t="n"/>
-      <c r="AW24" s="45" t="n"/>
+      <c r="AW24" s="53">
+        <f>IFERROR('Makine Giris'!B18,"M14")</f>
+        <v/>
+      </c>
       <c r="AX24" s="45" t="n"/>
-      <c r="AY24" s="46" t="n"/>
+      <c r="AY24" s="45" t="n"/>
+      <c r="AZ24" s="53">
+        <f>IFERROR('Makine Giris'!B19,"M15")</f>
+        <v/>
+      </c>
+      <c r="BA24" s="45" t="n"/>
+      <c r="BB24" s="45" t="n"/>
+      <c r="BC24" s="53">
+        <f>IFERROR('Makine Giris'!B20,"M16")</f>
+        <v/>
+      </c>
+      <c r="BD24" s="45" t="n"/>
+      <c r="BE24" s="45" t="n"/>
+      <c r="BF24" s="53">
+        <f>IFERROR('Makine Giris'!B21,"M17")</f>
+        <v/>
+      </c>
+      <c r="BG24" s="45" t="n"/>
+      <c r="BH24" s="45" t="n"/>
+      <c r="BI24" s="53">
+        <f>IFERROR('Makine Giris'!B22,"M18")</f>
+        <v/>
+      </c>
+      <c r="BJ24" s="45" t="n"/>
+      <c r="BK24" s="45" t="n"/>
+      <c r="BL24" s="53">
+        <f>IFERROR('Makine Giris'!B23,"M19")</f>
+        <v/>
+      </c>
+      <c r="BM24" s="45" t="n"/>
+      <c r="BN24" s="45" t="n"/>
+      <c r="BO24" s="53">
+        <f>IFERROR('Makine Giris'!B24,"M20")</f>
+        <v/>
+      </c>
+      <c r="BP24" s="45" t="n"/>
+      <c r="BQ24" s="45" t="n"/>
+      <c r="BR24" s="45" t="n"/>
+      <c r="BS24" s="45" t="n"/>
+      <c r="BT24" s="45" t="n"/>
+      <c r="BU24" s="45" t="n"/>
+      <c r="BV24" s="45" t="n"/>
+      <c r="BW24" s="45" t="n"/>
+      <c r="BX24" s="45" t="n"/>
+      <c r="BY24" s="45" t="n"/>
+      <c r="BZ24" s="45" t="n"/>
+      <c r="CA24" s="45" t="n"/>
+      <c r="CB24" s="45" t="n"/>
+      <c r="CC24" s="45" t="n"/>
+      <c r="CD24" s="46" t="n"/>
     </row>
     <row r="25" ht="15" customHeight="1">
       <c r="B25" s="44" t="n"/>
@@ -4688,14 +6167,11 @@
       <c r="G25" s="45" t="n"/>
       <c r="H25" s="45" t="n"/>
       <c r="I25" s="45" t="n"/>
-      <c r="J25" s="53">
-        <f>IFERROR('Makine Giris'!B5,"Makine 1")</f>
-        <v/>
-      </c>
-      <c r="K25" s="51" t="n"/>
-      <c r="L25" s="51" t="n"/>
-      <c r="M25" s="51" t="n"/>
-      <c r="N25" s="52" t="n"/>
+      <c r="J25" s="45" t="n"/>
+      <c r="K25" s="45" t="n"/>
+      <c r="L25" s="45" t="n"/>
+      <c r="M25" s="45" t="n"/>
+      <c r="N25" s="45" t="n"/>
       <c r="O25" s="45" t="n"/>
       <c r="P25" s="45" t="n"/>
       <c r="Q25" s="45" t="n"/>
@@ -4703,14 +6179,11 @@
       <c r="S25" s="45" t="n"/>
       <c r="T25" s="45" t="n"/>
       <c r="U25" s="45" t="n"/>
-      <c r="V25" s="53">
-        <f>IFERROR('Makine Giris'!B6,"Makine 2")</f>
-        <v/>
-      </c>
-      <c r="W25" s="51" t="n"/>
-      <c r="X25" s="51" t="n"/>
-      <c r="Y25" s="51" t="n"/>
-      <c r="Z25" s="52" t="n"/>
+      <c r="V25" s="45" t="n"/>
+      <c r="W25" s="45" t="n"/>
+      <c r="X25" s="45" t="n"/>
+      <c r="Y25" s="45" t="n"/>
+      <c r="Z25" s="45" t="n"/>
       <c r="AA25" s="45" t="n"/>
       <c r="AB25" s="45" t="n"/>
       <c r="AC25" s="45" t="n"/>
@@ -4718,14 +6191,11 @@
       <c r="AE25" s="45" t="n"/>
       <c r="AF25" s="45" t="n"/>
       <c r="AG25" s="45" t="n"/>
-      <c r="AH25" s="53">
-        <f>IFERROR('Makine Giris'!B7,"Makine 3")</f>
-        <v/>
-      </c>
-      <c r="AI25" s="51" t="n"/>
-      <c r="AJ25" s="51" t="n"/>
-      <c r="AK25" s="51" t="n"/>
-      <c r="AL25" s="52" t="n"/>
+      <c r="AH25" s="45" t="n"/>
+      <c r="AI25" s="45" t="n"/>
+      <c r="AJ25" s="45" t="n"/>
+      <c r="AK25" s="45" t="n"/>
+      <c r="AL25" s="45" t="n"/>
       <c r="AM25" s="45" t="n"/>
       <c r="AN25" s="45" t="n"/>
       <c r="AO25" s="45" t="n"/>
@@ -4738,7 +6208,38 @@
       <c r="AV25" s="45" t="n"/>
       <c r="AW25" s="45" t="n"/>
       <c r="AX25" s="45" t="n"/>
-      <c r="AY25" s="46" t="n"/>
+      <c r="AY25" s="45" t="n"/>
+      <c r="AZ25" s="45" t="n"/>
+      <c r="BA25" s="45" t="n"/>
+      <c r="BB25" s="45" t="n"/>
+      <c r="BC25" s="45" t="n"/>
+      <c r="BD25" s="45" t="n"/>
+      <c r="BE25" s="45" t="n"/>
+      <c r="BF25" s="45" t="n"/>
+      <c r="BG25" s="45" t="n"/>
+      <c r="BH25" s="45" t="n"/>
+      <c r="BI25" s="45" t="n"/>
+      <c r="BJ25" s="45" t="n"/>
+      <c r="BK25" s="45" t="n"/>
+      <c r="BL25" s="45" t="n"/>
+      <c r="BM25" s="45" t="n"/>
+      <c r="BN25" s="45" t="n"/>
+      <c r="BO25" s="45" t="n"/>
+      <c r="BP25" s="45" t="n"/>
+      <c r="BQ25" s="45" t="n"/>
+      <c r="BR25" s="45" t="n"/>
+      <c r="BS25" s="45" t="n"/>
+      <c r="BT25" s="45" t="n"/>
+      <c r="BU25" s="45" t="n"/>
+      <c r="BV25" s="45" t="n"/>
+      <c r="BW25" s="45" t="n"/>
+      <c r="BX25" s="45" t="n"/>
+      <c r="BY25" s="45" t="n"/>
+      <c r="BZ25" s="45" t="n"/>
+      <c r="CA25" s="45" t="n"/>
+      <c r="CB25" s="45" t="n"/>
+      <c r="CC25" s="45" t="n"/>
+      <c r="CD25" s="46" t="n"/>
     </row>
     <row r="26" ht="15" customHeight="1">
       <c r="B26" s="44" t="n"/>
@@ -4790,7 +6291,38 @@
       <c r="AV26" s="45" t="n"/>
       <c r="AW26" s="45" t="n"/>
       <c r="AX26" s="45" t="n"/>
-      <c r="AY26" s="46" t="n"/>
+      <c r="AY26" s="45" t="n"/>
+      <c r="AZ26" s="45" t="n"/>
+      <c r="BA26" s="45" t="n"/>
+      <c r="BB26" s="45" t="n"/>
+      <c r="BC26" s="45" t="n"/>
+      <c r="BD26" s="45" t="n"/>
+      <c r="BE26" s="45" t="n"/>
+      <c r="BF26" s="45" t="n"/>
+      <c r="BG26" s="45" t="n"/>
+      <c r="BH26" s="45" t="n"/>
+      <c r="BI26" s="45" t="n"/>
+      <c r="BJ26" s="45" t="n"/>
+      <c r="BK26" s="45" t="n"/>
+      <c r="BL26" s="45" t="n"/>
+      <c r="BM26" s="45" t="n"/>
+      <c r="BN26" s="45" t="n"/>
+      <c r="BO26" s="45" t="n"/>
+      <c r="BP26" s="45" t="n"/>
+      <c r="BQ26" s="45" t="n"/>
+      <c r="BR26" s="45" t="n"/>
+      <c r="BS26" s="45" t="n"/>
+      <c r="BT26" s="45" t="n"/>
+      <c r="BU26" s="45" t="n"/>
+      <c r="BV26" s="45" t="n"/>
+      <c r="BW26" s="45" t="n"/>
+      <c r="BX26" s="45" t="n"/>
+      <c r="BY26" s="45" t="n"/>
+      <c r="BZ26" s="45" t="n"/>
+      <c r="CA26" s="45" t="n"/>
+      <c r="CB26" s="45" t="n"/>
+      <c r="CC26" s="45" t="n"/>
+      <c r="CD26" s="46" t="n"/>
     </row>
     <row r="27" ht="15" customHeight="1">
       <c r="B27" s="44" t="n"/>
@@ -4842,7 +6374,38 @@
       <c r="AV27" s="45" t="n"/>
       <c r="AW27" s="45" t="n"/>
       <c r="AX27" s="45" t="n"/>
-      <c r="AY27" s="46" t="n"/>
+      <c r="AY27" s="45" t="n"/>
+      <c r="AZ27" s="45" t="n"/>
+      <c r="BA27" s="45" t="n"/>
+      <c r="BB27" s="45" t="n"/>
+      <c r="BC27" s="45" t="n"/>
+      <c r="BD27" s="45" t="n"/>
+      <c r="BE27" s="45" t="n"/>
+      <c r="BF27" s="45" t="n"/>
+      <c r="BG27" s="45" t="n"/>
+      <c r="BH27" s="45" t="n"/>
+      <c r="BI27" s="45" t="n"/>
+      <c r="BJ27" s="45" t="n"/>
+      <c r="BK27" s="45" t="n"/>
+      <c r="BL27" s="45" t="n"/>
+      <c r="BM27" s="45" t="n"/>
+      <c r="BN27" s="45" t="n"/>
+      <c r="BO27" s="45" t="n"/>
+      <c r="BP27" s="45" t="n"/>
+      <c r="BQ27" s="45" t="n"/>
+      <c r="BR27" s="45" t="n"/>
+      <c r="BS27" s="45" t="n"/>
+      <c r="BT27" s="45" t="n"/>
+      <c r="BU27" s="45" t="n"/>
+      <c r="BV27" s="45" t="n"/>
+      <c r="BW27" s="45" t="n"/>
+      <c r="BX27" s="45" t="n"/>
+      <c r="BY27" s="45" t="n"/>
+      <c r="BZ27" s="45" t="n"/>
+      <c r="CA27" s="45" t="n"/>
+      <c r="CB27" s="45" t="n"/>
+      <c r="CC27" s="45" t="n"/>
+      <c r="CD27" s="46" t="n"/>
     </row>
     <row r="28" ht="15" customHeight="1">
       <c r="B28" s="44" t="n"/>
@@ -4894,7 +6457,38 @@
       <c r="AV28" s="45" t="n"/>
       <c r="AW28" s="45" t="n"/>
       <c r="AX28" s="45" t="n"/>
-      <c r="AY28" s="46" t="n"/>
+      <c r="AY28" s="45" t="n"/>
+      <c r="AZ28" s="45" t="n"/>
+      <c r="BA28" s="45" t="n"/>
+      <c r="BB28" s="45" t="n"/>
+      <c r="BC28" s="45" t="n"/>
+      <c r="BD28" s="45" t="n"/>
+      <c r="BE28" s="45" t="n"/>
+      <c r="BF28" s="45" t="n"/>
+      <c r="BG28" s="45" t="n"/>
+      <c r="BH28" s="45" t="n"/>
+      <c r="BI28" s="45" t="n"/>
+      <c r="BJ28" s="45" t="n"/>
+      <c r="BK28" s="45" t="n"/>
+      <c r="BL28" s="45" t="n"/>
+      <c r="BM28" s="45" t="n"/>
+      <c r="BN28" s="45" t="n"/>
+      <c r="BO28" s="45" t="n"/>
+      <c r="BP28" s="45" t="n"/>
+      <c r="BQ28" s="45" t="n"/>
+      <c r="BR28" s="45" t="n"/>
+      <c r="BS28" s="45" t="n"/>
+      <c r="BT28" s="45" t="n"/>
+      <c r="BU28" s="45" t="n"/>
+      <c r="BV28" s="45" t="n"/>
+      <c r="BW28" s="45" t="n"/>
+      <c r="BX28" s="45" t="n"/>
+      <c r="BY28" s="45" t="n"/>
+      <c r="BZ28" s="45" t="n"/>
+      <c r="CA28" s="45" t="n"/>
+      <c r="CB28" s="45" t="n"/>
+      <c r="CC28" s="45" t="n"/>
+      <c r="CD28" s="46" t="n"/>
     </row>
     <row r="29" ht="15" customHeight="1">
       <c r="B29" s="44" t="n"/>
@@ -4946,7 +6540,38 @@
       <c r="AV29" s="45" t="n"/>
       <c r="AW29" s="45" t="n"/>
       <c r="AX29" s="45" t="n"/>
-      <c r="AY29" s="46" t="n"/>
+      <c r="AY29" s="45" t="n"/>
+      <c r="AZ29" s="45" t="n"/>
+      <c r="BA29" s="45" t="n"/>
+      <c r="BB29" s="45" t="n"/>
+      <c r="BC29" s="45" t="n"/>
+      <c r="BD29" s="45" t="n"/>
+      <c r="BE29" s="45" t="n"/>
+      <c r="BF29" s="45" t="n"/>
+      <c r="BG29" s="45" t="n"/>
+      <c r="BH29" s="45" t="n"/>
+      <c r="BI29" s="45" t="n"/>
+      <c r="BJ29" s="45" t="n"/>
+      <c r="BK29" s="45" t="n"/>
+      <c r="BL29" s="45" t="n"/>
+      <c r="BM29" s="45" t="n"/>
+      <c r="BN29" s="45" t="n"/>
+      <c r="BO29" s="45" t="n"/>
+      <c r="BP29" s="45" t="n"/>
+      <c r="BQ29" s="45" t="n"/>
+      <c r="BR29" s="45" t="n"/>
+      <c r="BS29" s="45" t="n"/>
+      <c r="BT29" s="45" t="n"/>
+      <c r="BU29" s="45" t="n"/>
+      <c r="BV29" s="45" t="n"/>
+      <c r="BW29" s="45" t="n"/>
+      <c r="BX29" s="45" t="n"/>
+      <c r="BY29" s="45" t="n"/>
+      <c r="BZ29" s="45" t="n"/>
+      <c r="CA29" s="45" t="n"/>
+      <c r="CB29" s="45" t="n"/>
+      <c r="CC29" s="45" t="n"/>
+      <c r="CD29" s="46" t="n"/>
     </row>
     <row r="30" ht="15" customHeight="1">
       <c r="B30" s="44" t="n"/>
@@ -4998,7 +6623,38 @@
       <c r="AV30" s="45" t="n"/>
       <c r="AW30" s="45" t="n"/>
       <c r="AX30" s="45" t="n"/>
-      <c r="AY30" s="46" t="n"/>
+      <c r="AY30" s="45" t="n"/>
+      <c r="AZ30" s="45" t="n"/>
+      <c r="BA30" s="45" t="n"/>
+      <c r="BB30" s="45" t="n"/>
+      <c r="BC30" s="45" t="n"/>
+      <c r="BD30" s="45" t="n"/>
+      <c r="BE30" s="45" t="n"/>
+      <c r="BF30" s="45" t="n"/>
+      <c r="BG30" s="45" t="n"/>
+      <c r="BH30" s="45" t="n"/>
+      <c r="BI30" s="45" t="n"/>
+      <c r="BJ30" s="45" t="n"/>
+      <c r="BK30" s="45" t="n"/>
+      <c r="BL30" s="45" t="n"/>
+      <c r="BM30" s="45" t="n"/>
+      <c r="BN30" s="45" t="n"/>
+      <c r="BO30" s="45" t="n"/>
+      <c r="BP30" s="45" t="n"/>
+      <c r="BQ30" s="45" t="n"/>
+      <c r="BR30" s="45" t="n"/>
+      <c r="BS30" s="45" t="n"/>
+      <c r="BT30" s="45" t="n"/>
+      <c r="BU30" s="45" t="n"/>
+      <c r="BV30" s="45" t="n"/>
+      <c r="BW30" s="45" t="n"/>
+      <c r="BX30" s="45" t="n"/>
+      <c r="BY30" s="45" t="n"/>
+      <c r="BZ30" s="45" t="n"/>
+      <c r="CA30" s="45" t="n"/>
+      <c r="CB30" s="45" t="n"/>
+      <c r="CC30" s="45" t="n"/>
+      <c r="CD30" s="46" t="n"/>
     </row>
     <row r="31" ht="15" customHeight="1">
       <c r="B31" s="44" t="n"/>
@@ -5050,7 +6706,38 @@
       <c r="AV31" s="45" t="n"/>
       <c r="AW31" s="45" t="n"/>
       <c r="AX31" s="45" t="n"/>
-      <c r="AY31" s="46" t="n"/>
+      <c r="AY31" s="45" t="n"/>
+      <c r="AZ31" s="45" t="n"/>
+      <c r="BA31" s="45" t="n"/>
+      <c r="BB31" s="45" t="n"/>
+      <c r="BC31" s="45" t="n"/>
+      <c r="BD31" s="45" t="n"/>
+      <c r="BE31" s="45" t="n"/>
+      <c r="BF31" s="45" t="n"/>
+      <c r="BG31" s="45" t="n"/>
+      <c r="BH31" s="45" t="n"/>
+      <c r="BI31" s="45" t="n"/>
+      <c r="BJ31" s="45" t="n"/>
+      <c r="BK31" s="45" t="n"/>
+      <c r="BL31" s="45" t="n"/>
+      <c r="BM31" s="45" t="n"/>
+      <c r="BN31" s="45" t="n"/>
+      <c r="BO31" s="45" t="n"/>
+      <c r="BP31" s="45" t="n"/>
+      <c r="BQ31" s="45" t="n"/>
+      <c r="BR31" s="45" t="n"/>
+      <c r="BS31" s="45" t="n"/>
+      <c r="BT31" s="45" t="n"/>
+      <c r="BU31" s="45" t="n"/>
+      <c r="BV31" s="45" t="n"/>
+      <c r="BW31" s="45" t="n"/>
+      <c r="BX31" s="45" t="n"/>
+      <c r="BY31" s="45" t="n"/>
+      <c r="BZ31" s="45" t="n"/>
+      <c r="CA31" s="45" t="n"/>
+      <c r="CB31" s="45" t="n"/>
+      <c r="CC31" s="45" t="n"/>
+      <c r="CD31" s="46" t="n"/>
     </row>
     <row r="32" ht="15" customHeight="1">
       <c r="B32" s="44" t="n"/>
@@ -5102,7 +6789,38 @@
       <c r="AV32" s="45" t="n"/>
       <c r="AW32" s="45" t="n"/>
       <c r="AX32" s="45" t="n"/>
-      <c r="AY32" s="46" t="n"/>
+      <c r="AY32" s="45" t="n"/>
+      <c r="AZ32" s="45" t="n"/>
+      <c r="BA32" s="45" t="n"/>
+      <c r="BB32" s="45" t="n"/>
+      <c r="BC32" s="45" t="n"/>
+      <c r="BD32" s="45" t="n"/>
+      <c r="BE32" s="45" t="n"/>
+      <c r="BF32" s="45" t="n"/>
+      <c r="BG32" s="45" t="n"/>
+      <c r="BH32" s="45" t="n"/>
+      <c r="BI32" s="45" t="n"/>
+      <c r="BJ32" s="45" t="n"/>
+      <c r="BK32" s="45" t="n"/>
+      <c r="BL32" s="45" t="n"/>
+      <c r="BM32" s="45" t="n"/>
+      <c r="BN32" s="45" t="n"/>
+      <c r="BO32" s="45" t="n"/>
+      <c r="BP32" s="45" t="n"/>
+      <c r="BQ32" s="45" t="n"/>
+      <c r="BR32" s="45" t="n"/>
+      <c r="BS32" s="45" t="n"/>
+      <c r="BT32" s="45" t="n"/>
+      <c r="BU32" s="45" t="n"/>
+      <c r="BV32" s="45" t="n"/>
+      <c r="BW32" s="45" t="n"/>
+      <c r="BX32" s="45" t="n"/>
+      <c r="BY32" s="45" t="n"/>
+      <c r="BZ32" s="45" t="n"/>
+      <c r="CA32" s="45" t="n"/>
+      <c r="CB32" s="45" t="n"/>
+      <c r="CC32" s="45" t="n"/>
+      <c r="CD32" s="46" t="n"/>
     </row>
     <row r="33" ht="15" customHeight="1">
       <c r="B33" s="44" t="n"/>
@@ -5154,7 +6872,38 @@
       <c r="AV33" s="45" t="n"/>
       <c r="AW33" s="45" t="n"/>
       <c r="AX33" s="45" t="n"/>
-      <c r="AY33" s="46" t="n"/>
+      <c r="AY33" s="45" t="n"/>
+      <c r="AZ33" s="45" t="n"/>
+      <c r="BA33" s="45" t="n"/>
+      <c r="BB33" s="45" t="n"/>
+      <c r="BC33" s="45" t="n"/>
+      <c r="BD33" s="45" t="n"/>
+      <c r="BE33" s="45" t="n"/>
+      <c r="BF33" s="45" t="n"/>
+      <c r="BG33" s="45" t="n"/>
+      <c r="BH33" s="45" t="n"/>
+      <c r="BI33" s="45" t="n"/>
+      <c r="BJ33" s="45" t="n"/>
+      <c r="BK33" s="45" t="n"/>
+      <c r="BL33" s="45" t="n"/>
+      <c r="BM33" s="45" t="n"/>
+      <c r="BN33" s="45" t="n"/>
+      <c r="BO33" s="45" t="n"/>
+      <c r="BP33" s="45" t="n"/>
+      <c r="BQ33" s="45" t="n"/>
+      <c r="BR33" s="45" t="n"/>
+      <c r="BS33" s="45" t="n"/>
+      <c r="BT33" s="45" t="n"/>
+      <c r="BU33" s="45" t="n"/>
+      <c r="BV33" s="45" t="n"/>
+      <c r="BW33" s="45" t="n"/>
+      <c r="BX33" s="45" t="n"/>
+      <c r="BY33" s="45" t="n"/>
+      <c r="BZ33" s="45" t="n"/>
+      <c r="CA33" s="45" t="n"/>
+      <c r="CB33" s="45" t="n"/>
+      <c r="CC33" s="45" t="n"/>
+      <c r="CD33" s="46" t="n"/>
     </row>
     <row r="34" ht="15" customHeight="1">
       <c r="B34" s="44" t="n"/>
@@ -5206,7 +6955,38 @@
       <c r="AV34" s="45" t="n"/>
       <c r="AW34" s="45" t="n"/>
       <c r="AX34" s="45" t="n"/>
-      <c r="AY34" s="46" t="n"/>
+      <c r="AY34" s="45" t="n"/>
+      <c r="AZ34" s="45" t="n"/>
+      <c r="BA34" s="45" t="n"/>
+      <c r="BB34" s="45" t="n"/>
+      <c r="BC34" s="45" t="n"/>
+      <c r="BD34" s="45" t="n"/>
+      <c r="BE34" s="45" t="n"/>
+      <c r="BF34" s="45" t="n"/>
+      <c r="BG34" s="45" t="n"/>
+      <c r="BH34" s="45" t="n"/>
+      <c r="BI34" s="45" t="n"/>
+      <c r="BJ34" s="45" t="n"/>
+      <c r="BK34" s="45" t="n"/>
+      <c r="BL34" s="45" t="n"/>
+      <c r="BM34" s="45" t="n"/>
+      <c r="BN34" s="45" t="n"/>
+      <c r="BO34" s="45" t="n"/>
+      <c r="BP34" s="45" t="n"/>
+      <c r="BQ34" s="45" t="n"/>
+      <c r="BR34" s="45" t="n"/>
+      <c r="BS34" s="45" t="n"/>
+      <c r="BT34" s="45" t="n"/>
+      <c r="BU34" s="45" t="n"/>
+      <c r="BV34" s="45" t="n"/>
+      <c r="BW34" s="45" t="n"/>
+      <c r="BX34" s="45" t="n"/>
+      <c r="BY34" s="45" t="n"/>
+      <c r="BZ34" s="45" t="n"/>
+      <c r="CA34" s="45" t="n"/>
+      <c r="CB34" s="45" t="n"/>
+      <c r="CC34" s="45" t="n"/>
+      <c r="CD34" s="46" t="n"/>
     </row>
     <row r="35" ht="15" customHeight="1">
       <c r="B35" s="44" t="n"/>
@@ -5258,7 +7038,38 @@
       <c r="AV35" s="45" t="n"/>
       <c r="AW35" s="45" t="n"/>
       <c r="AX35" s="45" t="n"/>
-      <c r="AY35" s="46" t="n"/>
+      <c r="AY35" s="45" t="n"/>
+      <c r="AZ35" s="45" t="n"/>
+      <c r="BA35" s="45" t="n"/>
+      <c r="BB35" s="45" t="n"/>
+      <c r="BC35" s="45" t="n"/>
+      <c r="BD35" s="45" t="n"/>
+      <c r="BE35" s="45" t="n"/>
+      <c r="BF35" s="45" t="n"/>
+      <c r="BG35" s="45" t="n"/>
+      <c r="BH35" s="45" t="n"/>
+      <c r="BI35" s="45" t="n"/>
+      <c r="BJ35" s="45" t="n"/>
+      <c r="BK35" s="45" t="n"/>
+      <c r="BL35" s="45" t="n"/>
+      <c r="BM35" s="45" t="n"/>
+      <c r="BN35" s="45" t="n"/>
+      <c r="BO35" s="45" t="n"/>
+      <c r="BP35" s="45" t="n"/>
+      <c r="BQ35" s="45" t="n"/>
+      <c r="BR35" s="45" t="n"/>
+      <c r="BS35" s="45" t="n"/>
+      <c r="BT35" s="45" t="n"/>
+      <c r="BU35" s="45" t="n"/>
+      <c r="BV35" s="45" t="n"/>
+      <c r="BW35" s="45" t="n"/>
+      <c r="BX35" s="45" t="n"/>
+      <c r="BY35" s="45" t="n"/>
+      <c r="BZ35" s="45" t="n"/>
+      <c r="CA35" s="45" t="n"/>
+      <c r="CB35" s="45" t="n"/>
+      <c r="CC35" s="45" t="n"/>
+      <c r="CD35" s="46" t="n"/>
     </row>
     <row r="36" ht="15" customHeight="1">
       <c r="B36" s="44" t="n"/>
@@ -5310,7 +7121,38 @@
       <c r="AV36" s="45" t="n"/>
       <c r="AW36" s="45" t="n"/>
       <c r="AX36" s="45" t="n"/>
-      <c r="AY36" s="46" t="n"/>
+      <c r="AY36" s="45" t="n"/>
+      <c r="AZ36" s="45" t="n"/>
+      <c r="BA36" s="45" t="n"/>
+      <c r="BB36" s="45" t="n"/>
+      <c r="BC36" s="45" t="n"/>
+      <c r="BD36" s="45" t="n"/>
+      <c r="BE36" s="45" t="n"/>
+      <c r="BF36" s="45" t="n"/>
+      <c r="BG36" s="45" t="n"/>
+      <c r="BH36" s="45" t="n"/>
+      <c r="BI36" s="45" t="n"/>
+      <c r="BJ36" s="45" t="n"/>
+      <c r="BK36" s="45" t="n"/>
+      <c r="BL36" s="45" t="n"/>
+      <c r="BM36" s="45" t="n"/>
+      <c r="BN36" s="45" t="n"/>
+      <c r="BO36" s="45" t="n"/>
+      <c r="BP36" s="45" t="n"/>
+      <c r="BQ36" s="45" t="n"/>
+      <c r="BR36" s="45" t="n"/>
+      <c r="BS36" s="45" t="n"/>
+      <c r="BT36" s="45" t="n"/>
+      <c r="BU36" s="45" t="n"/>
+      <c r="BV36" s="45" t="n"/>
+      <c r="BW36" s="45" t="n"/>
+      <c r="BX36" s="45" t="n"/>
+      <c r="BY36" s="45" t="n"/>
+      <c r="BZ36" s="45" t="n"/>
+      <c r="CA36" s="45" t="n"/>
+      <c r="CB36" s="45" t="n"/>
+      <c r="CC36" s="45" t="n"/>
+      <c r="CD36" s="46" t="n"/>
     </row>
     <row r="37" ht="15" customHeight="1">
       <c r="B37" s="44" t="n"/>
@@ -5362,7 +7204,38 @@
       <c r="AV37" s="45" t="n"/>
       <c r="AW37" s="45" t="n"/>
       <c r="AX37" s="45" t="n"/>
-      <c r="AY37" s="46" t="n"/>
+      <c r="AY37" s="45" t="n"/>
+      <c r="AZ37" s="45" t="n"/>
+      <c r="BA37" s="45" t="n"/>
+      <c r="BB37" s="45" t="n"/>
+      <c r="BC37" s="45" t="n"/>
+      <c r="BD37" s="45" t="n"/>
+      <c r="BE37" s="45" t="n"/>
+      <c r="BF37" s="45" t="n"/>
+      <c r="BG37" s="45" t="n"/>
+      <c r="BH37" s="45" t="n"/>
+      <c r="BI37" s="45" t="n"/>
+      <c r="BJ37" s="45" t="n"/>
+      <c r="BK37" s="45" t="n"/>
+      <c r="BL37" s="45" t="n"/>
+      <c r="BM37" s="45" t="n"/>
+      <c r="BN37" s="45" t="n"/>
+      <c r="BO37" s="45" t="n"/>
+      <c r="BP37" s="45" t="n"/>
+      <c r="BQ37" s="45" t="n"/>
+      <c r="BR37" s="45" t="n"/>
+      <c r="BS37" s="45" t="n"/>
+      <c r="BT37" s="45" t="n"/>
+      <c r="BU37" s="45" t="n"/>
+      <c r="BV37" s="45" t="n"/>
+      <c r="BW37" s="45" t="n"/>
+      <c r="BX37" s="45" t="n"/>
+      <c r="BY37" s="45" t="n"/>
+      <c r="BZ37" s="45" t="n"/>
+      <c r="CA37" s="45" t="n"/>
+      <c r="CB37" s="45" t="n"/>
+      <c r="CC37" s="45" t="n"/>
+      <c r="CD37" s="46" t="n"/>
     </row>
     <row r="38" ht="15" customHeight="1">
       <c r="B38" s="44" t="n"/>
@@ -5414,7 +7287,38 @@
       <c r="AV38" s="45" t="n"/>
       <c r="AW38" s="45" t="n"/>
       <c r="AX38" s="45" t="n"/>
-      <c r="AY38" s="46" t="n"/>
+      <c r="AY38" s="45" t="n"/>
+      <c r="AZ38" s="45" t="n"/>
+      <c r="BA38" s="45" t="n"/>
+      <c r="BB38" s="45" t="n"/>
+      <c r="BC38" s="45" t="n"/>
+      <c r="BD38" s="45" t="n"/>
+      <c r="BE38" s="45" t="n"/>
+      <c r="BF38" s="45" t="n"/>
+      <c r="BG38" s="45" t="n"/>
+      <c r="BH38" s="45" t="n"/>
+      <c r="BI38" s="45" t="n"/>
+      <c r="BJ38" s="45" t="n"/>
+      <c r="BK38" s="45" t="n"/>
+      <c r="BL38" s="45" t="n"/>
+      <c r="BM38" s="45" t="n"/>
+      <c r="BN38" s="45" t="n"/>
+      <c r="BO38" s="45" t="n"/>
+      <c r="BP38" s="45" t="n"/>
+      <c r="BQ38" s="45" t="n"/>
+      <c r="BR38" s="45" t="n"/>
+      <c r="BS38" s="45" t="n"/>
+      <c r="BT38" s="45" t="n"/>
+      <c r="BU38" s="45" t="n"/>
+      <c r="BV38" s="45" t="n"/>
+      <c r="BW38" s="45" t="n"/>
+      <c r="BX38" s="45" t="n"/>
+      <c r="BY38" s="45" t="n"/>
+      <c r="BZ38" s="45" t="n"/>
+      <c r="CA38" s="45" t="n"/>
+      <c r="CB38" s="45" t="n"/>
+      <c r="CC38" s="45" t="n"/>
+      <c r="CD38" s="46" t="n"/>
     </row>
     <row r="39" ht="15" customHeight="1">
       <c r="B39" s="44" t="n"/>
@@ -5466,7 +7370,38 @@
       <c r="AV39" s="45" t="n"/>
       <c r="AW39" s="45" t="n"/>
       <c r="AX39" s="45" t="n"/>
-      <c r="AY39" s="46" t="n"/>
+      <c r="AY39" s="45" t="n"/>
+      <c r="AZ39" s="45" t="n"/>
+      <c r="BA39" s="45" t="n"/>
+      <c r="BB39" s="45" t="n"/>
+      <c r="BC39" s="45" t="n"/>
+      <c r="BD39" s="45" t="n"/>
+      <c r="BE39" s="45" t="n"/>
+      <c r="BF39" s="45" t="n"/>
+      <c r="BG39" s="45" t="n"/>
+      <c r="BH39" s="45" t="n"/>
+      <c r="BI39" s="45" t="n"/>
+      <c r="BJ39" s="45" t="n"/>
+      <c r="BK39" s="45" t="n"/>
+      <c r="BL39" s="45" t="n"/>
+      <c r="BM39" s="45" t="n"/>
+      <c r="BN39" s="45" t="n"/>
+      <c r="BO39" s="45" t="n"/>
+      <c r="BP39" s="45" t="n"/>
+      <c r="BQ39" s="45" t="n"/>
+      <c r="BR39" s="45" t="n"/>
+      <c r="BS39" s="45" t="n"/>
+      <c r="BT39" s="45" t="n"/>
+      <c r="BU39" s="45" t="n"/>
+      <c r="BV39" s="45" t="n"/>
+      <c r="BW39" s="45" t="n"/>
+      <c r="BX39" s="45" t="n"/>
+      <c r="BY39" s="45" t="n"/>
+      <c r="BZ39" s="45" t="n"/>
+      <c r="CA39" s="45" t="n"/>
+      <c r="CB39" s="45" t="n"/>
+      <c r="CC39" s="45" t="n"/>
+      <c r="CD39" s="46" t="n"/>
     </row>
     <row r="40" ht="15" customHeight="1">
       <c r="B40" s="44" t="n"/>
@@ -5518,7 +7453,38 @@
       <c r="AV40" s="45" t="n"/>
       <c r="AW40" s="45" t="n"/>
       <c r="AX40" s="45" t="n"/>
-      <c r="AY40" s="46" t="n"/>
+      <c r="AY40" s="45" t="n"/>
+      <c r="AZ40" s="45" t="n"/>
+      <c r="BA40" s="45" t="n"/>
+      <c r="BB40" s="45" t="n"/>
+      <c r="BC40" s="45" t="n"/>
+      <c r="BD40" s="45" t="n"/>
+      <c r="BE40" s="45" t="n"/>
+      <c r="BF40" s="45" t="n"/>
+      <c r="BG40" s="45" t="n"/>
+      <c r="BH40" s="45" t="n"/>
+      <c r="BI40" s="45" t="n"/>
+      <c r="BJ40" s="45" t="n"/>
+      <c r="BK40" s="45" t="n"/>
+      <c r="BL40" s="45" t="n"/>
+      <c r="BM40" s="45" t="n"/>
+      <c r="BN40" s="45" t="n"/>
+      <c r="BO40" s="45" t="n"/>
+      <c r="BP40" s="45" t="n"/>
+      <c r="BQ40" s="45" t="n"/>
+      <c r="BR40" s="45" t="n"/>
+      <c r="BS40" s="45" t="n"/>
+      <c r="BT40" s="45" t="n"/>
+      <c r="BU40" s="45" t="n"/>
+      <c r="BV40" s="45" t="n"/>
+      <c r="BW40" s="45" t="n"/>
+      <c r="BX40" s="45" t="n"/>
+      <c r="BY40" s="45" t="n"/>
+      <c r="BZ40" s="45" t="n"/>
+      <c r="CA40" s="45" t="n"/>
+      <c r="CB40" s="45" t="n"/>
+      <c r="CC40" s="45" t="n"/>
+      <c r="CD40" s="46" t="n"/>
     </row>
     <row r="41" ht="15" customHeight="1">
       <c r="B41" s="44" t="n"/>
@@ -5570,7 +7536,38 @@
       <c r="AV41" s="45" t="n"/>
       <c r="AW41" s="45" t="n"/>
       <c r="AX41" s="45" t="n"/>
-      <c r="AY41" s="46" t="n"/>
+      <c r="AY41" s="45" t="n"/>
+      <c r="AZ41" s="45" t="n"/>
+      <c r="BA41" s="45" t="n"/>
+      <c r="BB41" s="45" t="n"/>
+      <c r="BC41" s="45" t="n"/>
+      <c r="BD41" s="45" t="n"/>
+      <c r="BE41" s="45" t="n"/>
+      <c r="BF41" s="45" t="n"/>
+      <c r="BG41" s="45" t="n"/>
+      <c r="BH41" s="45" t="n"/>
+      <c r="BI41" s="45" t="n"/>
+      <c r="BJ41" s="45" t="n"/>
+      <c r="BK41" s="45" t="n"/>
+      <c r="BL41" s="45" t="n"/>
+      <c r="BM41" s="45" t="n"/>
+      <c r="BN41" s="45" t="n"/>
+      <c r="BO41" s="45" t="n"/>
+      <c r="BP41" s="45" t="n"/>
+      <c r="BQ41" s="45" t="n"/>
+      <c r="BR41" s="45" t="n"/>
+      <c r="BS41" s="45" t="n"/>
+      <c r="BT41" s="45" t="n"/>
+      <c r="BU41" s="45" t="n"/>
+      <c r="BV41" s="45" t="n"/>
+      <c r="BW41" s="45" t="n"/>
+      <c r="BX41" s="45" t="n"/>
+      <c r="BY41" s="45" t="n"/>
+      <c r="BZ41" s="45" t="n"/>
+      <c r="CA41" s="45" t="n"/>
+      <c r="CB41" s="45" t="n"/>
+      <c r="CC41" s="45" t="n"/>
+      <c r="CD41" s="46" t="n"/>
     </row>
     <row r="42" ht="15" customHeight="1">
       <c r="B42" s="54" t="n"/>
@@ -5622,7 +7619,38 @@
       <c r="AV42" s="55" t="n"/>
       <c r="AW42" s="55" t="n"/>
       <c r="AX42" s="55" t="n"/>
-      <c r="AY42" s="56" t="n"/>
+      <c r="AY42" s="55" t="n"/>
+      <c r="AZ42" s="55" t="n"/>
+      <c r="BA42" s="55" t="n"/>
+      <c r="BB42" s="55" t="n"/>
+      <c r="BC42" s="55" t="n"/>
+      <c r="BD42" s="55" t="n"/>
+      <c r="BE42" s="55" t="n"/>
+      <c r="BF42" s="55" t="n"/>
+      <c r="BG42" s="55" t="n"/>
+      <c r="BH42" s="55" t="n"/>
+      <c r="BI42" s="55" t="n"/>
+      <c r="BJ42" s="55" t="n"/>
+      <c r="BK42" s="55" t="n"/>
+      <c r="BL42" s="55" t="n"/>
+      <c r="BM42" s="55" t="n"/>
+      <c r="BN42" s="55" t="n"/>
+      <c r="BO42" s="55" t="n"/>
+      <c r="BP42" s="55" t="n"/>
+      <c r="BQ42" s="55" t="n"/>
+      <c r="BR42" s="55" t="n"/>
+      <c r="BS42" s="55" t="n"/>
+      <c r="BT42" s="55" t="n"/>
+      <c r="BU42" s="55" t="n"/>
+      <c r="BV42" s="55" t="n"/>
+      <c r="BW42" s="55" t="n"/>
+      <c r="BX42" s="55" t="n"/>
+      <c r="BY42" s="55" t="n"/>
+      <c r="BZ42" s="55" t="n"/>
+      <c r="CA42" s="55" t="n"/>
+      <c r="CB42" s="55" t="n"/>
+      <c r="CC42" s="55" t="n"/>
+      <c r="CD42" s="56" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="23" t="inlineStr">
@@ -5697,21 +7725,18 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="15">
+  <mergeCells count="12">
     <mergeCell ref="A1:T1"/>
     <mergeCell ref="A44:J44"/>
     <mergeCell ref="C48:J48"/>
-    <mergeCell ref="V25:Z25"/>
-    <mergeCell ref="J25:N25"/>
+    <mergeCell ref="C51:J51"/>
     <mergeCell ref="C46:J46"/>
     <mergeCell ref="C47:J47"/>
-    <mergeCell ref="C51:J51"/>
-    <mergeCell ref="AH25:AL25"/>
     <mergeCell ref="A53:T53"/>
     <mergeCell ref="C50:J50"/>
     <mergeCell ref="A2:T2"/>
     <mergeCell ref="C45:J45"/>
-    <mergeCell ref="AU11:AX11"/>
+    <mergeCell ref="BZ11:CC11"/>
     <mergeCell ref="C49:J49"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
